--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -816,13 +816,13 @@
         <v>0.59</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>139854</v>
+        <v>137942</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.590015</v>
+        <v>51.87985</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.749046</v>
+        <v>37.232964</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -837,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.6461735</v>
+        <v>11.486955</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -950,13 +950,13 @@
         <v>1.14</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>183213</v>
+        <v>183492</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>73.70247999999999</v>
+        <v>73.81461</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>59.035583</v>
+        <v>59.1254</v>
       </c>
       <c r="AD3" s="4" t="inlineStr"/>
       <c r="AE3" s="4" t="n">
@@ -969,7 +969,7 @@
         <v>-1</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.879639</v>
+        <v>11.897712</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>44</v>
@@ -1080,13 +1080,13 @@
         <v>0.73</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>411487</v>
+        <v>406142</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>30.645163</v>
+        <v>30.247084</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>23.027498</v>
+        <v>22.728373</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.59</v>
@@ -1101,7 +1101,7 @@
         <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.280397</v>
+        <v>4.2247953</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>42</v>
@@ -1214,13 +1214,13 @@
         <v>1.55</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>315135</v>
+        <v>313670</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.140839</v>
+        <v>14.081297</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.93597</v>
+        <v>17.852625</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>27.26</v>
@@ -1235,7 +1235,7 @@
         <v>991.8</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>3.149806</v>
+        <v>3.1351693</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>55</v>
@@ -1348,13 +1348,13 @@
         <v>4.31</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>12643</v>
+        <v>12734</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>30.567175</v>
+        <v>30.785805</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>18.259304</v>
+        <v>18.389902</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>10.66</v>
@@ -1369,7 +1369,7 @@
         <v>5.9</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>3.2903805</v>
+        <v>3.3139148</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>79</v>
@@ -1482,13 +1482,13 @@
         <v>0.82</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>107778</v>
+        <v>107740</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>61.20309</v>
+        <v>61.181015</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>44.07573</v>
+        <v>44.059834</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>41.39</v>
@@ -1503,7 +1503,7 @@
         <v>14.5</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>25.410913</v>
+        <v>25.401749</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>48</v>
@@ -1616,13 +1616,13 @@
         <v>0.73</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>277446</v>
+        <v>276019</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>79.141914</v>
+        <v>78.73487</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>60.736362</v>
+        <v>60.42398</v>
       </c>
       <c r="AD8" s="2" t="n">
         <v>76.34</v>
@@ -1637,7 +1637,7 @@
         <v>27.4</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>53.800995</v>
+        <v>53.52429</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>84</v>
@@ -1750,13 +1750,13 @@
         <v>1.84</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>29439</v>
+        <v>29617</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>26.740614</v>
+        <v>26.902729</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>10.671962</v>
+        <v>10.736661</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>6.97</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AG9" s="4" t="inlineStr"/>
       <c r="AH9" s="4" t="n">
-        <v>1.634505</v>
+        <v>1.6444142</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>65</v>
@@ -1882,13 +1882,13 @@
         <v>0.6</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>372628</v>
+        <v>373005</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>9.798214</v>
+        <v>9.808138</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>6.994827</v>
+        <v>7.001911</v>
       </c>
       <c r="AD10" s="2" t="inlineStr"/>
       <c r="AE10" s="2" t="n">
@@ -1901,7 +1901,7 @@
         <v>16.2</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>1.0123416</v>
+        <v>1.0133669</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>622</v>
@@ -2012,13 +2012,13 @@
         <v>0.96</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>8943</v>
+        <v>9061</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>79.70238500000001</v>
+        <v>80.46856</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>40.999268</v>
+        <v>41.54123</v>
       </c>
       <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="n">
@@ -2031,7 +2031,7 @@
         <v>35.8</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>13.719543</v>
+        <v>13.900899</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>0</v>
@@ -2142,13 +2142,13 @@
         <v>1.16</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>151502</v>
+        <v>150950</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>66.59327</v>
+        <v>66.35079</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>69.11971</v>
+        <v>68.86803</v>
       </c>
       <c r="AD12" s="2" t="inlineStr"/>
       <c r="AE12" s="2" t="n">
@@ -2161,10 +2161,10 @@
         <v>26.1</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>17.943857</v>
+        <v>17.878517</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ12" s="2" t="inlineStr"/>
       <c r="AK12" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB13" s="4" t="inlineStr"/>
       <c r="AC13" s="4" t="n">
-        <v>27.849463</v>
+        <v>27.844086</v>
       </c>
       <c r="AD13" s="4" t="n">
         <v>-2.82</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AG13" s="4" t="inlineStr"/>
       <c r="AH13" s="4" t="n">
-        <v>5.671657</v>
+        <v>5.6705623</v>
       </c>
       <c r="AI13" s="4" t="n">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.67</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>376146</v>
+        <v>373582</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>37.22795</v>
+        <v>36.97422</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>48.402573</v>
+        <v>48.07268</v>
       </c>
       <c r="AD14" s="2" t="n">
         <v>13.66</v>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="n">
-        <v>4.3759727</v>
+        <v>4.346148</v>
       </c>
       <c r="AI14" s="2" t="n">
         <v>5</v>
@@ -2534,13 +2534,13 @@
         <v>0.64</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>453762</v>
+        <v>451627</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>41.51921</v>
+        <v>41.323822</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>33.42379</v>
+        <v>33.2665</v>
       </c>
       <c r="AD15" s="4" t="inlineStr"/>
       <c r="AE15" s="4" t="n">
@@ -2553,7 +2553,7 @@
         <v>15.7</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>5.8287253</v>
+        <v>5.8012958</v>
       </c>
       <c r="AI15" s="4" t="n">
         <v>87</v>
@@ -2664,13 +2664,13 @@
         <v>0.7</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>281575</v>
+        <v>281606</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>9.054697000000001</v>
+        <v>9.055688</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>7.9895134</v>
+        <v>7.990388</v>
       </c>
       <c r="AD16" s="2" t="n">
         <v>28.12</v>
@@ -2685,7 +2685,7 @@
         <v>12.9</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>2.363928</v>
+        <v>2.3641868</v>
       </c>
       <c r="AI16" s="2" t="n">
         <v>476</v>
@@ -2798,13 +2798,13 @@
         <v>0.85</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>116099</v>
+        <v>115402</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>64.53404</v>
+        <v>64.146416</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>48.52542</v>
+        <v>48.233948</v>
       </c>
       <c r="AD17" s="4" t="inlineStr"/>
       <c r="AE17" s="4" t="n">
@@ -2817,7 +2817,7 @@
         <v>35</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>12.766956</v>
+        <v>12.690271</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>25</v>
@@ -2928,13 +2928,13 @@
         <v>1.29</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>78174</v>
+        <v>77730</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>557.1428</v>
+        <v>553.9796</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>176.0132</v>
+        <v>175.01387</v>
       </c>
       <c r="AD18" s="2" t="inlineStr"/>
       <c r="AE18" s="2" t="n">
@@ -2947,7 +2947,7 @@
         <v>144.4</v>
       </c>
       <c r="AH18" s="2" t="n">
-        <v>56.439945</v>
+        <v>56.1195</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.76</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>87452</v>
+        <v>87043</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>25.323225</v>
+        <v>25.204933</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>19.88931</v>
+        <v>19.796402</v>
       </c>
       <c r="AD19" s="4" t="inlineStr"/>
       <c r="AE19" s="4" t="n">
@@ -3077,10 +3077,10 @@
         <v>7.6</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>2.5189137</v>
+        <v>2.507147</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ19" s="4" t="inlineStr"/>
       <c r="AK19" s="4" t="inlineStr">
@@ -3188,13 +3188,13 @@
         <v>1.43</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>1168405</v>
+        <v>1165603</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>43.219917</v>
+        <v>43.11627</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>22.989098</v>
+        <v>22.933964</v>
       </c>
       <c r="AD20" s="2" t="n">
         <v>19.36</v>
@@ -3209,7 +3209,7 @@
         <v>-34</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>7.5228457</v>
+        <v>7.5048046</v>
       </c>
       <c r="AI20" s="2" t="n">
         <v>83</v>
@@ -3322,13 +3322,13 @@
         <v>0.62</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>21378</v>
+        <v>21144</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>388.05554</v>
+        <v>383.80554</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>26.865385</v>
+        <v>26.571154</v>
       </c>
       <c r="AD21" s="4" t="n">
         <v>7.27</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AG21" s="4" t="inlineStr"/>
       <c r="AH21" s="4" t="n">
-        <v>4.311728</v>
+        <v>4.264506</v>
       </c>
       <c r="AI21" s="4" t="n">
         <v>7</v>
@@ -3454,13 +3454,13 @@
         <v>2.71</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>263306</v>
+        <v>261023</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>28.762941</v>
+        <v>28.513622</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>11.229788</v>
+        <v>11.132447</v>
       </c>
       <c r="AD22" s="2" t="n">
         <v>11.16</v>
@@ -3475,10 +3475,10 @@
         <v>125.4</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>2.7698402</v>
+        <v>2.745831</v>
       </c>
       <c r="AI22" s="2" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="AJ22" s="2" t="n">
         <v>0.748</v>
@@ -3588,13 +3588,13 @@
         <v>0.71</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>20411</v>
+        <v>20024</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>23.397161</v>
+        <v>22.9539</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>17.383423</v>
+        <v>17.054092</v>
       </c>
       <c r="AD23" s="4" t="inlineStr"/>
       <c r="AE23" s="4" t="inlineStr"/>
@@ -3605,7 +3605,7 @@
         <v>367.9</v>
       </c>
       <c r="AH23" s="4" t="n">
-        <v>1.2192732</v>
+        <v>1.1961739</v>
       </c>
       <c r="AI23" s="4" t="n">
         <v>33</v>
@@ -3716,13 +3716,13 @@
         <v>0.58</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>18659</v>
+        <v>18957</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>57.384483</v>
+        <v>58.30273</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>34.052444</v>
+        <v>34.59734</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>14.14</v>
@@ -3737,7 +3737,7 @@
         <v>43.7</v>
       </c>
       <c r="AH24" s="2" t="n">
-        <v>6.4218326</v>
+        <v>6.524593</v>
       </c>
       <c r="AI24" s="2" t="n">
         <v>15</v>
@@ -3850,13 +3850,13 @@
         <v>0.42</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>30920</v>
+        <v>30804</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>25.287218</v>
+        <v>25.192358</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>8.876007</v>
+        <v>8.842710500000001</v>
       </c>
       <c r="AD25" s="4" t="n">
         <v>4.88</v>
@@ -3869,7 +3869,7 @@
         <v>68</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>1.2073802</v>
+        <v>1.2028509</v>
       </c>
       <c r="AI25" s="4" t="n">
         <v>79</v>
@@ -3980,13 +3980,13 @@
         <v>0.73</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>23999</v>
+        <v>24001</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>15.580895</v>
+        <v>15.581756</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>12.651418</v>
+        <v>12.652116</v>
       </c>
       <c r="AD26" s="2" t="n">
         <v>12.55</v>
@@ -4001,7 +4001,7 @@
         <v>17.8</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>1.8858393</v>
+        <v>1.8859434</v>
       </c>
       <c r="AI26" s="2" t="n">
         <v>340</v>
@@ -4114,13 +4114,13 @@
         <v>0.52</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>59571</v>
+        <v>59198</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>52.94301</v>
+        <v>52.6114</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>40.231575</v>
+        <v>39.979588</v>
       </c>
       <c r="AD27" s="4" t="n">
         <v>17.23</v>
@@ -4135,7 +4135,7 @@
         <v>27.7</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>8.616531</v>
+        <v>8.562563000000001</v>
       </c>
       <c r="AI27" s="4" t="n">
         <v>72</v>
@@ -4248,13 +4248,13 @@
         <v>0.58</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>110535</v>
+        <v>111168</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>26.383148</v>
+        <v>26.53418</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>20.688011</v>
+        <v>20.806442</v>
       </c>
       <c r="AD28" s="2" t="n">
         <v>11.83</v>
@@ -4269,7 +4269,7 @@
         <v>-86.2</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>2.9354148</v>
+        <v>2.9522188</v>
       </c>
       <c r="AI28" s="2" t="n">
         <v>60</v>
@@ -4382,13 +4382,13 @@
         <v>0.6</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>148941</v>
+        <v>148168</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>60.797676</v>
+        <v>60.48193</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>48.274868</v>
+        <v>48.02416</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>23.52</v>
@@ -4403,10 +4403,10 @@
         <v>37</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>15.5933</v>
+        <v>15.512319</v>
       </c>
       <c r="AI29" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AJ29" s="4" t="n">
         <v>2.38</v>
@@ -4516,13 +4516,13 @@
         <v>1.7</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>277391</v>
+        <v>277716</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>14.83093</v>
+        <v>14.848334</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>14.820517</v>
+        <v>14.979996</v>
       </c>
       <c r="AD30" s="2" t="n">
         <v>16.49</v>
@@ -4537,7 +4537,7 @@
         <v>9.6</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>2.7996547</v>
+        <v>2.8029401</v>
       </c>
       <c r="AI30" s="2" t="n">
         <v>413</v>
@@ -4650,13 +4650,13 @@
         <v>0.89</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>114506</v>
+        <v>113884</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>29.49438</v>
+        <v>29.334166</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>22.376104</v>
+        <v>22.254555</v>
       </c>
       <c r="AD31" s="4" t="n">
         <v>11.74</v>
@@ -4671,7 +4671,7 @@
         <v>-54.6</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>3.478263</v>
+        <v>3.4593687</v>
       </c>
       <c r="AI31" s="4" t="n">
         <v>91</v>
@@ -4784,13 +4784,13 @@
         <v>0.9</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>70731</v>
+        <v>70620</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>16.412235</v>
+        <v>16.386507</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>12.08132</v>
+        <v>12.062381</v>
       </c>
       <c r="AD32" s="2" t="n">
         <v>11.73</v>
@@ -4803,7 +4803,7 @@
         <v>22.2</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>1.9434006</v>
+        <v>1.9403541</v>
       </c>
       <c r="AI32" s="2" t="n">
         <v>42</v>
@@ -4914,13 +4914,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>542302</v>
+        <v>539400</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>33.765312</v>
+        <v>33.584583</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>21.442049</v>
+        <v>21.32728</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>16.95</v>
@@ -4935,7 +4935,7 @@
         <v>-34.5</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>4.9619246</v>
+        <v>4.9353657</v>
       </c>
       <c r="AI33" s="4" t="n">
         <v>97</v>
@@ -5048,13 +5048,13 @@
         <v>0.86</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>251289</v>
+        <v>249315</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>65.54889</v>
+        <v>65.03375</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>52.329422</v>
+        <v>51.91818</v>
       </c>
       <c r="AD34" s="2" t="inlineStr"/>
       <c r="AE34" s="2" t="n">
@@ -5067,7 +5067,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>12.82813</v>
+        <v>12.727317</v>
       </c>
       <c r="AI34" s="2" t="n">
         <v>96</v>
@@ -5178,13 +5178,13 @@
         <v>0.6</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>367175</v>
+        <v>363866</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>72.466736</v>
+        <v>71.81373000000001</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>48.085255</v>
+        <v>47.65195</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>37.13</v>
@@ -5199,7 +5199,7 @@
         <v>35.1</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>28.670078</v>
+        <v>28.411728</v>
       </c>
       <c r="AI35" s="4" t="n">
         <v>26</v>
@@ -5312,13 +5312,13 @@
         <v>0.49</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>274894</v>
+        <v>276257</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>92.37563</v>
+        <v>92.83365999999999</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>59.4446</v>
+        <v>59.739346</v>
       </c>
       <c r="AD36" s="2" t="n">
         <v>12.94</v>
@@ -5333,7 +5333,7 @@
         <v>19.6</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>11.211924</v>
+        <v>11.267516</v>
       </c>
       <c r="AI36" s="2" t="n">
         <v>0</v>
@@ -5446,13 +5446,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>143026</v>
+        <v>142432</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>5.5224257</v>
+        <v>5.4994903</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>6.6577044</v>
+        <v>6.630054</v>
       </c>
       <c r="AD37" s="4" t="n">
         <v>20.47</v>
@@ -5467,7 +5467,7 @@
         <v>10.8</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>1.0764304</v>
+        <v>1.0719599</v>
       </c>
       <c r="AI37" s="4" t="n">
         <v>340</v>
@@ -5580,13 +5580,13 @@
         <v>0.87</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>379867</v>
+        <v>377588</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>21.691584</v>
+        <v>21.561462</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>14.632711</v>
+        <v>14.544933</v>
       </c>
       <c r="AD38" s="2" t="inlineStr"/>
       <c r="AE38" s="2" t="n">
@@ -5599,7 +5599,7 @@
         <v>-1.6</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>1.9763296</v>
+        <v>1.9644741</v>
       </c>
       <c r="AI38" s="2" t="n">
         <v>292</v>
@@ -5706,13 +5706,13 @@
         <v>0.75</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>39051</v>
+        <v>38925</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>72.89869</v>
+        <v>72.66298999999999</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>42.94922</v>
+        <v>42.81035</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>13.8</v>
@@ -5727,7 +5727,7 @@
         <v>18.9</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>10.337079</v>
+        <v>10.303656</v>
       </c>
       <c r="AI39" s="4" t="n">
         <v>24</v>
@@ -5840,13 +5840,13 @@
         <v>0.8</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>132894</v>
+        <v>132607</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>35.456097</v>
+        <v>35.37937</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>27.500029</v>
+        <v>27.44052</v>
       </c>
       <c r="AD40" s="2" t="n">
         <v>11.34</v>
@@ -5861,10 +5861,10 @@
         <v>-4.6</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>3.5102673</v>
+        <v>3.5026712</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AJ40" s="2" t="n">
         <v>0.806</v>
@@ -5974,13 +5974,13 @@
         <v>0.74</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>189263</v>
+        <v>188797</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>35.391125</v>
+        <v>35.303925</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>29.976454</v>
+        <v>29.902594</v>
       </c>
       <c r="AD41" s="4" t="inlineStr"/>
       <c r="AE41" s="4" t="n">
@@ -5993,7 +5993,7 @@
         <v>21.3</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>8.568083</v>
+        <v>8.546970999999999</v>
       </c>
       <c r="AI41" s="4" t="n">
         <v>101</v>
@@ -6598,13 +6598,13 @@
         <v>0.59</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>139854</v>
+        <v>137942</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.590015</v>
+        <v>51.87985</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.749046</v>
+        <v>37.232964</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -6619,7 +6619,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.6461735</v>
+        <v>11.486955</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -6732,13 +6732,13 @@
         <v>1.14</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>183213</v>
+        <v>183492</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>73.70247999999999</v>
+        <v>73.81461</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>59.035583</v>
+        <v>59.1254</v>
       </c>
       <c r="AD3" s="4" t="inlineStr"/>
       <c r="AE3" s="4" t="n">
@@ -6751,7 +6751,7 @@
         <v>-1</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.879639</v>
+        <v>11.897712</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>44</v>
@@ -6862,13 +6862,13 @@
         <v>0.73</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>411487</v>
+        <v>406142</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>30.645163</v>
+        <v>30.247084</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>23.027498</v>
+        <v>22.728373</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.59</v>
@@ -6883,7 +6883,7 @@
         <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.280397</v>
+        <v>4.2247953</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>42</v>
@@ -6996,13 +6996,13 @@
         <v>1.55</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>315135</v>
+        <v>313670</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.140839</v>
+        <v>14.081297</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.93597</v>
+        <v>17.852625</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>27.26</v>
@@ -7017,7 +7017,7 @@
         <v>991.8</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>3.149806</v>
+        <v>3.1351693</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>55</v>
@@ -7130,13 +7130,13 @@
         <v>4.31</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>12643</v>
+        <v>12734</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>30.567175</v>
+        <v>30.785805</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>18.259304</v>
+        <v>18.389902</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>10.66</v>
@@ -7151,7 +7151,7 @@
         <v>5.9</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>3.2903805</v>
+        <v>3.3139148</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>79</v>
@@ -7264,13 +7264,13 @@
         <v>0.82</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>107778</v>
+        <v>107740</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>61.20309</v>
+        <v>61.181015</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>44.07573</v>
+        <v>44.059834</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>41.39</v>
@@ -7285,7 +7285,7 @@
         <v>14.5</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>25.410913</v>
+        <v>25.401749</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>48</v>
@@ -7645,13 +7645,13 @@
         <v>0.59</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>139854</v>
+        <v>137942</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.590015</v>
+        <v>51.87985</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.749046</v>
+        <v>37.232964</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -7666,7 +7666,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.6461735</v>
+        <v>11.486955</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -7779,13 +7779,13 @@
         <v>1.14</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>183213</v>
+        <v>183492</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>73.70247999999999</v>
+        <v>73.81461</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>59.035583</v>
+        <v>59.1254</v>
       </c>
       <c r="AD3" s="4" t="inlineStr"/>
       <c r="AE3" s="4" t="n">
@@ -7798,7 +7798,7 @@
         <v>-1</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.879639</v>
+        <v>11.897712</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>44</v>
@@ -7909,13 +7909,13 @@
         <v>0.73</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>411487</v>
+        <v>406142</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>30.645163</v>
+        <v>30.247084</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>23.027498</v>
+        <v>22.728373</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.59</v>
@@ -7930,7 +7930,7 @@
         <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.280397</v>
+        <v>4.2247953</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>42</v>
@@ -8043,13 +8043,13 @@
         <v>1.55</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>315135</v>
+        <v>313670</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.140839</v>
+        <v>14.081297</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.93597</v>
+        <v>17.852625</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>27.26</v>
@@ -8064,7 +8064,7 @@
         <v>991.8</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>3.149806</v>
+        <v>3.1351693</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>55</v>
@@ -8177,13 +8177,13 @@
         <v>4.31</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>12643</v>
+        <v>12734</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>30.567175</v>
+        <v>30.785805</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>18.259304</v>
+        <v>18.389902</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>10.66</v>
@@ -8198,7 +8198,7 @@
         <v>5.9</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>3.2903805</v>
+        <v>3.3139148</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>79</v>
@@ -8311,13 +8311,13 @@
         <v>0.82</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>107778</v>
+        <v>107740</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>61.20309</v>
+        <v>61.181015</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>44.07573</v>
+        <v>44.059834</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>41.39</v>
@@ -8332,7 +8332,7 @@
         <v>14.5</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>25.410913</v>
+        <v>25.401749</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>48</v>
@@ -8377,7 +8377,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 19-May-2026 07:00 IST</t>
+          <t>Run Date: 19-May-2026 12:02 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -1354,7 +1354,7 @@
         <v>30.785805</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>18.389902</v>
+        <v>18.240303</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>10.66</v>
@@ -5712,7 +5712,7 @@
         <v>72.66298999999999</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>42.81035</v>
+        <v>42.825382</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>13.8</v>
@@ -7136,7 +7136,7 @@
         <v>30.785805</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>18.389902</v>
+        <v>18.240303</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>10.66</v>
@@ -8183,7 +8183,7 @@
         <v>30.785805</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>18.389902</v>
+        <v>18.240303</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>10.66</v>
@@ -8377,7 +8377,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 19-May-2026 12:02 IST</t>
+          <t>Run Date: 19-May-2026 12:41 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -2018,7 +2018,7 @@
         <v>80.46856</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>41.54123</v>
+        <v>41.47935</v>
       </c>
       <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="n">
@@ -8377,7 +8377,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 19-May-2026 12:41 IST</t>
+          <t>Run Date: 19-May-2026 18:17 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📊 All Stocks'!$A$1:$AL$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏆 Grade A'!$A$1:$AL$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Grade B Watch'!$A$1:$AL$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Watchlist'!$A$1:$AL$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Grade B Watch'!$A$1:$AL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Watchlist'!$A$1:$AL$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9151</v>
+        <v>9162.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8603.049999999999</v>
+        <v>8656.33</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8140.78</v>
+        <v>8180.85</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7437.66</v>
+        <v>7454.82</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -788,41 +788,41 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>98.59</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>70.92</v>
+        <v>71.12</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>379.7859</v>
+        <v>377.019</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>328.2022</v>
+        <v>337.9656</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>51.5837</v>
+        <v>39.0534</v>
       </c>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>36.33</v>
+        <v>36.86</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>295160</v>
+        <v>337327</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>496919</v>
+        <v>491631</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>137942</v>
+        <v>138582</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>51.87985</v>
+        <v>52.052704</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.232964</v>
+        <v>37.40567</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -837,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.486955</v>
+        <v>11.540236</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -859,32 +859,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Adani Ports and Special Economic Zone Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Marine Shipping</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>64.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>18.8</v>
+        <v>24.8</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -897,19 +897,19 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6835</v>
+        <v>1762.8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1.1</v>
+        <v>-1.39</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>6595.56</v>
+        <v>1697.95</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>6406.09</v>
+        <v>1598.79</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>6275.56</v>
+        <v>1474.12</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -922,99 +922,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>66.76000000000001</v>
+        <v>63.75</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>165.1763</v>
+        <v>68.4268</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>149.3397</v>
+        <v>69.70050000000001</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>15.8366</v>
+        <v>-1.2737</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>40.22</v>
+        <v>30.14</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>340352</v>
+        <v>2274987</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>299253</v>
+        <v>3422075</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>1.14</v>
+        <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>183492</v>
+        <v>407110</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>73.81461</v>
+        <v>30.376484</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>59.1254</v>
-      </c>
-      <c r="AD3" s="4" t="inlineStr"/>
+        <v>22.782524</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>15.59</v>
+      </c>
       <c r="AE3" s="4" t="n">
-        <v>0.584</v>
+        <v>64.051</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>12.3</v>
+        <v>26.5</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>-1</v>
+        <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.897712</v>
+        <v>4.234861</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
+        <v>1.394</v>
+      </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>63.8</v>
+        <v>64.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24.8</v>
+        <v>18.8</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -1027,19 +1031,19 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1787.7</v>
+        <v>6912</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.41</v>
+        <v>1.13</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1691.12</v>
+        <v>6625.7</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1592.09</v>
+        <v>6425.93</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1471.22</v>
+        <v>6281.9</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1052,103 +1056,99 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.02</v>
+        <v>98.19</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>68.23</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>71.4542</v>
+        <v>169.8444</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>70.01900000000001</v>
+        <v>153.4407</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.4352</v>
+        <v>16.4038</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>29.99</v>
+        <v>40.15</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>2562978</v>
+        <v>322081</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>3522169</v>
+        <v>304930</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>406142</v>
+        <v>183041</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>30.247084</v>
+        <v>73.89348</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>22.728373</v>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>15.59</v>
-      </c>
+        <v>58.979984</v>
+      </c>
+      <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>64.051</v>
+        <v>0.584</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>26.5</v>
+        <v>12.3</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>3.6</v>
+        <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.2247953</v>
+        <v>11.86845</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ4" s="2" t="n">
-        <v>1.394</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr"/>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>JSW Steel Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1292.8</v>
+        <v>831.45</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1264.22</v>
+        <v>811.24</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1236.23</v>
+        <v>787.47</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1169.81</v>
+        <v>748.28</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -1186,128 +1186,128 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>98.39</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>59.8</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>17.6126</v>
+        <v>19.2999</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>18.4128</v>
+        <v>17.5484</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.8002</v>
+        <v>1.7515</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>19.95</v>
+        <v>37.74</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>2965138</v>
+        <v>1431476</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1911846</v>
+        <v>1863164</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>1.55</v>
+        <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>313670</v>
+        <v>107856</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.081297</v>
+        <v>61.428043</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.852625</v>
+        <v>44.107525</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>27.26</v>
+        <v>41.39</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>94.155</v>
+        <v>12.394</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>14.2</v>
+        <v>22.1</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>991.8</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>3.1351693</v>
+        <v>25.429243</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.491</v>
+        <v>1.31</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/JSWSTEEL/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Arvind Limited</t>
+          <t>Nestlé India Limited</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Textile Manufacturing</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>63</v>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>59</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>19</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>472.6</v>
+        <v>1431.4</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4.77</v>
+        <v>-0.02</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>420.6</v>
+        <v>1426.09</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>392.3</v>
+        <v>1361.23</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>351.43</v>
+        <v>1270.13</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1320,128 +1320,128 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>97.84999999999999</v>
+        <v>95.55</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>58.23</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>21.187</v>
+        <v>36.2617</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>16.5472</v>
+        <v>48.0862</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>4.6399</v>
+        <v>-11.8245</v>
       </c>
       <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="n">
-        <v>39.04</v>
+        <v>49.73</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>5974822</v>
+        <v>1803745</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>1385854</v>
+        <v>2397000</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>4.31</v>
+        <v>0.75</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>12734</v>
+        <v>271912</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>30.785805</v>
+        <v>77.563255</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>18.240303</v>
+        <v>59.524837</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>10.66</v>
+        <v>76.34</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>40.071</v>
+        <v>8.613</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>15.9</v>
+        <v>23.8</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>5.9</v>
+        <v>27.4</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>3.3139148</v>
+        <v>52.727818</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>1.141</v>
+        <v>0.964</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ARVIND/</t>
+          <t>https://www.screener.in/company/NESTLEIND/</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ARVIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>ideaForge Technology Limited</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>62</v>
+          <t>Computer Hardware</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>58.4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>12.4</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>833.75</v>
+        <v>776.85</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.88</v>
+        <v>-5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>809.11</v>
+        <v>710.3</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>785.6799999999999</v>
+        <v>592.8099999999999</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>747.4400000000001</v>
+        <v>494.44</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -1454,103 +1454,99 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>98.23</v>
+        <v>87.48</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>66.78</v>
+        <v>63.43</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>20.0313</v>
+        <v>86.2445</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>17.1105</v>
+        <v>85.8182</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>2.9208</v>
+        <v>0.4263</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>36.69</v>
+        <v>46.15</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1500121</v>
+        <v>337994</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1837251</v>
+        <v>3606152</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.82</v>
+        <v>0.09</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>107740</v>
-      </c>
-      <c r="AB7" s="4" t="n">
-        <v>61.181015</v>
-      </c>
+        <v>3297</v>
+      </c>
+      <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="n">
-        <v>44.059834</v>
+        <v>27.240143</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>41.39</v>
+        <v>-2.82</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>12.394</v>
+        <v>13.974</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AG7" s="4" t="n">
-        <v>14.5</v>
-      </c>
+        <v>594.4</v>
+      </c>
+      <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
-        <v>25.401749</v>
+        <v>5.547567</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>1.31</v>
+        <v>2.622</v>
       </c>
       <c r="AK7" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/IDEAFORGE/</t>
         </is>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEAFORGE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Nestlé India Limited</t>
+          <t>Oil and Natural Gas Corporation Limited</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Packaged Foods</t>
+          <t>Oil &amp; Gas Integrated</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>59</v>
+        <v>57.8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>19</v>
+        <v>15.8</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -1559,23 +1555,23 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1431.7</v>
+        <v>296.5</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.08</v>
+        <v>-0.24</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1425.54</v>
+        <v>291.49</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1358.36</v>
+        <v>283.44</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1268.51</v>
+        <v>258.05</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -1588,103 +1584,99 @@
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>95.56999999999999</v>
+        <v>96.42</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>58.34</v>
+        <v>57.56</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>40.5973</v>
+        <v>3.6831</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>51.0423</v>
+        <v>3.2872</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>-10.4451</v>
+        <v>0.396</v>
       </c>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="2" t="n">
-        <v>51.58</v>
+        <v>27.05</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>2030857</v>
+        <v>9565497</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>2786138</v>
+        <v>17468489</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>276019</v>
+        <v>377031</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>78.73487</v>
+        <v>9.910715</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>60.42398</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>76.34</v>
-      </c>
+        <v>7.0774803</v>
+      </c>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
-        <v>8.613</v>
+        <v>43.805</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>23.8</v>
+        <v>0.8</v>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>27.4</v>
+        <v>16.2</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>53.52429</v>
+        <v>1.0243038</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="AJ8" s="2" t="n">
-        <v>0.964</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NESTLEIND/</t>
+          <t>https://www.screener.in/company/ONGC/</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ONGC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Manappuram Finance Limited</t>
+          <t>Avalon Technologies Limited</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>58.4</v>
+        <v>57.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>16.4</v>
+        <v>14.8</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -1697,19 +1689,19 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>306.1</v>
+        <v>1356.7</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.44</v>
+        <v>3.01</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>298.63</v>
+        <v>1217.13</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>288.49</v>
+        <v>1111.46</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>278.75</v>
+        <v>989.4299999999999</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -1722,81 +1714,79 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>95.48999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>58.57</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>8.787599999999999</v>
+        <v>81.4867</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>9.1533</v>
+        <v>70.6683</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.3657</v>
+        <v>10.8184</v>
       </c>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="n">
-        <v>25.9</v>
+        <v>32.69</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>8902426</v>
+        <v>506973</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4834157</v>
+        <v>620953</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.84</v>
+        <v>0.82</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>29617</v>
+        <v>9758</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>26.902729</v>
+        <v>86.86682999999999</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>10.736661</v>
-      </c>
-      <c r="AD9" s="4" t="n">
-        <v>6.97</v>
-      </c>
+        <v>44.671246</v>
+      </c>
+      <c r="AD9" s="4" t="inlineStr"/>
       <c r="AE9" s="4" t="n">
-        <v>360.191</v>
+        <v>25.091</v>
       </c>
       <c r="AF9" s="4" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AG9" s="4" t="inlineStr"/>
+        <v>48.7</v>
+      </c>
+      <c r="AG9" s="4" t="n">
+        <v>35.8</v>
+      </c>
       <c r="AH9" s="4" t="n">
-        <v>1.6444142</v>
+        <v>14.970593</v>
       </c>
       <c r="AI9" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ9" s="4" t="n">
-        <v>94.116</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
       <c r="AK9" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MANAPPURAM/</t>
+          <t>https://www.screener.in/company/AVALON/</t>
         </is>
       </c>
       <c r="AL9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Oil and Natural Gas Corporation Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1806,17 +1796,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Integrated</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15.8</v>
+        <v>18.6</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -1829,19 +1819,19 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>297.2</v>
+        <v>2725</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.72</v>
+        <v>1.31</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>290.96</v>
+        <v>2483.88</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>282.91</v>
+        <v>2310.17</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>257.67</v>
+        <v>2274.87</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1854,99 +1844,101 @@
         </is>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>96.65000000000001</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>58.4</v>
+        <v>74.12</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>3.6843</v>
+        <v>139.6768</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>3.1882</v>
+        <v>123.6037</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4961</v>
+        <v>16.0732</v>
       </c>
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="2" t="n">
-        <v>27.58</v>
+        <v>45.45</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>10521642</v>
+        <v>4204144</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>17672498</v>
+        <v>3176567</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>373005</v>
+        <v>371005</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>9.808138</v>
+        <v>36.779015</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>7.001911</v>
-      </c>
-      <c r="AD10" s="2" t="inlineStr"/>
+        <v>47.741024</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>13.66</v>
+      </c>
       <c r="AE10" s="2" t="n">
-        <v>43.805</v>
+        <v>119.56</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AG10" s="2" t="n">
-        <v>16.2</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="n">
-        <v>1.0133669</v>
+        <v>4.3161635</v>
       </c>
       <c r="AI10" s="2" t="n">
-        <v>622</v>
-      </c>
-      <c r="AJ10" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="2" t="n">
+        <v>1.035</v>
+      </c>
       <c r="AK10" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ONGC/</t>
+          <t>https://www.screener.in/company/ADANIENT/</t>
         </is>
       </c>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ONGC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>57.8</v>
+        <v>57</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1955,23 +1947,23 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1317</v>
+        <v>1882.3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.46</v>
+        <v>-1.23</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1202.43</v>
+        <v>1820.96</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1101.45</v>
+        <v>1776.26</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>985.73</v>
+        <v>1723.8</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -1984,99 +1976,99 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>92.23999999999999</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>66.05</v>
+        <v>63</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>79.0244</v>
+        <v>41.2494</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>67.9637</v>
+        <v>33.6078</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>11.0607</v>
+        <v>7.6415</v>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="n">
-        <v>32.05</v>
+        <v>27.71</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>578441</v>
+        <v>2200951</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>602183</v>
+        <v>5366107</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.96</v>
+        <v>0.41</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>9061</v>
+        <v>450067</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>80.46856</v>
+        <v>41.18112</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>41.47935</v>
+        <v>33.151623</v>
       </c>
       <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="n">
-        <v>25.091</v>
+        <v>6.675</v>
       </c>
       <c r="AF11" s="4" t="n">
-        <v>48.7</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" s="4" t="n">
-        <v>35.8</v>
+        <v>15.7</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>13.900899</v>
+        <v>5.7812624</v>
       </c>
       <c r="AI11" s="4" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AJ11" s="4" t="inlineStr"/>
       <c r="AK11" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AVALON/</t>
+          <t>https://www.screener.in/company/SUNPHARMA/</t>
         </is>
       </c>
       <c r="AL11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Limited</t>
+          <t>JSW Steel Limited</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>11.8</v>
+        <v>27</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -2085,23 +2077,23 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4393.7</v>
+        <v>1285.2</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.59</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4308.4</v>
+        <v>1266.22</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4234.28</v>
+        <v>1238.15</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3915.71</v>
+        <v>1170.96</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2114,99 +2106,103 @@
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>96.45999999999999</v>
+        <v>97.81</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>57.82</v>
+        <v>57.49</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>58.9597</v>
+        <v>17.1624</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>46.3322</v>
+        <v>18.1627</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>12.6274</v>
+        <v>-1.0003</v>
       </c>
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="n">
-        <v>24.02</v>
+        <v>19.84</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>329331</v>
+        <v>1136358</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>283470</v>
+        <v>1863220</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>1.16</v>
+        <v>0.61</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>150950</v>
+        <v>310497</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>66.35079</v>
+        <v>13.941917</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>68.86803</v>
-      </c>
-      <c r="AD12" s="2" t="inlineStr"/>
+        <v>17.644154</v>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>27.26</v>
+      </c>
       <c r="AE12" s="2" t="n">
-        <v>33.4</v>
+        <v>94.155</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>17.6</v>
+        <v>14.2</v>
       </c>
       <c r="AG12" s="2" t="n">
-        <v>26.1</v>
+        <v>991.8</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>17.878517</v>
+        <v>3.1034567</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ12" s="2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AJ12" s="2" t="n">
+        <v>1.491</v>
+      </c>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TORNTPHARM/</t>
+          <t>https://www.screener.in/company/JSWSTEEL/</t>
         </is>
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ideaForge Technology Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>55.4</v>
+        <v>56.8</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -2215,23 +2211,23 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>817.7</v>
+        <v>8026</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>703.29</v>
+        <v>7886.36</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>585.3</v>
+        <v>7707.65</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>491.6</v>
+        <v>7437.54</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -2244,99 +2240,99 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>92.08</v>
+        <v>98.12</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>70.23</v>
+        <v>61.19</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>91.7236</v>
+        <v>127.0425</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>85.7116</v>
+        <v>115.0295</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>6.0119</v>
+        <v>12.013</v>
       </c>
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="n">
-        <v>46.96</v>
+        <v>25.48</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1647067</v>
+        <v>396261</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3634794</v>
+        <v>383079</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.45</v>
+        <v>1.03</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>3371</v>
-      </c>
-      <c r="AB13" s="4" t="inlineStr"/>
+        <v>115919</v>
+      </c>
+      <c r="AB13" s="4" t="n">
+        <v>64.38782999999999</v>
+      </c>
       <c r="AC13" s="4" t="n">
-        <v>27.844086</v>
-      </c>
-      <c r="AD13" s="4" t="n">
-        <v>-2.82</v>
-      </c>
+        <v>48.4503</v>
+      </c>
+      <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="n">
-        <v>13.974</v>
+        <v>83.60599999999999</v>
       </c>
       <c r="AF13" s="4" t="n">
-        <v>594.4</v>
-      </c>
-      <c r="AG13" s="4" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="AG13" s="4" t="n">
+        <v>35</v>
+      </c>
       <c r="AH13" s="4" t="n">
-        <v>5.6705623</v>
+        <v>12.747192</v>
       </c>
       <c r="AI13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="4" t="n">
-        <v>2.622</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr"/>
       <c r="AK13" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/IDEAFORGE/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEAFORGE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited</t>
+          <t>Torrent Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>54.6</v>
+        <v>56.8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>18.6</v>
+        <v>11.8</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -2349,19 +2345,19 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2689.8</v>
+        <v>4460.1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-0.96</v>
+        <v>1.51</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2458.5</v>
+        <v>4322.84</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2293.23</v>
+        <v>4243.14</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2270.34</v>
+        <v>3921.13</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -2374,101 +2370,99 @@
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>95.95999999999999</v>
+        <v>97.91</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>72.69</v>
+        <v>61.52</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>135.1597</v>
+        <v>63.561</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>119.5854</v>
+        <v>49.778</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>15.5743</v>
+        <v>13.783</v>
       </c>
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="n">
-        <v>44.56</v>
+        <v>24.12</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>2033884</v>
+        <v>314462</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>3057271</v>
+        <v>287650</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.67</v>
+        <v>1.09</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>373582</v>
+        <v>149166</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>36.97422</v>
+        <v>65.88042</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>48.07268</v>
-      </c>
-      <c r="AD14" s="2" t="n">
-        <v>13.66</v>
-      </c>
+        <v>68.05428999999999</v>
+      </c>
+      <c r="AD14" s="2" t="inlineStr"/>
       <c r="AE14" s="2" t="n">
-        <v>119.56</v>
+        <v>33.4</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AG14" s="2" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>26.1</v>
+      </c>
       <c r="AH14" s="2" t="n">
-        <v>4.346148</v>
+        <v>17.667267</v>
       </c>
       <c r="AI14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ14" s="2" t="n">
-        <v>1.035</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr"/>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIENT/</t>
+          <t>https://www.screener.in/company/TORNTPHARM/</t>
         </is>
       </c>
       <c r="AL14" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>CESC Limited</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>54</v>
+        <v>56.4</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>15</v>
+        <v>19.4</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -2477,23 +2471,23 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1905.8</v>
+        <v>181.06</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.47</v>
+        <v>2.64</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1814.5</v>
+        <v>180.32</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1771.94</v>
+        <v>172.58</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1722.21</v>
+        <v>164.15</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -2506,99 +2500,103 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>99.73</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>67.98</v>
+        <v>53.25</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>41.0645</v>
+        <v>3.0933</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>31.6974</v>
+        <v>5.0068</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>9.367000000000001</v>
+        <v>-1.9135</v>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="n">
-        <v>26.77</v>
+        <v>35.61</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3456331</v>
+        <v>1885950</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>5437634</v>
+        <v>4745597</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>451627</v>
+        <v>23966</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>41.323822</v>
+        <v>15.559381</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>33.2665</v>
-      </c>
-      <c r="AD15" s="4" t="inlineStr"/>
+        <v>12.633947</v>
+      </c>
+      <c r="AD15" s="4" t="n">
+        <v>12.55</v>
+      </c>
       <c r="AE15" s="4" t="n">
-        <v>6.675</v>
+        <v>164.311</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>13.5</v>
+        <v>5.6</v>
       </c>
       <c r="AG15" s="4" t="n">
-        <v>15.7</v>
+        <v>17.8</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>5.8012958</v>
+        <v>1.8832353</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
+        <v>331</v>
+      </c>
+      <c r="AJ15" s="4" t="n">
+        <v>0.921</v>
+      </c>
       <c r="AK15" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/SUNPHARMA/</t>
+          <t>https://www.screener.in/company/CESC/</t>
         </is>
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>Aurobindo Pharma Limited</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>54</v>
+        <v>56.2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>27</v>
+        <v>14.2</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -2607,23 +2605,23 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>462.1</v>
+        <v>1512.8</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.82</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>461.25</v>
+        <v>1455.44</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>452.27</v>
+        <v>1380.88</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>415.67</v>
+        <v>1243.85</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2636,103 +2634,99 @@
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>98.88</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>52.03</v>
+        <v>71.95</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>2.9176</v>
+        <v>43.1802</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>4.5398</v>
+        <v>41.2168</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>-1.6222</v>
+        <v>1.9634</v>
       </c>
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="2" t="n">
-        <v>17.16</v>
+        <v>27.42</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>7735499</v>
+        <v>1538969</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>11078205</v>
+        <v>1242008</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>281606</v>
+        <v>87688</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>9.055688</v>
+        <v>25.374624</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>7.990388</v>
-      </c>
-      <c r="AD16" s="2" t="n">
-        <v>28.12</v>
-      </c>
+        <v>19.942963</v>
+      </c>
+      <c r="AD16" s="2" t="inlineStr"/>
       <c r="AE16" s="2" t="n">
-        <v>11.629</v>
+        <v>22.248</v>
       </c>
       <c r="AF16" s="2" t="n">
-        <v>16.2</v>
+        <v>8.4</v>
       </c>
       <c r="AG16" s="2" t="n">
-        <v>12.9</v>
+        <v>7.6</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>2.3641868</v>
+        <v>2.5257087</v>
       </c>
       <c r="AI16" s="2" t="n">
-        <v>476</v>
-      </c>
-      <c r="AJ16" s="2" t="n">
-        <v>1.856</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr"/>
       <c r="AK16" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/COALINDIA/</t>
+          <t>https://www.screener.in/company/AUROPHARMA/</t>
         </is>
       </c>
       <c r="AL16" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:COALINDIA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>Arvind Limited</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Textile Manufacturing</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>53.8</v>
+        <v>53</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>11.8</v>
+        <v>17</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -2745,19 +2739,19 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>8020.5</v>
+        <v>485.8</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.77</v>
+        <v>2.79</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>7871.66</v>
+        <v>426.81</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>7694.66</v>
+        <v>395.97</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>7431.62</v>
+        <v>352.77</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
@@ -2770,99 +2764,103 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>98.05</v>
+        <v>99.16</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>60.96</v>
+        <v>79.91</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>131.0527</v>
+        <v>23.7396</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>112.0263</v>
+        <v>17.9857</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>19.0264</v>
+        <v>5.7539</v>
       </c>
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="n">
-        <v>24.54</v>
+        <v>41.07</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>323387</v>
+        <v>1111479</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>378904</v>
+        <v>1424073</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>115402</v>
+        <v>12929</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>64.146416</v>
+        <v>31.238125</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>48.233948</v>
-      </c>
-      <c r="AD17" s="4" t="inlineStr"/>
+        <v>18.520027</v>
+      </c>
+      <c r="AD17" s="4" t="n">
+        <v>10.66</v>
+      </c>
       <c r="AE17" s="4" t="n">
-        <v>83.60599999999999</v>
+        <v>40.071</v>
       </c>
       <c r="AF17" s="4" t="n">
-        <v>17.2</v>
+        <v>15.9</v>
       </c>
       <c r="AG17" s="4" t="n">
-        <v>35</v>
+        <v>5.9</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>12.690271</v>
+        <v>3.1932802</v>
       </c>
       <c r="AI17" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ17" s="4" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="AJ17" s="4" t="n">
+        <v>1.141</v>
+      </c>
       <c r="AK17" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/ARVIND/</t>
         </is>
       </c>
       <c r="AL17" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ARVIND</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Limited</t>
+          <t>Manappuram Finance Limited</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>53.8</v>
+        <v>52.4</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>14.8</v>
+        <v>16.4</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -2875,19 +2873,19 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>272.7</v>
+        <v>315.3</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.11</v>
+        <v>3.01</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>266.9</v>
+        <v>300.22</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>261.6</v>
+        <v>289.54</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>246.79</v>
+        <v>279.12</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -2900,99 +2898,101 @@
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>95.48</v>
+        <v>98.36</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>58.42</v>
+        <v>63.61</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>3.6638</v>
+        <v>9.038</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>3.7613</v>
+        <v>9.1302</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>-0.0975</v>
+        <v>-0.0922</v>
       </c>
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="n">
-        <v>23.72</v>
+        <v>25.02</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>4619071</v>
+        <v>3193575</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>3571474</v>
+        <v>4723663</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>1.29</v>
+        <v>0.68</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>77730</v>
+        <v>30298</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>553.9796</v>
+        <v>27.568375</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>175.01387</v>
-      </c>
-      <c r="AD18" s="2" t="inlineStr"/>
+        <v>10.98354</v>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v>6.97</v>
+      </c>
       <c r="AE18" s="2" t="n">
-        <v>97.748</v>
+        <v>360.191</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="AG18" s="2" t="n">
-        <v>144.4</v>
-      </c>
+        <v>109.3</v>
+      </c>
+      <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="n">
-        <v>56.1195</v>
+        <v>1.6822258</v>
       </c>
       <c r="AI18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="2" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="AJ18" s="2" t="n">
+        <v>94.116</v>
+      </c>
       <c r="AK18" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NYKAA/</t>
+          <t>https://www.screener.in/company/MANAPPURAM/</t>
         </is>
       </c>
       <c r="AL18" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>53.2</v>
+        <v>50.8</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -3005,19 +3005,19 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1500.5</v>
+        <v>271.45</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.75</v>
+        <v>-0.46</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1449.4</v>
+        <v>267.34</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1375.49</v>
+        <v>261.98</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1241.15</v>
+        <v>247.03</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -3030,99 +3030,99 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>98.2</v>
+        <v>95.05</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>70.02</v>
+        <v>56.83</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>43.4003</v>
+        <v>3.5829</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>40.726</v>
+        <v>3.7256</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.6743</v>
+        <v>-0.1427</v>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="n">
-        <v>26.75</v>
+        <v>23.08</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>939496</v>
+        <v>2436357</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1233202</v>
+        <v>3457819</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>87043</v>
+        <v>77587</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>25.204933</v>
+        <v>552.95917</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>19.796402</v>
+        <v>174.6915</v>
       </c>
       <c r="AD19" s="4" t="inlineStr"/>
       <c r="AE19" s="4" t="n">
-        <v>22.248</v>
+        <v>97.748</v>
       </c>
       <c r="AF19" s="4" t="n">
-        <v>8.4</v>
+        <v>26.7</v>
       </c>
       <c r="AG19" s="4" t="n">
-        <v>7.6</v>
+        <v>144.4</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>2.507147</v>
+        <v>56.01613</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AJ19" s="4" t="inlineStr"/>
       <c r="AK19" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AUROPHARMA/</t>
+          <t>https://www.screener.in/company/NYKAA/</t>
         </is>
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bharti Airtel Limited</t>
+          <t>RBL Bank Limited</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Telecom Services</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.1</v>
+        <v>50.2</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>34.5</v>
+        <v>24</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18.6</v>
+        <v>26.2</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -3131,27 +3131,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1938.1</v>
+        <v>323.65</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.72</v>
+        <v>-0.6</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1845.84</v>
+        <v>328.74</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1862.19</v>
+        <v>321.13</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1915.71</v>
+        <v>294.76</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3160,103 +3160,97 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>89.13</v>
+        <v>92.5</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>63.12</v>
+        <v>48.12</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>5.7931</v>
+        <v>3.7575</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>-5.2733</v>
+        <v>5.5177</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>11.0665</v>
+        <v>-1.7601</v>
       </c>
       <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="n">
-        <v>25.89</v>
+        <v>21.07</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>13888648</v>
+        <v>2758793</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>9714502</v>
+        <v>6498683</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>1.43</v>
+        <v>0.42</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>1165603</v>
+        <v>20021</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>43.11627</v>
+        <v>22.982956</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>22.933964</v>
-      </c>
-      <c r="AD20" s="2" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="AE20" s="2" t="n">
-        <v>99.718</v>
-      </c>
+        <v>17.051458</v>
+      </c>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
       <c r="AF20" s="2" t="n">
-        <v>15.7</v>
+        <v>40.8</v>
       </c>
       <c r="AG20" s="2" t="n">
-        <v>-34</v>
+        <v>367.9</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>7.5048046</v>
+        <v>1.1959891</v>
       </c>
       <c r="AI20" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="AJ20" s="2" t="n">
-        <v>0.517</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr"/>
       <c r="AK20" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BHARTIARTL/</t>
+          <t>https://www.screener.in/company/RBLBANK/</t>
         </is>
       </c>
       <c r="AL20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BHARTIARTL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>HFCL Limited</t>
+          <t>Berger Paints India Limited</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>53</v>
+        <v>50.1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>43</v>
+        <v>35.5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>10</v>
+        <v>14.6</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -3265,27 +3259,27 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>139.69</v>
+        <v>507.7</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5.54</v>
+        <v>-3.22</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>128.43</v>
+        <v>492.65</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>105.37</v>
+        <v>475.02</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>83.27</v>
+        <v>496.27</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -3294,101 +3288,103 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>89.95</v>
+        <v>84.48</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>58.5</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>16.3487</v>
+        <v>17.7539</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>15.9315</v>
+        <v>14.9843</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.4172</v>
+        <v>2.7695</v>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="n">
-        <v>64.59999999999999</v>
+        <v>33.04</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>50784047</v>
+        <v>353321</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>82077029</v>
+        <v>958473</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>21144</v>
+        <v>59221</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>383.80554</v>
+        <v>52.632126</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>26.571154</v>
+        <v>39.99534</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>7.27</v>
+        <v>17.23</v>
       </c>
       <c r="AE21" s="4" t="n">
-        <v>38.321</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="AF21" s="4" t="n">
-        <v>127.8</v>
-      </c>
-      <c r="AG21" s="4" t="inlineStr"/>
+        <v>6.1</v>
+      </c>
+      <c r="AG21" s="4" t="n">
+        <v>27.7</v>
+      </c>
       <c r="AH21" s="4" t="n">
-        <v>4.264506</v>
+        <v>8.565935</v>
       </c>
       <c r="AI21" s="4" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>1.991</v>
+        <v>2.115</v>
       </c>
       <c r="AK21" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/HFCL/</t>
+          <t>https://www.screener.in/company/BERGEPAINT/</t>
         </is>
       </c>
       <c r="AL21" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Tata Steel Limited</t>
+          <t>Syrma SGS Technology Limited</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>51</v>
+        <v>49.6</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -3397,23 +3393,23 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>209.71</v>
+        <v>984.15</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-3.29</v>
+        <v>1.46</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>212.82</v>
+        <v>1002.96</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>206.91</v>
+        <v>932.92</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>186.98</v>
+        <v>798.12</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -3422,87 +3418,87 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>93.45</v>
+        <v>82.84</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>47.81</v>
+        <v>49.94</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>2.8066</v>
+        <v>31.245</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>3.3451</v>
+        <v>46.1609</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>-0.5386</v>
+        <v>-14.9159</v>
       </c>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="n">
-        <v>21.53</v>
+        <v>38.19</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>73796001</v>
+        <v>802254</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>27274863</v>
+        <v>1735329</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>2.71</v>
+        <v>0.46</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>261023</v>
+        <v>18912</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>28.513622</v>
+        <v>57.99173</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>11.132447</v>
+        <v>34.514725</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>11.16</v>
+        <v>14.14</v>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>89.01600000000001</v>
+        <v>13.045</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>12.5</v>
+        <v>58.4</v>
       </c>
       <c r="AG22" s="2" t="n">
-        <v>125.4</v>
+        <v>43.7</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>2.745831</v>
+        <v>6.5090127</v>
       </c>
       <c r="AI22" s="2" t="n">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="AJ22" s="2" t="n">
-        <v>0.748</v>
+        <v>1.7</v>
       </c>
       <c r="AK22" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TATASTEEL/</t>
+          <t>https://www.screener.in/company/SYRMA/</t>
         </is>
       </c>
       <c r="AL22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SYRMA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>RBL Bank Limited</t>
+          <t>Bandhan Bank Limited</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -3516,13 +3512,13 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>50.2</v>
+        <v>49.4</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>26.2</v>
+        <v>21.4</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -3535,19 +3531,19 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>325.6</v>
+        <v>191.21</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.7</v>
+        <v>0.46</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>329.28</v>
+        <v>192.1</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>321.03</v>
+        <v>181.1</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>294.47</v>
+        <v>166.43</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -3560,77 +3556,79 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>93.06</v>
+        <v>89.91</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>49.26</v>
+        <v>52.46</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.771</v>
+        <v>5.7453</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>5.9577</v>
+        <v>7.9352</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.1867</v>
+        <v>-2.1899</v>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="n">
-        <v>22.57</v>
+        <v>28.05</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>4664716</v>
+        <v>4802152</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>6608352</v>
+        <v>17758522</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.71</v>
+        <v>0.27</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>20024</v>
+        <v>30696</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>22.9539</v>
+        <v>25.104082</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>17.054092</v>
-      </c>
-      <c r="AD23" s="4" t="inlineStr"/>
+        <v>8.811726</v>
+      </c>
+      <c r="AD23" s="4" t="n">
+        <v>4.88</v>
+      </c>
       <c r="AE23" s="4" t="inlineStr"/>
       <c r="AF23" s="4" t="n">
-        <v>40.8</v>
+        <v>119.3</v>
       </c>
       <c r="AG23" s="4" t="n">
-        <v>367.9</v>
+        <v>68</v>
       </c>
       <c r="AH23" s="4" t="n">
-        <v>1.1961739</v>
+        <v>1.198636</v>
       </c>
       <c r="AI23" s="4" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="AJ23" s="4" t="inlineStr"/>
       <c r="AK23" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/RBLBANK/</t>
+          <t>https://www.screener.in/company/BANDHANBNK/</t>
         </is>
       </c>
       <c r="AL23" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BANDHANBNK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Limited</t>
+          <t>HFCL Limited</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3640,17 +3638,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>49.6</v>
+        <v>47</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>21.6</v>
+        <v>10</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -3659,23 +3657,23 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>969.95</v>
+        <v>138.17</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-4.27</v>
+        <v>-1.09</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1004.94</v>
+        <v>129.36</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>930.83</v>
+        <v>106.66</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>796.25</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -3684,107 +3682,105 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>81.65000000000001</v>
+        <v>88.97</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>47.45</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>37.2275</v>
+        <v>15.1185</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>49.8899</v>
+        <v>15.7689</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>-12.6624</v>
+        <v>-0.6504</v>
       </c>
       <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="2" t="n">
-        <v>39.9</v>
+        <v>62.38</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>1069302</v>
+        <v>46887470</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>1856222</v>
+        <v>82404133</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>18957</v>
+        <v>21590</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>58.30273</v>
+        <v>391.91663</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>34.59734</v>
+        <v>27.132692</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>14.14</v>
+        <v>7.27</v>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>13.045</v>
+        <v>38.321</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="AG24" s="2" t="n">
-        <v>43.7</v>
-      </c>
+        <v>127.8</v>
+      </c>
+      <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="n">
-        <v>6.524593</v>
+        <v>4.3546295</v>
       </c>
       <c r="AI24" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AJ24" s="2" t="n">
-        <v>1.7</v>
+        <v>1.991</v>
       </c>
       <c r="AK24" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/SYRMA/</t>
+          <t>https://www.screener.in/company/HFCL/</t>
         </is>
       </c>
       <c r="AL24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SYRMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bandhan Bank Limited</t>
+          <t>Dr. Reddy's Laboratories Limited</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>49.4</v>
+        <v>46</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>21.4</v>
+        <v>10</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -3793,23 +3789,23 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>190.34</v>
+        <v>1335.2</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.12</v>
+        <v>0.3</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>192.2</v>
+        <v>1298.2</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>180.69</v>
+        <v>1281.78</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>166.18</v>
+        <v>1256.26</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -3822,99 +3818,103 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>89.5</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>51.6</v>
+        <v>59.29</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>6.6065</v>
+        <v>13.6196</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>8.482699999999999</v>
+        <v>10.6891</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.8761</v>
+        <v>2.9306</v>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="n">
-        <v>29.82</v>
+        <v>16.8</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>7391229</v>
+        <v>2488019</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>17727837</v>
+        <v>3363296</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>30804</v>
+        <v>110602</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>25.192358</v>
+        <v>26.388557</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>8.842710500000001</v>
+        <v>20.700478</v>
       </c>
       <c r="AD25" s="4" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="AE25" s="4" t="inlineStr"/>
+        <v>11.83</v>
+      </c>
+      <c r="AE25" s="4" t="n">
+        <v>20.328</v>
+      </c>
       <c r="AF25" s="4" t="n">
-        <v>119.3</v>
+        <v>-11.6</v>
       </c>
       <c r="AG25" s="4" t="n">
-        <v>68</v>
+        <v>-86.2</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>1.2028509</v>
+        <v>2.9371836</v>
       </c>
       <c r="AI25" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="AJ25" s="4" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AJ25" s="4" t="n">
+        <v>1.802</v>
+      </c>
       <c r="AK25" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BANDHANBNK/</t>
+          <t>https://www.screener.in/company/DRREDDY/</t>
         </is>
       </c>
       <c r="AL25" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BANDHANBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CESC Limited</t>
+          <t>The Federal Bank Limited</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>47.4</v>
+        <v>45.6</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>19.4</v>
+        <v>23.6</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -3927,19 +3927,19 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>176.4</v>
+        <v>286.6</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-2.05</v>
+        <v>0.93</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>180.25</v>
+        <v>286.79</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>172.23</v>
+        <v>283.8</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>163.98</v>
+        <v>256.93</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -3952,103 +3952,99 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>86.26000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>47.98</v>
+        <v>50.33</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>3.4036</v>
+        <v>0.0164</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>5.4851</v>
+        <v>1.3961</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>-2.0816</v>
+        <v>-1.3796</v>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="2" t="n">
-        <v>36.86</v>
+        <v>14.81</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>3507494</v>
+        <v>6905213</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>4798294</v>
+        <v>8003545</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>24001</v>
+        <v>70731</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>15.581756</v>
+        <v>16.421625</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>12.652116</v>
+        <v>12.08132</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="AE26" s="2" t="n">
-        <v>164.311</v>
-      </c>
+        <v>11.73</v>
+      </c>
+      <c r="AE26" s="2" t="inlineStr"/>
       <c r="AF26" s="2" t="n">
-        <v>5.6</v>
+        <v>12.3</v>
       </c>
       <c r="AG26" s="2" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>1.8859434</v>
+        <v>1.9434006</v>
       </c>
       <c r="AI26" s="2" t="n">
-        <v>340</v>
-      </c>
-      <c r="AJ26" s="2" t="n">
-        <v>0.921</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr"/>
       <c r="AK26" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CESC/</t>
+          <t>https://www.screener.in/company/FEDERALBNK/</t>
         </is>
       </c>
       <c r="AL26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Berger Paints India Limited</t>
+          <t>Cipla Limited</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>47.1</v>
+        <v>45.5</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>14.6</v>
+        <v>10</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -4061,19 +4057,19 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>524.6</v>
+        <v>1409.8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.66</v>
+        <v>-1.15</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>491.06</v>
+        <v>1344.58</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>473.69</v>
+        <v>1319.63</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>496.15</v>
+        <v>1393.22</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -4086,103 +4082,103 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>87.29000000000001</v>
+        <v>84.27</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>66.43000000000001</v>
+        <v>64.67</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>18.7975</v>
+        <v>36.617</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>14.292</v>
+        <v>26.6395</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.5056</v>
+        <v>9.977499999999999</v>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="n">
-        <v>33.51</v>
+        <v>38.14</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>490228</v>
+        <v>1379218</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>947465</v>
+        <v>2264053</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>59198</v>
+        <v>113544</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>52.6114</v>
+        <v>29.3261</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>39.979588</v>
+        <v>22.188253</v>
       </c>
       <c r="AD27" s="4" t="n">
-        <v>17.23</v>
+        <v>11.74</v>
       </c>
       <c r="AE27" s="4" t="n">
-        <v>9.164999999999999</v>
+        <v>1.778</v>
       </c>
       <c r="AF27" s="4" t="n">
-        <v>6.1</v>
+        <v>-3.8</v>
       </c>
       <c r="AG27" s="4" t="n">
-        <v>27.7</v>
+        <v>-54.6</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>8.562563000000001</v>
+        <v>3.4490626</v>
       </c>
       <c r="AI27" s="4" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>2.115</v>
+        <v>3.443</v>
       </c>
       <c r="AK27" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BERGEPAINT/</t>
+          <t>https://www.screener.in/company/CIPLA/</t>
         </is>
       </c>
       <c r="AL27" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CIPLA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -4191,23 +4187,23 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1331.2</v>
+        <v>456.95</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-0.41</v>
+        <v>-1.11</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1294.3</v>
+        <v>460.84</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1279.6</v>
+        <v>452.45</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1255.47</v>
+        <v>416.08</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -4220,71 +4216,71 @@
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>96.75</v>
+        <v>93.02</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>58.62</v>
+        <v>48.28</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>11.833</v>
+        <v>2.2506</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>9.9564</v>
+        <v>4.0819</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>1.8766</v>
+        <v>-1.8313</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
       <c r="W28" s="2" t="n">
-        <v>17.79</v>
+        <v>16</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>1926791</v>
+        <v>7319865</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>3300432</v>
+        <v>11177370</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>111168</v>
+        <v>281976</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>26.53418</v>
+        <v>9.069375000000001</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>20.806442</v>
+        <v>8.000878999999999</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>11.83</v>
+        <v>28.12</v>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>20.328</v>
+        <v>11.629</v>
       </c>
       <c r="AF28" s="2" t="n">
-        <v>-11.6</v>
+        <v>16.2</v>
       </c>
       <c r="AG28" s="2" t="n">
-        <v>-86.2</v>
+        <v>12.9</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>2.9522188</v>
+        <v>2.367291</v>
       </c>
       <c r="AI28" s="2" t="n">
-        <v>60</v>
+        <v>481</v>
       </c>
       <c r="AJ28" s="2" t="n">
-        <v>1.802</v>
+        <v>1.856</v>
       </c>
       <c r="AK28" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DRREDDY/</t>
+          <t>https://www.screener.in/company/COALINDIA/</t>
         </is>
       </c>
       <c r="AL28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DRREDDY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:COALINDIA</t>
         </is>
       </c>
     </row>
@@ -4329,19 +4325,19 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1450.2</v>
+        <v>1455.8</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.19</v>
+        <v>0.39</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1422.31</v>
+        <v>1425.5</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1407.05</v>
+        <v>1408.97</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1439.82</v>
+        <v>1439.98</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -4354,41 +4350,41 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>92.08</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>57.07</v>
+        <v>57.98</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>24.4097</v>
+        <v>23.9486</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>18.7509</v>
+        <v>19.7904</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.6588</v>
+        <v>4.1582</v>
       </c>
       <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="n">
-        <v>19.4</v>
+        <v>19.31</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>655599</v>
+        <v>617156</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1085279</v>
+        <v>1080727</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>148168</v>
+        <v>148158</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>60.48193</v>
+        <v>60.60366</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>48.02416</v>
+        <v>48.02086</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>23.52</v>
@@ -4403,7 +4399,7 @@
         <v>37</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>15.512319</v>
+        <v>15.511251</v>
       </c>
       <c r="AI29" s="4" t="n">
         <v>69</v>
@@ -4425,32 +4421,32 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Limited</t>
+          <t>Tata Steel Limited</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>43.4</v>
+        <v>44</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>27</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -4459,23 +4455,23 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>296.55</v>
+        <v>209.29</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-3.04</v>
+        <v>-0.2</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>309.13</v>
+        <v>212.48</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>304.6</v>
+        <v>207.01</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>288.32</v>
+        <v>187.2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -4484,107 +4480,107 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>91.26000000000001</v>
+        <v>93.27</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>34.16</v>
+        <v>47.27</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>-1.2054</v>
+        <v>2.1949</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>1.6088</v>
+        <v>3.1151</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>-2.8142</v>
+        <v>-0.9202</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="n">
-        <v>25.66</v>
+        <v>20.45</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>16036198</v>
+        <v>32573663</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>9449791</v>
+        <v>28032195</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>1.7</v>
+        <v>1.16</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>277716</v>
+        <v>255186</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>14.848334</v>
+        <v>27.838097</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>14.979996</v>
+        <v>10.883512</v>
       </c>
       <c r="AD30" s="2" t="n">
-        <v>16.49</v>
+        <v>11.16</v>
       </c>
       <c r="AE30" s="2" t="n">
-        <v>150.993</v>
+        <v>89.01600000000001</v>
       </c>
       <c r="AF30" s="2" t="n">
-        <v>-5</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" s="2" t="n">
-        <v>9.6</v>
+        <v>125.4</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>2.8029401</v>
+        <v>2.6844308</v>
       </c>
       <c r="AI30" s="2" t="n">
-        <v>413</v>
+        <v>191</v>
       </c>
       <c r="AJ30" s="2" t="n">
-        <v>0.625</v>
+        <v>0.748</v>
       </c>
       <c r="AK30" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POWERGRID/</t>
+          <t>https://www.screener.in/company/TATASTEEL/</t>
         </is>
       </c>
       <c r="AL30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERGRID</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Cipla Limited</t>
+          <t>Power Grid Corporation of India Limited</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>42.5</v>
+        <v>40.4</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>32.5</v>
+        <v>24</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10</v>
+        <v>16.4</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -4593,132 +4589,132 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1426.2</v>
+        <v>298.6</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1337.72</v>
+        <v>308.13</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1315.95</v>
+        <v>304.36</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1393.05</v>
+        <v>288.42</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>85.25</v>
+        <v>91.89</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>68.56999999999999</v>
+        <v>37.48</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>35.4247</v>
+        <v>-1.8407</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>24.1451</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>11.2796</v>
+        <v>-2.7596</v>
       </c>
       <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="n">
-        <v>37.95</v>
+        <v>25.9</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2013605</v>
+        <v>12580156</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2266506</v>
+        <v>9661682</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.89</v>
+        <v>1.3</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>113884</v>
+        <v>276693</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>29.334166</v>
+        <v>14.778937</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>22.254555</v>
+        <v>14.924811</v>
       </c>
       <c r="AD31" s="4" t="n">
-        <v>11.74</v>
+        <v>16.49</v>
       </c>
       <c r="AE31" s="4" t="n">
-        <v>1.778</v>
+        <v>150.993</v>
       </c>
       <c r="AF31" s="4" t="n">
-        <v>-3.8</v>
+        <v>-5</v>
       </c>
       <c r="AG31" s="4" t="n">
-        <v>-54.6</v>
+        <v>9.6</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>3.4593687</v>
+        <v>2.7926145</v>
       </c>
       <c r="AI31" s="4" t="n">
-        <v>91</v>
+        <v>410</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>3.443</v>
+        <v>0.625</v>
       </c>
       <c r="AK31" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CIPLA/</t>
+          <t>https://www.screener.in/company/POWERGRID/</t>
         </is>
       </c>
       <c r="AL31" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CIPLA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>The Federal Bank Limited</t>
+          <t>Larsen &amp; Toubro Limited</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>41.6</v>
+        <v>39.8</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>23.6</v>
+        <v>21.8</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -4731,19 +4727,19 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>283.95</v>
+        <v>3921</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>286.81</v>
+        <v>3954.21</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>283.69</v>
+        <v>3938.57</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>256.63</v>
+        <v>3857.06</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -4756,99 +4752,103 @@
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>94.02</v>
+        <v>88.31</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>47.08</v>
+        <v>47.61</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>0.001</v>
+        <v>-2.3427</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>1.741</v>
+        <v>17.0988</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>-1.74</v>
+        <v>-19.4415</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="2" t="n">
-        <v>15.48</v>
+        <v>10.91</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>7212332</v>
+        <v>2318170</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>8045626</v>
+        <v>2545237</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>70620</v>
+        <v>538712</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>16.386507</v>
+        <v>33.51305</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>12.062381</v>
+        <v>21.300083</v>
       </c>
       <c r="AD32" s="2" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="AE32" s="2" t="inlineStr"/>
+        <v>16.95</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>97.64</v>
+      </c>
       <c r="AF32" s="2" t="n">
-        <v>12.3</v>
+        <v>11.7</v>
       </c>
       <c r="AG32" s="2" t="n">
-        <v>22.2</v>
+        <v>-34.5</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>1.9403541</v>
+        <v>4.9290724</v>
       </c>
       <c r="AI32" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ32" s="2" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>1.251</v>
+      </c>
       <c r="AK32" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/FEDERALBNK/</t>
+          <t>https://www.screener.in/company/LT/</t>
         </is>
       </c>
       <c r="AL32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Limited</t>
+          <t>Avenue Supermarts Limited</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Discount Stores</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>21.8</v>
+        <v>15.4</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -4857,23 +4857,23 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3917.8</v>
+        <v>4236</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.23</v>
+        <v>-1.6</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3957.7</v>
+        <v>4372.54</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3939.28</v>
+        <v>4273.56</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3856.42</v>
+        <v>4125.13</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
@@ -4882,75 +4882,75 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>88.23999999999999</v>
+        <v>85.58</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>47.35</v>
+        <v>40.28</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.2257</v>
+        <v>-4.1313</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>21.9592</v>
+        <v>33.4747</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-21.7335</v>
+        <v>-37.606</v>
       </c>
       <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="n">
-        <v>10.99</v>
+        <v>22.68</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>1771638</v>
+        <v>367515</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2550665</v>
+        <v>341896</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>539400</v>
+        <v>269578</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>33.584583</v>
+        <v>90.35191</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>21.32728</v>
+        <v>58.295223</v>
       </c>
       <c r="AD33" s="4" t="n">
-        <v>16.95</v>
+        <v>12.94</v>
       </c>
       <c r="AE33" s="4" t="n">
-        <v>97.64</v>
+        <v>9.913</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>11.7</v>
+        <v>18.9</v>
       </c>
       <c r="AG33" s="4" t="n">
-        <v>-34.5</v>
+        <v>19.6</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>4.9353657</v>
+        <v>10.995138</v>
       </c>
       <c r="AI33" s="4" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>1.251</v>
+        <v>1.977</v>
       </c>
       <c r="AK33" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/LT/</t>
+          <t>https://www.screener.in/company/DMART/</t>
         </is>
       </c>
       <c r="AL33" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DMART</t>
         </is>
       </c>
     </row>
@@ -4995,19 +4995,19 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2614</v>
+        <v>2600.7</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.32</v>
+        <v>-0.51</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2517.39</v>
+        <v>2525.33</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2455.24</v>
+        <v>2460.95</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2476.27</v>
+        <v>2477.5</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -5020,41 +5020,41 @@
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>87.55</v>
+        <v>87.11</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>63.88</v>
+        <v>62.02</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>62.0639</v>
+        <v>61.0116</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>55.2095</v>
+        <v>56.3699</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>6.8544</v>
+        <v>4.6417</v>
       </c>
       <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="2" t="n">
-        <v>28.75</v>
+        <v>28.64</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>898479</v>
+        <v>688639</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>1044843</v>
+        <v>995181</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>0.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>249315</v>
+        <v>249104</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>65.03375</v>
+        <v>64.8814</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>51.91818</v>
+        <v>51.87426</v>
       </c>
       <c r="AD34" s="2" t="inlineStr"/>
       <c r="AE34" s="2" t="n">
@@ -5067,7 +5067,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>12.727317</v>
+        <v>12.716551</v>
       </c>
       <c r="AI34" s="2" t="n">
         <v>96</v>
@@ -5087,32 +5087,32 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Titan Company Limited</t>
+          <t>Muthoot Finance Limited</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Luxury Goods</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -5121,27 +5121,27 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>💎 High ROE</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4169.7</v>
+        <v>3303.6</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.01</v>
+        <v>0.39</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>4273.26</v>
+        <v>3431.06</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4262.86</v>
+        <v>3446.4</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3964.22</v>
+        <v>3292.31</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
@@ -5150,103 +5150,103 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>90.55</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>43.35</v>
+        <v>42.22</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-45.1009</v>
+        <v>-21.8665</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-10.2276</v>
+        <v>4.7548</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-34.8733</v>
+        <v>-26.6212</v>
       </c>
       <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="n">
-        <v>10.46</v>
+        <v>12.94</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>851825</v>
+        <v>908258</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>1426733</v>
+        <v>812804</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.6</v>
+        <v>1.12</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>363866</v>
+        <v>131878</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>71.81373000000001</v>
+        <v>12.460266</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>47.65195</v>
+        <v>9.512487</v>
       </c>
       <c r="AD35" s="4" t="n">
-        <v>37.13</v>
+        <v>30.41</v>
       </c>
       <c r="AE35" s="4" t="n">
-        <v>195.001</v>
+        <v>379.707</v>
       </c>
       <c r="AF35" s="4" t="n">
-        <v>80.5</v>
+        <v>53.7</v>
       </c>
       <c r="AG35" s="4" t="n">
-        <v>35.1</v>
+        <v>126.7</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>28.411728</v>
+        <v>3.7022343</v>
       </c>
       <c r="AI35" s="4" t="n">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>1.276</v>
+        <v>128.286</v>
       </c>
       <c r="AK35" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TITAN/</t>
+          <t>https://www.screener.in/company/MUTHOOTFIN/</t>
         </is>
       </c>
       <c r="AL35" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Limited</t>
+          <t>Titan Company Limited</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Discount Stores</t>
+          <t>Luxury Goods</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15.4</v>
+        <v>22</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
@@ -5255,23 +5255,23 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4304.7</v>
+        <v>4102</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-1.24</v>
+        <v>-1.62</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4386.92</v>
+        <v>4256.95</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4275.09</v>
+        <v>4256.55</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>4124.02</v>
+        <v>3965.59</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -5280,136 +5280,132 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>86.97</v>
+        <v>89.08</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>44.8</v>
+        <v>40.13</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>7.9181</v>
+        <v>-52.488</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>42.8762</v>
+        <v>-18.6797</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>-34.9581</v>
+        <v>-33.8083</v>
       </c>
       <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="n">
-        <v>21.69</v>
+        <v>9.85</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>168644</v>
+        <v>711398</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>344094</v>
+        <v>1429498</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>276257</v>
+        <v>362668</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>92.83365999999999</v>
+        <v>71.70291</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>59.739346</v>
+        <v>47.495125</v>
       </c>
       <c r="AD36" s="2" t="n">
-        <v>12.94</v>
+        <v>37.13</v>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>9.913</v>
+        <v>195.001</v>
       </c>
       <c r="AF36" s="2" t="n">
-        <v>18.9</v>
+        <v>80.5</v>
       </c>
       <c r="AG36" s="2" t="n">
-        <v>19.6</v>
+        <v>35.1</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>11.267516</v>
+        <v>28.318222</v>
       </c>
       <c r="AI36" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AJ36" s="2" t="n">
-        <v>1.977</v>
+        <v>1.276</v>
       </c>
       <c r="AK36" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DMART/</t>
+          <t>https://www.screener.in/company/TITAN/</t>
         </is>
       </c>
       <c r="AL36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DMART</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>K.P.R. Mill Limited</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Textile Manufacturing</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>35</v>
+        <v>36.5</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>15</v>
+        <v>28.5</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>📈 EMA Bull Stack | 💎 High ROE</t>
-        </is>
-      </c>
+      <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="n">
-        <v>429.8</v>
+        <v>956.65</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-3.58</v>
+        <v>4.91</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>448.51</v>
+        <v>925.9</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>434.85</v>
+        <v>910.24</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>402.45</v>
+        <v>945.46</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -5418,103 +5414,99 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>88.34999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>41.54</v>
+        <v>58.91</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>1.7339</v>
+        <v>9.0938</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>6.3047</v>
+        <v>13.1193</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>-4.5708</v>
+        <v>-4.0255</v>
       </c>
       <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="n">
-        <v>15</v>
+        <v>25.21</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>4593536</v>
+        <v>310934</v>
       </c>
       <c r="Y37" s="4" t="n">
-        <v>6665798</v>
+        <v>225577</v>
       </c>
       <c r="Z37" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.38</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>142432</v>
+        <v>32654</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>5.4994903</v>
+        <v>37.607494</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>6.630054</v>
-      </c>
-      <c r="AD37" s="4" t="n">
-        <v>20.47</v>
-      </c>
+        <v>26.450455</v>
+      </c>
+      <c r="AD37" s="4" t="inlineStr"/>
       <c r="AE37" s="4" t="n">
-        <v>586.0170000000001</v>
+        <v>6.46</v>
       </c>
       <c r="AF37" s="4" t="n">
-        <v>-15.4</v>
+        <v>-4</v>
       </c>
       <c r="AG37" s="4" t="n">
-        <v>10.8</v>
+        <v>3</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>1.0719599</v>
+        <v>6.092783</v>
       </c>
       <c r="AI37" s="4" t="n">
-        <v>340</v>
-      </c>
-      <c r="AJ37" s="4" t="n">
-        <v>287.366</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr"/>
       <c r="AK37" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/PFC/</t>
+          <t>https://www.screener.in/company/KPRMILL/</t>
         </is>
       </c>
       <c r="AL37" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PFC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:KPRMILL</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>NTPC Limited</t>
+          <t>Power Finance Corporation Limited</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>32.2</v>
+        <v>35</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>14.2</v>
+        <v>20</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -5523,23 +5515,23 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>388.3</v>
+        <v>431.6</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-1.76</v>
+        <v>0.42</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>394.44</v>
+        <v>446.9</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>386.36</v>
+        <v>434.72</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>358.57</v>
+        <v>402.74</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -5548,128 +5540,136 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>93.7</v>
+        <v>88.72</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>45.3</v>
+        <v>42.61</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>1.6257</v>
+        <v>0.276</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>3.5888</v>
+        <v>5.099</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>-1.9631</v>
+        <v>-4.823</v>
       </c>
       <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="n">
-        <v>14.33</v>
+        <v>15.42</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>7632596</v>
+        <v>3990614</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>8756050</v>
+        <v>6591422</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>0.87</v>
+        <v>0.61</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>377588</v>
+        <v>141277</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>21.561462</v>
+        <v>5.4528084</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>14.544933</v>
-      </c>
-      <c r="AD38" s="2" t="inlineStr"/>
+        <v>6.576288</v>
+      </c>
+      <c r="AD38" s="2" t="n">
+        <v>20.47</v>
+      </c>
       <c r="AE38" s="2" t="n">
-        <v>118.127</v>
+        <v>586.0170000000001</v>
       </c>
       <c r="AF38" s="2" t="n">
-        <v>8</v>
+        <v>-15.4</v>
       </c>
       <c r="AG38" s="2" t="n">
-        <v>-1.6</v>
+        <v>10.8</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>1.9644741</v>
+        <v>1.063267</v>
       </c>
       <c r="AI38" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="AJ38" s="2" t="inlineStr"/>
+        <v>338</v>
+      </c>
+      <c r="AJ38" s="2" t="n">
+        <v>287.366</v>
+      </c>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NTPC/</t>
+          <t>https://www.screener.in/company/PFC/</t>
         </is>
       </c>
       <c r="AL38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NTPC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PFC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Astral Limited</t>
+          <t>Tata Power Company Limited</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Building Products &amp; Equipment</t>
+          <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>28.9</v>
+        <v>33.8</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>15.4</v>
+        <v>6.8</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>📈 EMA Bull Stack</t>
+        </is>
+      </c>
       <c r="J39" s="4" t="n">
-        <v>1545.7</v>
+        <v>415</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-0.33</v>
+        <v>2.63</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>1559.41</v>
+        <v>422.22</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>1568.22</v>
+        <v>412.91</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>1506.09</v>
+        <v>393.74</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -5678,83 +5678,83 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>87.39</v>
+        <v>89.27</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>46.29</v>
+        <v>45.94</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-9.483000000000001</v>
+        <v>-1.2882</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>-10.4589</v>
+        <v>4.1587</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.9759</v>
+        <v>-5.4469</v>
       </c>
       <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="n">
-        <v>9.25</v>
+        <v>24.94</v>
       </c>
       <c r="X39" s="4" t="n">
-        <v>414511</v>
+        <v>7454213</v>
       </c>
       <c r="Y39" s="4" t="n">
-        <v>555523</v>
+        <v>7388673</v>
       </c>
       <c r="Z39" s="4" t="n">
-        <v>0.75</v>
+        <v>1.01</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>38925</v>
+        <v>131664</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>72.66298999999999</v>
+        <v>35.21795</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>42.825382</v>
+        <v>27.24546</v>
       </c>
       <c r="AD39" s="4" t="n">
-        <v>13.8</v>
+        <v>11.34</v>
       </c>
       <c r="AE39" s="4" t="n">
-        <v>6.168</v>
+        <v>167.811</v>
       </c>
       <c r="AF39" s="4" t="n">
-        <v>24.2</v>
+        <v>-12.8</v>
       </c>
       <c r="AG39" s="4" t="n">
-        <v>18.9</v>
+        <v>-4.6</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>10.303656</v>
+        <v>3.4777727</v>
       </c>
       <c r="AI39" s="4" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>1.762</v>
+        <v>0.806</v>
       </c>
       <c r="AK39" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ASTRAL/</t>
+          <t>https://www.screener.in/company/TATAPOWER/</t>
         </is>
       </c>
       <c r="AL39" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ASTRAL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Tata Power Company Limited</t>
+          <t>NTPC Limited</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Independent Power Producers</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>27.8</v>
+        <v>32.2</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6.8</v>
+        <v>14.2</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
@@ -5783,23 +5783,23 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>404.35</v>
+        <v>389.4</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-0.65</v>
+        <v>0.28</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>422.99</v>
+        <v>393.96</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>412.82</v>
+        <v>386.48</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>393.52</v>
+        <v>358.87</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -5808,75 +5808,71 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>86.98</v>
+        <v>93.97</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>37.54</v>
+        <v>46.48</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>-0.8866000000000001</v>
+        <v>1.0704</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>5.5204</v>
+        <v>3.0851</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>-6.407</v>
+        <v>-2.0147</v>
       </c>
       <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="2" t="n">
-        <v>24.88</v>
+        <v>14.52</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>6007649</v>
+        <v>6693518</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>7466709</v>
+        <v>8616044</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>132607</v>
+        <v>378800</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>35.37937</v>
+        <v>21.618706</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>27.44052</v>
-      </c>
-      <c r="AD40" s="2" t="n">
-        <v>11.34</v>
-      </c>
+        <v>14.591623</v>
+      </c>
+      <c r="AD40" s="2" t="inlineStr"/>
       <c r="AE40" s="2" t="n">
-        <v>167.811</v>
+        <v>118.127</v>
       </c>
       <c r="AF40" s="2" t="n">
-        <v>-12.8</v>
+        <v>8</v>
       </c>
       <c r="AG40" s="2" t="n">
-        <v>-4.6</v>
+        <v>-1.6</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>3.5026712</v>
+        <v>1.9707801</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="AJ40" s="2" t="n">
-        <v>0.806</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="AJ40" s="2" t="inlineStr"/>
       <c r="AK40" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TATAPOWER/</t>
+          <t>https://www.screener.in/company/NTPC/</t>
         </is>
       </c>
       <c r="AL40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NTPC</t>
         </is>
       </c>
     </row>
@@ -5921,19 +5917,19 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>6913</v>
+        <v>6882.5</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-1.45</v>
+        <v>-0.44</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>7118.55</v>
+        <v>7096.07</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>7158.95</v>
+        <v>7148.11</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>6880.19</v>
+        <v>6880.21</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
@@ -5946,41 +5942,41 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>84</v>
+        <v>83.63</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>40.73</v>
+        <v>39.68</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>-28.1291</v>
+        <v>-43.2231</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>6.0195</v>
+        <v>-3.829</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>-34.1486</v>
+        <v>-39.3941</v>
       </c>
       <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="n">
-        <v>14.22</v>
+        <v>15.4</v>
       </c>
       <c r="X41" s="4" t="n">
-        <v>316357</v>
+        <v>406588</v>
       </c>
       <c r="Y41" s="4" t="n">
-        <v>428555</v>
+        <v>431235</v>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>0.74</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>188797</v>
+        <v>188358</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>35.303925</v>
+        <v>35.254402</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>29.902594</v>
+        <v>29.833076</v>
       </c>
       <c r="AD41" s="4" t="inlineStr"/>
       <c r="AE41" s="4" t="n">
@@ -5993,10 +5989,10 @@
         <v>21.3</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>8.546970999999999</v>
+        <v>8.527101999999999</v>
       </c>
       <c r="AI41" s="4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AJ41" s="4" t="inlineStr"/>
       <c r="AK41" s="4" t="inlineStr">
@@ -6269,7 +6265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6545,19 +6541,19 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9151</v>
+        <v>9162.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8603.049999999999</v>
+        <v>8656.33</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8140.78</v>
+        <v>8180.85</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7437.66</v>
+        <v>7454.82</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -6570,41 +6566,41 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>98.59</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>70.92</v>
+        <v>71.12</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>379.7859</v>
+        <v>377.019</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>328.2022</v>
+        <v>337.9656</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>51.5837</v>
+        <v>39.0534</v>
       </c>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>36.33</v>
+        <v>36.86</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>295160</v>
+        <v>337327</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>496919</v>
+        <v>491631</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>137942</v>
+        <v>138582</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>51.87985</v>
+        <v>52.052704</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.232964</v>
+        <v>37.40567</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -6619,7 +6615,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.486955</v>
+        <v>11.540236</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -6641,32 +6637,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Adani Ports and Special Economic Zone Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Marine Shipping</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>64.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>18.8</v>
+        <v>24.8</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -6679,19 +6675,19 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6835</v>
+        <v>1762.8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1.1</v>
+        <v>-1.39</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>6595.56</v>
+        <v>1697.95</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>6406.09</v>
+        <v>1598.79</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>6275.56</v>
+        <v>1474.12</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -6704,99 +6700,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>66.76000000000001</v>
+        <v>63.75</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>165.1763</v>
+        <v>68.4268</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>149.3397</v>
+        <v>69.70050000000001</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>15.8366</v>
+        <v>-1.2737</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>40.22</v>
+        <v>30.14</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>340352</v>
+        <v>2274987</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>299253</v>
+        <v>3422075</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>1.14</v>
+        <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>183492</v>
+        <v>407110</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>73.81461</v>
+        <v>30.376484</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>59.1254</v>
-      </c>
-      <c r="AD3" s="4" t="inlineStr"/>
+        <v>22.782524</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>15.59</v>
+      </c>
       <c r="AE3" s="4" t="n">
-        <v>0.584</v>
+        <v>64.051</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>12.3</v>
+        <v>26.5</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>-1</v>
+        <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.897712</v>
+        <v>4.234861</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
+        <v>1.394</v>
+      </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>63.8</v>
+        <v>64.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24.8</v>
+        <v>18.8</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -6809,19 +6809,19 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1787.7</v>
+        <v>6912</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.41</v>
+        <v>1.13</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1691.12</v>
+        <v>6625.7</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1592.09</v>
+        <v>6425.93</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1471.22</v>
+        <v>6281.9</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -6834,103 +6834,99 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.02</v>
+        <v>98.19</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>68.23</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>71.4542</v>
+        <v>169.8444</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>70.01900000000001</v>
+        <v>153.4407</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.4352</v>
+        <v>16.4038</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>29.99</v>
+        <v>40.15</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>2562978</v>
+        <v>322081</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>3522169</v>
+        <v>304930</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>406142</v>
+        <v>183041</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>30.247084</v>
+        <v>73.89348</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>22.728373</v>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>15.59</v>
-      </c>
+        <v>58.979984</v>
+      </c>
+      <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>64.051</v>
+        <v>0.584</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>26.5</v>
+        <v>12.3</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>3.6</v>
+        <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.2247953</v>
+        <v>11.86845</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ4" s="2" t="n">
-        <v>1.394</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr"/>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>JSW Steel Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -6943,19 +6939,19 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1292.8</v>
+        <v>831.45</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1264.22</v>
+        <v>811.24</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1236.23</v>
+        <v>787.47</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1169.81</v>
+        <v>748.28</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -6968,344 +6964,76 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>98.39</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>59.8</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>17.6126</v>
+        <v>19.2999</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>18.4128</v>
+        <v>17.5484</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.8002</v>
+        <v>1.7515</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>19.95</v>
+        <v>37.74</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>2965138</v>
+        <v>1431476</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1911846</v>
+        <v>1863164</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>1.55</v>
+        <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>313670</v>
+        <v>107856</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.081297</v>
+        <v>61.428043</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.852625</v>
+        <v>44.107525</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>27.26</v>
+        <v>41.39</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>94.155</v>
+        <v>12.394</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>14.2</v>
+        <v>22.1</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>991.8</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>3.1351693</v>
+        <v>25.429243</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.491</v>
+        <v>1.31</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/JSWSTEEL/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ARVIND</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Arvind Limited</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Textile Manufacturing</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>472.6</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>420.6</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>392.3</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>351.43</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>97.84999999999999</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>77.51000000000001</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>21.187</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>16.5472</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>4.6399</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>5974822</v>
-      </c>
-      <c r="Y6" s="2" t="n">
-        <v>1385854</v>
-      </c>
-      <c r="Z6" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="AA6" s="2" t="n">
-        <v>12734</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>30.785805</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>18.240303</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>40.071</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AG6" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AH6" s="2" t="n">
-        <v>3.3139148</v>
-      </c>
-      <c r="AI6" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="AJ6" s="2" t="n">
-        <v>1.141</v>
-      </c>
-      <c r="AK6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/ARVIND/</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ARVIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Marico Limited</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Household &amp; Personal Products</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>833.75</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>809.11</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>785.6799999999999</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>747.4400000000001</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>98.23</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>66.78</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>20.0313</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>17.1105</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>2.9208</v>
-      </c>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="n">
-        <v>36.69</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>1500121</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>1837251</v>
-      </c>
-      <c r="Z7" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AA7" s="4" t="n">
-        <v>107740</v>
-      </c>
-      <c r="AB7" s="4" t="n">
-        <v>61.181015</v>
-      </c>
-      <c r="AC7" s="4" t="n">
-        <v>44.059834</v>
-      </c>
-      <c r="AD7" s="4" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="AE7" s="4" t="n">
-        <v>12.394</v>
-      </c>
-      <c r="AF7" s="4" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AG7" s="4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH7" s="4" t="n">
-        <v>25.401749</v>
-      </c>
-      <c r="AI7" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ7" s="4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/MARICO/</t>
-        </is>
-      </c>
-      <c r="AL7" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL7"/>
+  <autoFilter ref="A1:AL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7316,7 +7044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7592,19 +7320,19 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9151</v>
+        <v>9162.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8603.049999999999</v>
+        <v>8656.33</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8140.78</v>
+        <v>8180.85</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7437.66</v>
+        <v>7454.82</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -7617,41 +7345,41 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>98.59</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>70.92</v>
+        <v>71.12</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>379.7859</v>
+        <v>377.019</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>328.2022</v>
+        <v>337.9656</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>51.5837</v>
+        <v>39.0534</v>
       </c>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>36.33</v>
+        <v>36.86</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>295160</v>
+        <v>337327</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>496919</v>
+        <v>491631</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>137942</v>
+        <v>138582</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>51.87985</v>
+        <v>52.052704</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.232964</v>
+        <v>37.40567</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -7666,7 +7394,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.486955</v>
+        <v>11.540236</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -7688,32 +7416,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Adani Ports and Special Economic Zone Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Marine Shipping</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>64.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>18.8</v>
+        <v>24.8</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -7726,19 +7454,19 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6835</v>
+        <v>1762.8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1.1</v>
+        <v>-1.39</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>6595.56</v>
+        <v>1697.95</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>6406.09</v>
+        <v>1598.79</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>6275.56</v>
+        <v>1474.12</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -7751,99 +7479,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>66.76000000000001</v>
+        <v>63.75</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>165.1763</v>
+        <v>68.4268</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>149.3397</v>
+        <v>69.70050000000001</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>15.8366</v>
+        <v>-1.2737</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>40.22</v>
+        <v>30.14</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>340352</v>
+        <v>2274987</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>299253</v>
+        <v>3422075</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>1.14</v>
+        <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>183492</v>
+        <v>407110</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>73.81461</v>
+        <v>30.376484</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>59.1254</v>
-      </c>
-      <c r="AD3" s="4" t="inlineStr"/>
+        <v>22.782524</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>15.59</v>
+      </c>
       <c r="AE3" s="4" t="n">
-        <v>0.584</v>
+        <v>64.051</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>12.3</v>
+        <v>26.5</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>-1</v>
+        <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.897712</v>
+        <v>4.234861</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
+        <v>1.394</v>
+      </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>63.8</v>
+        <v>64.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24.8</v>
+        <v>18.8</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -7856,19 +7588,19 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1787.7</v>
+        <v>6912</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.41</v>
+        <v>1.13</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1691.12</v>
+        <v>6625.7</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1592.09</v>
+        <v>6425.93</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1471.22</v>
+        <v>6281.9</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -7881,103 +7613,99 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.02</v>
+        <v>98.19</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>68.23</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>71.4542</v>
+        <v>169.8444</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>70.01900000000001</v>
+        <v>153.4407</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.4352</v>
+        <v>16.4038</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>29.99</v>
+        <v>40.15</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>2562978</v>
+        <v>322081</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>3522169</v>
+        <v>304930</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>406142</v>
+        <v>183041</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>30.247084</v>
+        <v>73.89348</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>22.728373</v>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>15.59</v>
-      </c>
+        <v>58.979984</v>
+      </c>
+      <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>64.051</v>
+        <v>0.584</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>26.5</v>
+        <v>12.3</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>3.6</v>
+        <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.2247953</v>
+        <v>11.86845</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ4" s="2" t="n">
-        <v>1.394</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr"/>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>JSW Steel Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -7990,19 +7718,19 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1292.8</v>
+        <v>831.45</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1264.22</v>
+        <v>811.24</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1236.23</v>
+        <v>787.47</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1169.81</v>
+        <v>748.28</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -8015,344 +7743,76 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>98.39</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>59.8</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>17.6126</v>
+        <v>19.2999</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>18.4128</v>
+        <v>17.5484</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.8002</v>
+        <v>1.7515</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>19.95</v>
+        <v>37.74</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>2965138</v>
+        <v>1431476</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1911846</v>
+        <v>1863164</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>1.55</v>
+        <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>313670</v>
+        <v>107856</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.081297</v>
+        <v>61.428043</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.852625</v>
+        <v>44.107525</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>27.26</v>
+        <v>41.39</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>94.155</v>
+        <v>12.394</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>14.2</v>
+        <v>22.1</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>991.8</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>3.1351693</v>
+        <v>25.429243</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.491</v>
+        <v>1.31</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/JSWSTEEL/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ARVIND</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Arvind Limited</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Textile Manufacturing</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>472.6</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>420.6</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>392.3</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>351.43</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>97.84999999999999</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>77.51000000000001</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>21.187</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>16.5472</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>4.6399</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>5974822</v>
-      </c>
-      <c r="Y6" s="2" t="n">
-        <v>1385854</v>
-      </c>
-      <c r="Z6" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="AA6" s="2" t="n">
-        <v>12734</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>30.785805</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>18.240303</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>40.071</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AG6" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AH6" s="2" t="n">
-        <v>3.3139148</v>
-      </c>
-      <c r="AI6" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="AJ6" s="2" t="n">
-        <v>1.141</v>
-      </c>
-      <c r="AK6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/ARVIND/</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ARVIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Marico Limited</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Household &amp; Personal Products</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>833.75</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>809.11</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>785.6799999999999</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>747.4400000000001</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>98.23</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>66.78</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>20.0313</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>17.1105</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>2.9208</v>
-      </c>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="n">
-        <v>36.69</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>1500121</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>1837251</v>
-      </c>
-      <c r="Z7" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AA7" s="4" t="n">
-        <v>107740</v>
-      </c>
-      <c r="AB7" s="4" t="n">
-        <v>61.181015</v>
-      </c>
-      <c r="AC7" s="4" t="n">
-        <v>44.059834</v>
-      </c>
-      <c r="AD7" s="4" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="AE7" s="4" t="n">
-        <v>12.394</v>
-      </c>
-      <c r="AF7" s="4" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AG7" s="4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH7" s="4" t="n">
-        <v>25.401749</v>
-      </c>
-      <c r="AI7" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ7" s="4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/MARICO/</t>
-        </is>
-      </c>
-      <c r="AL7" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL7"/>
+  <autoFilter ref="A1:AL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8377,7 +7837,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 19-May-2026 18:17 IST</t>
+          <t>Run Date: 20-May-2026 07:00 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -8435,7 +7895,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -8445,7 +7905,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -8481,7 +7941,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="14">
@@ -8533,7 +7993,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -8543,31 +8003,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63.8</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -816,13 +816,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138582</v>
+        <v>138634</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.052704</v>
+        <v>52.072495</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.40567</v>
+        <v>37.41989</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -837,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.540236</v>
+        <v>11.544624</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -950,13 +950,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>407110</v>
+        <v>405981</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.376484</v>
+        <v>30.292248</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.782524</v>
+        <v>22.719347</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -971,7 +971,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.234861</v>
+        <v>4.2231174</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -1084,13 +1084,13 @@
         <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>183041</v>
+        <v>182775</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.89348</v>
+        <v>73.78631</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.979984</v>
+        <v>58.894444</v>
       </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
@@ -1103,7 +1103,7 @@
         <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.86845</v>
+        <v>11.851236</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>43</v>
@@ -1214,13 +1214,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>107856</v>
+        <v>108076</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.428043</v>
+        <v>61.553505</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.107525</v>
+        <v>44.19761</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -1235,7 +1235,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.429243</v>
+        <v>25.481182</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -1348,13 +1348,13 @@
         <v>0.75</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>271912</v>
+        <v>271873</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>77.563255</v>
+        <v>77.55225</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>59.524837</v>
+        <v>59.5164</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>76.34</v>
@@ -1369,7 +1369,7 @@
         <v>27.4</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>52.727818</v>
+        <v>52.72034</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>84</v>
@@ -1482,11 +1482,11 @@
         <v>0.09</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>3297</v>
+        <v>3284</v>
       </c>
       <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="n">
-        <v>27.240143</v>
+        <v>27.132616</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>-2.82</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
-        <v>5.547567</v>
+        <v>5.5256686</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>0.55</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>377031</v>
+        <v>376276</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>9.910715</v>
+        <v>9.890872999999999</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>7.0774803</v>
+        <v>7.063311</v>
       </c>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
@@ -1631,7 +1631,7 @@
         <v>16.2</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>1.0243038</v>
+        <v>1.0222532</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>624</v>
@@ -1742,13 +1742,13 @@
         <v>0.82</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>9758</v>
+        <v>9968</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>86.86682999999999</v>
+        <v>88.73365</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>44.671246</v>
+        <v>45.63126</v>
       </c>
       <c r="AD9" s="4" t="inlineStr"/>
       <c r="AE9" s="4" t="n">
@@ -1761,7 +1761,7 @@
         <v>35.8</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>14.970593</v>
+        <v>15.292321</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>1.32</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>371005</v>
+        <v>370799</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>36.779015</v>
+        <v>36.75863</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>47.741024</v>
+        <v>47.71456</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>13.66</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="n">
-        <v>4.3161635</v>
+        <v>4.3137712</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>5</v>
@@ -2004,13 +2004,13 @@
         <v>0.41</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>450067</v>
+        <v>450307</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>41.18112</v>
+        <v>41.203075</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>33.151623</v>
+        <v>33.169296</v>
       </c>
       <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="n">
@@ -2023,7 +2023,7 @@
         <v>15.7</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>5.7812624</v>
+        <v>5.7843447</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>88</v>
@@ -2134,13 +2134,13 @@
         <v>0.61</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>310497</v>
+        <v>311278</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>13.941917</v>
+        <v>13.976987</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>17.644154</v>
+        <v>17.688536</v>
       </c>
       <c r="AD12" s="2" t="n">
         <v>27.26</v>
@@ -2155,7 +2155,7 @@
         <v>991.8</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>3.1034567</v>
+        <v>3.111263</v>
       </c>
       <c r="AI12" s="2" t="n">
         <v>55</v>
@@ -2268,13 +2268,13 @@
         <v>1.03</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>115919</v>
+        <v>116336</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>64.38782999999999</v>
+        <v>64.61944</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>48.4503</v>
+        <v>48.62458</v>
       </c>
       <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="n">
@@ -2287,7 +2287,7 @@
         <v>35</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>12.747192</v>
+        <v>12.793045</v>
       </c>
       <c r="AI13" s="4" t="n">
         <v>25</v>
@@ -2398,13 +2398,13 @@
         <v>1.09</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>149166</v>
+        <v>149501</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>65.88042</v>
+        <v>66.0284</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>68.05428999999999</v>
+        <v>68.20715</v>
       </c>
       <c r="AD14" s="2" t="inlineStr"/>
       <c r="AE14" s="2" t="n">
@@ -2417,7 +2417,7 @@
         <v>26.1</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>17.667267</v>
+        <v>17.706951</v>
       </c>
       <c r="AI14" s="2" t="n">
         <v>78</v>
@@ -2528,13 +2528,13 @@
         <v>0.4</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>23966</v>
+        <v>23839</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>15.559381</v>
+        <v>15.476764</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>12.633947</v>
+        <v>12.566864</v>
       </c>
       <c r="AD15" s="4" t="n">
         <v>12.55</v>
@@ -2549,7 +2549,7 @@
         <v>17.8</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>1.8832353</v>
+        <v>1.8732358</v>
       </c>
       <c r="AI15" s="4" t="n">
         <v>331</v>
@@ -2662,13 +2662,13 @@
         <v>1.24</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>87688</v>
+        <v>87457</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>25.374624</v>
+        <v>25.308025</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>19.942963</v>
+        <v>19.89062</v>
       </c>
       <c r="AD16" s="2" t="inlineStr"/>
       <c r="AE16" s="2" t="n">
@@ -2681,7 +2681,7 @@
         <v>7.6</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>2.5257087</v>
+        <v>2.5190794</v>
       </c>
       <c r="AI16" s="2" t="n">
         <v>26</v>
@@ -2792,13 +2792,13 @@
         <v>0.78</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>12929</v>
+        <v>12920</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>31.238125</v>
+        <v>30.369686</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>18.520027</v>
+        <v>18.506886</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>10.66</v>
@@ -2813,7 +2813,7 @@
         <v>5.9</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>3.1932802</v>
+        <v>3.3623478</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>77</v>
@@ -2926,13 +2926,13 @@
         <v>0.68</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>30298</v>
+        <v>30157</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>27.568375</v>
+        <v>27.44017</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>10.98354</v>
+        <v>10.932461</v>
       </c>
       <c r="AD18" s="2" t="n">
         <v>6.97</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="n">
-        <v>1.6822258</v>
+        <v>1.6744027</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>63</v>
@@ -3058,13 +3058,13 @@
         <v>0.7</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>77587</v>
+        <v>77429</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>552.95917</v>
+        <v>551.83673</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>174.6915</v>
+        <v>174.33688</v>
       </c>
       <c r="AD19" s="4" t="inlineStr"/>
       <c r="AE19" s="4" t="n">
@@ -3077,7 +3077,7 @@
         <v>144.4</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>56.01613</v>
+        <v>55.90242</v>
       </c>
       <c r="AI19" s="4" t="n">
         <v>0</v>
@@ -3188,13 +3188,13 @@
         <v>0.42</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>20021</v>
+        <v>19975</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>22.982956</v>
+        <v>22.929688</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>17.051458</v>
+        <v>17.011938</v>
       </c>
       <c r="AD20" s="2" t="inlineStr"/>
       <c r="AE20" s="2" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
         <v>367.9</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>1.1959891</v>
+        <v>1.1932173</v>
       </c>
       <c r="AI20" s="2" t="n">
         <v>33</v>
@@ -3316,13 +3316,13 @@
         <v>0.37</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>59221</v>
+        <v>59198</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>52.632126</v>
+        <v>52.6114</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>39.99534</v>
+        <v>39.979588</v>
       </c>
       <c r="AD21" s="4" t="n">
         <v>17.23</v>
@@ -3337,7 +3337,7 @@
         <v>27.7</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>8.565935</v>
+        <v>8.562563000000001</v>
       </c>
       <c r="AI21" s="4" t="n">
         <v>75</v>
@@ -3450,13 +3450,13 @@
         <v>0.46</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>18912</v>
+        <v>18869</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>57.99173</v>
+        <v>57.85883</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>34.514725</v>
+        <v>34.435627</v>
       </c>
       <c r="AD22" s="2" t="n">
         <v>14.14</v>
@@ -3471,7 +3471,7 @@
         <v>43.7</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>6.5090127</v>
+        <v>6.494096</v>
       </c>
       <c r="AI22" s="2" t="n">
         <v>15</v>
@@ -3584,13 +3584,13 @@
         <v>0.27</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>30696</v>
+        <v>30605</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>25.104082</v>
+        <v>25.028986</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>8.811726</v>
+        <v>8.785365000000001</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>4.88</v>
@@ -3603,7 +3603,7 @@
         <v>68</v>
       </c>
       <c r="AH23" s="4" t="n">
-        <v>1.198636</v>
+        <v>1.1950505</v>
       </c>
       <c r="AI23" s="4" t="n">
         <v>78</v>
@@ -3714,13 +3714,13 @@
         <v>0.57</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>21590</v>
+        <v>21499</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>391.91663</v>
+        <v>390.25</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>27.132692</v>
+        <v>27.01731</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>7.27</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="n">
-        <v>4.3546295</v>
+        <v>4.336111</v>
       </c>
       <c r="AI24" s="2" t="n">
         <v>7</v>
@@ -3846,13 +3846,13 @@
         <v>0.74</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>110602</v>
+        <v>110502</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>26.388557</v>
+        <v>26.36472</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>20.700478</v>
+        <v>20.681778</v>
       </c>
       <c r="AD25" s="4" t="n">
         <v>11.83</v>
@@ -3867,7 +3867,7 @@
         <v>-86.2</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>2.9371836</v>
+        <v>2.9345303</v>
       </c>
       <c r="AI25" s="4" t="n">
         <v>60</v>
@@ -3980,13 +3980,13 @@
         <v>0.86</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>70731</v>
+        <v>70830</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>16.421625</v>
+        <v>16.44451</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>12.08132</v>
+        <v>12.098156</v>
       </c>
       <c r="AD26" s="2" t="n">
         <v>11.73</v>
@@ -3999,7 +3999,7 @@
         <v>22.2</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>1.9434006</v>
+        <v>1.9461088</v>
       </c>
       <c r="AI26" s="2" t="n">
         <v>42</v>
@@ -4110,13 +4110,13 @@
         <v>0.61</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>113544</v>
+        <v>113682</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>29.3261</v>
+        <v>29.36157</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>22.188253</v>
+        <v>22.215092</v>
       </c>
       <c r="AD27" s="4" t="n">
         <v>11.74</v>
@@ -4131,7 +4131,7 @@
         <v>-54.6</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>3.4490626</v>
+        <v>3.4532342</v>
       </c>
       <c r="AI27" s="4" t="n">
         <v>92</v>
@@ -4244,13 +4244,13 @@
         <v>0.65</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>281976</v>
+        <v>282838</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>9.069375000000001</v>
+        <v>9.097125999999999</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>8.000878999999999</v>
+        <v>8.025361</v>
       </c>
       <c r="AD28" s="2" t="n">
         <v>28.12</v>
@@ -4265,7 +4265,7 @@
         <v>12.9</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>2.367291</v>
+        <v>2.3745344</v>
       </c>
       <c r="AI28" s="2" t="n">
         <v>481</v>
@@ -4378,13 +4378,13 @@
         <v>0.57</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>148158</v>
+        <v>147893</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>60.60366</v>
+        <v>60.49542</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>48.02086</v>
+        <v>47.93509</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>23.52</v>
@@ -4399,7 +4399,7 @@
         <v>37</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>15.511251</v>
+        <v>15.483547</v>
       </c>
       <c r="AI29" s="4" t="n">
         <v>69</v>
@@ -4512,13 +4512,13 @@
         <v>1.16</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>255186</v>
+        <v>255211</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>27.838097</v>
+        <v>27.840816</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>10.883512</v>
+        <v>10.884575</v>
       </c>
       <c r="AD30" s="2" t="n">
         <v>11.16</v>
@@ -4533,7 +4533,7 @@
         <v>125.4</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>2.6844308</v>
+        <v>2.6846933</v>
       </c>
       <c r="AI30" s="2" t="n">
         <v>191</v>
@@ -4646,13 +4646,13 @@
         <v>1.3</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>276693</v>
+        <v>277297</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>14.778937</v>
+        <v>14.811228</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>14.924811</v>
+        <v>14.957419</v>
       </c>
       <c r="AD31" s="4" t="n">
         <v>16.49</v>
@@ -4667,7 +4667,7 @@
         <v>9.6</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>2.7926145</v>
+        <v>2.7987158</v>
       </c>
       <c r="AI31" s="4" t="n">
         <v>410</v>
@@ -4780,13 +4780,13 @@
         <v>0.91</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>538712</v>
+        <v>538326</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>33.51305</v>
+        <v>33.48909</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>21.300083</v>
+        <v>21.284853</v>
       </c>
       <c r="AD32" s="2" t="n">
         <v>16.95</v>
@@ -4801,7 +4801,7 @@
         <v>-34.5</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>4.9290724</v>
+        <v>4.925548</v>
       </c>
       <c r="AI32" s="2" t="n">
         <v>97</v>
@@ -4914,13 +4914,13 @@
         <v>1.07</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>269578</v>
+        <v>269083</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>90.35191</v>
+        <v>90.18579</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>58.295223</v>
+        <v>58.188038</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>12.94</v>
@@ -4935,7 +4935,7 @@
         <v>19.6</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>10.995138</v>
+        <v>10.974922</v>
       </c>
       <c r="AI33" s="4" t="n">
         <v>0</v>
@@ -5048,13 +5048,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>249104</v>
+        <v>250254</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>64.8814</v>
+        <v>65.18102</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>51.87426</v>
+        <v>52.11382</v>
       </c>
       <c r="AD34" s="2" t="inlineStr"/>
       <c r="AE34" s="2" t="n">
@@ -5067,7 +5067,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>12.716551</v>
+        <v>12.775277</v>
       </c>
       <c r="AI34" s="2" t="n">
         <v>96</v>
@@ -5178,13 +5178,13 @@
         <v>1.12</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>131878</v>
+        <v>132139</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>12.460266</v>
+        <v>12.484921</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>9.512487</v>
+        <v>9.53131</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>30.41</v>
@@ -5199,7 +5199,7 @@
         <v>126.7</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>3.7022343</v>
+        <v>3.70956</v>
       </c>
       <c r="AI35" s="4" t="n">
         <v>91</v>
@@ -5312,13 +5312,13 @@
         <v>0.5</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>362668</v>
+        <v>361835</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>71.70291</v>
+        <v>71.538055</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>47.495125</v>
+        <v>47.38593</v>
       </c>
       <c r="AD36" s="2" t="n">
         <v>37.13</v>
@@ -5333,7 +5333,7 @@
         <v>35.1</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>28.318222</v>
+        <v>28.253117</v>
       </c>
       <c r="AI36" s="2" t="n">
         <v>27</v>
@@ -5442,13 +5442,13 @@
         <v>1.38</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>32654</v>
+        <v>32546</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>37.607494</v>
+        <v>37.483234</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>26.450455</v>
+        <v>26.36306</v>
       </c>
       <c r="AD37" s="4" t="inlineStr"/>
       <c r="AE37" s="4" t="n">
@@ -5461,7 +5461,7 @@
         <v>3</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>6.092783</v>
+        <v>6.072652</v>
       </c>
       <c r="AI37" s="4" t="n">
         <v>54</v>
@@ -5572,13 +5572,13 @@
         <v>0.61</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>141277</v>
+        <v>140419</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>5.4528084</v>
+        <v>5.4196916</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>6.576288</v>
+        <v>6.5363483</v>
       </c>
       <c r="AD38" s="2" t="n">
         <v>20.47</v>
@@ -5593,7 +5593,7 @@
         <v>10.8</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>1.063267</v>
+        <v>1.0568094</v>
       </c>
       <c r="AI38" s="2" t="n">
         <v>338</v>
@@ -5706,13 +5706,13 @@
         <v>1.01</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>131664</v>
+        <v>131696</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>35.21795</v>
+        <v>35.226498</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>27.24546</v>
+        <v>27.252073</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>11.34</v>
@@ -5727,7 +5727,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>3.4777727</v>
+        <v>3.4786167</v>
       </c>
       <c r="AI39" s="4" t="n">
         <v>60</v>
@@ -5840,13 +5840,13 @@
         <v>0.78</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>378800</v>
+        <v>379382</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>21.618706</v>
+        <v>21.651909</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>14.591623</v>
+        <v>14.614035</v>
       </c>
       <c r="AD40" s="2" t="inlineStr"/>
       <c r="AE40" s="2" t="n">
@@ -5859,7 +5859,7 @@
         <v>-1.6</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>1.9707801</v>
+        <v>1.9738071</v>
       </c>
       <c r="AI40" s="2" t="n">
         <v>291</v>
@@ -5970,13 +5970,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>188358</v>
+        <v>188605</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>35.254402</v>
+        <v>35.30061</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>29.833076</v>
+        <v>29.872179</v>
       </c>
       <c r="AD41" s="4" t="inlineStr"/>
       <c r="AE41" s="4" t="n">
@@ -5989,7 +5989,7 @@
         <v>21.3</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>8.527101999999999</v>
+        <v>8.538278999999999</v>
       </c>
       <c r="AI41" s="4" t="n">
         <v>102</v>
@@ -6594,13 +6594,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138582</v>
+        <v>138634</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.052704</v>
+        <v>52.072495</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.40567</v>
+        <v>37.41989</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -6615,7 +6615,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.540236</v>
+        <v>11.544624</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -6728,13 +6728,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>407110</v>
+        <v>405981</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.376484</v>
+        <v>30.292248</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.782524</v>
+        <v>22.719347</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -6749,7 +6749,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.234861</v>
+        <v>4.2231174</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -6862,13 +6862,13 @@
         <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>183041</v>
+        <v>182775</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.89348</v>
+        <v>73.78631</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.979984</v>
+        <v>58.894444</v>
       </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
@@ -6881,7 +6881,7 @@
         <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.86845</v>
+        <v>11.851236</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>43</v>
@@ -6992,13 +6992,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>107856</v>
+        <v>108076</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.428043</v>
+        <v>61.553505</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.107525</v>
+        <v>44.19761</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -7013,7 +7013,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.429243</v>
+        <v>25.481182</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -7373,13 +7373,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138582</v>
+        <v>138634</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.052704</v>
+        <v>52.072495</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.40567</v>
+        <v>37.41989</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -7394,7 +7394,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.540236</v>
+        <v>11.544624</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -7507,13 +7507,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>407110</v>
+        <v>405981</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.376484</v>
+        <v>30.292248</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.782524</v>
+        <v>22.719347</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -7528,7 +7528,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.234861</v>
+        <v>4.2231174</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -7641,13 +7641,13 @@
         <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>183041</v>
+        <v>182775</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.89348</v>
+        <v>73.78631</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.979984</v>
+        <v>58.894444</v>
       </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
@@ -7660,7 +7660,7 @@
         <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.86845</v>
+        <v>11.851236</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>43</v>
@@ -7771,13 +7771,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>107856</v>
+        <v>108076</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.428043</v>
+        <v>61.553505</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.107525</v>
+        <v>44.19761</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -7792,7 +7792,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.429243</v>
+        <v>25.481182</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -7837,7 +7837,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 20-May-2026 07:00 IST</t>
+          <t>Run Date: 20-May-2026 07:38 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -517,7 +517,7 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="8" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
@@ -816,13 +816,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138634</v>
+        <v>138476</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.072495</v>
+        <v>52.01312</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.41989</v>
+        <v>37.377224</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -837,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.544624</v>
+        <v>11.531461</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -950,13 +950,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>405981</v>
+        <v>408492</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.292248</v>
+        <v>30.47963</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.719347</v>
+        <v>22.859884</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -971,7 +971,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.2231174</v>
+        <v>4.249241</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -1214,13 +1214,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108076</v>
+        <v>108711</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.553505</v>
+        <v>61.91513</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.19761</v>
+        <v>44.45727</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -1235,7 +1235,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.481182</v>
+        <v>25.630882</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -1348,13 +1348,13 @@
         <v>0.75</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>271873</v>
+        <v>274052</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>77.55225</v>
+        <v>78.17381</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>59.5164</v>
+        <v>59.993404</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>76.34</v>
@@ -1369,7 +1369,7 @@
         <v>27.4</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>52.72034</v>
+        <v>53.142876</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>84</v>
@@ -1482,11 +1482,11 @@
         <v>0.09</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>3284</v>
+        <v>3263</v>
       </c>
       <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="n">
-        <v>27.132616</v>
+        <v>26.953405</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>-2.82</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
-        <v>5.5256686</v>
+        <v>5.4891715</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>0.55</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>376276</v>
+        <v>375710</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>9.890872999999999</v>
+        <v>9.875992</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>7.063311</v>
+        <v>7.052684</v>
       </c>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
@@ -1631,7 +1631,7 @@
         <v>16.2</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>1.0222532</v>
+        <v>1.0207151</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>624</v>
@@ -1742,13 +1742,13 @@
         <v>0.82</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>9968</v>
+        <v>9771</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>88.73365</v>
+        <v>86.97978999999999</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>45.63126</v>
+        <v>44.729336</v>
       </c>
       <c r="AD9" s="4" t="inlineStr"/>
       <c r="AE9" s="4" t="n">
@@ -1761,7 +1761,7 @@
         <v>35.8</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>15.292321</v>
+        <v>14.990062</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>1.32</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>370799</v>
+        <v>370827</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>36.75863</v>
+        <v>36.761345</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>47.71456</v>
+        <v>47.71809</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>13.66</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="n">
-        <v>4.3137712</v>
+        <v>4.31409</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>5</v>
@@ -2004,13 +2004,13 @@
         <v>0.41</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>450307</v>
+        <v>451195</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>41.203075</v>
+        <v>41.2843</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>33.169296</v>
+        <v>33.234688</v>
       </c>
       <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="n">
@@ -2023,7 +2023,7 @@
         <v>15.7</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>5.7843447</v>
+        <v>5.7957478</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>88</v>
@@ -2134,13 +2134,13 @@
         <v>0.61</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>311278</v>
+        <v>313206</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>13.976987</v>
+        <v>14.063562</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>17.688536</v>
+        <v>17.798101</v>
       </c>
       <c r="AD12" s="2" t="n">
         <v>27.26</v>
@@ -2155,7 +2155,7 @@
         <v>991.8</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>3.111263</v>
+        <v>3.1305346</v>
       </c>
       <c r="AI12" s="2" t="n">
         <v>55</v>
@@ -2268,13 +2268,13 @@
         <v>1.03</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>116336</v>
+        <v>116106</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>64.61944</v>
+        <v>64.49165000000001</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>48.62458</v>
+        <v>48.528423</v>
       </c>
       <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="n">
@@ -2287,7 +2287,7 @@
         <v>35</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>12.793045</v>
+        <v>12.767747</v>
       </c>
       <c r="AI13" s="4" t="n">
         <v>25</v>
@@ -2398,13 +2398,13 @@
         <v>1.09</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>149501</v>
+        <v>149894</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>66.0284</v>
+        <v>66.20179</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>68.20715</v>
+        <v>68.38627</v>
       </c>
       <c r="AD14" s="2" t="inlineStr"/>
       <c r="AE14" s="2" t="n">
@@ -2417,7 +2417,7 @@
         <v>26.1</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>17.706951</v>
+        <v>17.75345</v>
       </c>
       <c r="AI14" s="2" t="n">
         <v>78</v>
@@ -2528,13 +2528,13 @@
         <v>0.4</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>23839</v>
+        <v>23940</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>15.476764</v>
+        <v>15.54217</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>12.566864</v>
+        <v>12.619972</v>
       </c>
       <c r="AD15" s="4" t="n">
         <v>12.55</v>
@@ -2549,7 +2549,7 @@
         <v>17.8</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>1.8732358</v>
+        <v>1.8811522</v>
       </c>
       <c r="AI15" s="4" t="n">
         <v>331</v>
@@ -2662,13 +2662,13 @@
         <v>1.24</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>87457</v>
+        <v>87250</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>25.308025</v>
+        <v>25.248085</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>19.89062</v>
+        <v>19.843512</v>
       </c>
       <c r="AD16" s="2" t="inlineStr"/>
       <c r="AE16" s="2" t="n">
@@ -2681,7 +2681,7 @@
         <v>7.6</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>2.5190794</v>
+        <v>2.5131133</v>
       </c>
       <c r="AI16" s="2" t="n">
         <v>26</v>
@@ -2792,13 +2792,13 @@
         <v>0.78</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>12920</v>
+        <v>12671</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>30.369686</v>
+        <v>30.614313</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>18.506886</v>
+        <v>18.15019</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>10.66</v>
@@ -2813,7 +2813,7 @@
         <v>5.9</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>3.3623478</v>
+        <v>3.297543</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>77</v>
@@ -2926,13 +2926,13 @@
         <v>0.68</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>30157</v>
+        <v>30007</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>27.44017</v>
+        <v>27.303421</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>10.932461</v>
+        <v>10.877978</v>
       </c>
       <c r="AD18" s="2" t="n">
         <v>6.97</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="n">
-        <v>1.6744027</v>
+        <v>1.6660582</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>63</v>
@@ -3058,13 +3058,13 @@
         <v>0.7</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>77429</v>
+        <v>78417</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>551.83673</v>
+        <v>558.87756</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>174.33688</v>
+        <v>176.56123</v>
       </c>
       <c r="AD19" s="4" t="inlineStr"/>
       <c r="AE19" s="4" t="n">
@@ -3077,7 +3077,7 @@
         <v>144.4</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>55.90242</v>
+        <v>56.615673</v>
       </c>
       <c r="AI19" s="4" t="n">
         <v>0</v>
@@ -3188,13 +3188,13 @@
         <v>0.42</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>19975</v>
+        <v>20321</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>22.929688</v>
+        <v>23.327415</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>17.011938</v>
+        <v>17.307018</v>
       </c>
       <c r="AD20" s="2" t="inlineStr"/>
       <c r="AE20" s="2" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
         <v>367.9</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>1.1932173</v>
+        <v>1.2139143</v>
       </c>
       <c r="AI20" s="2" t="n">
         <v>33</v>
@@ -3316,13 +3316,13 @@
         <v>0.37</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>59198</v>
+        <v>59379</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>52.6114</v>
+        <v>52.772022</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>39.979588</v>
+        <v>40.101646</v>
       </c>
       <c r="AD21" s="4" t="n">
         <v>17.23</v>
@@ -3337,7 +3337,7 @@
         <v>27.7</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>8.562563000000001</v>
+        <v>8.588704</v>
       </c>
       <c r="AI21" s="4" t="n">
         <v>75</v>
@@ -3450,13 +3450,13 @@
         <v>0.46</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>18869</v>
+        <v>19406</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>57.85883</v>
+        <v>59.506794</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>34.435627</v>
+        <v>35.41644</v>
       </c>
       <c r="AD22" s="2" t="n">
         <v>14.14</v>
@@ -3471,7 +3471,7 @@
         <v>43.7</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>6.494096</v>
+        <v>6.679064</v>
       </c>
       <c r="AI22" s="2" t="n">
         <v>15</v>
@@ -3584,13 +3584,13 @@
         <v>0.27</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>30605</v>
+        <v>31044</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>25.028986</v>
+        <v>25.388668</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>8.785365000000001</v>
+        <v>8.911617</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>4.88</v>
@@ -3603,7 +3603,7 @@
         <v>68</v>
       </c>
       <c r="AH23" s="4" t="n">
-        <v>1.1950505</v>
+        <v>1.2122241</v>
       </c>
       <c r="AI23" s="4" t="n">
         <v>78</v>
@@ -3714,13 +3714,13 @@
         <v>0.57</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>21499</v>
+        <v>21385</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>390.25</v>
+        <v>388.19443</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>27.01731</v>
+        <v>26.875002</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>7.27</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="n">
-        <v>4.336111</v>
+        <v>4.3132715</v>
       </c>
       <c r="AI24" s="2" t="n">
         <v>7</v>
@@ -3846,13 +3846,13 @@
         <v>0.74</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>110502</v>
+        <v>109944</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>26.36472</v>
+        <v>26.231625</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>20.681778</v>
+        <v>20.577372</v>
       </c>
       <c r="AD25" s="4" t="n">
         <v>11.83</v>
@@ -3867,7 +3867,7 @@
         <v>-86.2</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>2.9345303</v>
+        <v>2.9197161</v>
       </c>
       <c r="AI25" s="4" t="n">
         <v>60</v>
@@ -3980,13 +3980,13 @@
         <v>0.86</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>70830</v>
+        <v>71470</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>16.44451</v>
+        <v>16.593248</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>12.098156</v>
+        <v>12.207583</v>
       </c>
       <c r="AD26" s="2" t="n">
         <v>11.73</v>
@@ -3999,7 +3999,7 @@
         <v>22.2</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>1.9461088</v>
+        <v>1.9637114</v>
       </c>
       <c r="AI26" s="2" t="n">
         <v>42</v>
@@ -4110,13 +4110,13 @@
         <v>0.61</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>113682</v>
+        <v>112987</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>29.36157</v>
+        <v>29.18214</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>22.215092</v>
+        <v>22.079332</v>
       </c>
       <c r="AD27" s="4" t="n">
         <v>11.74</v>
@@ -4131,7 +4131,7 @@
         <v>-54.6</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>3.4532342</v>
+        <v>3.4321313</v>
       </c>
       <c r="AI27" s="4" t="n">
         <v>92</v>
@@ -4244,13 +4244,13 @@
         <v>0.65</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>282838</v>
+        <v>282808</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>9.097125999999999</v>
+        <v>9.096133999999999</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>8.025361</v>
+        <v>8.024487000000001</v>
       </c>
       <c r="AD28" s="2" t="n">
         <v>28.12</v>
@@ -4265,7 +4265,7 @@
         <v>12.9</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>2.3745344</v>
+        <v>2.3742757</v>
       </c>
       <c r="AI28" s="2" t="n">
         <v>481</v>
@@ -4378,13 +4378,13 @@
         <v>0.57</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>147893</v>
+        <v>148249</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>60.49542</v>
+        <v>60.64113</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>47.93509</v>
+        <v>48.05055</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>23.52</v>
@@ -4399,7 +4399,7 @@
         <v>37</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>15.483547</v>
+        <v>15.520842</v>
       </c>
       <c r="AI29" s="4" t="n">
         <v>69</v>
@@ -4512,13 +4512,13 @@
         <v>1.16</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>255211</v>
+        <v>258230</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>27.840816</v>
+        <v>28.170069</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>10.884575</v>
+        <v>11.013298</v>
       </c>
       <c r="AD30" s="2" t="n">
         <v>11.16</v>
@@ -4533,7 +4533,7 @@
         <v>125.4</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>2.6846933</v>
+        <v>2.716443</v>
       </c>
       <c r="AI30" s="2" t="n">
         <v>191</v>
@@ -4646,13 +4646,13 @@
         <v>1.3</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>277297</v>
+        <v>278786</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>14.811228</v>
+        <v>14.890711</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>14.957419</v>
+        <v>15.037688</v>
       </c>
       <c r="AD31" s="4" t="n">
         <v>16.49</v>
@@ -4667,7 +4667,7 @@
         <v>9.6</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>2.7987158</v>
+        <v>2.813735</v>
       </c>
       <c r="AI31" s="4" t="n">
         <v>410</v>
@@ -4780,13 +4780,13 @@
         <v>0.91</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>538326</v>
+        <v>537666</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>33.48909</v>
+        <v>33.44801</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>21.284853</v>
+        <v>21.258745</v>
       </c>
       <c r="AD32" s="2" t="n">
         <v>16.95</v>
@@ -4801,7 +4801,7 @@
         <v>-34.5</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>4.925548</v>
+        <v>4.919506</v>
       </c>
       <c r="AI32" s="2" t="n">
         <v>97</v>
@@ -4914,13 +4914,13 @@
         <v>1.07</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>269083</v>
+        <v>270811</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>90.18579</v>
+        <v>90.76503</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>58.188038</v>
+        <v>58.561764</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>12.94</v>
@@ -4935,7 +4935,7 @@
         <v>19.6</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>10.974922</v>
+        <v>11.04541</v>
       </c>
       <c r="AI33" s="4" t="n">
         <v>0</v>
@@ -5048,13 +5048,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>250254</v>
+        <v>249420</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>65.18102</v>
+        <v>64.96380000000001</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>52.11382</v>
+        <v>51.94014</v>
       </c>
       <c r="AD34" s="2" t="inlineStr"/>
       <c r="AE34" s="2" t="n">
@@ -5067,7 +5067,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>12.775277</v>
+        <v>12.732701</v>
       </c>
       <c r="AI34" s="2" t="n">
         <v>96</v>
@@ -5178,13 +5178,13 @@
         <v>1.12</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>132139</v>
+        <v>133007</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>12.484921</v>
+        <v>12.5668545</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>9.53131</v>
+        <v>9.593861</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>30.41</v>
@@ -5199,7 +5199,7 @@
         <v>126.7</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>3.70956</v>
+        <v>3.7339044</v>
       </c>
       <c r="AI35" s="4" t="n">
         <v>91</v>
@@ -5312,13 +5312,13 @@
         <v>0.5</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>361835</v>
+        <v>364176</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>71.538055</v>
+        <v>72.00105000000001</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>47.38593</v>
+        <v>47.692608</v>
       </c>
       <c r="AD36" s="2" t="n">
         <v>37.13</v>
@@ -5333,7 +5333,7 @@
         <v>35.1</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>28.253117</v>
+        <v>28.43597</v>
       </c>
       <c r="AI36" s="2" t="n">
         <v>27</v>
@@ -5442,13 +5442,13 @@
         <v>1.38</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>32546</v>
+        <v>32819</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>37.483234</v>
+        <v>37.796844</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>26.36306</v>
+        <v>26.58363</v>
       </c>
       <c r="AD37" s="4" t="inlineStr"/>
       <c r="AE37" s="4" t="n">
@@ -5461,7 +5461,7 @@
         <v>3</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>6.072652</v>
+        <v>6.12346</v>
       </c>
       <c r="AI37" s="4" t="n">
         <v>54</v>
@@ -5572,13 +5572,13 @@
         <v>0.61</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>140419</v>
+        <v>142086</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>5.4196916</v>
+        <v>5.4840145</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>6.5363483</v>
+        <v>6.613924</v>
       </c>
       <c r="AD38" s="2" t="n">
         <v>20.47</v>
@@ -5593,7 +5593,7 @@
         <v>10.8</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>1.0568094</v>
+        <v>1.0693519</v>
       </c>
       <c r="AI38" s="2" t="n">
         <v>338</v>
@@ -5706,13 +5706,13 @@
         <v>1.01</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>131696</v>
+        <v>132111</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>35.226498</v>
+        <v>35.33761</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>27.252073</v>
+        <v>27.338032</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>11.34</v>
@@ -5727,7 +5727,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>3.4786167</v>
+        <v>3.489589</v>
       </c>
       <c r="AI39" s="4" t="n">
         <v>60</v>
@@ -5840,13 +5840,13 @@
         <v>0.78</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>379382</v>
+        <v>380643</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>21.651909</v>
+        <v>21.723852</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>14.614035</v>
+        <v>14.662592</v>
       </c>
       <c r="AD40" s="2" t="inlineStr"/>
       <c r="AE40" s="2" t="n">
@@ -5859,7 +5859,7 @@
         <v>-1.6</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>1.9738071</v>
+        <v>1.9803654</v>
       </c>
       <c r="AI40" s="2" t="n">
         <v>291</v>
@@ -5970,13 +5970,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>188605</v>
+        <v>188001</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>35.30061</v>
+        <v>35.187656</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>29.872179</v>
+        <v>29.776596</v>
       </c>
       <c r="AD41" s="4" t="inlineStr"/>
       <c r="AE41" s="4" t="n">
@@ -5989,7 +5989,7 @@
         <v>21.3</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>8.538278999999999</v>
+        <v>8.510959</v>
       </c>
       <c r="AI41" s="4" t="n">
         <v>102</v>
@@ -6594,13 +6594,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138634</v>
+        <v>138476</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.072495</v>
+        <v>52.01312</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.41989</v>
+        <v>37.377224</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -6615,7 +6615,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.544624</v>
+        <v>11.531461</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -6728,13 +6728,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>405981</v>
+        <v>408492</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.292248</v>
+        <v>30.47963</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.719347</v>
+        <v>22.859884</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -6749,7 +6749,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.2231174</v>
+        <v>4.249241</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -6992,13 +6992,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108076</v>
+        <v>108711</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.553505</v>
+        <v>61.91513</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.19761</v>
+        <v>44.45727</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -7013,7 +7013,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.481182</v>
+        <v>25.630882</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -7373,13 +7373,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138634</v>
+        <v>138476</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.072495</v>
+        <v>52.01312</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.41989</v>
+        <v>37.377224</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -7394,7 +7394,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.544624</v>
+        <v>11.531461</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -7507,13 +7507,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>405981</v>
+        <v>408492</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.292248</v>
+        <v>30.47963</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.719347</v>
+        <v>22.859884</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -7528,7 +7528,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.2231174</v>
+        <v>4.249241</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -7771,13 +7771,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108076</v>
+        <v>108711</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.553505</v>
+        <v>61.91513</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.19761</v>
+        <v>44.45727</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -7792,7 +7792,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.481182</v>
+        <v>25.630882</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -7837,7 +7837,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 20-May-2026 07:38 IST</t>
+          <t>Run Date: 20-May-2026 09:55 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -517,7 +517,7 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="8" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
@@ -816,13 +816,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138476</v>
+        <v>138491</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.01312</v>
+        <v>52.018776</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.377224</v>
+        <v>37.381287</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -837,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.531461</v>
+        <v>11.532714</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -950,13 +950,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>408492</v>
+        <v>408400</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.47963</v>
+        <v>30.472754</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.859884</v>
+        <v>22.854727</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -971,7 +971,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.249241</v>
+        <v>4.248282</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -1084,13 +1084,13 @@
         <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>182775</v>
+        <v>182987</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.78631</v>
+        <v>73.87204</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.894444</v>
+        <v>58.962875</v>
       </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
@@ -1103,7 +1103,7 @@
         <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.851236</v>
+        <v>11.865007</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>43</v>
@@ -1214,13 +1214,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108711</v>
+        <v>108647</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.91513</v>
+        <v>61.878227</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.45727</v>
+        <v>44.430775</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -1235,7 +1235,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.630882</v>
+        <v>25.615606</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -1348,13 +1348,13 @@
         <v>0.75</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>274052</v>
+        <v>273840</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>78.17381</v>
+        <v>78.11331</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>59.993404</v>
+        <v>59.94697</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>76.34</v>
@@ -1369,7 +1369,7 @@
         <v>27.4</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>53.142876</v>
+        <v>53.101746</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>84</v>
@@ -1482,11 +1482,11 @@
         <v>0.09</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>3263</v>
+        <v>3269</v>
       </c>
       <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="n">
-        <v>26.953405</v>
+        <v>27.001791</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>-2.82</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
-        <v>5.4891715</v>
+        <v>5.499026</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>0.55</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>375710</v>
+        <v>375270</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>9.875992</v>
+        <v>9.864418000000001</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>7.052684</v>
+        <v>7.0444183</v>
       </c>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
@@ -1631,7 +1631,7 @@
         <v>16.2</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>1.0207151</v>
+        <v>1.0195189</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>624</v>
@@ -1742,13 +1742,13 @@
         <v>0.82</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>9771</v>
+        <v>9780</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>86.97978999999999</v>
+        <v>87.06303</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>44.729336</v>
+        <v>44.77214</v>
       </c>
       <c r="AD9" s="4" t="inlineStr"/>
       <c r="AE9" s="4" t="n">
@@ -1761,7 +1761,7 @@
         <v>35.8</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>14.990062</v>
+        <v>15.004406</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>1.32</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>370827</v>
+        <v>370813</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>36.761345</v>
+        <v>36.75999</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>47.71809</v>
+        <v>47.716328</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>13.66</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="n">
-        <v>4.31409</v>
+        <v>4.3139305</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>5</v>
@@ -2004,13 +2004,13 @@
         <v>0.41</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>451195</v>
+        <v>451147</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>41.2843</v>
+        <v>41.279915</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>33.234688</v>
+        <v>33.23115</v>
       </c>
       <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="n">
@@ -2023,7 +2023,7 @@
         <v>15.7</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>5.7957478</v>
+        <v>5.7951317</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>88</v>
@@ -2134,13 +2134,13 @@
         <v>0.61</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>313206</v>
+        <v>313182</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>14.063562</v>
+        <v>14.062466</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>17.798101</v>
+        <v>17.796713</v>
       </c>
       <c r="AD12" s="2" t="n">
         <v>27.26</v>
@@ -2155,7 +2155,7 @@
         <v>991.8</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>3.1305346</v>
+        <v>3.1302905</v>
       </c>
       <c r="AI12" s="2" t="n">
         <v>55</v>
@@ -2268,13 +2268,13 @@
         <v>1.03</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>116106</v>
+        <v>116156</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>64.49165000000001</v>
+        <v>64.51961</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>48.528423</v>
+        <v>48.549458</v>
       </c>
       <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="n">
@@ -2287,7 +2287,7 @@
         <v>35</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>12.767747</v>
+        <v>12.773281</v>
       </c>
       <c r="AI13" s="4" t="n">
         <v>25</v>
@@ -2398,13 +2398,13 @@
         <v>1.09</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>149894</v>
+        <v>149904</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>66.20179</v>
+        <v>66.206276</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>68.38627</v>
+        <v>68.39091000000001</v>
       </c>
       <c r="AD14" s="2" t="inlineStr"/>
       <c r="AE14" s="2" t="n">
@@ -2417,7 +2417,7 @@
         <v>26.1</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>17.75345</v>
+        <v>17.754654</v>
       </c>
       <c r="AI14" s="2" t="n">
         <v>78</v>
@@ -2528,13 +2528,13 @@
         <v>0.4</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>23940</v>
+        <v>23946</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>15.54217</v>
+        <v>15.546472</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>12.619972</v>
+        <v>12.623466</v>
       </c>
       <c r="AD15" s="4" t="n">
         <v>12.55</v>
@@ -2549,7 +2549,7 @@
         <v>17.8</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>1.8811522</v>
+        <v>1.8816729</v>
       </c>
       <c r="AI15" s="4" t="n">
         <v>331</v>
@@ -2662,13 +2662,13 @@
         <v>1.24</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>87250</v>
+        <v>87314</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>25.248085</v>
+        <v>25.2664</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>19.843512</v>
+        <v>19.857904</v>
       </c>
       <c r="AD16" s="2" t="inlineStr"/>
       <c r="AE16" s="2" t="n">
@@ -2681,7 +2681,7 @@
         <v>7.6</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>2.5131133</v>
+        <v>2.5149362</v>
       </c>
       <c r="AI16" s="2" t="n">
         <v>26</v>
@@ -2792,13 +2792,13 @@
         <v>0.78</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>12671</v>
+        <v>12777</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>30.614313</v>
+        <v>30.870806</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>18.15019</v>
+        <v>18.302256</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>10.66</v>
@@ -2813,7 +2813,7 @@
         <v>5.9</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>3.297543</v>
+        <v>3.1557312</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>77</v>
@@ -2926,13 +2926,13 @@
         <v>0.68</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>30007</v>
+        <v>29979</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>27.303421</v>
+        <v>27.277779</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>10.877978</v>
+        <v>10.867763</v>
       </c>
       <c r="AD18" s="2" t="n">
         <v>6.97</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="n">
-        <v>1.6660582</v>
+        <v>1.6644936</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>63</v>
@@ -3058,13 +3058,13 @@
         <v>0.7</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>78417</v>
+        <v>78260</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>558.87756</v>
+        <v>557.75507</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>176.56123</v>
+        <v>176.20662</v>
       </c>
       <c r="AD19" s="4" t="inlineStr"/>
       <c r="AE19" s="4" t="n">
@@ -3077,7 +3077,7 @@
         <v>144.4</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>56.615673</v>
+        <v>56.501965</v>
       </c>
       <c r="AI19" s="4" t="n">
         <v>0</v>
@@ -3188,13 +3188,13 @@
         <v>0.42</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>20321</v>
+        <v>20324</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>23.327415</v>
+        <v>23.330967</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>17.307018</v>
+        <v>17.309652</v>
       </c>
       <c r="AD20" s="2" t="inlineStr"/>
       <c r="AE20" s="2" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
         <v>367.9</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>1.2139143</v>
+        <v>1.214099</v>
       </c>
       <c r="AI20" s="2" t="n">
         <v>33</v>
@@ -3316,13 +3316,13 @@
         <v>0.37</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>59379</v>
+        <v>59285</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>52.772022</v>
+        <v>52.68912</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>40.101646</v>
+        <v>40.03865</v>
       </c>
       <c r="AD21" s="4" t="n">
         <v>17.23</v>
@@ -3337,7 +3337,7 @@
         <v>27.7</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>8.588704</v>
+        <v>8.575212000000001</v>
       </c>
       <c r="AI21" s="4" t="n">
         <v>75</v>
@@ -3450,13 +3450,13 @@
         <v>0.46</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>19406</v>
+        <v>19340</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>59.506794</v>
+        <v>59.303013</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>35.41644</v>
+        <v>35.29516</v>
       </c>
       <c r="AD22" s="2" t="n">
         <v>14.14</v>
@@ -3471,7 +3471,7 @@
         <v>43.7</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>6.679064</v>
+        <v>6.6561913</v>
       </c>
       <c r="AI22" s="2" t="n">
         <v>15</v>
@@ -3584,13 +3584,13 @@
         <v>0.27</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>31044</v>
+        <v>30956</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>25.388668</v>
+        <v>25.316204</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>8.911617</v>
+        <v>8.886181000000001</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>4.88</v>
@@ -3603,7 +3603,7 @@
         <v>68</v>
       </c>
       <c r="AH23" s="4" t="n">
-        <v>1.2122241</v>
+        <v>1.2087642</v>
       </c>
       <c r="AI23" s="4" t="n">
         <v>78</v>
@@ -3714,13 +3714,13 @@
         <v>0.57</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>21385</v>
+        <v>21323</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>388.19443</v>
+        <v>387.05554</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>26.875002</v>
+        <v>26.796154</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>7.27</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="n">
-        <v>4.3132715</v>
+        <v>4.3006167</v>
       </c>
       <c r="AI24" s="2" t="n">
         <v>7</v>
@@ -3846,13 +3846,13 @@
         <v>0.74</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>109944</v>
+        <v>110061</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>26.231625</v>
+        <v>26.259436</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>20.577372</v>
+        <v>20.599188</v>
       </c>
       <c r="AD25" s="4" t="n">
         <v>11.83</v>
@@ -3867,7 +3867,7 @@
         <v>-86.2</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>2.9197161</v>
+        <v>2.9228117</v>
       </c>
       <c r="AI25" s="4" t="n">
         <v>60</v>
@@ -3980,13 +3980,13 @@
         <v>0.86</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>71470</v>
+        <v>71434</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>16.593248</v>
+        <v>16.58467</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>12.207583</v>
+        <v>12.20127</v>
       </c>
       <c r="AD26" s="2" t="n">
         <v>11.73</v>
@@ -3999,7 +3999,7 @@
         <v>22.2</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>1.9637114</v>
+        <v>1.9626958</v>
       </c>
       <c r="AI26" s="2" t="n">
         <v>42</v>
@@ -4110,13 +4110,13 @@
         <v>0.61</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>112987</v>
+        <v>113052</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>29.18214</v>
+        <v>29.198832</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>22.079332</v>
+        <v>22.091963</v>
       </c>
       <c r="AD27" s="4" t="n">
         <v>11.74</v>
@@ -4131,7 +4131,7 @@
         <v>-54.6</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>3.4321313</v>
+        <v>3.4340944</v>
       </c>
       <c r="AI27" s="4" t="n">
         <v>92</v>
@@ -4244,13 +4244,13 @@
         <v>0.65</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>282808</v>
+        <v>282684</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>9.096133999999999</v>
+        <v>9.092171</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>8.024487000000001</v>
+        <v>8.020989</v>
       </c>
       <c r="AD28" s="2" t="n">
         <v>28.12</v>
@@ -4265,7 +4265,7 @@
         <v>12.9</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>2.3742757</v>
+        <v>2.373241</v>
       </c>
       <c r="AI28" s="2" t="n">
         <v>481</v>
@@ -4378,13 +4378,13 @@
         <v>0.57</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>148249</v>
+        <v>148147</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>60.64113</v>
+        <v>60.5995</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>48.05055</v>
+        <v>48.01756</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>23.52</v>
@@ -4399,7 +4399,7 @@
         <v>37</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>15.520842</v>
+        <v>15.510186</v>
       </c>
       <c r="AI29" s="4" t="n">
         <v>69</v>
@@ -4512,13 +4512,13 @@
         <v>1.16</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>258230</v>
+        <v>258180</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>28.170069</v>
+        <v>28.164625</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>11.013298</v>
+        <v>11.01117</v>
       </c>
       <c r="AD30" s="2" t="n">
         <v>11.16</v>
@@ -4533,7 +4533,7 @@
         <v>125.4</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>2.716443</v>
+        <v>2.715918</v>
       </c>
       <c r="AI30" s="2" t="n">
         <v>191</v>
@@ -4646,13 +4646,13 @@
         <v>1.3</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>278786</v>
+        <v>278925</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>14.890711</v>
+        <v>14.898162</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>15.037688</v>
+        <v>15.045213</v>
       </c>
       <c r="AD31" s="4" t="n">
         <v>16.49</v>
@@ -4667,7 +4667,7 @@
         <v>9.6</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>2.813735</v>
+        <v>2.815143</v>
       </c>
       <c r="AI31" s="4" t="n">
         <v>410</v>
@@ -4780,13 +4780,13 @@
         <v>0.91</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>537666</v>
+        <v>537983</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>33.44801</v>
+        <v>33.467693</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>21.258745</v>
+        <v>21.271255</v>
       </c>
       <c r="AD32" s="2" t="n">
         <v>16.95</v>
@@ -4801,7 +4801,7 @@
         <v>-34.5</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>4.919506</v>
+        <v>4.9224014</v>
       </c>
       <c r="AI32" s="2" t="n">
         <v>97</v>
@@ -4914,13 +4914,13 @@
         <v>1.07</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>270811</v>
+        <v>270270</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>90.76503</v>
+        <v>90.58360999999999</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>58.561764</v>
+        <v>58.444714</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>12.94</v>
@@ -4935,7 +4935,7 @@
         <v>19.6</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>11.04541</v>
+        <v>11.023334</v>
       </c>
       <c r="AI33" s="4" t="n">
         <v>0</v>
@@ -5048,13 +5048,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>249420</v>
+        <v>249113</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>64.96380000000001</v>
+        <v>64.88389599999999</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>51.94014</v>
+        <v>51.87626</v>
       </c>
       <c r="AD34" s="2" t="inlineStr"/>
       <c r="AE34" s="2" t="n">
@@ -5067,7 +5067,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>12.732701</v>
+        <v>12.717041</v>
       </c>
       <c r="AI34" s="2" t="n">
         <v>96</v>
@@ -5178,13 +5178,13 @@
         <v>1.12</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>133007</v>
+        <v>132858</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>12.5668545</v>
+        <v>12.55282</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>9.593861</v>
+        <v>9.583145999999999</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>30.41</v>
@@ -5199,7 +5199,7 @@
         <v>126.7</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>3.7339044</v>
+        <v>3.7297342</v>
       </c>
       <c r="AI35" s="4" t="n">
         <v>91</v>
@@ -5312,13 +5312,13 @@
         <v>0.5</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>364176</v>
+        <v>364256</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>72.00105000000001</v>
+        <v>72.01683</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>47.692608</v>
+        <v>47.703064</v>
       </c>
       <c r="AD36" s="2" t="n">
         <v>37.13</v>
@@ -5333,7 +5333,7 @@
         <v>35.1</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>28.43597</v>
+        <v>28.442204</v>
       </c>
       <c r="AI36" s="2" t="n">
         <v>27</v>
@@ -5442,13 +5442,13 @@
         <v>1.38</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>32819</v>
+        <v>32833</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>37.796844</v>
+        <v>37.812622</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>26.58363</v>
+        <v>26.594727</v>
       </c>
       <c r="AD37" s="4" t="inlineStr"/>
       <c r="AE37" s="4" t="n">
@@ -5461,7 +5461,7 @@
         <v>3</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>6.12346</v>
+        <v>6.126016</v>
       </c>
       <c r="AI37" s="4" t="n">
         <v>54</v>
@@ -5572,13 +5572,13 @@
         <v>0.61</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>142086</v>
+        <v>141690</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>5.4840145</v>
+        <v>5.46873</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>6.613924</v>
+        <v>6.5954905</v>
       </c>
       <c r="AD38" s="2" t="n">
         <v>20.47</v>
@@ -5593,7 +5593,7 @@
         <v>10.8</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>1.0693519</v>
+        <v>1.0663716</v>
       </c>
       <c r="AI38" s="2" t="n">
         <v>338</v>
@@ -5706,13 +5706,13 @@
         <v>1.01</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>132111</v>
+        <v>132127</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>35.33761</v>
+        <v>35.34188</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>27.338032</v>
+        <v>27.341337</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>11.34</v>
@@ -5727,7 +5727,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>3.489589</v>
+        <v>3.490011</v>
       </c>
       <c r="AI39" s="4" t="n">
         <v>60</v>
@@ -5840,13 +5840,13 @@
         <v>0.78</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>380643</v>
+        <v>380546</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>21.723852</v>
+        <v>21.718319</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>14.662592</v>
+        <v>14.658858</v>
       </c>
       <c r="AD40" s="2" t="inlineStr"/>
       <c r="AE40" s="2" t="n">
@@ -5859,7 +5859,7 @@
         <v>-1.6</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>1.9803654</v>
+        <v>1.979861</v>
       </c>
       <c r="AI40" s="2" t="n">
         <v>291</v>
@@ -5970,13 +5970,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>188001</v>
+        <v>187892</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>35.187656</v>
+        <v>35.167118</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>29.776596</v>
+        <v>29.759216</v>
       </c>
       <c r="AD41" s="4" t="inlineStr"/>
       <c r="AE41" s="4" t="n">
@@ -5989,7 +5989,7 @@
         <v>21.3</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>8.510959</v>
+        <v>8.505991</v>
       </c>
       <c r="AI41" s="4" t="n">
         <v>102</v>
@@ -6594,13 +6594,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138476</v>
+        <v>138491</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.01312</v>
+        <v>52.018776</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.377224</v>
+        <v>37.381287</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -6615,7 +6615,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.531461</v>
+        <v>11.532714</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -6728,13 +6728,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>408492</v>
+        <v>408400</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.47963</v>
+        <v>30.472754</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.859884</v>
+        <v>22.854727</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -6749,7 +6749,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.249241</v>
+        <v>4.248282</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -6862,13 +6862,13 @@
         <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>182775</v>
+        <v>182987</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.78631</v>
+        <v>73.87204</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.894444</v>
+        <v>58.962875</v>
       </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
@@ -6881,7 +6881,7 @@
         <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.851236</v>
+        <v>11.865007</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>43</v>
@@ -6992,13 +6992,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108711</v>
+        <v>108647</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.91513</v>
+        <v>61.878227</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.45727</v>
+        <v>44.430775</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -7013,7 +7013,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.630882</v>
+        <v>25.615606</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -7373,13 +7373,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138476</v>
+        <v>138491</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.01312</v>
+        <v>52.018776</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.377224</v>
+        <v>37.381287</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>24.58</v>
@@ -7394,7 +7394,7 @@
         <v>8</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.531461</v>
+        <v>11.532714</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>38</v>
@@ -7507,13 +7507,13 @@
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>408492</v>
+        <v>408400</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.47963</v>
+        <v>30.472754</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.859884</v>
+        <v>22.854727</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>15.59</v>
@@ -7528,7 +7528,7 @@
         <v>3.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.249241</v>
+        <v>4.248282</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>43</v>
@@ -7641,13 +7641,13 @@
         <v>1.06</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>182775</v>
+        <v>182987</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.78631</v>
+        <v>73.87204</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.894444</v>
+        <v>58.962875</v>
       </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
@@ -7660,7 +7660,7 @@
         <v>-1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.851236</v>
+        <v>11.865007</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>43</v>
@@ -7771,13 +7771,13 @@
         <v>0.77</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108711</v>
+        <v>108647</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.91513</v>
+        <v>61.878227</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.45727</v>
+        <v>44.430775</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>41.39</v>
@@ -7792,7 +7792,7 @@
         <v>14.5</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.630882</v>
+        <v>25.615606</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>48</v>
@@ -7837,7 +7837,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 20-May-2026 09:55 IST</t>
+          <t>Run Date: 20-May-2026 10:49 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -2534,7 +2534,7 @@
         <v>15.546472</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>12.623466</v>
+        <v>12.598603</v>
       </c>
       <c r="AD15" s="4" t="n">
         <v>12.55</v>
@@ -2813,7 +2813,7 @@
         <v>5.9</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>3.1557312</v>
+        <v>3.3251705</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>77</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="n">
-        <v>4.3006167</v>
+        <v>4.2029376</v>
       </c>
       <c r="AI24" s="2" t="n">
         <v>7</v>
@@ -3852,7 +3852,7 @@
         <v>26.259436</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>20.599188</v>
+        <v>20.629068</v>
       </c>
       <c r="AD25" s="4" t="n">
         <v>11.83</v>
@@ -4652,7 +4652,7 @@
         <v>14.898162</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>15.045213</v>
+        <v>15.056037</v>
       </c>
       <c r="AD31" s="4" t="n">
         <v>16.49</v>
@@ -7837,7 +7837,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 20-May-2026 10:49 IST</t>
+          <t>Run Date: 20-May-2026 18:44 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -14,10 +14,10 @@
     <sheet name="📈 Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📊 All Stocks'!$A$1:$AL$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📊 All Stocks'!$A$1:$AL$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏆 Grade A'!$A$1:$AL$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Grade B Watch'!$A$1:$AL$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Watchlist'!$A$1:$AL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Grade B Watch'!$A$1:$AL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Watchlist'!$A$1:$AL$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL41"/>
+  <dimension ref="A1:AL43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -725,32 +725,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Polycab India Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>68.2</v>
+        <v>71.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.2</v>
+        <v>18.8</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -759,23 +759,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9162.5</v>
+        <v>6893</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8656.33</v>
+        <v>6651.15</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8180.85</v>
+        <v>6444.25</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7454.82</v>
+        <v>6287.98</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -788,83 +788,79 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>98.59</v>
+        <v>97.92</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>71.12</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>377.019</v>
+        <v>170.0506</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>337.9656</v>
+        <v>156.7626</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>39.0534</v>
+        <v>13.2879</v>
       </c>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>36.86</v>
+        <v>39.66</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>337327</v>
+        <v>957736</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>491631</v>
+        <v>340695</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.81</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138491</v>
+        <v>182058</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.018776</v>
+        <v>73.69439</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.381287</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>24.58</v>
-      </c>
+        <v>58.663486</v>
+      </c>
+      <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="n">
-        <v>2.558</v>
+        <v>0.584</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>26.9</v>
+        <v>12.3</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.532714</v>
+        <v>11.804761</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ2" s="2" t="n">
-        <v>1.841</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POLYCAB/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -874,17 +870,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>64.8</v>
+        <v>68.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -893,23 +889,23 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1762.8</v>
+        <v>9199</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-1.39</v>
+        <v>0.4</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1697.95</v>
+        <v>8708.02</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1598.79</v>
+        <v>8220.77</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1474.12</v>
+        <v>7472.18</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -922,103 +918,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>96.65000000000001</v>
+        <v>98.98</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>63.75</v>
+        <v>71.77</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>68.4268</v>
+        <v>373.4664</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>69.70050000000001</v>
+        <v>345.0657</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-1.2737</v>
+        <v>28.4006</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>30.14</v>
+        <v>36.92</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>2274987</v>
+        <v>320359</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>3422075</v>
+        <v>484200</v>
       </c>
       <c r="Z3" s="4" t="n">
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>408400</v>
+        <v>138409</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.472754</v>
+        <v>52.05243</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.854727</v>
+        <v>37.358936</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>15.59</v>
+        <v>24.58</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>64.051</v>
+        <v>2.558</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.248282</v>
+        <v>11.525819</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>1.394</v>
+        <v>1.841</v>
       </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/POLYCAB/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>46</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -1027,23 +1023,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6912</v>
+        <v>838.45</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1.13</v>
+        <v>0.84</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>6625.7</v>
+        <v>813.83</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6425.93</v>
+        <v>789.47</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>6281.9</v>
+        <v>749.1799999999999</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1056,96 +1052,100 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.19</v>
+        <v>98.78</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>69.31999999999999</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>169.8444</v>
+        <v>19.0654</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>153.4407</v>
+        <v>17.8518</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>16.4038</v>
+        <v>1.2136</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>40.15</v>
+        <v>37.95</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>322081</v>
+        <v>1973862</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>304930</v>
+        <v>1885384</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>182987</v>
+        <v>107791</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.87204</v>
+        <v>61.25552</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.962875</v>
-      </c>
-      <c r="AD4" s="2" t="inlineStr"/>
+        <v>44.081028</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>41.39</v>
+      </c>
       <c r="AE4" s="2" t="n">
-        <v>0.584</v>
+        <v>12.394</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>12.3</v>
+        <v>22.1</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>-1</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.865007</v>
+        <v>25.413969</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AJ4" s="2" t="n">
+        <v>1.31</v>
+      </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>19</v>
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>831.45</v>
+        <v>8078.5</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.28</v>
+        <v>0.65</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>811.24</v>
+        <v>7904.66</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>787.47</v>
+        <v>7722.2</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>748.28</v>
+        <v>7443.91</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -1186,128 +1186,128 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>97.95999999999999</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>65.23999999999999</v>
+        <v>63.39</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>19.2999</v>
+        <v>126.6408</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>17.5484</v>
+        <v>117.3518</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>1.7515</v>
+        <v>9.289</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>37.74</v>
+        <v>24.38</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>1431476</v>
+        <v>492013</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1863164</v>
+        <v>377258</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>0.77</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108647</v>
+        <v>119463</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.878227</v>
+        <v>61.5855</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.430775</v>
+        <v>49.931694</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>41.39</v>
+        <v>21.5</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>12.394</v>
+        <v>85.146</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>22.1</v>
+        <v>18.9</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>14.5</v>
+        <v>35.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.615606</v>
+        <v>12.598754</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.31</v>
+        <v>1.065</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Nestlé India Limited</t>
+          <t>Manappuram Finance Limited</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Packaged Foods</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>59</v>
+          <t>Credit Services</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>62.4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>16.4</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1431.4</v>
+        <v>319.15</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.02</v>
+        <v>1.22</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1426.09</v>
+        <v>302.02</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1361.23</v>
+        <v>290.7</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1270.13</v>
+        <v>279.51</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1320,128 +1320,130 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>95.55</v>
+        <v>98.56</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>58.23</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>36.2617</v>
+        <v>9.4383</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>48.0862</v>
+        <v>9.1919</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>-11.8245</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr"/>
+        <v>0.2465</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W6" s="2" t="n">
-        <v>49.73</v>
+        <v>24.87</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>1803745</v>
+        <v>4971139</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>2397000</v>
+        <v>4423393</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.75</v>
+        <v>1.12</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>273840</v>
+        <v>30284</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>78.11331</v>
+        <v>27.532022</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>59.94697</v>
+        <v>10.978432</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>76.34</v>
+        <v>6.97</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>8.613</v>
+        <v>360.191</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AG6" s="2" t="n">
-        <v>27.4</v>
-      </c>
+        <v>109.3</v>
+      </c>
+      <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="n">
-        <v>53.101746</v>
+        <v>1.6814436</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.964</v>
+        <v>94.116</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NESTLEIND/</t>
+          <t>https://www.screener.in/company/MANAPPURAM/</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ideaForge Technology Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>58.4</v>
+          <t>Thermal Coal</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>61.6</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>18.6</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>776.85</v>
+        <v>2704.8</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5</v>
+        <v>-0.74</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>710.3</v>
+        <v>2504.92</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>592.8099999999999</v>
+        <v>2325.64</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>494.44</v>
+        <v>2279.15</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -1454,103 +1456,105 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>87.48</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>63.43</v>
+        <v>71.8</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>86.2445</v>
+        <v>140.0127</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>85.8182</v>
+        <v>126.8855</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.4263</v>
+        <v>13.1273</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>46.15</v>
+        <v>46.07</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>337994</v>
+        <v>1187449</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3606152</v>
+        <v>3060077</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>3269</v>
-      </c>
-      <c r="AB7" s="4" t="inlineStr"/>
+        <v>369826</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>36.66712</v>
+      </c>
       <c r="AC7" s="4" t="n">
-        <v>27.001791</v>
+        <v>47.58931</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>-2.82</v>
+        <v>13.66</v>
       </c>
       <c r="AE7" s="4" t="n">
-        <v>13.974</v>
+        <v>119.56</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>594.4</v>
+        <v>20.3</v>
       </c>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
-        <v>5.499026</v>
+        <v>4.3024473</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>2.622</v>
+        <v>1.035</v>
       </c>
       <c r="AK7" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/IDEAFORGE/</t>
+          <t>https://www.screener.in/company/ADANIENT/</t>
         </is>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEAFORGE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Oil and Natural Gas Corporation Limited</t>
+          <t>Adani Ports and Special Economic Zone Limited</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Integrated</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>57.8</v>
+          <t>Marine Shipping</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>60.8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>24.8</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1559,19 +1563,19 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>296.5</v>
+        <v>1772.6</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>291.49</v>
+        <v>1705.06</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>283.44</v>
+        <v>1605.6</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>258.05</v>
+        <v>1477.09</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -1584,67 +1588,71 @@
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>96.42</v>
+        <v>97.19</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>57.56</v>
+        <v>64.73</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>3.6831</v>
+        <v>66.0569</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>3.2872</v>
+        <v>68.9718</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.396</v>
+        <v>-2.9149</v>
       </c>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="2" t="n">
-        <v>27.05</v>
+        <v>29.85</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>9565497</v>
+        <v>1283223</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>17468489</v>
+        <v>3390298</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.55</v>
+        <v>0.38</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>375270</v>
+        <v>413169</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>9.864418000000001</v>
+        <v>30.749315</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>7.0444183</v>
-      </c>
-      <c r="AD8" s="2" t="inlineStr"/>
+        <v>23.12162</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>15.59</v>
+      </c>
       <c r="AE8" s="2" t="n">
-        <v>43.805</v>
+        <v>64.051</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.8</v>
+        <v>26.5</v>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>16.2</v>
+        <v>3.6</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>1.0195189</v>
+        <v>4.2978926</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>624</v>
-      </c>
-      <c r="AJ8" s="2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="AJ8" s="2" t="n">
+        <v>1.394</v>
+      </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ONGC/</t>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ONGC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
         </is>
       </c>
     </row>
@@ -1669,39 +1677,39 @@
           <t>Electronic Components</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>57.8</v>
+      <c r="E9" s="3" t="n">
+        <v>60.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>14.8</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1356.7</v>
+        <v>1464.4</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.01</v>
+        <v>7.94</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1217.13</v>
+        <v>1240.68</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1111.46</v>
+        <v>1125.3</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>989.4299999999999</v>
+        <v>994.15</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -1714,41 +1722,41 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>95.02</v>
+        <v>97.69</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>68.73999999999999</v>
+        <v>74.62</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>81.4867</v>
+        <v>91.0787</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>70.6683</v>
+        <v>74.7504</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>10.8184</v>
+        <v>16.3283</v>
       </c>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="n">
-        <v>32.69</v>
+        <v>34.25</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>506973</v>
+        <v>5017988</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>620953</v>
+        <v>862253</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.82</v>
+        <v>5.82</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>9780</v>
+        <v>9763</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>87.06303</v>
+        <v>86.80522999999999</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>44.77214</v>
+        <v>44.69265</v>
       </c>
       <c r="AD9" s="4" t="inlineStr"/>
       <c r="AE9" s="4" t="n">
@@ -1761,7 +1769,7 @@
         <v>35.8</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>15.004406</v>
+        <v>14.977766</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>0</v>
@@ -1781,12 +1789,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited</t>
+          <t>Oil and Natural Gas Corporation Limited</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1796,17 +1804,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Oil &amp; Gas Integrated</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>18.6</v>
+        <v>15.8</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -1819,19 +1827,19 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2725</v>
+        <v>298.3</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1.31</v>
+        <v>0.61</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2483.88</v>
+        <v>292.13</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2310.17</v>
+        <v>284.02</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2274.87</v>
+        <v>258.45</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1844,69 +1852,67 @@
         </is>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>74.12</v>
+        <v>59.19</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>139.6768</v>
+        <v>3.7839</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>123.6037</v>
+        <v>3.3865</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>16.0732</v>
+        <v>0.3973</v>
       </c>
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="2" t="n">
-        <v>45.45</v>
+        <v>26.94</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>4204144</v>
+        <v>12258794</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>3176567</v>
+        <v>17711670</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>1.32</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>370813</v>
+        <v>372188</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>36.75999</v>
+        <v>9.780165999999999</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>47.716328</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>13.66</v>
-      </c>
+        <v>6.9865613</v>
+      </c>
+      <c r="AD10" s="2" t="inlineStr"/>
       <c r="AE10" s="2" t="n">
-        <v>119.56</v>
+        <v>43.805</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AG10" s="2" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="AG10" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="AH10" s="2" t="n">
-        <v>4.3139305</v>
+        <v>1.0111454</v>
       </c>
       <c r="AI10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ10" s="2" t="n">
-        <v>1.035</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr"/>
       <c r="AK10" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIENT/</t>
+          <t>https://www.screener.in/company/ONGC/</t>
         </is>
       </c>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ONGC</t>
         </is>
       </c>
     </row>
@@ -1951,19 +1957,19 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1882.3</v>
+        <v>1880.3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.23</v>
+        <v>-0.11</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1820.96</v>
+        <v>1826.61</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1776.26</v>
+        <v>1780.34</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1723.8</v>
+        <v>1725.36</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -1976,41 +1982,41 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>98.20999999999999</v>
+        <v>98.11</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>63</v>
+        <v>62.58</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>41.2494</v>
+        <v>40.7646</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>33.6078</v>
+        <v>35.0392</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>7.6415</v>
+        <v>5.7254</v>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="n">
-        <v>27.71</v>
+        <v>28.25</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2200951</v>
+        <v>1376695</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5366107</v>
+        <v>5326466</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>451147</v>
+        <v>453786</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>41.279915</v>
+        <v>41.567036</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>33.23115</v>
+        <v>33.42556</v>
       </c>
       <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="n">
@@ -2023,7 +2029,7 @@
         <v>15.7</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>5.7951317</v>
+        <v>5.829034</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>88</v>
@@ -2081,19 +2087,19 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1285.2</v>
+        <v>1283.2</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.16</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1266.22</v>
+        <v>1267.84</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1238.15</v>
+        <v>1239.91</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1170.96</v>
+        <v>1172.08</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2106,41 +2112,41 @@
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>97.81</v>
+        <v>97.66</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>57.49</v>
+        <v>56.86</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>17.1624</v>
+        <v>16.4546</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>18.1627</v>
+        <v>17.8211</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>-1.0003</v>
+        <v>-1.3665</v>
       </c>
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="n">
-        <v>19.84</v>
+        <v>18.79</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>1136358</v>
+        <v>1039407</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>1863220</v>
+        <v>1771059</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>313182</v>
+        <v>312718</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>14.062466</v>
+        <v>14.043183</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>17.796713</v>
+        <v>17.770363</v>
       </c>
       <c r="AD12" s="2" t="n">
         <v>27.26</v>
@@ -2155,10 +2161,10 @@
         <v>991.8</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>3.1302905</v>
+        <v>3.125656</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="2" t="n">
         <v>1.491</v>
@@ -2177,12 +2183,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>Torrent Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2192,7 +2198,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
@@ -2215,19 +2221,19 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>8026</v>
+        <v>4429.2</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7886.36</v>
+        <v>4332.97</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7707.65</v>
+        <v>4250.44</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>7437.54</v>
+        <v>3926.18</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -2240,99 +2246,99 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>98.12</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>61.19</v>
+        <v>58.93</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>127.0425</v>
+        <v>63.9767</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>115.0295</v>
+        <v>52.6177</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>12.013</v>
+        <v>11.359</v>
       </c>
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="n">
-        <v>25.48</v>
+        <v>24.37</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>396261</v>
+        <v>331283</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>383079</v>
+        <v>283560</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>116156</v>
+        <v>151258</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>64.51961</v>
+        <v>66.387405</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>48.549458</v>
+        <v>69.008545</v>
       </c>
       <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="n">
-        <v>83.60599999999999</v>
+        <v>33.4</v>
       </c>
       <c r="AF13" s="4" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="AG13" s="4" t="n">
-        <v>35</v>
+        <v>26.1</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>12.773281</v>
+        <v>17.914995</v>
       </c>
       <c r="AI13" s="4" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="AJ13" s="4" t="inlineStr"/>
       <c r="AK13" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/TORNTPHARM/</t>
         </is>
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Limited</t>
+          <t>CESC Limited</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>11.8</v>
+        <v>19.4</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -2341,23 +2347,23 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4460.1</v>
+        <v>180.65</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.51</v>
+        <v>-0.23</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4322.84</v>
+        <v>180.35</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4243.14</v>
+        <v>172.9</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3921.13</v>
+        <v>164.32</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -2370,99 +2376,103 @@
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>97.91</v>
+        <v>88.34</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>61.52</v>
+        <v>52.74</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>63.561</v>
+        <v>2.7822</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>49.778</v>
+        <v>4.5618</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>13.783</v>
+        <v>-1.7797</v>
       </c>
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="n">
-        <v>24.12</v>
+        <v>34.61</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>314462</v>
+        <v>1561563</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>287650</v>
+        <v>4730283</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>1.09</v>
+        <v>0.33</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>149904</v>
+        <v>23839</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>66.206276</v>
+        <v>15.463456</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>68.39091000000001</v>
-      </c>
-      <c r="AD14" s="2" t="inlineStr"/>
+        <v>12.542114</v>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>12.55</v>
+      </c>
       <c r="AE14" s="2" t="n">
-        <v>33.4</v>
+        <v>164.311</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>17.6</v>
+        <v>5.6</v>
       </c>
       <c r="AG14" s="2" t="n">
-        <v>26.1</v>
+        <v>17.8</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>17.754654</v>
+        <v>1.8732358</v>
       </c>
       <c r="AI14" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="AJ14" s="2" t="inlineStr"/>
+        <v>332</v>
+      </c>
+      <c r="AJ14" s="2" t="n">
+        <v>0.921</v>
+      </c>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TORNTPHARM/</t>
+          <t>https://www.screener.in/company/CESC/</t>
         </is>
       </c>
       <c r="AL14" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CESC Limited</t>
+          <t>Syrma SGS Technology Limited</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>37</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -2471,23 +2481,23 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>181.06</v>
+        <v>1004</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.64</v>
+        <v>2.02</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>180.32</v>
+        <v>1003.06</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>172.58</v>
+        <v>935.7</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>164.15</v>
+        <v>800.17</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -2496,107 +2506,107 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>88.54000000000001</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>53.25</v>
+        <v>53.29</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>3.0933</v>
+        <v>27.7853</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>5.0068</v>
+        <v>42.4858</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.9135</v>
+        <v>-14.7005</v>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="n">
-        <v>35.61</v>
+        <v>37</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1885950</v>
+        <v>1282108</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4745597</v>
+        <v>1728475</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>23946</v>
+        <v>19737</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>15.546472</v>
+        <v>60.380085</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>12.598603</v>
+        <v>36.0211</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>12.55</v>
+        <v>14.14</v>
       </c>
       <c r="AE15" s="4" t="n">
-        <v>164.311</v>
+        <v>13.045</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>5.6</v>
+        <v>58.4</v>
       </c>
       <c r="AG15" s="4" t="n">
-        <v>17.8</v>
+        <v>43.7</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>1.8816729</v>
+        <v>6.7930946</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>331</v>
+        <v>15</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.921</v>
+        <v>1.7</v>
       </c>
       <c r="AK15" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CESC/</t>
+          <t>https://www.screener.in/company/SYRMA/</t>
         </is>
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SYRMA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Limited</t>
+          <t>Bandhan Bank Limited</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.2</v>
+        <v>54.4</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>14.2</v>
+        <v>21.4</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -2605,23 +2615,23 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1512.8</v>
+        <v>192.15</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.82</v>
+        <v>0.49</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1455.44</v>
+        <v>192.11</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1380.88</v>
+        <v>181.54</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1243.85</v>
+        <v>166.68</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2634,67 +2644,67 @@
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>98.88</v>
+        <v>90.36</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>71.95</v>
+        <v>53.42</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>43.1802</v>
+        <v>5.0801</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>41.2168</v>
+        <v>7.3642</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>1.9634</v>
+        <v>-2.2841</v>
       </c>
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="2" t="n">
-        <v>27.42</v>
+        <v>26.18</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>1538969</v>
+        <v>6147752</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>1242008</v>
+        <v>17643695</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>1.24</v>
+        <v>0.35</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>87314</v>
+        <v>30783</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>25.2664</v>
+        <v>25.17523</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>19.857904</v>
-      </c>
-      <c r="AD16" s="2" t="inlineStr"/>
-      <c r="AE16" s="2" t="n">
-        <v>22.248</v>
-      </c>
+        <v>8.836698999999999</v>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AE16" s="2" t="inlineStr"/>
       <c r="AF16" s="2" t="n">
-        <v>8.4</v>
+        <v>119.3</v>
       </c>
       <c r="AG16" s="2" t="n">
-        <v>7.6</v>
+        <v>68</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>2.5149362</v>
+        <v>1.2020332</v>
       </c>
       <c r="AI16" s="2" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="AJ16" s="2" t="inlineStr"/>
       <c r="AK16" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AUROPHARMA/</t>
+          <t>https://www.screener.in/company/BANDHANBNK/</t>
         </is>
       </c>
       <c r="AL16" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BANDHANBNK</t>
         </is>
       </c>
     </row>
@@ -2739,19 +2749,19 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>485.8</v>
+        <v>487.45</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.79</v>
+        <v>0.34</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>426.81</v>
+        <v>432.58</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>395.97</v>
+        <v>399.55</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>352.77</v>
+        <v>354.11</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
@@ -2764,41 +2774,41 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>99.16</v>
+        <v>97.73</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>79.91</v>
+        <v>80.19</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>23.7396</v>
+        <v>25.6006</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>17.9857</v>
+        <v>19.5086</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>5.7539</v>
+        <v>6.0919</v>
       </c>
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="n">
-        <v>41.07</v>
+        <v>43.12</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1111479</v>
+        <v>1124399</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1424073</v>
+        <v>1468702</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>12777</v>
+        <v>12848</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>30.870806</v>
+        <v>31.041798</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>18.302256</v>
+        <v>18.403631</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>10.66</v>
@@ -2813,7 +2823,7 @@
         <v>5.9</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>3.3251705</v>
+        <v>3.3435886</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>77</v>
@@ -2835,32 +2845,32 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Manappuram Finance Limited</t>
+          <t>ideaForge Technology Limited</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
         <v>52.4</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -2869,23 +2879,23 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>315.3</v>
+        <v>753.35</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3.01</v>
+        <v>-3.03</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>300.22</v>
+        <v>714.4</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>289.54</v>
+        <v>599.1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>279.12</v>
+        <v>497.02</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -2898,101 +2908,99 @@
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>98.36</v>
+        <v>84.84</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>63.61</v>
+        <v>59.84</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>9.038</v>
+        <v>79.0943</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>9.1302</v>
+        <v>84.4734</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>-0.0922</v>
+        <v>-5.3791</v>
       </c>
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="n">
-        <v>25.02</v>
+        <v>44.42</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>3193575</v>
+        <v>370201</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>4723663</v>
+        <v>2866456</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>0.68</v>
+        <v>0.13</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>29979</v>
-      </c>
-      <c r="AB18" s="2" t="n">
-        <v>27.277779</v>
-      </c>
+        <v>3206</v>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="n">
-        <v>10.867763</v>
+        <v>26.487455</v>
       </c>
       <c r="AD18" s="2" t="n">
-        <v>6.97</v>
+        <v>-2.82</v>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>360.191</v>
+        <v>13.974</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>109.3</v>
+        <v>594.4</v>
       </c>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="n">
-        <v>1.6644936</v>
+        <v>5.394279</v>
       </c>
       <c r="AI18" s="2" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="AJ18" s="2" t="n">
-        <v>94.116</v>
+        <v>2.622</v>
       </c>
       <c r="AK18" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MANAPPURAM/</t>
+          <t>https://www.screener.in/company/IDEAFORGE/</t>
         </is>
       </c>
       <c r="AL18" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEAFORGE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Limited</t>
+          <t>Nestlé India Limited</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Packaged Foods</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>14.8</v>
+        <v>19</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -3001,23 +3009,23 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>271.45</v>
+        <v>1420.1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.46</v>
+        <v>-0.79</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>267.34</v>
+        <v>1425.52</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>261.98</v>
+        <v>1363.54</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>247.03</v>
+        <v>1271.62</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -3030,99 +3038,103 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>95.05</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>56.83</v>
+        <v>54.17</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3.5829</v>
+        <v>31.5502</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>3.7256</v>
+        <v>44.779</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.1427</v>
+        <v>-13.2288</v>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="n">
-        <v>23.08</v>
+        <v>46.76</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2436357</v>
+        <v>1425216</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3457819</v>
+        <v>2082086</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>78260</v>
+        <v>271217</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>557.75507</v>
+        <v>77.365234</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>176.20662</v>
-      </c>
-      <c r="AD19" s="4" t="inlineStr"/>
+        <v>59.37287</v>
+      </c>
+      <c r="AD19" s="4" t="n">
+        <v>76.34</v>
+      </c>
       <c r="AE19" s="4" t="n">
-        <v>97.748</v>
+        <v>8.613</v>
       </c>
       <c r="AF19" s="4" t="n">
-        <v>26.7</v>
+        <v>23.8</v>
       </c>
       <c r="AG19" s="4" t="n">
-        <v>144.4</v>
+        <v>27.4</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>56.501965</v>
+        <v>52.5932</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="4" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="AJ19" s="4" t="n">
+        <v>0.964</v>
+      </c>
       <c r="AK19" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NYKAA/</t>
+          <t>https://www.screener.in/company/NESTLEIND/</t>
         </is>
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RBL Bank Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>26.2</v>
+        <v>14.8</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -3131,23 +3143,23 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>323.65</v>
+        <v>273.3</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-0.6</v>
+        <v>0.68</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>328.74</v>
+        <v>267.9</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>321.13</v>
+        <v>262.43</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>294.76</v>
+        <v>247.29</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -3160,97 +3172,99 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>92.5</v>
+        <v>95.69</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>48.12</v>
+        <v>58.63</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>3.7575</v>
+        <v>3.6262</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>5.5177</v>
+        <v>3.7057</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>-1.7601</v>
+        <v>-0.0795</v>
       </c>
       <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="n">
-        <v>21.07</v>
+        <v>22.02</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>2758793</v>
+        <v>2354029</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>6498683</v>
+        <v>3091447</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>20324</v>
+        <v>78603</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>23.330967</v>
+        <v>560.20404</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>17.309652</v>
+        <v>108.05895</v>
       </c>
       <c r="AD20" s="2" t="inlineStr"/>
-      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="n">
+        <v>97.748</v>
+      </c>
       <c r="AF20" s="2" t="n">
-        <v>40.8</v>
+        <v>26.7</v>
       </c>
       <c r="AG20" s="2" t="n">
-        <v>367.9</v>
+        <v>144.4</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>1.214099</v>
+        <v>56.750053</v>
       </c>
       <c r="AI20" s="2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="2" t="inlineStr"/>
       <c r="AK20" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/RBLBANK/</t>
+          <t>https://www.screener.in/company/NYKAA/</t>
         </is>
       </c>
       <c r="AL20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Berger Paints India Limited</t>
+          <t>The Federal Bank Limited</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>35.5</v>
+        <v>27</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>14.6</v>
+        <v>23.6</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -3259,27 +3273,27 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>507.7</v>
+        <v>289.9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.22</v>
+        <v>1.15</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>492.65</v>
+        <v>287.08</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>475.02</v>
+        <v>284.04</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>496.27</v>
+        <v>257.26</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -3288,103 +3302,99 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>84.48</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>58.5</v>
+        <v>54.11</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>17.7539</v>
+        <v>0.2916</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>14.9843</v>
+        <v>1.1752</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.7695</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="n">
-        <v>33.04</v>
+        <v>13.84</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>353321</v>
+        <v>6657728</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>958473</v>
+        <v>8014234</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.37</v>
+        <v>0.83</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>59285</v>
+        <v>69918</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>52.68912</v>
+        <v>16.232838</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>40.03865</v>
+        <v>11.9424305</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="AE21" s="4" t="n">
-        <v>9.164999999999999</v>
-      </c>
+        <v>11.73</v>
+      </c>
+      <c r="AE21" s="4" t="inlineStr"/>
       <c r="AF21" s="4" t="n">
-        <v>6.1</v>
+        <v>12.3</v>
       </c>
       <c r="AG21" s="4" t="n">
-        <v>27.7</v>
+        <v>22.2</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>8.575212000000001</v>
+        <v>1.9210589</v>
       </c>
       <c r="AI21" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ21" s="4" t="n">
-        <v>2.115</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr"/>
       <c r="AK21" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BERGEPAINT/</t>
+          <t>https://www.screener.in/company/FEDERALBNK/</t>
         </is>
       </c>
       <c r="AL21" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Limited</t>
+          <t>Berger Paints India Limited</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>28</v>
+        <v>35.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>21.6</v>
+        <v>14.6</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -3393,112 +3403,112 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>984.15</v>
+        <v>508.45</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.46</v>
+        <v>0.15</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1002.96</v>
+        <v>494.15</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>932.92</v>
+        <v>476.34</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>798.12</v>
+        <v>496.39</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>82.84</v>
+        <v>84.61</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>49.94</v>
+        <v>58.74</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>31.245</v>
+        <v>16.7937</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>46.1609</v>
+        <v>15.3462</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>-14.9159</v>
+        <v>1.4475</v>
       </c>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="n">
-        <v>38.19</v>
+        <v>32</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>802254</v>
+        <v>200794</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>1735329</v>
+        <v>960359</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.46</v>
+        <v>0.21</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>19340</v>
+        <v>58224</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>59.303013</v>
+        <v>51.692547</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>35.29516</v>
+        <v>39.322056</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>14.14</v>
+        <v>17.23</v>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>13.045</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>58.4</v>
+        <v>6.1</v>
       </c>
       <c r="AG22" s="2" t="n">
-        <v>43.7</v>
+        <v>27.7</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>6.6561913</v>
+        <v>8.421737</v>
       </c>
       <c r="AI22" s="2" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="AJ22" s="2" t="n">
-        <v>1.7</v>
+        <v>2.115</v>
       </c>
       <c r="AK22" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/SYRMA/</t>
+          <t>https://www.screener.in/company/BERGEPAINT/</t>
         </is>
       </c>
       <c r="AL22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SYRMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bandhan Bank Limited</t>
+          <t>RBL Bank Limited</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -3512,13 +3522,13 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>49.4</v>
+        <v>48.2</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>21.4</v>
+        <v>26.2</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -3531,19 +3541,19 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>191.21</v>
+        <v>328.5</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.46</v>
+        <v>1.5</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>192.1</v>
+        <v>328.72</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>181.1</v>
+        <v>321.42</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>166.43</v>
+        <v>295.09</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -3556,67 +3566,65 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>89.91</v>
+        <v>93.88</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>52.46</v>
+        <v>51.15</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.7453</v>
+        <v>3.3076</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>7.9352</v>
+        <v>5.0757</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.1899</v>
+        <v>-1.768</v>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="n">
-        <v>28.05</v>
+        <v>19.89</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>4802152</v>
+        <v>3142131</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>17758522</v>
+        <v>6437985</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>30956</v>
+        <v>20340</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>25.316204</v>
+        <v>23.33215</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>8.886181000000001</v>
-      </c>
-      <c r="AD23" s="4" t="n">
-        <v>4.88</v>
-      </c>
+        <v>17.322826</v>
+      </c>
+      <c r="AD23" s="4" t="inlineStr"/>
       <c r="AE23" s="4" t="inlineStr"/>
       <c r="AF23" s="4" t="n">
-        <v>119.3</v>
+        <v>40.8</v>
       </c>
       <c r="AG23" s="4" t="n">
-        <v>68</v>
+        <v>367.9</v>
       </c>
       <c r="AH23" s="4" t="n">
-        <v>1.2087642</v>
+        <v>1.2150229</v>
       </c>
       <c r="AI23" s="4" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="AJ23" s="4" t="inlineStr"/>
       <c r="AK23" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BANDHANBNK/</t>
+          <t>https://www.screener.in/company/RBLBANK/</t>
         </is>
       </c>
       <c r="AL23" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BANDHANBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
@@ -3661,19 +3669,19 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>138.17</v>
+        <v>139.34</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-1.09</v>
+        <v>0.85</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>129.36</v>
+        <v>130.31</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>106.66</v>
+        <v>107.94</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>83.81999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -3686,41 +3694,41 @@
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>88.97</v>
+        <v>89.72</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>65.86</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15.1185</v>
+        <v>14.0758</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>15.7689</v>
+        <v>15.4303</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>-0.6504</v>
+        <v>-1.3545</v>
       </c>
       <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="2" t="n">
-        <v>62.38</v>
+        <v>60.32</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>46887470</v>
+        <v>27652548</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>82404133</v>
+        <v>81313582</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.57</v>
+        <v>0.34</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>21323</v>
+        <v>21691</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>387.05554</v>
+        <v>393.74997</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>26.796154</v>
+        <v>27.259617</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>7.27</v>
@@ -3733,7 +3741,7 @@
       </c>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="n">
-        <v>4.2029376</v>
+        <v>4.275631</v>
       </c>
       <c r="AI24" s="2" t="n">
         <v>7</v>
@@ -3755,12 +3763,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Limited</t>
+          <t>Aurobindo Pharma Limited</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -3774,13 +3782,13 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>10</v>
+        <v>14.2</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -3793,19 +3801,19 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1335.2</v>
+        <v>1517.5</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1298.2</v>
+        <v>1461.35</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1281.78</v>
+        <v>1386.23</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1256.26</v>
+        <v>1246.57</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -3818,103 +3826,99 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>97.04000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>59.29</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>13.6196</v>
+        <v>42.8906</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>10.6891</v>
+        <v>41.5516</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.9306</v>
+        <v>1.339</v>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="n">
-        <v>16.8</v>
+        <v>28.27</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2488019</v>
+        <v>1068558</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3363296</v>
+        <v>1210257</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>110061</v>
+        <v>88994</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>26.259436</v>
+        <v>25.739723</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>20.629068</v>
-      </c>
-      <c r="AD25" s="4" t="n">
-        <v>11.83</v>
-      </c>
+        <v>20.209826</v>
+      </c>
+      <c r="AD25" s="4" t="inlineStr"/>
       <c r="AE25" s="4" t="n">
-        <v>20.328</v>
+        <v>22.248</v>
       </c>
       <c r="AF25" s="4" t="n">
-        <v>-11.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG25" s="4" t="n">
-        <v>-86.2</v>
+        <v>7.6</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>2.9228117</v>
+        <v>2.563329</v>
       </c>
       <c r="AI25" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ25" s="4" t="n">
-        <v>1.802</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr"/>
       <c r="AK25" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DRREDDY/</t>
+          <t>https://www.screener.in/company/AUROPHARMA/</t>
         </is>
       </c>
       <c r="AL25" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DRREDDY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The Federal Bank Limited</t>
+          <t>Dr. Reddy's Laboratories Limited</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>45.6</v>
+        <v>46</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -3923,23 +3927,23 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>286.6</v>
+        <v>1321.9</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.93</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>286.79</v>
+        <v>1300.45</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>283.8</v>
+        <v>1283.35</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>256.93</v>
+        <v>1256.92</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -3952,67 +3956,71 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>94.90000000000001</v>
+        <v>96.08</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>50.33</v>
+        <v>56.03</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>0.0164</v>
+        <v>13.8033</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>1.3961</v>
+        <v>11.3119</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>-1.3796</v>
+        <v>2.4914</v>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="2" t="n">
-        <v>14.81</v>
+        <v>15.87</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>6905213</v>
+        <v>1277182</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>8003545</v>
+        <v>3348492</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.86</v>
+        <v>0.38</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>71434</v>
+        <v>109778</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>16.58467</v>
+        <v>26.181494</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>12.20127</v>
+        <v>20.576008</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="AE26" s="2" t="inlineStr"/>
+        <v>11.83</v>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>20.328</v>
+      </c>
       <c r="AF26" s="2" t="n">
-        <v>12.3</v>
+        <v>-11.6</v>
       </c>
       <c r="AG26" s="2" t="n">
-        <v>22.2</v>
+        <v>-86.2</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>1.9626958</v>
+        <v>2.915294</v>
       </c>
       <c r="AI26" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ26" s="2" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="AJ26" s="2" t="n">
+        <v>1.802</v>
+      </c>
       <c r="AK26" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/FEDERALBNK/</t>
+          <t>https://www.screener.in/company/DRREDDY/</t>
         </is>
       </c>
       <c r="AL26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DRREDDY</t>
         </is>
       </c>
     </row>
@@ -4057,19 +4065,19 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1409.8</v>
+        <v>1399.5</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.15</v>
+        <v>-0.73</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1344.58</v>
+        <v>1349.81</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1319.63</v>
+        <v>1322.76</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1393.22</v>
+        <v>1393.28</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -4082,41 +4090,41 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>84.27</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>64.67</v>
+        <v>62.28</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>36.617</v>
+        <v>36.3121</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>26.6395</v>
+        <v>28.574</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>9.977499999999999</v>
+        <v>7.7381</v>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="n">
-        <v>38.14</v>
+        <v>37.68</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1379218</v>
+        <v>1316586</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2264053</v>
+        <v>2271270</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>113052</v>
+        <v>113246</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>29.198832</v>
+        <v>29.206251</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>22.091963</v>
+        <v>22.21495</v>
       </c>
       <c r="AD27" s="4" t="n">
         <v>11.74</v>
@@ -4131,10 +4139,10 @@
         <v>-54.6</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>3.4340944</v>
+        <v>3.4399836</v>
       </c>
       <c r="AI27" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AJ27" s="4" t="n">
         <v>3.443</v>
@@ -4191,19 +4199,19 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>456.95</v>
+        <v>458.7</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-1.11</v>
+        <v>0.38</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>460.84</v>
+        <v>460.64</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>452.45</v>
+        <v>452.7</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>416.08</v>
+        <v>416.51</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -4216,41 +4224,41 @@
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>93.02</v>
+        <v>93.37</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>48.28</v>
+        <v>49.61</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>2.2506</v>
+        <v>1.842</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>4.0819</v>
+        <v>3.6339</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>-1.8313</v>
+        <v>-1.792</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
       <c r="W28" s="2" t="n">
-        <v>16</v>
+        <v>15.07</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>7319865</v>
+        <v>3756072</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>11177370</v>
+        <v>11015577</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.65</v>
+        <v>0.34</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>282684</v>
+        <v>283609</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>9.092171</v>
+        <v>9.120094999999999</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>8.020989</v>
+        <v>8.047218000000001</v>
       </c>
       <c r="AD28" s="2" t="n">
         <v>28.12</v>
@@ -4265,10 +4273,10 @@
         <v>12.9</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>2.373241</v>
+        <v>2.3810017</v>
       </c>
       <c r="AI28" s="2" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AJ28" s="2" t="n">
         <v>1.856</v>
@@ -4325,19 +4333,19 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1455.8</v>
+        <v>1455.6</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.39</v>
+        <v>-0.01</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1425.5</v>
+        <v>1428.36</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1408.97</v>
+        <v>1410.79</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1439.98</v>
+        <v>1440.14</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -4350,41 +4358,41 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>92.43000000000001</v>
+        <v>92.42</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>57.98</v>
+        <v>57.93</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>23.9486</v>
+        <v>23.2985</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>19.7904</v>
+        <v>20.492</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.1582</v>
+        <v>2.8065</v>
       </c>
       <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="n">
-        <v>19.31</v>
+        <v>18.81</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>617156</v>
+        <v>356329</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1080727</v>
+        <v>1067046</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>148147</v>
+        <v>149898</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>60.5995</v>
+        <v>61.31557</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>48.01756</v>
+        <v>48.584957</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>23.52</v>
@@ -4399,7 +4407,7 @@
         <v>37</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>15.510186</v>
+        <v>15.693462</v>
       </c>
       <c r="AI29" s="4" t="n">
         <v>69</v>
@@ -4455,23 +4463,23 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>209.29</v>
+        <v>207.01</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-0.2</v>
+        <v>-1.09</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>212.48</v>
+        <v>211.96</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>207.01</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>187.2</v>
+        <v>187.4</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -4480,45 +4488,45 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>93.27</v>
+        <v>92.25</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>47.27</v>
+        <v>44.36</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>2.1949</v>
+        <v>1.5088</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>3.1151</v>
+        <v>2.7938</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>-0.9202</v>
+        <v>-1.285</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="n">
-        <v>20.45</v>
+        <v>20.34</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>32573663</v>
+        <v>56670462</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>28032195</v>
+        <v>29825933</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>258180</v>
+        <v>260138</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>28.164625</v>
+        <v>28.378231</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>11.01117</v>
+        <v>11.094682</v>
       </c>
       <c r="AD30" s="2" t="n">
         <v>11.16</v>
@@ -4533,10 +4541,10 @@
         <v>125.4</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>2.715918</v>
+        <v>2.7365162</v>
       </c>
       <c r="AI30" s="2" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AJ30" s="2" t="n">
         <v>0.748</v>
@@ -4555,32 +4563,32 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Limited</t>
+          <t>Larsen &amp; Toubro Limited</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>40.4</v>
+        <v>39.8</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>16.4</v>
+        <v>21.8</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -4589,23 +4597,23 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>298.6</v>
+        <v>3910.7</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.26</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>308.13</v>
+        <v>3950.06</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>304.36</v>
+        <v>3937.47</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>288.42</v>
+        <v>3857.6</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
@@ -4614,107 +4622,107 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>91.89</v>
+        <v>88.08</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>37.48</v>
+        <v>46.81</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.8407</v>
+        <v>-5.15</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.9189000000000001</v>
+        <v>12.649</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-2.7596</v>
+        <v>-17.7991</v>
       </c>
       <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="n">
-        <v>25.9</v>
+        <v>11.01</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>12580156</v>
+        <v>1972259</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>9661682</v>
+        <v>2534946</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>1.3</v>
+        <v>0.78</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>278925</v>
+        <v>540431</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>14.898162</v>
+        <v>33.597023</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>15.056037</v>
+        <v>21.368074</v>
       </c>
       <c r="AD31" s="4" t="n">
-        <v>16.49</v>
+        <v>16.95</v>
       </c>
       <c r="AE31" s="4" t="n">
-        <v>150.993</v>
+        <v>97.64</v>
       </c>
       <c r="AF31" s="4" t="n">
-        <v>-5</v>
+        <v>11.7</v>
       </c>
       <c r="AG31" s="4" t="n">
-        <v>9.6</v>
+        <v>-34.5</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>2.815143</v>
+        <v>4.944806</v>
       </c>
       <c r="AI31" s="4" t="n">
-        <v>410</v>
+        <v>97</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.625</v>
+        <v>1.251</v>
       </c>
       <c r="AK31" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POWERGRID/</t>
+          <t>https://www.screener.in/company/LT/</t>
         </is>
       </c>
       <c r="AL31" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERGRID</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Limited</t>
+          <t>Avenue Supermarts Limited</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Discount Stores</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>21.8</v>
+        <v>15.4</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -4723,23 +4731,23 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>3921</v>
+        <v>4144.2</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.08</v>
+        <v>-2.17</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3954.21</v>
+        <v>4350.8</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3938.57</v>
+        <v>4268.49</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>3857.06</v>
+        <v>4125.32</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -4748,107 +4756,107 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>88.31</v>
+        <v>83.73</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>47.61</v>
+        <v>35.17</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>-2.3427</v>
+        <v>-20.8476</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>17.0988</v>
+        <v>22.6102</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>-19.4415</v>
+        <v>-43.4579</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="2" t="n">
-        <v>10.91</v>
+        <v>24.28</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>2318170</v>
+        <v>346215</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>2545237</v>
+        <v>342934</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>537983</v>
+        <v>269813</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>33.467693</v>
+        <v>90.74798</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>21.271255</v>
+        <v>58.345993</v>
       </c>
       <c r="AD32" s="2" t="n">
-        <v>16.95</v>
+        <v>12.94</v>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>97.64</v>
+        <v>9.913</v>
       </c>
       <c r="AF32" s="2" t="n">
-        <v>11.7</v>
+        <v>18.9</v>
       </c>
       <c r="AG32" s="2" t="n">
-        <v>-34.5</v>
+        <v>19.6</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>4.9224014</v>
+        <v>11.004714</v>
       </c>
       <c r="AI32" s="2" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="2" t="n">
-        <v>1.251</v>
+        <v>1.977</v>
       </c>
       <c r="AK32" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/LT/</t>
+          <t>https://www.screener.in/company/DMART/</t>
         </is>
       </c>
       <c r="AL32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DMART</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Limited</t>
+          <t>Asian Paints Limited</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Discount Stores</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>24</v>
+        <v>31.5</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>15.4</v>
+        <v>7.8</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -4857,132 +4865,128 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4236</v>
+        <v>2598.6</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.6</v>
+        <v>-0.08</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4372.54</v>
+        <v>2532.31</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4273.56</v>
+        <v>2466.35</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4125.13</v>
+        <v>2478.71</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>85.58</v>
+        <v>87.03</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>40.28</v>
+        <v>61.71</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-4.1313</v>
+        <v>59.3243</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>33.4747</v>
+        <v>56.9608</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-37.606</v>
+        <v>2.3635</v>
       </c>
       <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="n">
-        <v>22.68</v>
+        <v>27.93</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>367515</v>
+        <v>586190</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>341896</v>
+        <v>968162</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>1.07</v>
+        <v>0.61</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>270270</v>
+        <v>249132</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>90.58360999999999</v>
+        <v>64.93753</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>58.444714</v>
-      </c>
-      <c r="AD33" s="4" t="n">
-        <v>12.94</v>
-      </c>
+        <v>51.941814</v>
+      </c>
+      <c r="AD33" s="4" t="inlineStr"/>
       <c r="AE33" s="4" t="n">
-        <v>9.913</v>
+        <v>17.609</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>18.9</v>
+        <v>3.7</v>
       </c>
       <c r="AG33" s="4" t="n">
-        <v>19.6</v>
+        <v>-4.6</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>11.023334</v>
+        <v>12.7180195</v>
       </c>
       <c r="AI33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="4" t="n">
-        <v>1.977</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr"/>
       <c r="AK33" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DMART/</t>
+          <t>https://www.screener.in/company/ASIANPAINT/</t>
         </is>
       </c>
       <c r="AL33" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DMART</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Asian Paints Limited</t>
+          <t>Muthoot Finance Limited</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>39.3</v>
+        <v>37.5</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>31.5</v>
+        <v>7.5</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
@@ -4991,23 +4995,23 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>💎 High ROE</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2600.7</v>
+        <v>3309.3</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-0.51</v>
+        <v>0.17</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2525.33</v>
+        <v>3419.46</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2460.95</v>
+        <v>3441.02</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2477.5</v>
+        <v>3292.48</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -5016,103 +5020,107 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>87.11</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>62.02</v>
+        <v>42.61</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>61.0116</v>
+        <v>-28.4915</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>56.3699</v>
+        <v>-1.8945</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>4.6417</v>
+        <v>-26.597</v>
       </c>
       <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="2" t="n">
-        <v>28.64</v>
+        <v>13.67</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>688639</v>
+        <v>1017971</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>995181</v>
+        <v>822401</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>249113</v>
+        <v>131389</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>64.88389599999999</v>
+        <v>12.408341</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>51.87626</v>
-      </c>
-      <c r="AD34" s="2" t="inlineStr"/>
+        <v>9.477159</v>
+      </c>
+      <c r="AD34" s="2" t="n">
+        <v>30.41</v>
+      </c>
       <c r="AE34" s="2" t="n">
-        <v>17.609</v>
+        <v>379.707</v>
       </c>
       <c r="AF34" s="2" t="n">
-        <v>3.7</v>
+        <v>53.7</v>
       </c>
       <c r="AG34" s="2" t="n">
-        <v>-4.6</v>
+        <v>126.7</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>12.717041</v>
+        <v>3.6884842</v>
       </c>
       <c r="AI34" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="AJ34" s="2" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>128.286</v>
+      </c>
       <c r="AK34" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ASIANPAINT/</t>
+          <t>https://www.screener.in/company/MUTHOOTFIN/</t>
         </is>
       </c>
       <c r="AL34" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ASIANPAINT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Muthoot Finance Limited</t>
+          <t>Power Grid Corporation of India Limited</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.5</v>
+        <v>21</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>30</v>
+        <v>16.4</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -5121,27 +5129,27 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>💎 High ROE</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3303.6</v>
+        <v>299.9</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>3431.06</v>
+        <v>307.34</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>3446.4</v>
+        <v>304.19</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3292.31</v>
+        <v>288.54</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
@@ -5150,103 +5158,103 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>80.29000000000001</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>42.22</v>
+        <v>39.56</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-21.8665</v>
+        <v>-2.2137</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>4.7548</v>
+        <v>0.2924</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-26.6212</v>
+        <v>-2.5061</v>
       </c>
       <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="n">
-        <v>12.94</v>
+        <v>25.96</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>908258</v>
+        <v>5672695</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>812804</v>
+        <v>9589690</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>1.12</v>
+        <v>0.59</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>132858</v>
+        <v>278600</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>12.55282</v>
+        <v>14.888169</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>9.583145999999999</v>
+        <v>15.038465</v>
       </c>
       <c r="AD35" s="4" t="n">
-        <v>30.41</v>
+        <v>16.49</v>
       </c>
       <c r="AE35" s="4" t="n">
-        <v>379.707</v>
+        <v>150.993</v>
       </c>
       <c r="AF35" s="4" t="n">
-        <v>53.7</v>
+        <v>-5</v>
       </c>
       <c r="AG35" s="4" t="n">
-        <v>126.7</v>
+        <v>9.6</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>3.7297342</v>
+        <v>2.8118575</v>
       </c>
       <c r="AI35" s="4" t="n">
-        <v>91</v>
+        <v>408</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>128.286</v>
+        <v>0.625</v>
       </c>
       <c r="AK35" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MUTHOOTFIN/</t>
+          <t>https://www.screener.in/company/POWERGRID/</t>
         </is>
       </c>
       <c r="AL35" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Titan Company Limited</t>
+          <t>Power Finance Corporation Limited</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Luxury Goods</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
@@ -5259,19 +5267,19 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4102</v>
+        <v>429.35</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-1.62</v>
+        <v>-0.52</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4256.95</v>
+        <v>445.23</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4256.55</v>
+        <v>434.51</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>3965.59</v>
+        <v>403.01</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -5284,71 +5292,71 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>89.08</v>
+        <v>88.25</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>40.13</v>
+        <v>41.59</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>-52.488</v>
+        <v>-1.0489</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>-18.6797</v>
+        <v>3.8694</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>-33.8083</v>
+        <v>-4.9183</v>
       </c>
       <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="n">
-        <v>9.85</v>
+        <v>16.08</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>711398</v>
+        <v>4861888</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>1429498</v>
+        <v>6573529</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>364256</v>
+        <v>142234</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>72.01683</v>
+        <v>5.4911456</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>47.703064</v>
+        <v>6.6208367</v>
       </c>
       <c r="AD36" s="2" t="n">
-        <v>37.13</v>
+        <v>20.47</v>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>195.001</v>
+        <v>586.0170000000001</v>
       </c>
       <c r="AF36" s="2" t="n">
-        <v>80.5</v>
+        <v>-15.4</v>
       </c>
       <c r="AG36" s="2" t="n">
-        <v>35.1</v>
+        <v>10.8</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>28.442204</v>
+        <v>1.0704696</v>
       </c>
       <c r="AI36" s="2" t="n">
-        <v>27</v>
+        <v>340</v>
       </c>
       <c r="AJ36" s="2" t="n">
-        <v>1.276</v>
+        <v>287.366</v>
       </c>
       <c r="AK36" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TITAN/</t>
+          <t>https://www.screener.in/company/PFC/</t>
         </is>
       </c>
       <c r="AL36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PFC</t>
         </is>
       </c>
     </row>
@@ -5374,10 +5382,10 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>36.5</v>
+        <v>33.5</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>28.5</v>
+        <v>25.5</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>8</v>
@@ -5389,19 +5397,19 @@
       </c>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="n">
-        <v>956.65</v>
+        <v>958.55</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>4.91</v>
+        <v>0.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>925.9</v>
+        <v>929.01</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>910.24</v>
+        <v>912.14</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>945.46</v>
+        <v>945.59</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
@@ -5414,41 +5422,41 @@
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>76.31999999999999</v>
+        <v>76.47</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>58.91</v>
+        <v>59.29</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>9.0938</v>
+        <v>10.6694</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>13.1193</v>
+        <v>12.6293</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>-4.0255</v>
+        <v>-1.9599</v>
       </c>
       <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="n">
-        <v>25.21</v>
+        <v>24.85</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>310934</v>
+        <v>121297</v>
       </c>
       <c r="Y37" s="4" t="n">
-        <v>225577</v>
+        <v>224989</v>
       </c>
       <c r="Z37" s="4" t="n">
-        <v>1.38</v>
+        <v>0.54</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>32833</v>
+        <v>32598</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>37.812622</v>
+        <v>37.601738</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>26.594727</v>
+        <v>26.390295</v>
       </c>
       <c r="AD37" s="4" t="inlineStr"/>
       <c r="AE37" s="4" t="n">
@@ -5461,7 +5469,7 @@
         <v>3</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>6.126016</v>
+        <v>6.082238</v>
       </c>
       <c r="AI37" s="4" t="n">
         <v>54</v>
@@ -5481,32 +5489,32 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>NTPC Limited</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>35</v>
+        <v>32.2</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>20</v>
+        <v>14.2</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -5515,23 +5523,23 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>431.6</v>
+        <v>392.45</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.42</v>
+        <v>0.78</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>446.9</v>
+        <v>393.81</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>434.72</v>
+        <v>386.71</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>402.74</v>
+        <v>359.21</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -5540,75 +5548,71 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>88.72</v>
+        <v>94.7</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>42.61</v>
+        <v>49.72</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>0.276</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>5.099</v>
+        <v>2.6414</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>-4.823</v>
+        <v>-1.775</v>
       </c>
       <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="n">
-        <v>15.42</v>
+        <v>14.96</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>3990614</v>
+        <v>5386249</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>6591422</v>
+        <v>8064800</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>141690</v>
+        <v>377006</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>5.46873</v>
+        <v>21.492537</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>6.5954905</v>
-      </c>
-      <c r="AD38" s="2" t="n">
-        <v>20.47</v>
-      </c>
+        <v>14.522522</v>
+      </c>
+      <c r="AD38" s="2" t="inlineStr"/>
       <c r="AE38" s="2" t="n">
-        <v>586.0170000000001</v>
+        <v>118.127</v>
       </c>
       <c r="AF38" s="2" t="n">
-        <v>-15.4</v>
+        <v>8</v>
       </c>
       <c r="AG38" s="2" t="n">
-        <v>10.8</v>
+        <v>-1.6</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>1.0663716</v>
+        <v>1.9614471</v>
       </c>
       <c r="AI38" s="2" t="n">
-        <v>338</v>
-      </c>
-      <c r="AJ38" s="2" t="n">
-        <v>287.366</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr"/>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/PFC/</t>
+          <t>https://www.screener.in/company/NTPC/</t>
         </is>
       </c>
       <c r="AL38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PFC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NTPC</t>
         </is>
       </c>
     </row>
@@ -5634,10 +5638,10 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>33.8</v>
+        <v>30.8</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>6.8</v>
@@ -5653,19 +5657,19 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>415</v>
+        <v>413.5</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2.63</v>
+        <v>-0.36</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>422.22</v>
+        <v>421.39</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>412.91</v>
+        <v>412.93</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>393.74</v>
+        <v>393.93</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
@@ -5678,41 +5682,41 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>89.27</v>
+        <v>88.94</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>45.94</v>
+        <v>45.02</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-1.2882</v>
+        <v>-1.7079</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>4.1587</v>
+        <v>2.9854</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>-5.4469</v>
+        <v>-4.6933</v>
       </c>
       <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="n">
-        <v>24.94</v>
+        <v>25</v>
       </c>
       <c r="X39" s="4" t="n">
-        <v>7454213</v>
+        <v>4390666</v>
       </c>
       <c r="Y39" s="4" t="n">
-        <v>7388673</v>
+        <v>7310922</v>
       </c>
       <c r="Z39" s="4" t="n">
-        <v>1.01</v>
+        <v>0.6</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>132127</v>
+        <v>131169</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>35.34188</v>
+        <v>35.085472</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>27.341337</v>
+        <v>27.142973</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>11.34</v>
@@ -5727,7 +5731,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>3.490011</v>
+        <v>3.4646904</v>
       </c>
       <c r="AI39" s="4" t="n">
         <v>60</v>
@@ -5749,12 +5753,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>NTPC Limited</t>
+          <t>NHPC Limited</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5764,127 +5768,127 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Utilities - Renewable</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>32.2</v>
+        <v>27.5</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>14.2</v>
+        <v>17</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="n">
-        <v>389.4</v>
+        <v>79.5</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>393.96</v>
+        <v>79.77</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>386.48</v>
+        <v>79.16</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>358.87</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>93.97</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>46.48</v>
+        <v>49.15</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>1.0704</v>
+        <v>-0.365</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>3.0851</v>
+        <v>0.1361</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>-2.0147</v>
+        <v>-0.5012</v>
       </c>
       <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="2" t="n">
-        <v>14.52</v>
+        <v>18.41</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>6693518</v>
+        <v>15924979</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>8616044</v>
+        <v>14208123</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>0.78</v>
+        <v>1.12</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>380546</v>
+        <v>79356</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>21.718319</v>
+        <v>28.519855</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>14.658858</v>
-      </c>
-      <c r="AD40" s="2" t="inlineStr"/>
+        <v>12.34375</v>
+      </c>
+      <c r="AD40" s="2" t="n">
+        <v>9.02</v>
+      </c>
       <c r="AE40" s="2" t="n">
-        <v>118.127</v>
+        <v>113.111</v>
       </c>
       <c r="AF40" s="2" t="n">
-        <v>8</v>
+        <v>19.2</v>
       </c>
       <c r="AG40" s="2" t="n">
-        <v>-1.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>1.979861</v>
+        <v>1.9183139</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>291</v>
-      </c>
-      <c r="AJ40" s="2" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="AJ40" s="2" t="n">
+        <v>0.944</v>
+      </c>
       <c r="AK40" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NTPC/</t>
+          <t>https://www.screener.in/company/NHPC/</t>
         </is>
       </c>
       <c r="AL40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NTPC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NHPC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Eicher Motors Limited</t>
+          <t>Titan Company Limited</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -5894,17 +5898,17 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Luxury Goods</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>19.5</v>
+        <v>26.5</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>4.5</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -5913,23 +5917,23 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>💎 High ROE</t>
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>6882.5</v>
+        <v>4106.4</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-0.44</v>
+        <v>0.11</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>7096.07</v>
+        <v>4242.61</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>7148.11</v>
+        <v>4250.67</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>6880.21</v>
+        <v>3966.99</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
@@ -5938,76 +5942,338 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>83.63</v>
+        <v>89.17</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>39.68</v>
+        <v>40.44</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>-43.2231</v>
+        <v>-57.3265</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-3.829</v>
+        <v>-26.4091</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>-39.3941</v>
+        <v>-30.9174</v>
       </c>
       <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="n">
-        <v>15.4</v>
+        <v>9.68</v>
       </c>
       <c r="X41" s="4" t="n">
-        <v>406588</v>
+        <v>913576</v>
       </c>
       <c r="Y41" s="4" t="n">
-        <v>431235</v>
+        <v>1445359</v>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>187892</v>
+        <v>362189</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>35.167118</v>
+        <v>71.53293600000001</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>29.759216</v>
-      </c>
-      <c r="AD41" s="4" t="inlineStr"/>
+        <v>47.432396</v>
+      </c>
+      <c r="AD41" s="4" t="n">
+        <v>37.13</v>
+      </c>
       <c r="AE41" s="4" t="n">
-        <v>2.018</v>
+        <v>195.001</v>
       </c>
       <c r="AF41" s="4" t="n">
-        <v>22.9</v>
+        <v>80.5</v>
       </c>
       <c r="AG41" s="4" t="n">
-        <v>21.3</v>
+        <v>35.1</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>8.505991</v>
+        <v>28.28082</v>
       </c>
       <c r="AI41" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="AJ41" s="4" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AJ41" s="4" t="n">
+        <v>1.276</v>
+      </c>
       <c r="AK41" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/EICHERMOT/</t>
+          <t>https://www.screener.in/company/TITAN/</t>
         </is>
       </c>
       <c r="AL41" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>One97 Communications Limited</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>✅ Supertrend Buy</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1153.5</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>1132.16</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>1124.66</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1128.93</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>8.263</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>11.506</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>-3.243</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="X42" s="2" t="n">
+        <v>1415263</v>
+      </c>
+      <c r="Y42" s="2" t="n">
+        <v>3376447</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>73979</v>
+      </c>
+      <c r="AB42" s="2" t="n">
+        <v>135.31616</v>
+      </c>
+      <c r="AC42" s="2" t="n">
+        <v>36.530087</v>
+      </c>
+      <c r="AD42" s="2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="AF42" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="n">
+        <v>4.6229362</v>
+      </c>
+      <c r="AI42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="AK42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/PAYTM/</t>
+        </is>
+      </c>
+      <c r="AL42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PAYTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Axis Bank Limited</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Banks - Regional</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="n">
+        <v>1249.8</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>1270.86</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>1283.82</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>1248.48</v>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>-15.4628</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>-10.5176</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>-4.9452</v>
+      </c>
+      <c r="V43" s="4" t="inlineStr"/>
+      <c r="W43" s="4" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="X43" s="4" t="n">
+        <v>3562641</v>
+      </c>
+      <c r="Y43" s="4" t="n">
+        <v>7081996</v>
+      </c>
+      <c r="Z43" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA43" s="4" t="n">
+        <v>389727</v>
+      </c>
+      <c r="AB43" s="4" t="n">
+        <v>14.833709</v>
+      </c>
+      <c r="AC43" s="4" t="n">
+        <v>9.868505000000001</v>
+      </c>
+      <c r="AD43" s="4" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AE43" s="4" t="inlineStr"/>
+      <c r="AF43" s="4" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="AG43" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AH43" s="4" t="n">
+        <v>1.8108186</v>
+      </c>
+      <c r="AI43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ43" s="4" t="inlineStr"/>
+      <c r="AK43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/AXISBANK/</t>
+        </is>
+      </c>
+      <c r="AL43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISBANK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL41"/>
+  <autoFilter ref="A1:AL43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6265,7 +6531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6503,32 +6769,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Polycab India Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>68.2</v>
+        <v>71.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.2</v>
+        <v>18.8</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -6537,23 +6803,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9162.5</v>
+        <v>6893</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8656.33</v>
+        <v>6651.15</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8180.85</v>
+        <v>6444.25</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7454.82</v>
+        <v>6287.98</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -6566,83 +6832,79 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>98.59</v>
+        <v>97.92</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>71.12</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>377.019</v>
+        <v>170.0506</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>337.9656</v>
+        <v>156.7626</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>39.0534</v>
+        <v>13.2879</v>
       </c>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>36.86</v>
+        <v>39.66</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>337327</v>
+        <v>957736</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>491631</v>
+        <v>340695</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.81</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138491</v>
+        <v>182058</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.018776</v>
+        <v>73.69439</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.381287</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>24.58</v>
-      </c>
+        <v>58.663486</v>
+      </c>
+      <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="n">
-        <v>2.558</v>
+        <v>0.584</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>26.9</v>
+        <v>12.3</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.532714</v>
+        <v>11.804761</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ2" s="2" t="n">
-        <v>1.841</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POLYCAB/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -6652,17 +6914,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>64.8</v>
+        <v>68.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -6671,23 +6933,23 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1762.8</v>
+        <v>9199</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-1.39</v>
+        <v>0.4</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1697.95</v>
+        <v>8708.02</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1598.79</v>
+        <v>8220.77</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1474.12</v>
+        <v>7472.18</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -6700,103 +6962,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>96.65000000000001</v>
+        <v>98.98</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>63.75</v>
+        <v>71.77</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>68.4268</v>
+        <v>373.4664</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>69.70050000000001</v>
+        <v>345.0657</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-1.2737</v>
+        <v>28.4006</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>30.14</v>
+        <v>36.92</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>2274987</v>
+        <v>320359</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>3422075</v>
+        <v>484200</v>
       </c>
       <c r="Z3" s="4" t="n">
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>408400</v>
+        <v>138409</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.472754</v>
+        <v>52.05243</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.854727</v>
+        <v>37.358936</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>15.59</v>
+        <v>24.58</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>64.051</v>
+        <v>2.558</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.248282</v>
+        <v>11.525819</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>1.394</v>
+        <v>1.841</v>
       </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/POLYCAB/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>46</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -6805,23 +7067,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6912</v>
+        <v>838.45</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1.13</v>
+        <v>0.84</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>6625.7</v>
+        <v>813.83</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6425.93</v>
+        <v>789.47</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>6281.9</v>
+        <v>749.1799999999999</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -6834,96 +7096,100 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.19</v>
+        <v>98.78</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>69.31999999999999</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>169.8444</v>
+        <v>19.0654</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>153.4407</v>
+        <v>17.8518</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>16.4038</v>
+        <v>1.2136</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>40.15</v>
+        <v>37.95</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>322081</v>
+        <v>1973862</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>304930</v>
+        <v>1885384</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>182987</v>
+        <v>107791</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.87204</v>
+        <v>61.25552</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.962875</v>
-      </c>
-      <c r="AD4" s="2" t="inlineStr"/>
+        <v>44.081028</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>41.39</v>
+      </c>
       <c r="AE4" s="2" t="n">
-        <v>0.584</v>
+        <v>12.394</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>12.3</v>
+        <v>22.1</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>-1</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.865007</v>
+        <v>25.413969</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AJ4" s="2" t="n">
+        <v>1.31</v>
+      </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>19</v>
@@ -6939,19 +7205,19 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>831.45</v>
+        <v>8078.5</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.28</v>
+        <v>0.65</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>811.24</v>
+        <v>7904.66</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>787.47</v>
+        <v>7722.2</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>748.28</v>
+        <v>7443.91</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -6964,76 +7230,608 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>97.95999999999999</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>65.23999999999999</v>
+        <v>63.39</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>19.2999</v>
+        <v>126.6408</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>17.5484</v>
+        <v>117.3518</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>1.7515</v>
+        <v>9.289</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>37.74</v>
+        <v>24.38</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>1431476</v>
+        <v>492013</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1863164</v>
+        <v>377258</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>0.77</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108647</v>
+        <v>119463</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.878227</v>
+        <v>61.5855</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.430775</v>
+        <v>49.931694</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>41.39</v>
+        <v>21.5</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>12.394</v>
+        <v>85.146</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>22.1</v>
+        <v>18.9</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>14.5</v>
+        <v>35.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.615606</v>
+        <v>12.598754</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.31</v>
+        <v>1.065</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Manappuram Finance Limited</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Credit Services</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>319.15</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>302.02</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>279.51</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>9.4383</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>9.1919</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>4971139</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>4423393</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>30284</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>27.532022</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>10.978432</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>360.191</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="n">
+        <v>1.6814436</v>
+      </c>
+      <c r="AI6" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="AJ6" s="2" t="n">
+        <v>94.116</v>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/MANAPPURAM/</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Thermal Coal</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>2704.8</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>2504.92</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>2325.64</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>2279.15</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>96.48999999999999</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>140.0127</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>126.8855</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>13.1273</v>
+      </c>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="n">
+        <v>46.07</v>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>1187449</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>3060077</v>
+      </c>
+      <c r="Z7" s="4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>369826</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>36.66712</v>
+      </c>
+      <c r="AC7" s="4" t="n">
+        <v>47.58931</v>
+      </c>
+      <c r="AD7" s="4" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="AE7" s="4" t="n">
+        <v>119.56</v>
+      </c>
+      <c r="AF7" s="4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="n">
+        <v>4.3024473</v>
+      </c>
+      <c r="AI7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ7" s="4" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AK7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/ADANIENT/</t>
+        </is>
+      </c>
+      <c r="AL7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Adani Ports and Special Economic Zone Limited</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Marine Shipping</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1772.6</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>1705.06</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1605.6</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1477.09</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>66.0569</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>68.9718</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>-2.9149</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>1283223</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>3390298</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>413169</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>30.749315</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>23.12162</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>64.051</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AG8" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH8" s="2" t="n">
+        <v>4.2978926</v>
+      </c>
+      <c r="AI8" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ8" s="2" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Limited</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Electronic Components</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>1464.4</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>1240.68</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>1125.3</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>994.15</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>74.62</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>91.0787</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>74.7504</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>16.3283</v>
+      </c>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>5017988</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>862253</v>
+      </c>
+      <c r="Z9" s="4" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <v>9763</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>86.80522999999999</v>
+      </c>
+      <c r="AC9" s="4" t="n">
+        <v>44.69265</v>
+      </c>
+      <c r="AD9" s="4" t="inlineStr"/>
+      <c r="AE9" s="4" t="n">
+        <v>25.091</v>
+      </c>
+      <c r="AF9" s="4" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AG9" s="4" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>14.977766</v>
+      </c>
+      <c r="AI9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/AVALON/</t>
+        </is>
+      </c>
+      <c r="AL9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL5"/>
+  <autoFilter ref="A1:AL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7044,7 +7842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7282,32 +8080,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Polycab India Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>68.2</v>
+        <v>71.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.2</v>
+        <v>18.8</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -7316,23 +8114,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9162.5</v>
+        <v>6893</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8656.33</v>
+        <v>6651.15</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8180.85</v>
+        <v>6444.25</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7454.82</v>
+        <v>6287.98</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -7345,83 +8143,79 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>98.59</v>
+        <v>97.92</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>71.12</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>377.019</v>
+        <v>170.0506</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>337.9656</v>
+        <v>156.7626</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>39.0534</v>
+        <v>13.2879</v>
       </c>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>36.86</v>
+        <v>39.66</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>337327</v>
+        <v>957736</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>491631</v>
+        <v>340695</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.81</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>138491</v>
+        <v>182058</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>52.018776</v>
+        <v>73.69439</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>37.381287</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>24.58</v>
-      </c>
+        <v>58.663486</v>
+      </c>
+      <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="n">
-        <v>2.558</v>
+        <v>0.584</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>26.9</v>
+        <v>12.3</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.532714</v>
+        <v>11.804761</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ2" s="2" t="n">
-        <v>1.841</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POLYCAB/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -7431,17 +8225,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>64.8</v>
+        <v>68.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -7450,23 +8244,23 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1762.8</v>
+        <v>9199</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-1.39</v>
+        <v>0.4</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1697.95</v>
+        <v>8708.02</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1598.79</v>
+        <v>8220.77</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1474.12</v>
+        <v>7472.18</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -7479,103 +8273,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>96.65000000000001</v>
+        <v>98.98</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>63.75</v>
+        <v>71.77</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>68.4268</v>
+        <v>373.4664</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>69.70050000000001</v>
+        <v>345.0657</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-1.2737</v>
+        <v>28.4006</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>30.14</v>
+        <v>36.92</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>2274987</v>
+        <v>320359</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>3422075</v>
+        <v>484200</v>
       </c>
       <c r="Z3" s="4" t="n">
         <v>0.66</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>408400</v>
+        <v>138409</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>30.472754</v>
+        <v>52.05243</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>22.854727</v>
+        <v>37.358936</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>15.59</v>
+        <v>24.58</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>64.051</v>
+        <v>2.558</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>4.248282</v>
+        <v>11.525819</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>1.394</v>
+        <v>1.841</v>
       </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/POLYCAB/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>46</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -7584,23 +8378,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6912</v>
+        <v>838.45</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1.13</v>
+        <v>0.84</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>6625.7</v>
+        <v>813.83</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6425.93</v>
+        <v>789.47</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>6281.9</v>
+        <v>749.1799999999999</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -7613,96 +8407,100 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.19</v>
+        <v>98.78</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>69.31999999999999</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>169.8444</v>
+        <v>19.0654</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>153.4407</v>
+        <v>17.8518</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>16.4038</v>
+        <v>1.2136</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>40.15</v>
+        <v>37.95</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>322081</v>
+        <v>1973862</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>304930</v>
+        <v>1885384</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>182987</v>
+        <v>107791</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>73.87204</v>
+        <v>61.25552</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>58.962875</v>
-      </c>
-      <c r="AD4" s="2" t="inlineStr"/>
+        <v>44.081028</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>41.39</v>
+      </c>
       <c r="AE4" s="2" t="n">
-        <v>0.584</v>
+        <v>12.394</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>12.3</v>
+        <v>22.1</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>-1</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>11.865007</v>
+        <v>25.413969</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AJ4" s="2" t="n">
+        <v>1.31</v>
+      </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>19</v>
@@ -7718,19 +8516,19 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>831.45</v>
+        <v>8078.5</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.28</v>
+        <v>0.65</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>811.24</v>
+        <v>7904.66</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>787.47</v>
+        <v>7722.2</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>748.28</v>
+        <v>7443.91</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -7743,76 +8541,608 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>97.95999999999999</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>65.23999999999999</v>
+        <v>63.39</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>19.2999</v>
+        <v>126.6408</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>17.5484</v>
+        <v>117.3518</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>1.7515</v>
+        <v>9.289</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>37.74</v>
+        <v>24.38</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>1431476</v>
+        <v>492013</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1863164</v>
+        <v>377258</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>0.77</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>108647</v>
+        <v>119463</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.878227</v>
+        <v>61.5855</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>44.430775</v>
+        <v>49.931694</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>41.39</v>
+        <v>21.5</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>12.394</v>
+        <v>85.146</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>22.1</v>
+        <v>18.9</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>14.5</v>
+        <v>35.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>25.615606</v>
+        <v>12.598754</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.31</v>
+        <v>1.065</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Manappuram Finance Limited</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Credit Services</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>319.15</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>302.02</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>279.51</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>9.4383</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>9.1919</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>4971139</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>4423393</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>30284</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>27.532022</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>10.978432</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>360.191</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="n">
+        <v>1.6814436</v>
+      </c>
+      <c r="AI6" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="AJ6" s="2" t="n">
+        <v>94.116</v>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/MANAPPURAM/</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Thermal Coal</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>2704.8</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>2504.92</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>2325.64</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>2279.15</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>96.48999999999999</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>140.0127</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>126.8855</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>13.1273</v>
+      </c>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="n">
+        <v>46.07</v>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>1187449</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>3060077</v>
+      </c>
+      <c r="Z7" s="4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>369826</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>36.66712</v>
+      </c>
+      <c r="AC7" s="4" t="n">
+        <v>47.58931</v>
+      </c>
+      <c r="AD7" s="4" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="AE7" s="4" t="n">
+        <v>119.56</v>
+      </c>
+      <c r="AF7" s="4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="n">
+        <v>4.3024473</v>
+      </c>
+      <c r="AI7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ7" s="4" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AK7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/ADANIENT/</t>
+        </is>
+      </c>
+      <c r="AL7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Adani Ports and Special Economic Zone Limited</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Marine Shipping</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1772.6</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>1705.06</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1605.6</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1477.09</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>66.0569</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>68.9718</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>-2.9149</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>1283223</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>3390298</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>413169</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>30.749315</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>23.12162</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>64.051</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AG8" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH8" s="2" t="n">
+        <v>4.2978926</v>
+      </c>
+      <c r="AI8" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ8" s="2" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Limited</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Electronic Components</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>1464.4</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>1240.68</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>1125.3</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>994.15</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>74.62</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>91.0787</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>74.7504</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>16.3283</v>
+      </c>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>5017988</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>862253</v>
+      </c>
+      <c r="Z9" s="4" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <v>9763</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>86.80522999999999</v>
+      </c>
+      <c r="AC9" s="4" t="n">
+        <v>44.69265</v>
+      </c>
+      <c r="AD9" s="4" t="inlineStr"/>
+      <c r="AE9" s="4" t="n">
+        <v>25.091</v>
+      </c>
+      <c r="AF9" s="4" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AG9" s="4" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>14.977766</v>
+      </c>
+      <c r="AI9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/AVALON/</t>
+        </is>
+      </c>
+      <c r="AL9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL5"/>
+  <autoFilter ref="A1:AL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7837,7 +9167,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 20-May-2026 18:44 IST</t>
+          <t>Run Date: 21-May-2026 17:51 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -7865,7 +9195,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -7895,7 +9225,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -7905,7 +9235,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -7915,7 +9245,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -7941,7 +9271,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -7951,7 +9281,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68.2</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="15">
@@ -7961,7 +9291,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.5</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="16">
@@ -7983,51 +9313,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>68.2</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>64.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>62.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -14,7 +14,7 @@
     <sheet name="📈 Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📊 All Stocks'!$A$1:$AL$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📊 All Stocks'!$A$1:$AL$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏆 Grade A'!$A$1:$AL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Grade B Watch'!$A$1:$AL$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Watchlist'!$A$1:$AL$9</definedName>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL43"/>
+  <dimension ref="A1:AL44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="8" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
@@ -725,32 +725,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>71.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -759,23 +759,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6893</v>
+        <v>274.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.27</v>
+        <v>0.44</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>6651.15</v>
+        <v>268.53</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6444.25</v>
+        <v>262.9</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>6287.98</v>
+        <v>247.57</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -788,67 +788,75 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>97.92</v>
+        <v>96.11</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>67.93000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>170.0506</v>
+        <v>3.7145</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>156.7626</v>
+        <v>3.7075</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>13.2879</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr"/>
+        <v>0.007</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W2" s="2" t="n">
-        <v>39.66</v>
+        <v>21.42</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>957736</v>
+        <v>5838024</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>340695</v>
+        <v>3213435</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>2.81</v>
+        <v>1.82</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>182058</v>
+        <v>79391</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>73.69439</v>
+        <v>390.49298</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>58.663486</v>
-      </c>
-      <c r="AD2" s="2" t="inlineStr"/>
+        <v>104.479126</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>14.34</v>
+      </c>
       <c r="AE2" s="2" t="n">
-        <v>0.584</v>
+        <v>82.405</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>12.3</v>
+        <v>28.4</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>-1</v>
+        <v>290.2</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.804761</v>
+        <v>57.31859</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="2" t="n">
+        <v>1.156</v>
+      </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/NYKAA/</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
         </is>
       </c>
     </row>
@@ -893,19 +901,19 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9199</v>
+        <v>9193.5</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.06</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>8708.02</v>
+        <v>8754.25</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>8220.77</v>
+        <v>8258.92</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>7472.18</v>
+        <v>7500.27</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -918,41 +926,41 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>98.98</v>
+        <v>98.75</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>71.77</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>373.4664</v>
+        <v>365.9882</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>345.0657</v>
+        <v>349.2502</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>28.4006</v>
+        <v>16.738</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>36.92</v>
+        <v>37.17</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>320359</v>
+        <v>231631</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>484200</v>
+        <v>471656</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>138409</v>
+        <v>139462</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>52.05243</v>
+        <v>52.47847</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>37.358936</v>
+        <v>37.64339</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>24.58</v>
@@ -967,7 +975,7 @@
         <v>8</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.525819</v>
+        <v>11.613577</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>38</v>
@@ -989,29 +997,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>19</v>
@@ -1023,23 +1031,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>838.45</v>
+        <v>8308.5</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.84</v>
+        <v>2.85</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>813.83</v>
+        <v>7943.12</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>789.47</v>
+        <v>7745.19</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>749.1799999999999</v>
+        <v>7458.51</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1052,103 +1060,103 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.78</v>
+        <v>99.05</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>67.68000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>19.0654</v>
+        <v>143.2305</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>17.8518</v>
+        <v>122.5275</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.2136</v>
+        <v>20.703</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>37.95</v>
+        <v>24.91</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1973862</v>
+        <v>1425124</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>1885384</v>
+        <v>433308</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>1.05</v>
+        <v>3.29</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>107791</v>
+        <v>120240</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>61.25552</v>
+        <v>61.74777</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>44.081028</v>
+        <v>39.105675</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>41.39</v>
+        <v>21.5</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>12.394</v>
+        <v>85.146</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>22.1</v>
+        <v>18.1</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>14.5</v>
+        <v>35.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>25.413969</v>
+        <v>12.680638</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>1.31</v>
+        <v>1.065</v>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>JSW Steel Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1157,23 +1165,23 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>8078.5</v>
+        <v>1281.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.65</v>
+        <v>-0.15</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>7904.66</v>
+        <v>1269.12</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>7722.2</v>
+        <v>1241.54</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>7443.91</v>
+        <v>1173.14</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -1186,103 +1194,103 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>98.76000000000001</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>63.39</v>
+        <v>56.24</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>126.6408</v>
+        <v>15.561</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>117.3518</v>
+        <v>17.3691</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>9.289</v>
+        <v>-1.8081</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>24.38</v>
+        <v>17.96</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>492013</v>
+        <v>5339554</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>377258</v>
+        <v>1952278</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>1.3</v>
+        <v>2.74</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>119463</v>
+        <v>313743</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.5855</v>
+        <v>14.090759</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>49.931694</v>
+        <v>17.70393</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>21.5</v>
+        <v>27.26</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>85.146</v>
+        <v>94.155</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>18.9</v>
+        <v>14.2</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>35.6</v>
+        <v>991.8</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>12.598754</v>
+        <v>3.1359012</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.065</v>
+        <v>1.491</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/JSWSTEEL/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Manappuram Finance Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>62.4</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>46</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16.4</v>
+        <v>19</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -1291,23 +1299,23 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>319.15</v>
+        <v>831.85</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.22</v>
+        <v>-0.79</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>302.02</v>
+        <v>815.54</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>290.7</v>
+        <v>791.13</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>279.51</v>
+        <v>750.53</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1320,105 +1328,103 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>98.56</v>
+        <v>98</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>65.51000000000001</v>
+        <v>63.18</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>9.4383</v>
+        <v>18.1378</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>9.1919</v>
+        <v>17.909</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2465</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2288</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="n">
-        <v>24.87</v>
+        <v>38.41</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>4971139</v>
+        <v>1305803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>4423393</v>
+        <v>1841800</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>1.12</v>
+        <v>0.71</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>30284</v>
+        <v>106832</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>27.532022</v>
+        <v>60.800148</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>10.978432</v>
+        <v>43.688892</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>6.97</v>
+        <v>41.39</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>360.191</v>
+        <v>12.394</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AG6" s="2" t="inlineStr"/>
+        <v>22.1</v>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="AH6" s="2" t="n">
-        <v>1.6814436</v>
+        <v>25.187891</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>94.116</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MANAPPURAM/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>43</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1431,19 +1437,19 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2704.8</v>
+        <v>6858</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.74</v>
+        <v>-0.51</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2504.92</v>
+        <v>6670.85</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2325.64</v>
+        <v>6460.47</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2279.15</v>
+        <v>6300.69</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -1456,101 +1462,99 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>96.48999999999999</v>
+        <v>97.42</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>71.8</v>
+        <v>65.33</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>140.0127</v>
+        <v>165.4821</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>126.8855</v>
+        <v>158.5065</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>13.1273</v>
+        <v>6.9756</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>46.07</v>
+        <v>39.2</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1187449</v>
+        <v>151586</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3060077</v>
+        <v>336947</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>369826</v>
+        <v>182828</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>36.66712</v>
+        <v>73.83938999999999</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>47.58931</v>
-      </c>
-      <c r="AD7" s="4" t="n">
-        <v>13.66</v>
-      </c>
+        <v>58.911552</v>
+      </c>
+      <c r="AD7" s="4" t="inlineStr"/>
       <c r="AE7" s="4" t="n">
-        <v>119.56</v>
+        <v>0.584</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AG7" s="4" t="inlineStr"/>
+        <v>12.3</v>
+      </c>
+      <c r="AG7" s="4" t="n">
+        <v>-1</v>
+      </c>
       <c r="AH7" s="4" t="n">
-        <v>4.3024473</v>
+        <v>11.854679</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ7" s="4" t="n">
-        <v>1.035</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
       <c r="AK7" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIENT/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>60.8</v>
+        <v>61.6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>24.8</v>
+        <v>18.6</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1563,19 +1567,19 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1772.6</v>
+        <v>2697.6</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1705.06</v>
+        <v>2523.27</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1605.6</v>
+        <v>2340.23</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1477.09</v>
+        <v>2285.36</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -1588,103 +1592,101 @@
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>97.19</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>64.73</v>
+        <v>70.95</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>66.0569</v>
+        <v>138.106</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>68.9718</v>
+        <v>129.1296</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>-2.9149</v>
+        <v>8.9764</v>
       </c>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="2" t="n">
-        <v>29.85</v>
+        <v>46.9</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>1283223</v>
+        <v>1606690</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>3390298</v>
+        <v>2993011</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>413169</v>
+        <v>372527</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>30.749315</v>
+        <v>36.899784</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>23.12162</v>
+        <v>47.936844</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>15.59</v>
+        <v>13.66</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>64.051</v>
+        <v>119.56</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AG8" s="2" t="n">
-        <v>3.6</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="n">
-        <v>4.2978926</v>
+        <v>4.333867</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>1.394</v>
+        <v>1.035</v>
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/ADANIENT/</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>Manappuram Finance Limited</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>14.8</v>
+        <v>16.4</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -1693,23 +1695,23 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1464.4</v>
+        <v>322.4</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.94</v>
+        <v>1.02</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1240.68</v>
+        <v>303.96</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1125.3</v>
+        <v>291.94</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>994.15</v>
+        <v>280.07</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -1722,99 +1724,101 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>97.69</v>
+        <v>99.37</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>74.62</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>91.0787</v>
+        <v>9.903700000000001</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>74.7504</v>
+        <v>9.334199999999999</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>16.3283</v>
+        <v>0.5695</v>
       </c>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="n">
-        <v>34.25</v>
+        <v>24.79</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5017988</v>
+        <v>7531083</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>862253</v>
+        <v>4640929</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.82</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>9763</v>
+        <v>30444</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>86.80522999999999</v>
+        <v>27.700855</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>44.69265</v>
-      </c>
-      <c r="AD9" s="4" t="inlineStr"/>
+        <v>11.036321</v>
+      </c>
+      <c r="AD9" s="4" t="n">
+        <v>6.97</v>
+      </c>
       <c r="AE9" s="4" t="n">
-        <v>25.091</v>
+        <v>360.191</v>
       </c>
       <c r="AF9" s="4" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="AG9" s="4" t="n">
-        <v>35.8</v>
-      </c>
+        <v>109.3</v>
+      </c>
+      <c r="AG9" s="4" t="inlineStr"/>
       <c r="AH9" s="4" t="n">
-        <v>14.977766</v>
+        <v>1.6903098</v>
       </c>
       <c r="AI9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AJ9" s="4" t="n">
+        <v>94.116</v>
+      </c>
       <c r="AK9" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AVALON/</t>
+          <t>https://www.screener.in/company/MANAPPURAM/</t>
         </is>
       </c>
       <c r="AL9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Oil and Natural Gas Corporation Limited</t>
+          <t>Syrma SGS Technology Limited</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Integrated</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>57.8</v>
+        <v>58.4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15.8</v>
+        <v>18.4</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -1823,23 +1827,23 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>298.3</v>
+        <v>1024.65</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.61</v>
+        <v>2.06</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>292.13</v>
+        <v>1005.12</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>284.02</v>
+        <v>939.1900000000001</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>258.45</v>
+        <v>802.5599999999999</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1848,103 +1852,107 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>97.01000000000001</v>
+        <v>86.25</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>59.19</v>
+        <v>56.54</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>3.7839</v>
+        <v>26.4053</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>3.3865</v>
+        <v>39.2697</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.3973</v>
+        <v>-12.8644</v>
       </c>
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="2" t="n">
-        <v>26.94</v>
+        <v>36.43</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>12258794</v>
+        <v>1700509</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>17711670</v>
+        <v>1766545</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>372188</v>
+        <v>20011</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>9.780165999999999</v>
+        <v>61.434063</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>6.9865613</v>
-      </c>
-      <c r="AD10" s="2" t="inlineStr"/>
+        <v>36.52029</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>14.14</v>
+      </c>
       <c r="AE10" s="2" t="n">
-        <v>43.805</v>
+        <v>13.045</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.8</v>
+        <v>58.4</v>
       </c>
       <c r="AG10" s="2" t="n">
-        <v>16.2</v>
+        <v>43.7</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>1.0111454</v>
+        <v>6.8872356</v>
       </c>
       <c r="AI10" s="2" t="n">
-        <v>620</v>
-      </c>
-      <c r="AJ10" s="2" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AJ10" s="2" t="n">
+        <v>1.7</v>
+      </c>
       <c r="AK10" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ONGC/</t>
+          <t>https://www.screener.in/company/SYRMA/</t>
         </is>
       </c>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ONGC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SYRMA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>Oil and Natural Gas Corporation Limited</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Oil &amp; Gas Integrated</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>42</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1957,19 +1965,19 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1880.3</v>
+        <v>295.85</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.11</v>
+        <v>-0.82</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1826.61</v>
+        <v>292.49</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1780.34</v>
+        <v>284.49</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1725.36</v>
+        <v>258.97</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -1982,99 +1990,99 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>98.11</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>62.58</v>
+        <v>56.04</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>40.7646</v>
+        <v>3.6242</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>35.0392</v>
+        <v>3.434</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>5.7254</v>
+        <v>0.1902</v>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="n">
-        <v>28.25</v>
+        <v>26.84</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1376695</v>
+        <v>14084672</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5326466</v>
+        <v>17739652</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.26</v>
+        <v>0.79</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>453786</v>
+        <v>364828</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>41.567036</v>
+        <v>9.589947</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>33.42556</v>
+        <v>6.8484125</v>
       </c>
       <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="n">
-        <v>6.675</v>
+        <v>43.805</v>
       </c>
       <c r="AF11" s="4" t="n">
-        <v>13.5</v>
+        <v>0.8</v>
       </c>
       <c r="AG11" s="4" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>5.829034</v>
+        <v>0.99115145</v>
       </c>
       <c r="AI11" s="4" t="n">
-        <v>88</v>
+        <v>625</v>
       </c>
       <c r="AJ11" s="4" t="inlineStr"/>
       <c r="AK11" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/SUNPHARMA/</t>
+          <t>https://www.screener.in/company/ONGC/</t>
         </is>
       </c>
       <c r="AL11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ONGC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>JSW Steel Limited</t>
+          <t>Adani Ports and Special Economic Zone Limited</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Marine Shipping</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>27</v>
+        <v>24.8</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -2083,23 +2091,23 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1283.2</v>
+        <v>1793.3</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.16</v>
+        <v>1.17</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1267.84</v>
+        <v>1713.46</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1239.91</v>
+        <v>1612.96</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1172.08</v>
+        <v>1481.48</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2112,83 +2120,83 @@
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>97.66</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>56.86</v>
+        <v>66.78</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>16.4546</v>
+        <v>65.0986</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>17.8211</v>
+        <v>68.1972</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>-1.3665</v>
+        <v>-3.0985</v>
       </c>
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="n">
-        <v>18.79</v>
+        <v>29.96</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>1039407</v>
+        <v>1628329</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>1771059</v>
+        <v>3351371</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.59</v>
+        <v>0.49</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>312718</v>
+        <v>411694</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>14.043183</v>
+        <v>30.660604</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>17.770363</v>
+        <v>23.039103</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>27.26</v>
+        <v>15.59</v>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>94.155</v>
+        <v>64.051</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>14.2</v>
+        <v>26.5</v>
       </c>
       <c r="AG12" s="2" t="n">
-        <v>991.8</v>
+        <v>3.6</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>3.125656</v>
+        <v>4.282554</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ12" s="2" t="n">
-        <v>1.491</v>
+        <v>1.394</v>
       </c>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/JSWSTEEL/</t>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
         </is>
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2202,13 +2210,13 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>11.8</v>
+        <v>15</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -2221,19 +2229,19 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4429.2</v>
+        <v>1891.3</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4332.97</v>
+        <v>1832.77</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4250.44</v>
+        <v>1784.7</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3926.18</v>
+        <v>1727.92</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -2246,99 +2254,99 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>97.23999999999999</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>58.93</v>
+        <v>64</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>63.9767</v>
+        <v>40.7978</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>52.6177</v>
+        <v>36.1909</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>11.359</v>
+        <v>4.6069</v>
       </c>
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="n">
-        <v>24.37</v>
+        <v>28.89</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>331283</v>
+        <v>1605806</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>283560</v>
+        <v>5244498</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.17</v>
+        <v>0.31</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>151258</v>
+        <v>442581</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>66.387405</v>
+        <v>40.4695</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>69.008545</v>
+        <v>28.308376</v>
       </c>
       <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="n">
-        <v>33.4</v>
+        <v>6.675</v>
       </c>
       <c r="AF13" s="4" t="n">
-        <v>17.6</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" s="4" t="n">
-        <v>26.1</v>
+        <v>15.7</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>17.914995</v>
+        <v>5.685103</v>
       </c>
       <c r="AI13" s="4" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AJ13" s="4" t="inlineStr"/>
       <c r="AK13" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TORNTPHARM/</t>
+          <t>https://www.screener.in/company/SUNPHARMA/</t>
         </is>
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CESC Limited</t>
+          <t>Avalon Technologies Limited</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>56.4</v>
+        <v>54.4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -2347,23 +2355,23 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>180.65</v>
+        <v>1461.8</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>180.35</v>
+        <v>1261.74</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>172.9</v>
+        <v>1138.5</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>164.32</v>
+        <v>1000.81</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -2376,103 +2384,103 @@
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>88.34</v>
+        <v>96.66</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>52.74</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>2.7822</v>
+        <v>97.3484</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>4.5618</v>
+        <v>79.27</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>-1.7797</v>
+        <v>18.0784</v>
       </c>
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="n">
-        <v>34.61</v>
+        <v>35.79</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>1561563</v>
+        <v>695194</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>4730283</v>
+        <v>890863</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.33</v>
+        <v>0.78</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>23839</v>
+        <v>9838</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>15.463456</v>
+        <v>87.62642</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>12.542114</v>
+        <v>45.035072</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>12.55</v>
+        <v>16.94</v>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>164.311</v>
+        <v>29.503</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="AG14" s="2" t="n">
-        <v>17.8</v>
+        <v>69</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>1.8732358</v>
+        <v>15.092523</v>
       </c>
       <c r="AI14" s="2" t="n">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="2" t="n">
-        <v>0.921</v>
+        <v>2.052</v>
       </c>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CESC/</t>
+          <t>https://www.screener.in/company/AVALON/</t>
         </is>
       </c>
       <c r="AL14" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Limited</t>
+          <t>Torrent Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>55.4</v>
+        <v>53.8</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>18.4</v>
+        <v>11.8</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -2481,23 +2489,23 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1004</v>
+        <v>4469.2</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.02</v>
+        <v>0.9</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1003.06</v>
+        <v>4345.95</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>935.7</v>
+        <v>4259.02</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>800.17</v>
+        <v>3932.97</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -2506,87 +2514,83 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>84.51000000000001</v>
+        <v>98.11</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>53.29</v>
+        <v>61.21</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>27.7853</v>
+        <v>66.76430000000001</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>42.4858</v>
+        <v>55.447</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-14.7005</v>
+        <v>11.3172</v>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="n">
-        <v>37</v>
+        <v>24.61</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1282108</v>
+        <v>245755</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1728475</v>
+        <v>271204</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.74</v>
+        <v>0.91</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>19737</v>
+        <v>151833</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>60.380085</v>
+        <v>66.91826</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>36.0211</v>
-      </c>
-      <c r="AD15" s="4" t="n">
-        <v>14.14</v>
-      </c>
+        <v>69.271034</v>
+      </c>
+      <c r="AD15" s="4" t="inlineStr"/>
       <c r="AE15" s="4" t="n">
-        <v>13.045</v>
+        <v>33.4</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>58.4</v>
+        <v>17.6</v>
       </c>
       <c r="AG15" s="4" t="n">
-        <v>43.7</v>
+        <v>26.1</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>6.7930946</v>
+        <v>17.98314</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ15" s="4" t="n">
-        <v>1.7</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr"/>
       <c r="AK15" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/SYRMA/</t>
+          <t>https://www.screener.in/company/TORNTPHARM/</t>
         </is>
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SYRMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Bandhan Bank Limited</t>
+          <t>RBL Bank Limited</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2600,13 +2604,13 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>54.4</v>
+        <v>53.2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>21.4</v>
+        <v>26.2</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -2619,19 +2623,19 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>192.15</v>
+        <v>328.75</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.49</v>
+        <v>0.08</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>192.11</v>
+        <v>328.72</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>181.54</v>
+        <v>321.71</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>166.68</v>
+        <v>295.13</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2644,67 +2648,65 @@
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>90.36</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>53.42</v>
+        <v>51.31</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>5.0801</v>
+        <v>2.9374</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>7.3642</v>
+        <v>4.648</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>-2.2841</v>
+        <v>-1.7106</v>
       </c>
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="2" t="n">
-        <v>26.18</v>
+        <v>18.76</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>6147752</v>
+        <v>2458845</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>17643695</v>
+        <v>6409024</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>30783</v>
+        <v>20686</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>25.17523</v>
+        <v>23.712767</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>8.836698999999999</v>
-      </c>
-      <c r="AD16" s="2" t="n">
-        <v>4.88</v>
-      </c>
+        <v>17.617908</v>
+      </c>
+      <c r="AD16" s="2" t="inlineStr"/>
       <c r="AE16" s="2" t="inlineStr"/>
       <c r="AF16" s="2" t="n">
-        <v>119.3</v>
+        <v>40.8</v>
       </c>
       <c r="AG16" s="2" t="n">
-        <v>68</v>
+        <v>367.9</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>1.2020332</v>
+        <v>1.2357199</v>
       </c>
       <c r="AI16" s="2" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="AJ16" s="2" t="inlineStr"/>
       <c r="AK16" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BANDHANBNK/</t>
+          <t>https://www.screener.in/company/RBLBANK/</t>
         </is>
       </c>
       <c r="AL16" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BANDHANBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
@@ -2749,19 +2751,19 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>487.45</v>
+        <v>490.15</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>432.58</v>
+        <v>438.07</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>399.55</v>
+        <v>403.11</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>354.11</v>
+        <v>355.97</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
@@ -2774,41 +2776,41 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>97.73</v>
+        <v>98.28</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>80.19</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>25.6006</v>
+        <v>26.9822</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>19.5086</v>
+        <v>21.0034</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.0919</v>
+        <v>5.9789</v>
       </c>
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="n">
-        <v>43.12</v>
+        <v>45.03</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1124399</v>
+        <v>958244</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1468702</v>
+        <v>1503564</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>12848</v>
+        <v>12591</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>31.041798</v>
+        <v>30.440432</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>18.403631</v>
+        <v>18.035673</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>10.66</v>
@@ -2823,7 +2825,7 @@
         <v>5.9</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>3.3435886</v>
+        <v>3.109766</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>77</v>
@@ -2883,19 +2885,19 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>753.35</v>
+        <v>739</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-3.03</v>
+        <v>-1.9</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>714.4</v>
+        <v>716.74</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>599.1</v>
+        <v>604.59</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>497.02</v>
+        <v>498.97</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -2908,39 +2910,39 @@
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>84.84</v>
+        <v>83.22</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>59.84</v>
+        <v>57.69</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>79.0943</v>
+        <v>71.4462</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>84.4734</v>
+        <v>81.86799999999999</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>-5.3791</v>
+        <v>-10.4218</v>
       </c>
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="n">
-        <v>44.42</v>
+        <v>42.56</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>370201</v>
+        <v>276663</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>2866456</v>
+        <v>2822101</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>3206</v>
+        <v>3367</v>
       </c>
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="n">
-        <v>26.487455</v>
+        <v>27.811829</v>
       </c>
       <c r="AD18" s="2" t="n">
         <v>-2.82</v>
@@ -2953,7 +2955,7 @@
       </c>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="n">
-        <v>5.394279</v>
+        <v>5.663993</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>0</v>
@@ -2975,32 +2977,32 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Nestlé India Limited</t>
+          <t>CESC Limited</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Packaged Foods</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>32</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -3009,23 +3011,23 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1420.1</v>
+        <v>179.84</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.79</v>
+        <v>-0.45</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1425.52</v>
+        <v>180.31</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1363.54</v>
+        <v>173.17</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1271.62</v>
+        <v>164.53</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -3038,103 +3040,103 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>94.79000000000001</v>
+        <v>87.94</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>54.17</v>
+        <v>51.7</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>31.5502</v>
+        <v>2.4421</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>44.779</v>
+        <v>4.1379</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-13.2288</v>
+        <v>-1.6958</v>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="n">
-        <v>46.76</v>
+        <v>33.68</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1425216</v>
+        <v>1821751</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2082086</v>
+        <v>4697031</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.68</v>
+        <v>0.39</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>271217</v>
+        <v>23492</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>77.365234</v>
+        <v>15.225085</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>59.37287</v>
+        <v>12.359395</v>
       </c>
       <c r="AD19" s="4" t="n">
-        <v>76.34</v>
+        <v>12.55</v>
       </c>
       <c r="AE19" s="4" t="n">
-        <v>8.613</v>
+        <v>164.311</v>
       </c>
       <c r="AF19" s="4" t="n">
-        <v>23.8</v>
+        <v>5.6</v>
       </c>
       <c r="AG19" s="4" t="n">
-        <v>27.4</v>
+        <v>17.8</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>52.5932</v>
+        <v>1.8459456</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>85</v>
+        <v>334</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.964</v>
+        <v>0.921</v>
       </c>
       <c r="AK19" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NESTLEIND/</t>
+          <t>https://www.screener.in/company/CESC/</t>
         </is>
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Limited</t>
+          <t>Nestlé India Limited</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Packaged Foods</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14.8</v>
+        <v>19</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -3143,23 +3145,23 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>273.3</v>
+        <v>1406.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.68</v>
+        <v>-0.96</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>267.9</v>
+        <v>1423.71</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>262.43</v>
+        <v>1365.22</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>247.29</v>
+        <v>1272.27</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -3172,79 +3174,83 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>95.69</v>
+        <v>93.89</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>58.63</v>
+        <v>49.69</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>3.6262</v>
+        <v>26.4144</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>3.7057</v>
+        <v>41.1061</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>-0.0795</v>
+        <v>-14.6917</v>
       </c>
       <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="n">
-        <v>22.02</v>
+        <v>44.17</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>2354029</v>
+        <v>2049251</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>3091447</v>
+        <v>2036392</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>78603</v>
+        <v>274418</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>560.20404</v>
+        <v>78.450935</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>108.05895</v>
-      </c>
-      <c r="AD20" s="2" t="inlineStr"/>
+        <v>60.073612</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>76.34</v>
+      </c>
       <c r="AE20" s="2" t="n">
-        <v>97.748</v>
+        <v>8.613</v>
       </c>
       <c r="AF20" s="2" t="n">
-        <v>26.7</v>
+        <v>23.8</v>
       </c>
       <c r="AG20" s="2" t="n">
-        <v>144.4</v>
+        <v>27.4</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>56.750053</v>
+        <v>53.213924</v>
       </c>
       <c r="AI20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="2" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="AJ20" s="2" t="n">
+        <v>0.964</v>
+      </c>
       <c r="AK20" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NYKAA/</t>
+          <t>https://www.screener.in/company/NESTLEIND/</t>
         </is>
       </c>
       <c r="AL20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>The Federal Bank Limited</t>
+          <t>Bandhan Bank Limited</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3258,13 +3264,13 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>50.6</v>
+        <v>49.4</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>23.6</v>
+        <v>21.4</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -3273,23 +3279,23 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>289.9</v>
+        <v>191.08</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.15</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>287.08</v>
+        <v>192.01</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>284.04</v>
+        <v>181.91</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>257.26</v>
+        <v>167.05</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
@@ -3302,99 +3308,99 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>95.98999999999999</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>54.11</v>
+        <v>52.13</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.2916</v>
+        <v>4.4157</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.1752</v>
+        <v>6.7745</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-2.3588</v>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="n">
-        <v>13.84</v>
+        <v>24.67</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>6657728</v>
+        <v>7549122</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>8014234</v>
+        <v>17529679</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>69918</v>
+        <v>31352</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>16.232838</v>
+        <v>25.640316</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>11.9424305</v>
+        <v>9.035591</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>11.73</v>
+        <v>4.88</v>
       </c>
       <c r="AE21" s="4" t="inlineStr"/>
       <c r="AF21" s="4" t="n">
-        <v>12.3</v>
+        <v>119.3</v>
       </c>
       <c r="AG21" s="4" t="n">
-        <v>22.2</v>
+        <v>68</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>1.9210589</v>
+        <v>1.2242395</v>
       </c>
       <c r="AI21" s="4" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="AJ21" s="4" t="inlineStr"/>
       <c r="AK21" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/FEDERALBNK/</t>
+          <t>https://www.screener.in/company/BANDHANBNK/</t>
         </is>
       </c>
       <c r="AL21" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BANDHANBNK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Berger Paints India Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>50.1</v>
+        <v>49</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>35.5</v>
+        <v>22</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>14.6</v>
+        <v>27</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -3403,27 +3409,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>508.45</v>
+        <v>460.2</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>494.15</v>
+        <v>460.59</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>476.34</v>
+        <v>452.99</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>496.39</v>
+        <v>416.93</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3432,103 +3438,103 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>84.61</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>58.74</v>
+        <v>50.78</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>16.7937</v>
+        <v>1.6205</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>15.3462</v>
+        <v>3.2312</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>1.4475</v>
+        <v>-1.6108</v>
       </c>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="n">
-        <v>32</v>
+        <v>14.42</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>200794</v>
+        <v>7425043</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>960359</v>
+        <v>10937365</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.21</v>
+        <v>0.68</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>58224</v>
+        <v>281359</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>51.692547</v>
+        <v>9.051348000000001</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>39.322056</v>
+        <v>7.983393</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>17.23</v>
+        <v>28.12</v>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>9.164999999999999</v>
+        <v>11.629</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>6.1</v>
+        <v>16.2</v>
       </c>
       <c r="AG22" s="2" t="n">
-        <v>27.7</v>
+        <v>12.9</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>8.421737</v>
+        <v>2.362117</v>
       </c>
       <c r="AI22" s="2" t="n">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="AJ22" s="2" t="n">
-        <v>2.115</v>
+        <v>1.856</v>
       </c>
       <c r="AK22" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BERGEPAINT/</t>
+          <t>https://www.screener.in/company/COALINDIA/</t>
         </is>
       </c>
       <c r="AL22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>RBL Bank Limited</t>
+          <t>HFCL Limited</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>48.2</v>
+        <v>47</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>26.2</v>
+        <v>10</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -3541,19 +3547,19 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>328.5</v>
+        <v>141.75</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>328.72</v>
+        <v>131.4</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>321.42</v>
+        <v>109.27</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>295.09</v>
+        <v>85</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -3566,94 +3572,98 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>93.88</v>
+        <v>91.27</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>51.15</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.3076</v>
+        <v>13.2906</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>5.0757</v>
+        <v>15.0023</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.768</v>
+        <v>-1.7117</v>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="n">
-        <v>19.89</v>
+        <v>58.8</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3142131</v>
+        <v>40951694</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>6437985</v>
+        <v>82063174</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>20340</v>
+        <v>22680</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>23.33215</v>
+        <v>423.45718</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>17.322826</v>
-      </c>
-      <c r="AD23" s="4" t="inlineStr"/>
-      <c r="AE23" s="4" t="inlineStr"/>
+        <v>28.501925</v>
+      </c>
+      <c r="AD23" s="4" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AE23" s="4" t="n">
+        <v>38.321</v>
+      </c>
       <c r="AF23" s="4" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="AG23" s="4" t="n">
-        <v>367.9</v>
-      </c>
+        <v>127.8</v>
+      </c>
+      <c r="AG23" s="4" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>1.2150229</v>
+        <v>4.4704857</v>
       </c>
       <c r="AI23" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="AJ23" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AJ23" s="4" t="n">
+        <v>1.991</v>
+      </c>
       <c r="AK23" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/RBLBANK/</t>
+          <t>https://www.screener.in/company/HFCL/</t>
         </is>
       </c>
       <c r="AL23" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>HFCL Limited</t>
+          <t>Dr. Reddy's Laboratories Limited</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>10</v>
@@ -3665,23 +3675,23 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>139.34</v>
+        <v>1318.5</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.85</v>
+        <v>-0.26</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>130.31</v>
+        <v>1302.17</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>107.94</v>
+        <v>1284.73</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>84.37</v>
+        <v>1257.4</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -3694,81 +3704,83 @@
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>89.72</v>
+        <v>95.83</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>65.86</v>
+        <v>55.2</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>14.0758</v>
+        <v>13.5186</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>15.4303</v>
+        <v>11.7532</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>-1.3545</v>
+        <v>1.7654</v>
       </c>
       <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="2" t="n">
-        <v>60.32</v>
+        <v>14.81</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>27652548</v>
+        <v>2183121</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>81313582</v>
+        <v>2637262</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.34</v>
+        <v>0.83</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>21691</v>
+        <v>108837</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>393.74997</v>
+        <v>25.951956</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>27.259617</v>
+        <v>20.26368</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>7.27</v>
+        <v>11.83</v>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>38.321</v>
+        <v>20.328</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>127.8</v>
-      </c>
-      <c r="AG24" s="2" t="inlineStr"/>
+        <v>-11.6</v>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>-86.2</v>
+      </c>
       <c r="AH24" s="2" t="n">
-        <v>4.275631</v>
+        <v>2.8903089</v>
       </c>
       <c r="AI24" s="2" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="AJ24" s="2" t="n">
-        <v>1.991</v>
+        <v>1.802</v>
       </c>
       <c r="AK24" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/HFCL/</t>
+          <t>https://www.screener.in/company/DRREDDY/</t>
         </is>
       </c>
       <c r="AL24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Limited</t>
+          <t>Cipla Limited</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -3782,13 +3794,13 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>32</v>
+        <v>35.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>14.2</v>
+        <v>10</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -3797,27 +3809,27 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1517.5</v>
+        <v>1401.9</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1461.35</v>
+        <v>1354.77</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1386.23</v>
+        <v>1325.86</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1246.57</v>
+        <v>1393.85</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -3826,79 +3838,83 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>72.68000000000001</v>
+        <v>62.62</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>42.8906</v>
+        <v>35.851</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>41.5516</v>
+        <v>30.0294</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.339</v>
+        <v>5.8216</v>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="n">
-        <v>28.27</v>
+        <v>37.25</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1068558</v>
+        <v>1145360</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1210257</v>
+        <v>2064837</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.88</v>
+        <v>0.55</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>88994</v>
+        <v>113027</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>25.739723</v>
+        <v>29.186483</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>20.209826</v>
-      </c>
-      <c r="AD25" s="4" t="inlineStr"/>
+        <v>22.172165</v>
+      </c>
+      <c r="AD25" s="4" t="n">
+        <v>11.74</v>
+      </c>
       <c r="AE25" s="4" t="n">
-        <v>22.248</v>
+        <v>1.778</v>
       </c>
       <c r="AF25" s="4" t="n">
-        <v>8.4</v>
+        <v>-3.8</v>
       </c>
       <c r="AG25" s="4" t="n">
-        <v>7.6</v>
+        <v>-54.6</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>2.563329</v>
+        <v>3.4333582</v>
       </c>
       <c r="AI25" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ25" s="4" t="inlineStr"/>
+        <v>93</v>
+      </c>
+      <c r="AJ25" s="4" t="n">
+        <v>3.443</v>
+      </c>
       <c r="AK25" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AUROPHARMA/</t>
+          <t>https://www.screener.in/company/CIPLA/</t>
         </is>
       </c>
       <c r="AL25" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CIPLA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Limited</t>
+          <t>Aurobindo Pharma Limited</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3912,13 +3928,13 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -3931,19 +3947,19 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1321.9</v>
+        <v>1546.7</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-1</v>
+        <v>1.92</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1300.45</v>
+        <v>1469.48</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1283.35</v>
+        <v>1392.53</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1256.92</v>
+        <v>1251</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -3956,128 +3972,128 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>96.08</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>56.03</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>13.8033</v>
+        <v>44.5043</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>11.3119</v>
+        <v>42.1421</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>2.4914</v>
+        <v>2.3621</v>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="2" t="n">
-        <v>15.87</v>
+        <v>29.33</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>1277182</v>
+        <v>1013775</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>3348492</v>
+        <v>1149031</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.38</v>
+        <v>0.88</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>109778</v>
+        <v>84207</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>26.181494</v>
+        <v>24.262268</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>20.576008</v>
+        <v>16.824411</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>11.83</v>
+        <v>9.93</v>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>20.328</v>
+        <v>21.31</v>
       </c>
       <c r="AF26" s="2" t="n">
-        <v>-11.6</v>
+        <v>7</v>
       </c>
       <c r="AG26" s="2" t="n">
-        <v>-86.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>2.915294</v>
+        <v>2.4254427</v>
       </c>
       <c r="AI26" s="2" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="AJ26" s="2" t="n">
-        <v>1.802</v>
+        <v>1.813</v>
       </c>
       <c r="AK26" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DRREDDY/</t>
+          <t>https://www.screener.in/company/AUROPHARMA/</t>
         </is>
       </c>
       <c r="AL26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DRREDDY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Cipla Limited</t>
+          <t>Pidilite Industries Limited</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>45.5</v>
+          <t>Specialty Chemicals</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>44.5</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>35.5</v>
+        <v>25.5</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>19</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>✅ Supertrend Buy | 💎 High ROE</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1399.5</v>
+        <v>1472.8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.73</v>
+        <v>1.18</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1349.81</v>
+        <v>1432.59</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1322.76</v>
+        <v>1413.23</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1393.28</v>
+        <v>1441.19</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -4090,128 +4106,128 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>83.65000000000001</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>62.28</v>
+        <v>60.88</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>36.3121</v>
+        <v>23.8957</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>28.574</v>
+        <v>21.1728</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>7.7381</v>
+        <v>2.7229</v>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="n">
-        <v>37.68</v>
+        <v>18.65</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1316586</v>
+        <v>465411</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2271270</v>
+        <v>1074352</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>113246</v>
+        <v>150468</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>29.206251</v>
+        <v>61.574345</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>22.21495</v>
+        <v>48.76969</v>
       </c>
       <c r="AD27" s="4" t="n">
-        <v>11.74</v>
+        <v>23.52</v>
       </c>
       <c r="AE27" s="4" t="n">
-        <v>1.778</v>
+        <v>3.776</v>
       </c>
       <c r="AF27" s="4" t="n">
-        <v>-3.8</v>
+        <v>14.1</v>
       </c>
       <c r="AG27" s="4" t="n">
-        <v>-54.6</v>
+        <v>37</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>3.4399836</v>
+        <v>15.753133</v>
       </c>
       <c r="AI27" s="4" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>3.443</v>
+        <v>2.38</v>
       </c>
       <c r="AK27" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CIPLA/</t>
+          <t>https://www.screener.in/company/PIDILITIND/</t>
         </is>
       </c>
       <c r="AL27" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CIPLA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>45</v>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>43.4</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>28.4</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>458.7</v>
+        <v>3056.6</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.38</v>
+        <v>1.71</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>460.64</v>
+        <v>3132.01</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>452.7</v>
+        <v>3125.18</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>416.51</v>
+        <v>3021.85</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -4220,87 +4236,87 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>93.37</v>
+        <v>79.13</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>49.61</v>
+        <v>42.25</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>1.842</v>
+        <v>-52.7758</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>3.6339</v>
+        <v>-26.0231</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>-1.792</v>
+        <v>-26.7528</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
       <c r="W28" s="2" t="n">
-        <v>15.07</v>
+        <v>17.78</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>3756072</v>
+        <v>949176</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>11015577</v>
+        <v>1492341</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>283609</v>
+        <v>86223</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>9.120094999999999</v>
+        <v>26.43298</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>8.047218000000001</v>
+        <v>17.278694</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>28.12</v>
+        <v>31.57</v>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>11.629</v>
+        <v>21.402</v>
       </c>
       <c r="AF28" s="2" t="n">
-        <v>16.2</v>
+        <v>111.8</v>
       </c>
       <c r="AG28" s="2" t="n">
-        <v>12.9</v>
+        <v>71.2</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>2.3810017</v>
+        <v>5.9687614</v>
       </c>
       <c r="AI28" s="2" t="n">
-        <v>480</v>
+        <v>13</v>
       </c>
       <c r="AJ28" s="2" t="n">
-        <v>1.856</v>
+        <v>1.383</v>
       </c>
       <c r="AK28" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/COALINDIA/</t>
+          <t>https://www.screener.in/company/WAAREEENER/</t>
         </is>
       </c>
       <c r="AL28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:COALINDIA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:WAAREEENER</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Pidilite Industries Limited</t>
+          <t>Asian Paints Limited</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -4314,13 +4330,13 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>44.5</v>
+        <v>42.3</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>25.5</v>
+        <v>34.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
@@ -4329,23 +4345,23 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 💎 High ROE</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1455.6</v>
+        <v>2598.8</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1428.36</v>
+        <v>2538.64</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1410.79</v>
+        <v>2471.54</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1440.14</v>
+        <v>2479.35</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -4358,103 +4374,99 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>92.42</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>57.93</v>
+        <v>61.73</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>23.2985</v>
+        <v>57.3423</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>20.492</v>
+        <v>57.0371</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.8065</v>
+        <v>0.3052</v>
       </c>
       <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="n">
-        <v>18.81</v>
+        <v>27.67</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>356329</v>
+        <v>1031843</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1067046</v>
+        <v>950823</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.33</v>
+        <v>1.09</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>149898</v>
+        <v>253063</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>61.31557</v>
+        <v>65.96202</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>48.584957</v>
-      </c>
-      <c r="AD29" s="4" t="n">
-        <v>23.52</v>
-      </c>
+        <v>52.78058</v>
+      </c>
+      <c r="AD29" s="4" t="inlineStr"/>
       <c r="AE29" s="4" t="n">
-        <v>3.776</v>
+        <v>17.609</v>
       </c>
       <c r="AF29" s="4" t="n">
-        <v>14.1</v>
+        <v>3.7</v>
       </c>
       <c r="AG29" s="4" t="n">
-        <v>37</v>
+        <v>-4.6</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>15.693462</v>
+        <v>12.918666</v>
       </c>
       <c r="AI29" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="AJ29" s="4" t="n">
-        <v>2.38</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr"/>
       <c r="AK29" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/PIDILITIND/</t>
+          <t>https://www.screener.in/company/ASIANPAINT/</t>
         </is>
       </c>
       <c r="AL29" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tata Steel Limited</t>
+          <t>The Federal Bank Limited</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>44</v>
+        <v>41.6</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>17</v>
+        <v>23.6</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -4463,23 +4475,23 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>207.01</v>
+        <v>283.75</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-1.09</v>
+        <v>-2.12</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>211.96</v>
+        <v>286.77</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>207.01</v>
+        <v>284.03</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>187.4</v>
+        <v>257.5</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -4488,107 +4500,103 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>92.25</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>44.36</v>
+        <v>46.94</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>1.5088</v>
+        <v>0.0133</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>2.7938</v>
+        <v>0.9428</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>-1.285</v>
+        <v>-0.9295</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="n">
-        <v>20.34</v>
+        <v>13.3</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>56670462</v>
+        <v>6916472</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>29825933</v>
+        <v>8177205</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>1.9</v>
+        <v>0.85</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>260138</v>
+        <v>70768</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>28.378231</v>
+        <v>16.430206</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>11.094682</v>
+        <v>12.087634</v>
       </c>
       <c r="AD30" s="2" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="AE30" s="2" t="n">
-        <v>89.01600000000001</v>
-      </c>
+        <v>11.73</v>
+      </c>
+      <c r="AE30" s="2" t="inlineStr"/>
       <c r="AF30" s="2" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="AG30" s="2" t="n">
-        <v>125.4</v>
+        <v>22.2</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>2.7365162</v>
+        <v>1.767983</v>
       </c>
       <c r="AI30" s="2" t="n">
-        <v>193</v>
-      </c>
-      <c r="AJ30" s="2" t="n">
-        <v>0.748</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr"/>
       <c r="AK30" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TATASTEEL/</t>
+          <t>https://www.screener.in/company/FEDERALBNK/</t>
         </is>
       </c>
       <c r="AL30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Limited</t>
+          <t>Berger Paints India Limited</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>39.8</v>
+        <v>41.1</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>18</v>
+        <v>26.5</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>21.8</v>
+        <v>14.6</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -4597,27 +4605,27 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3910.7</v>
+        <v>499.35</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.26</v>
+        <v>-1.79</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3950.06</v>
+        <v>494.65</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3937.47</v>
+        <v>477.24</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3857.6</v>
+        <v>497.11</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -4626,103 +4634,103 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>88.08</v>
+        <v>83.09</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>46.81</v>
+        <v>54.68</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-5.15</v>
+        <v>15.1241</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>12.649</v>
+        <v>15.3018</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-17.7991</v>
+        <v>-0.1777</v>
       </c>
       <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="n">
-        <v>11.01</v>
+        <v>31.78</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1972259</v>
+        <v>440704</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2534946</v>
+        <v>976222</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.78</v>
+        <v>0.45</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>540431</v>
+        <v>58434</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>33.597023</v>
+        <v>51.98651</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>21.368074</v>
+        <v>39.4638</v>
       </c>
       <c r="AD31" s="4" t="n">
-        <v>16.95</v>
+        <v>17.23</v>
       </c>
       <c r="AE31" s="4" t="n">
-        <v>97.64</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="AF31" s="4" t="n">
-        <v>11.7</v>
+        <v>6.1</v>
       </c>
       <c r="AG31" s="4" t="n">
-        <v>-34.5</v>
+        <v>27.7</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>4.944806</v>
+        <v>8.452094000000001</v>
       </c>
       <c r="AI31" s="4" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>1.251</v>
+        <v>2.115</v>
       </c>
       <c r="AK31" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/LT/</t>
+          <t>https://www.screener.in/company/BERGEPAINT/</t>
         </is>
       </c>
       <c r="AL31" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Limited</t>
+          <t>Amber Enterprises India Limited</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Discount Stores</t>
+          <t>Furnishings, Fixtures &amp; Appliances</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>39.4</v>
+        <v>41</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>15.4</v>
+        <v>7</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -4731,23 +4739,23 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack | 📊 High Volume</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4144.2</v>
+        <v>7537</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-2.17</v>
+        <v>6.92</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4350.8</v>
+        <v>7842.48</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4268.49</v>
+        <v>7620.45</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>4125.32</v>
+        <v>7273</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -4760,103 +4768,103 @@
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>83.73</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>35.17</v>
+        <v>45.69</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>-20.8476</v>
+        <v>-19.7644</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>22.6102</v>
+        <v>156.9902</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>-43.4579</v>
+        <v>-176.7546</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="2" t="n">
-        <v>24.28</v>
+        <v>25.53</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>346215</v>
+        <v>1293057</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>342934</v>
+        <v>497897</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>269813</v>
+        <v>25918</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>90.74798</v>
+        <v>145.72278</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>58.345993</v>
+        <v>38.715847</v>
       </c>
       <c r="AD32" s="2" t="n">
-        <v>12.94</v>
+        <v>5.58</v>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>9.913</v>
+        <v>46.566</v>
       </c>
       <c r="AF32" s="2" t="n">
-        <v>18.9</v>
+        <v>10.5</v>
       </c>
       <c r="AG32" s="2" t="n">
-        <v>19.6</v>
+        <v>11</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>11.004714</v>
+        <v>5.9238043</v>
       </c>
       <c r="AI32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" s="2" t="n">
-        <v>1.977</v>
+        <v>1.131</v>
       </c>
       <c r="AK32" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DMART/</t>
+          <t>https://www.screener.in/company/AMBER/</t>
         </is>
       </c>
       <c r="AL32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DMART</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AMBER</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Asian Paints Limited</t>
+          <t>Power Grid Corporation of India Limited</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>39.3</v>
+        <v>40.4</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>31.5</v>
+        <v>24</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.8</v>
+        <v>16.4</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -4865,128 +4873,132 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2598.6</v>
+        <v>299.55</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2532.31</v>
+        <v>306.6</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2466.35</v>
+        <v>304.01</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2478.71</v>
+        <v>288.5</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>87.03</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>61.71</v>
+        <v>39.18</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>59.3243</v>
+        <v>-2.5086</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>56.9608</v>
+        <v>-0.2678</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.3635</v>
+        <v>-2.2408</v>
       </c>
       <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="n">
-        <v>27.93</v>
+        <v>25.28</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>586190</v>
+        <v>10353164</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>968162</v>
+        <v>9742600</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.61</v>
+        <v>1.06</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>249132</v>
+        <v>273717</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>64.93753</v>
+        <v>14.64179</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>51.941814</v>
-      </c>
-      <c r="AD33" s="4" t="inlineStr"/>
+        <v>14.774897</v>
+      </c>
+      <c r="AD33" s="4" t="n">
+        <v>16.49</v>
+      </c>
       <c r="AE33" s="4" t="n">
-        <v>17.609</v>
+        <v>150.993</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>3.7</v>
+        <v>-5</v>
       </c>
       <c r="AG33" s="4" t="n">
-        <v>-4.6</v>
+        <v>9.6</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>12.7180195</v>
+        <v>2.762576</v>
       </c>
       <c r="AI33" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="AJ33" s="4" t="inlineStr"/>
+        <v>409</v>
+      </c>
+      <c r="AJ33" s="4" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AK33" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ASIANPAINT/</t>
+          <t>https://www.screener.in/company/POWERGRID/</t>
         </is>
       </c>
       <c r="AL33" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ASIANPAINT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Muthoot Finance Limited</t>
+          <t>Larsen &amp; Toubro Limited</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>37.5</v>
+        <v>39.8</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7.5</v>
+        <v>18</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>21.8</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
@@ -4995,132 +5007,132 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>3309.3</v>
+        <v>3890.5</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3419.46</v>
+        <v>3909.82</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3441.02</v>
+        <v>3899.04</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3292.48</v>
+        <v>3819.98</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>80.43000000000001</v>
+        <v>88.48</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>42.61</v>
+        <v>48.43</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>-28.4915</v>
+        <v>-5.814</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>-1.8945</v>
+        <v>8.858599999999999</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>-26.597</v>
+        <v>-14.6726</v>
       </c>
       <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="2" t="n">
-        <v>13.67</v>
+        <v>10.76</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>1017971</v>
+        <v>1624945</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>822401</v>
+        <v>2504737</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>1.24</v>
+        <v>0.65</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>131389</v>
+        <v>540170</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>12.408341</v>
+        <v>33.54062</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>9.477159</v>
+        <v>21.401329</v>
       </c>
       <c r="AD34" s="2" t="n">
-        <v>30.41</v>
+        <v>16.95</v>
       </c>
       <c r="AE34" s="2" t="n">
-        <v>379.707</v>
+        <v>97.64</v>
       </c>
       <c r="AF34" s="2" t="n">
-        <v>53.7</v>
+        <v>11.7</v>
       </c>
       <c r="AG34" s="2" t="n">
-        <v>126.7</v>
+        <v>-34.5</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>3.6884842</v>
+        <v>4.9424148</v>
       </c>
       <c r="AI34" s="2" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AJ34" s="2" t="n">
-        <v>128.286</v>
+        <v>1.251</v>
       </c>
       <c r="AK34" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MUTHOOTFIN/</t>
+          <t>https://www.screener.in/company/LT/</t>
         </is>
       </c>
       <c r="AL34" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Limited</t>
+          <t>Avenue Supermarts Limited</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Discount Stores</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>37.4</v>
+        <v>39.4</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -5133,19 +5145,19 @@
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>299.9</v>
+        <v>4137.2</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.44</v>
+        <v>-0.17</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>307.34</v>
+        <v>4330.45</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>304.19</v>
+        <v>4263.34</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>288.54</v>
+        <v>4132.53</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
@@ -5158,71 +5170,71 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>92.29000000000001</v>
+        <v>83.59</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>39.56</v>
+        <v>34.81</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-2.2137</v>
+        <v>-34.2653</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.2924</v>
+        <v>11.2351</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-2.5061</v>
+        <v>-45.5004</v>
       </c>
       <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="n">
-        <v>25.96</v>
+        <v>25.56</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>5672695</v>
+        <v>498131</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>9589690</v>
+        <v>355027</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.59</v>
+        <v>1.4</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>278600</v>
+        <v>268496</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>14.888169</v>
+        <v>90.46364</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>15.038465</v>
+        <v>58.061115</v>
       </c>
       <c r="AD35" s="4" t="n">
-        <v>16.49</v>
+        <v>12.94</v>
       </c>
       <c r="AE35" s="4" t="n">
-        <v>150.993</v>
+        <v>9.913</v>
       </c>
       <c r="AF35" s="4" t="n">
-        <v>-5</v>
+        <v>18.9</v>
       </c>
       <c r="AG35" s="4" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>2.8118575</v>
+        <v>10.950983</v>
       </c>
       <c r="AI35" s="4" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.625</v>
+        <v>1.977</v>
       </c>
       <c r="AK35" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POWERGRID/</t>
+          <t>https://www.screener.in/company/DMART/</t>
         </is>
       </c>
       <c r="AL35" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERGRID</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DMART</t>
         </is>
       </c>
     </row>
@@ -5248,10 +5260,10 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>20</v>
@@ -5267,19 +5279,19 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>429.35</v>
+        <v>431</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-0.52</v>
+        <v>0.38</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>445.23</v>
+        <v>443.87</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>434.51</v>
+        <v>434.37</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>403.01</v>
+        <v>403.93</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -5292,41 +5304,41 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>88.25</v>
+        <v>88.59</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>41.59</v>
+        <v>42.68</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>-1.0489</v>
+        <v>-1.9433</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>3.8694</v>
+        <v>2.7069</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>-4.9183</v>
+        <v>-4.6502</v>
       </c>
       <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="n">
-        <v>16.08</v>
+        <v>15.69</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>4861888</v>
+        <v>6959709</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>6573529</v>
+        <v>6585962</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>0.74</v>
+        <v>1.06</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>142234</v>
+        <v>142086</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>5.4911456</v>
+        <v>5.485412</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>6.6208367</v>
+        <v>6.613924</v>
       </c>
       <c r="AD36" s="2" t="n">
         <v>20.47</v>
@@ -5341,10 +5353,10 @@
         <v>10.8</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>1.0704696</v>
+        <v>1.0693519</v>
       </c>
       <c r="AI36" s="2" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AJ36" s="2" t="n">
         <v>287.366</v>
@@ -5363,158 +5375,162 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Limited</t>
+          <t>NTPC Limited</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Textile Manufacturing</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>33.5</v>
+        <v>35.2</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>25.5</v>
+        <v>21</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>8</v>
+        <v>14.2</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+        </is>
+      </c>
       <c r="J37" s="4" t="n">
-        <v>958.55</v>
+        <v>388.8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.2</v>
+        <v>-0.93</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>929.01</v>
+        <v>393.34</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>912.14</v>
+        <v>386.79</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>945.59</v>
+        <v>359.48</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>76.47</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>59.29</v>
+        <v>46.12</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>10.6694</v>
+        <v>0.4056</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>12.6293</v>
+        <v>2.1942</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>-1.9599</v>
+        <v>-1.7887</v>
       </c>
       <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="n">
-        <v>24.85</v>
+        <v>14.95</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>121297</v>
+        <v>10596954</v>
       </c>
       <c r="Y37" s="4" t="n">
-        <v>224989</v>
+        <v>8137413</v>
       </c>
       <c r="Z37" s="4" t="n">
-        <v>0.54</v>
+        <v>1.3</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>32598</v>
+        <v>376861</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>37.601738</v>
+        <v>21.496128</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>26.390295</v>
+        <v>14.516919</v>
       </c>
       <c r="AD37" s="4" t="inlineStr"/>
       <c r="AE37" s="4" t="n">
-        <v>6.46</v>
+        <v>118.127</v>
       </c>
       <c r="AF37" s="4" t="n">
-        <v>-4</v>
+        <v>8</v>
       </c>
       <c r="AG37" s="4" t="n">
-        <v>3</v>
+        <v>-1.6</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>6.082238</v>
+        <v>1.9606904</v>
       </c>
       <c r="AI37" s="4" t="n">
-        <v>54</v>
+        <v>292</v>
       </c>
       <c r="AJ37" s="4" t="inlineStr"/>
       <c r="AK37" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/KPRMILL/</t>
+          <t>https://www.screener.in/company/NTPC/</t>
         </is>
       </c>
       <c r="AL37" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:KPRMILL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NTPC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>NTPC Limited</t>
+          <t>Tata Steel Limited</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>32.2</v>
+        <v>35</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>14.2</v>
+        <v>17</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -5523,23 +5539,23 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>392.45</v>
+        <v>208.58</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>393.81</v>
+        <v>211.64</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>386.71</v>
+        <v>207.07</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>359.21</v>
+        <v>187.7</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -5548,132 +5564,132 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>94.7</v>
+        <v>92.95</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>49.72</v>
+        <v>46.79</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>0.8663999999999999</v>
+        <v>1.0793</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>2.6414</v>
+        <v>2.4509</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>-1.775</v>
+        <v>-1.3716</v>
       </c>
       <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="n">
-        <v>14.96</v>
+        <v>19.73</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>5386249</v>
+        <v>24385712</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>8064800</v>
+        <v>30080012</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>377006</v>
+        <v>260899</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>21.492537</v>
+        <v>28.5</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>14.522522</v>
-      </c>
-      <c r="AD38" s="2" t="inlineStr"/>
+        <v>11.127129</v>
+      </c>
+      <c r="AD38" s="2" t="n">
+        <v>11.16</v>
+      </c>
       <c r="AE38" s="2" t="n">
-        <v>118.127</v>
+        <v>89.01600000000001</v>
       </c>
       <c r="AF38" s="2" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="AG38" s="2" t="n">
-        <v>-1.6</v>
+        <v>125.4</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>1.9614471</v>
+        <v>2.7445192</v>
       </c>
       <c r="AI38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="2" t="inlineStr"/>
+        <v>192</v>
+      </c>
+      <c r="AJ38" s="2" t="n">
+        <v>0.748</v>
+      </c>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NTPC/</t>
+          <t>https://www.screener.in/company/TATASTEEL/</t>
         </is>
       </c>
       <c r="AL38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NTPC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Tata Power Company Limited</t>
+          <t>K.P.R. Mill Limited</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Utilities - Independent Power Producers</t>
+          <t>Textile Manufacturing</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>30.8</v>
+        <v>33.5</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>📈 EMA Bull Stack</t>
-        </is>
-      </c>
+      <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="4" t="n">
-        <v>413.5</v>
+        <v>951.7</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-0.36</v>
+        <v>-0.71</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>421.39</v>
+        <v>931.17</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>412.93</v>
+        <v>913.6900000000001</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>393.93</v>
+        <v>949.7</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -5682,83 +5698,79 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>88.94</v>
+        <v>75.92</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>45.02</v>
+        <v>57.23</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-1.7079</v>
+        <v>11.2359</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>2.9854</v>
+        <v>12.3506</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>-4.6933</v>
+        <v>-1.1147</v>
       </c>
       <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="n">
-        <v>25</v>
+        <v>25.06</v>
       </c>
       <c r="X39" s="4" t="n">
-        <v>4390666</v>
+        <v>179112</v>
       </c>
       <c r="Y39" s="4" t="n">
-        <v>7310922</v>
+        <v>226792</v>
       </c>
       <c r="Z39" s="4" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>131169</v>
+        <v>32255</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>35.085472</v>
+        <v>37.191944</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>27.142973</v>
-      </c>
-      <c r="AD39" s="4" t="n">
-        <v>11.34</v>
-      </c>
+        <v>26.112999</v>
+      </c>
+      <c r="AD39" s="4" t="inlineStr"/>
       <c r="AE39" s="4" t="n">
-        <v>167.811</v>
+        <v>6.46</v>
       </c>
       <c r="AF39" s="4" t="n">
-        <v>-12.8</v>
+        <v>-4</v>
       </c>
       <c r="AG39" s="4" t="n">
-        <v>-4.6</v>
+        <v>3</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>3.4646904</v>
+        <v>6.018329</v>
       </c>
       <c r="AI39" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ39" s="4" t="n">
-        <v>0.806</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AJ39" s="4" t="inlineStr"/>
       <c r="AK39" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TATAPOWER/</t>
+          <t>https://www.screener.in/company/KPRMILL/</t>
         </is>
       </c>
       <c r="AL39" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:KPRMILL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>NHPC Limited</t>
+          <t>Tata Power Company Limited</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5768,42 +5780,46 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Renewable</t>
+          <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>27.5</v>
+        <v>31</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>📈 EMA Bull Stack</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="n">
-        <v>79.5</v>
+        <v>410.5</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>79.77</v>
+        <v>420.36</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>79.16</v>
+        <v>412.84</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>79.18000000000001</v>
+        <v>394.31</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5812,71 +5828,71 @@
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>88.18000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>49.15</v>
+        <v>43.16</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>-0.365</v>
+        <v>-2.2566</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>0.1361</v>
+        <v>1.937</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>-0.5012</v>
+        <v>-4.1935</v>
       </c>
       <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="2" t="n">
-        <v>18.41</v>
+        <v>24.93</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>15924979</v>
+        <v>5013888</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>14208123</v>
+        <v>7165231</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>1.12</v>
+        <v>0.7</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>79356</v>
+        <v>130657</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>28.519855</v>
+        <v>34.94872</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>12.34375</v>
+        <v>22.907728</v>
       </c>
       <c r="AD40" s="2" t="n">
-        <v>9.02</v>
+        <v>11.34</v>
       </c>
       <c r="AE40" s="2" t="n">
-        <v>113.111</v>
+        <v>167.811</v>
       </c>
       <c r="AF40" s="2" t="n">
-        <v>19.2</v>
+        <v>-12.8</v>
       </c>
       <c r="AG40" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>-4.6</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>1.9183139</v>
+        <v>3.4511862</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>240</v>
+        <v>61</v>
       </c>
       <c r="AJ40" s="2" t="n">
-        <v>0.944</v>
+        <v>0.806</v>
       </c>
       <c r="AK40" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NHPC/</t>
+          <t>https://www.screener.in/company/TATAPOWER/</t>
         </is>
       </c>
       <c r="AL40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NHPC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER</t>
         </is>
       </c>
     </row>
@@ -5921,19 +5937,19 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>4106.4</v>
+        <v>4083.1</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0.11</v>
+        <v>-0.57</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>4242.61</v>
+        <v>4227.42</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>4250.67</v>
+        <v>4244.1</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>3966.99</v>
+        <v>3974.84</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
@@ -5946,41 +5962,41 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>89.17</v>
+        <v>88.67</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>40.44</v>
+        <v>39.28</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>-57.3265</v>
+        <v>-62.3227</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-26.4091</v>
+        <v>-33.5918</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>-30.9174</v>
+        <v>-28.7309</v>
       </c>
       <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="n">
-        <v>9.68</v>
+        <v>9.31</v>
       </c>
       <c r="X41" s="4" t="n">
-        <v>913576</v>
+        <v>863060</v>
       </c>
       <c r="Y41" s="4" t="n">
-        <v>1445359</v>
+        <v>1454502</v>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>362189</v>
+        <v>361897</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>71.53293600000001</v>
+        <v>71.37509</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>47.432396</v>
+        <v>47.52608</v>
       </c>
       <c r="AD41" s="4" t="n">
         <v>37.13</v>
@@ -5995,7 +6011,7 @@
         <v>35.1</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>28.28082</v>
+        <v>28.257963</v>
       </c>
       <c r="AI41" s="4" t="n">
         <v>27</v>
@@ -6055,19 +6071,19 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1153.5</v>
+        <v>1155.6</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.86</v>
+        <v>0.18</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1132.16</v>
+        <v>1134.39</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1124.66</v>
+        <v>1125.87</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1128.93</v>
+        <v>1130.21</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -6080,41 +6096,41 @@
         </is>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>83.48</v>
+        <v>83.63</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>54.3</v>
+        <v>54.62</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>8.263</v>
+        <v>9.1768</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>11.506</v>
+        <v>11.0402</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>-3.243</v>
+        <v>-1.8633</v>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
       <c r="W42" s="2" t="n">
-        <v>16.48</v>
+        <v>15.88</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>1415263</v>
+        <v>1233342</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>3376447</v>
+        <v>3381646</v>
       </c>
       <c r="Z42" s="2" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="AA42" s="2" t="n">
-        <v>73979</v>
+        <v>71214</v>
       </c>
       <c r="AB42" s="2" t="n">
-        <v>135.31616</v>
+        <v>130.10527</v>
       </c>
       <c r="AC42" s="2" t="n">
-        <v>36.530087</v>
+        <v>35.164474</v>
       </c>
       <c r="AD42" s="2" t="n">
         <v>3.56</v>
@@ -6127,7 +6143,7 @@
       </c>
       <c r="AG42" s="2" t="inlineStr"/>
       <c r="AH42" s="2" t="n">
-        <v>4.6229362</v>
+        <v>4.4501166</v>
       </c>
       <c r="AI42" s="2" t="n">
         <v>0</v>
@@ -6183,19 +6199,19 @@
       </c>
       <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="4" t="n">
-        <v>1249.8</v>
+        <v>1253.3</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.93</v>
+        <v>0.28</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>1270.86</v>
+        <v>1269.19</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>1283.82</v>
+        <v>1282.63</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>1248.48</v>
+        <v>1248.46</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
@@ -6208,41 +6224,41 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>88.12</v>
+        <v>88.37</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>42.05</v>
+        <v>43.25</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>-15.4628</v>
+        <v>-14.8622</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-10.5176</v>
+        <v>-11.3865</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>-4.9452</v>
+        <v>-3.4757</v>
       </c>
       <c r="V43" s="4" t="inlineStr"/>
       <c r="W43" s="4" t="n">
-        <v>16.32</v>
+        <v>16.35</v>
       </c>
       <c r="X43" s="4" t="n">
-        <v>3562641</v>
+        <v>5171528</v>
       </c>
       <c r="Y43" s="4" t="n">
-        <v>7081996</v>
+        <v>7057010</v>
       </c>
       <c r="Z43" s="4" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>389727</v>
+        <v>399709</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>14.833709</v>
+        <v>15.2172365</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>9.868505000000001</v>
+        <v>10.201588</v>
       </c>
       <c r="AD43" s="4" t="n">
         <v>13.15</v>
@@ -6255,7 +6271,7 @@
         <v>6.4</v>
       </c>
       <c r="AH43" s="4" t="n">
-        <v>1.8108186</v>
+        <v>1.8571979</v>
       </c>
       <c r="AI43" s="4" t="n">
         <v>8</v>
@@ -6272,8 +6288,134 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Eicher Motors Limited</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Auto Manufacturers</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
+        <v>6892</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>7055.39</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>7126.81</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>6882.89</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>-64.0885</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>-24.4184</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>-39.67</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>491206</v>
+      </c>
+      <c r="Y44" s="2" t="n">
+        <v>429558</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA44" s="2" t="n">
+        <v>191512</v>
+      </c>
+      <c r="AB44" s="2" t="n">
+        <v>35.795223</v>
+      </c>
+      <c r="AC44" s="2" t="n">
+        <v>30.332722</v>
+      </c>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="n">
+        <v>2.018</v>
+      </c>
+      <c r="AF44" s="2" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AG44" s="2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AH44" s="2" t="n">
+        <v>8.669914</v>
+      </c>
+      <c r="AI44" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr"/>
+      <c r="AK44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.screener.in/company/EICHERMOT/</t>
+        </is>
+      </c>
+      <c r="AL44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL43"/>
+  <autoFilter ref="A1:AL44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6769,32 +6911,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>71.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -6803,23 +6945,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6893</v>
+        <v>274.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.27</v>
+        <v>0.44</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>6651.15</v>
+        <v>268.53</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6444.25</v>
+        <v>262.9</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>6287.98</v>
+        <v>247.57</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -6832,67 +6974,75 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>97.92</v>
+        <v>96.11</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>67.93000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>170.0506</v>
+        <v>3.7145</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>156.7626</v>
+        <v>3.7075</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>13.2879</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr"/>
+        <v>0.007</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W2" s="2" t="n">
-        <v>39.66</v>
+        <v>21.42</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>957736</v>
+        <v>5838024</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>340695</v>
+        <v>3213435</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>2.81</v>
+        <v>1.82</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>182058</v>
+        <v>79391</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>73.69439</v>
+        <v>390.49298</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>58.663486</v>
-      </c>
-      <c r="AD2" s="2" t="inlineStr"/>
+        <v>104.479126</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>14.34</v>
+      </c>
       <c r="AE2" s="2" t="n">
-        <v>0.584</v>
+        <v>82.405</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>12.3</v>
+        <v>28.4</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>-1</v>
+        <v>290.2</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.804761</v>
+        <v>57.31859</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="2" t="n">
+        <v>1.156</v>
+      </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/NYKAA/</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
         </is>
       </c>
     </row>
@@ -6937,19 +7087,19 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9199</v>
+        <v>9193.5</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.06</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>8708.02</v>
+        <v>8754.25</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>8220.77</v>
+        <v>8258.92</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>7472.18</v>
+        <v>7500.27</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -6962,41 +7112,41 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>98.98</v>
+        <v>98.75</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>71.77</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>373.4664</v>
+        <v>365.9882</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>345.0657</v>
+        <v>349.2502</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>28.4006</v>
+        <v>16.738</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>36.92</v>
+        <v>37.17</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>320359</v>
+        <v>231631</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>484200</v>
+        <v>471656</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>138409</v>
+        <v>139462</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>52.05243</v>
+        <v>52.47847</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>37.358936</v>
+        <v>37.64339</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>24.58</v>
@@ -7011,7 +7161,7 @@
         <v>8</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.525819</v>
+        <v>11.613577</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>38</v>
@@ -7033,29 +7183,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>19</v>
@@ -7067,23 +7217,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>838.45</v>
+        <v>8308.5</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.84</v>
+        <v>2.85</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>813.83</v>
+        <v>7943.12</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>789.47</v>
+        <v>7745.19</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>749.1799999999999</v>
+        <v>7458.51</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -7096,103 +7246,103 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.78</v>
+        <v>99.05</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>67.68000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>19.0654</v>
+        <v>143.2305</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>17.8518</v>
+        <v>122.5275</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.2136</v>
+        <v>20.703</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>37.95</v>
+        <v>24.91</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1973862</v>
+        <v>1425124</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>1885384</v>
+        <v>433308</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>1.05</v>
+        <v>3.29</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>107791</v>
+        <v>120240</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>61.25552</v>
+        <v>61.74777</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>44.081028</v>
+        <v>39.105675</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>41.39</v>
+        <v>21.5</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>12.394</v>
+        <v>85.146</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>22.1</v>
+        <v>18.1</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>14.5</v>
+        <v>35.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>25.413969</v>
+        <v>12.680638</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>1.31</v>
+        <v>1.065</v>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>JSW Steel Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -7201,23 +7351,23 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>8078.5</v>
+        <v>1281.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.65</v>
+        <v>-0.15</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>7904.66</v>
+        <v>1269.12</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>7722.2</v>
+        <v>1241.54</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>7443.91</v>
+        <v>1173.14</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -7230,103 +7380,103 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>98.76000000000001</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>63.39</v>
+        <v>56.24</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>126.6408</v>
+        <v>15.561</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>117.3518</v>
+        <v>17.3691</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>9.289</v>
+        <v>-1.8081</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>24.38</v>
+        <v>17.96</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>492013</v>
+        <v>5339554</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>377258</v>
+        <v>1952278</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>1.3</v>
+        <v>2.74</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>119463</v>
+        <v>313743</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.5855</v>
+        <v>14.090759</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>49.931694</v>
+        <v>17.70393</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>21.5</v>
+        <v>27.26</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>85.146</v>
+        <v>94.155</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>18.9</v>
+        <v>14.2</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>35.6</v>
+        <v>991.8</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>12.598754</v>
+        <v>3.1359012</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.065</v>
+        <v>1.491</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/JSWSTEEL/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Manappuram Finance Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>62.4</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>46</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16.4</v>
+        <v>19</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -7335,23 +7485,23 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>319.15</v>
+        <v>831.85</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.22</v>
+        <v>-0.79</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>302.02</v>
+        <v>815.54</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>290.7</v>
+        <v>791.13</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>279.51</v>
+        <v>750.53</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -7364,105 +7514,103 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>98.56</v>
+        <v>98</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>65.51000000000001</v>
+        <v>63.18</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>9.4383</v>
+        <v>18.1378</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>9.1919</v>
+        <v>17.909</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2465</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2288</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="n">
-        <v>24.87</v>
+        <v>38.41</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>4971139</v>
+        <v>1305803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>4423393</v>
+        <v>1841800</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>1.12</v>
+        <v>0.71</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>30284</v>
+        <v>106832</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>27.532022</v>
+        <v>60.800148</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>10.978432</v>
+        <v>43.688892</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>6.97</v>
+        <v>41.39</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>360.191</v>
+        <v>12.394</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AG6" s="2" t="inlineStr"/>
+        <v>22.1</v>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="AH6" s="2" t="n">
-        <v>1.6814436</v>
+        <v>25.187891</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>94.116</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MANAPPURAM/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>43</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -7475,19 +7623,19 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2704.8</v>
+        <v>6858</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.74</v>
+        <v>-0.51</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2504.92</v>
+        <v>6670.85</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2325.64</v>
+        <v>6460.47</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2279.15</v>
+        <v>6300.69</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -7500,101 +7648,99 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>96.48999999999999</v>
+        <v>97.42</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>71.8</v>
+        <v>65.33</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>140.0127</v>
+        <v>165.4821</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>126.8855</v>
+        <v>158.5065</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>13.1273</v>
+        <v>6.9756</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>46.07</v>
+        <v>39.2</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1187449</v>
+        <v>151586</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3060077</v>
+        <v>336947</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>369826</v>
+        <v>182828</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>36.66712</v>
+        <v>73.83938999999999</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>47.58931</v>
-      </c>
-      <c r="AD7" s="4" t="n">
-        <v>13.66</v>
-      </c>
+        <v>58.911552</v>
+      </c>
+      <c r="AD7" s="4" t="inlineStr"/>
       <c r="AE7" s="4" t="n">
-        <v>119.56</v>
+        <v>0.584</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AG7" s="4" t="inlineStr"/>
+        <v>12.3</v>
+      </c>
+      <c r="AG7" s="4" t="n">
+        <v>-1</v>
+      </c>
       <c r="AH7" s="4" t="n">
-        <v>4.3024473</v>
+        <v>11.854679</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ7" s="4" t="n">
-        <v>1.035</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
       <c r="AK7" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIENT/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>60.8</v>
+        <v>61.6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>24.8</v>
+        <v>18.6</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -7607,19 +7753,19 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1772.6</v>
+        <v>2697.6</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1705.06</v>
+        <v>2523.27</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1605.6</v>
+        <v>2340.23</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1477.09</v>
+        <v>2285.36</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -7632,103 +7778,101 @@
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>97.19</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>64.73</v>
+        <v>70.95</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>66.0569</v>
+        <v>138.106</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>68.9718</v>
+        <v>129.1296</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>-2.9149</v>
+        <v>8.9764</v>
       </c>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="2" t="n">
-        <v>29.85</v>
+        <v>46.9</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>1283223</v>
+        <v>1606690</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>3390298</v>
+        <v>2993011</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>413169</v>
+        <v>372527</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>30.749315</v>
+        <v>36.899784</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>23.12162</v>
+        <v>47.936844</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>15.59</v>
+        <v>13.66</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>64.051</v>
+        <v>119.56</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AG8" s="2" t="n">
-        <v>3.6</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="n">
-        <v>4.2978926</v>
+        <v>4.333867</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>1.394</v>
+        <v>1.035</v>
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/ADANIENT/</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>Manappuram Finance Limited</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>14.8</v>
+        <v>16.4</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -7737,23 +7881,23 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1464.4</v>
+        <v>322.4</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.94</v>
+        <v>1.02</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1240.68</v>
+        <v>303.96</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1125.3</v>
+        <v>291.94</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>994.15</v>
+        <v>280.07</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -7766,67 +7910,69 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>97.69</v>
+        <v>99.37</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>74.62</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>91.0787</v>
+        <v>9.903700000000001</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>74.7504</v>
+        <v>9.334199999999999</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>16.3283</v>
+        <v>0.5695</v>
       </c>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="n">
-        <v>34.25</v>
+        <v>24.79</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5017988</v>
+        <v>7531083</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>862253</v>
+        <v>4640929</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.82</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>9763</v>
+        <v>30444</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>86.80522999999999</v>
+        <v>27.700855</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>44.69265</v>
-      </c>
-      <c r="AD9" s="4" t="inlineStr"/>
+        <v>11.036321</v>
+      </c>
+      <c r="AD9" s="4" t="n">
+        <v>6.97</v>
+      </c>
       <c r="AE9" s="4" t="n">
-        <v>25.091</v>
+        <v>360.191</v>
       </c>
       <c r="AF9" s="4" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="AG9" s="4" t="n">
-        <v>35.8</v>
-      </c>
+        <v>109.3</v>
+      </c>
+      <c r="AG9" s="4" t="inlineStr"/>
       <c r="AH9" s="4" t="n">
-        <v>14.977766</v>
+        <v>1.6903098</v>
       </c>
       <c r="AI9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AJ9" s="4" t="n">
+        <v>94.116</v>
+      </c>
       <c r="AK9" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AVALON/</t>
+          <t>https://www.screener.in/company/MANAPPURAM/</t>
         </is>
       </c>
       <c r="AL9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
         </is>
       </c>
     </row>
@@ -8080,32 +8226,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>71.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -8114,23 +8260,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6893</v>
+        <v>274.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.27</v>
+        <v>0.44</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>6651.15</v>
+        <v>268.53</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6444.25</v>
+        <v>262.9</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>6287.98</v>
+        <v>247.57</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -8143,67 +8289,75 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>97.92</v>
+        <v>96.11</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>67.93000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>170.0506</v>
+        <v>3.7145</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>156.7626</v>
+        <v>3.7075</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>13.2879</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr"/>
+        <v>0.007</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W2" s="2" t="n">
-        <v>39.66</v>
+        <v>21.42</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>957736</v>
+        <v>5838024</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>340695</v>
+        <v>3213435</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>2.81</v>
+        <v>1.82</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>182058</v>
+        <v>79391</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>73.69439</v>
+        <v>390.49298</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>58.663486</v>
-      </c>
-      <c r="AD2" s="2" t="inlineStr"/>
+        <v>104.479126</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>14.34</v>
+      </c>
       <c r="AE2" s="2" t="n">
-        <v>0.584</v>
+        <v>82.405</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>12.3</v>
+        <v>28.4</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>-1</v>
+        <v>290.2</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>11.804761</v>
+        <v>57.31859</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="2" t="n">
+        <v>1.156</v>
+      </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/NYKAA/</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
         </is>
       </c>
     </row>
@@ -8248,19 +8402,19 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9199</v>
+        <v>9193.5</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.06</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>8708.02</v>
+        <v>8754.25</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>8220.77</v>
+        <v>8258.92</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>7472.18</v>
+        <v>7500.27</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -8273,41 +8427,41 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>98.98</v>
+        <v>98.75</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>71.77</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>373.4664</v>
+        <v>365.9882</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>345.0657</v>
+        <v>349.2502</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>28.4006</v>
+        <v>16.738</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>36.92</v>
+        <v>37.17</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>320359</v>
+        <v>231631</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>484200</v>
+        <v>471656</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>138409</v>
+        <v>139462</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>52.05243</v>
+        <v>52.47847</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>37.358936</v>
+        <v>37.64339</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>24.58</v>
@@ -8322,7 +8476,7 @@
         <v>8</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.525819</v>
+        <v>11.613577</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>38</v>
@@ -8344,29 +8498,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>19</v>
@@ -8378,23 +8532,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>838.45</v>
+        <v>8308.5</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.84</v>
+        <v>2.85</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>813.83</v>
+        <v>7943.12</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>789.47</v>
+        <v>7745.19</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>749.1799999999999</v>
+        <v>7458.51</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -8407,103 +8561,103 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>98.78</v>
+        <v>99.05</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>67.68000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>19.0654</v>
+        <v>143.2305</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>17.8518</v>
+        <v>122.5275</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.2136</v>
+        <v>20.703</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>37.95</v>
+        <v>24.91</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1973862</v>
+        <v>1425124</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>1885384</v>
+        <v>433308</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>1.05</v>
+        <v>3.29</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>107791</v>
+        <v>120240</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>61.25552</v>
+        <v>61.74777</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>44.081028</v>
+        <v>39.105675</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>41.39</v>
+        <v>21.5</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>12.394</v>
+        <v>85.146</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>22.1</v>
+        <v>18.1</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>14.5</v>
+        <v>35.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>25.413969</v>
+        <v>12.680638</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>1.31</v>
+        <v>1.065</v>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>JSW Steel Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -8512,23 +8666,23 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>8078.5</v>
+        <v>1281.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.65</v>
+        <v>-0.15</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>7904.66</v>
+        <v>1269.12</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>7722.2</v>
+        <v>1241.54</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>7443.91</v>
+        <v>1173.14</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -8541,103 +8695,103 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>98.76000000000001</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>63.39</v>
+        <v>56.24</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>126.6408</v>
+        <v>15.561</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>117.3518</v>
+        <v>17.3691</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>9.289</v>
+        <v>-1.8081</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>24.38</v>
+        <v>17.96</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>492013</v>
+        <v>5339554</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>377258</v>
+        <v>1952278</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>1.3</v>
+        <v>2.74</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>119463</v>
+        <v>313743</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>61.5855</v>
+        <v>14.090759</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>49.931694</v>
+        <v>17.70393</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>21.5</v>
+        <v>27.26</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>85.146</v>
+        <v>94.155</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>18.9</v>
+        <v>14.2</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>35.6</v>
+        <v>991.8</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>12.598754</v>
+        <v>3.1359012</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.065</v>
+        <v>1.491</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/JSWSTEEL/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Manappuram Finance Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>62.4</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>46</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16.4</v>
+        <v>19</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -8646,23 +8800,23 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>319.15</v>
+        <v>831.85</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.22</v>
+        <v>-0.79</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>302.02</v>
+        <v>815.54</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>290.7</v>
+        <v>791.13</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>279.51</v>
+        <v>750.53</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -8675,105 +8829,103 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>98.56</v>
+        <v>98</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>65.51000000000001</v>
+        <v>63.18</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>9.4383</v>
+        <v>18.1378</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>9.1919</v>
+        <v>17.909</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2465</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2288</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="n">
-        <v>24.87</v>
+        <v>38.41</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>4971139</v>
+        <v>1305803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>4423393</v>
+        <v>1841800</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>1.12</v>
+        <v>0.71</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>30284</v>
+        <v>106832</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>27.532022</v>
+        <v>60.800148</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>10.978432</v>
+        <v>43.688892</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>6.97</v>
+        <v>41.39</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>360.191</v>
+        <v>12.394</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AG6" s="2" t="inlineStr"/>
+        <v>22.1</v>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="AH6" s="2" t="n">
-        <v>1.6814436</v>
+        <v>25.187891</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>94.116</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MANAPPURAM/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>43</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -8786,19 +8938,19 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2704.8</v>
+        <v>6858</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.74</v>
+        <v>-0.51</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2504.92</v>
+        <v>6670.85</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2325.64</v>
+        <v>6460.47</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2279.15</v>
+        <v>6300.69</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -8811,101 +8963,99 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>96.48999999999999</v>
+        <v>97.42</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>71.8</v>
+        <v>65.33</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>140.0127</v>
+        <v>165.4821</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>126.8855</v>
+        <v>158.5065</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>13.1273</v>
+        <v>6.9756</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>46.07</v>
+        <v>39.2</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1187449</v>
+        <v>151586</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3060077</v>
+        <v>336947</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>369826</v>
+        <v>182828</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>36.66712</v>
+        <v>73.83938999999999</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>47.58931</v>
-      </c>
-      <c r="AD7" s="4" t="n">
-        <v>13.66</v>
-      </c>
+        <v>58.911552</v>
+      </c>
+      <c r="AD7" s="4" t="inlineStr"/>
       <c r="AE7" s="4" t="n">
-        <v>119.56</v>
+        <v>0.584</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AG7" s="4" t="inlineStr"/>
+        <v>12.3</v>
+      </c>
+      <c r="AG7" s="4" t="n">
+        <v>-1</v>
+      </c>
       <c r="AH7" s="4" t="n">
-        <v>4.3024473</v>
+        <v>11.854679</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ7" s="4" t="n">
-        <v>1.035</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
       <c r="AK7" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIENT/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>60.8</v>
+        <v>61.6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>24.8</v>
+        <v>18.6</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -8918,19 +9068,19 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1772.6</v>
+        <v>2697.6</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1705.06</v>
+        <v>2523.27</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1605.6</v>
+        <v>2340.23</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1477.09</v>
+        <v>2285.36</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -8943,103 +9093,101 @@
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>97.19</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>64.73</v>
+        <v>70.95</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>66.0569</v>
+        <v>138.106</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>68.9718</v>
+        <v>129.1296</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>-2.9149</v>
+        <v>8.9764</v>
       </c>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="2" t="n">
-        <v>29.85</v>
+        <v>46.9</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>1283223</v>
+        <v>1606690</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>3390298</v>
+        <v>2993011</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>413169</v>
+        <v>372527</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>30.749315</v>
+        <v>36.899784</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>23.12162</v>
+        <v>47.936844</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>15.59</v>
+        <v>13.66</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>64.051</v>
+        <v>119.56</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AG8" s="2" t="n">
-        <v>3.6</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="n">
-        <v>4.2978926</v>
+        <v>4.333867</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>1.394</v>
+        <v>1.035</v>
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/ADANIENT/</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>Manappuram Finance Limited</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>14.8</v>
+        <v>16.4</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -9048,23 +9196,23 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1464.4</v>
+        <v>322.4</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.94</v>
+        <v>1.02</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1240.68</v>
+        <v>303.96</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1125.3</v>
+        <v>291.94</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>994.15</v>
+        <v>280.07</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -9077,67 +9225,69 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>97.69</v>
+        <v>99.37</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>74.62</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>91.0787</v>
+        <v>9.903700000000001</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>74.7504</v>
+        <v>9.334199999999999</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>16.3283</v>
+        <v>0.5695</v>
       </c>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="n">
-        <v>34.25</v>
+        <v>24.79</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5017988</v>
+        <v>7531083</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>862253</v>
+        <v>4640929</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.82</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>9763</v>
+        <v>30444</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>86.80522999999999</v>
+        <v>27.700855</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>44.69265</v>
-      </c>
-      <c r="AD9" s="4" t="inlineStr"/>
+        <v>11.036321</v>
+      </c>
+      <c r="AD9" s="4" t="n">
+        <v>6.97</v>
+      </c>
       <c r="AE9" s="4" t="n">
-        <v>25.091</v>
+        <v>360.191</v>
       </c>
       <c r="AF9" s="4" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="AG9" s="4" t="n">
-        <v>35.8</v>
-      </c>
+        <v>109.3</v>
+      </c>
+      <c r="AG9" s="4" t="inlineStr"/>
       <c r="AH9" s="4" t="n">
-        <v>14.977766</v>
+        <v>1.6903098</v>
       </c>
       <c r="AI9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AJ9" s="4" t="n">
+        <v>94.116</v>
+      </c>
       <c r="AK9" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AVALON/</t>
+          <t>https://www.screener.in/company/MANAPPURAM/</t>
         </is>
       </c>
       <c r="AL9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 21-May-2026 17:51 IST</t>
+          <t>Run Date: 22-May-2026 17:28 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -9195,7 +9345,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -9235,7 +9385,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -9245,7 +9395,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -9271,7 +9421,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="14">
@@ -9281,7 +9431,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>71.8</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -9291,7 +9441,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="16">
@@ -9313,11 +9463,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>71.8</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -9333,31 +9483,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62.4</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -14,10 +14,10 @@
     <sheet name="📈 Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📊 All Stocks'!$A$1:$AL$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📊 All Stocks'!$A$1:$AL$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏆 Grade A'!$A$1:$AL$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Grade B Watch'!$A$1:$AL$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Watchlist'!$A$1:$AL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Grade B Watch'!$A$1:$AL$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Watchlist'!$A$1:$AL$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -759,23 +759,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>274.5</v>
+        <v>277.25</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>268.53</v>
+        <v>269.36</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>262.9</v>
+        <v>263.46</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>247.57</v>
+        <v>247.34</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -788,45 +788,41 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>96.11</v>
+        <v>97.08</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>59.8</v>
+        <v>62.41</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>3.7145</v>
+        <v>3.9607</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>3.7075</v>
+        <v>3.7581</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2026</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>21.42</v>
+        <v>21.99</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>5838024</v>
+        <v>31687149</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>3213435</v>
+        <v>4585803</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>1.82</v>
+        <v>6.91</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>79391</v>
+        <v>77329</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>390.49298</v>
+        <v>391.3768</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>104.479126</v>
+        <v>101.846466</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>14.34</v>
@@ -841,7 +837,7 @@
         <v>290.2</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>57.31859</v>
+        <v>55.83006</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
@@ -863,32 +859,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Polycab India Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>68.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>25.2</v>
+        <v>21.4</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -897,23 +893,23 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9193.5</v>
+        <v>6887</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-0.06</v>
+        <v>0.42</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>8754.25</v>
+        <v>6691.44</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>8258.92</v>
+        <v>6477.2</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>7500.27</v>
+        <v>6281.44</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -926,103 +922,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>98.75</v>
+        <v>97.83</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>71.51000000000001</v>
+        <v>66.47</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>365.9882</v>
+        <v>162.3304</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>349.2502</v>
+        <v>159.2713</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>16.738</v>
+        <v>3.0591</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>37.17</v>
+        <v>38.27</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>231631</v>
+        <v>354149</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>471656</v>
+        <v>334396</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.49</v>
+        <v>1.06</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>139462</v>
+        <v>179364</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>52.47847</v>
+        <v>72.13858</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>37.64339</v>
+        <v>47.168694</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>24.58</v>
+        <v>16.19</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>2.558</v>
+        <v>0.042</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>26.9</v>
+        <v>9.5</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>8</v>
+        <v>13.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.613577</v>
+        <v>11.630048</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>1.841</v>
+        <v>5.431</v>
       </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POLYCAB/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>Adani Ports and Special Economic Zone Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Marine Shipping</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>68</v>
+        <v>61.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>19</v>
+        <v>24.8</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -1031,23 +1027,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8308.5</v>
+        <v>1786.9</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.85</v>
+        <v>-0.36</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7943.12</v>
+        <v>1720.46</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7745.19</v>
+        <v>1619.78</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>7458.51</v>
+        <v>1479.36</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1060,103 +1056,103 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>99.05</v>
+        <v>97.97</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>71.14</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>143.2305</v>
+        <v>63.0954</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>122.5275</v>
+        <v>67.1768</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>20.703</v>
+        <v>-4.0814</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>24.91</v>
+        <v>30.09</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1425124</v>
+        <v>1487044</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>433308</v>
+        <v>3311212</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>3.29</v>
+        <v>0.45</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>120240</v>
+        <v>415381</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>61.74777</v>
+        <v>30.951073</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>39.105675</v>
+        <v>23.245396</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>21.5</v>
+        <v>15.59</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>85.146</v>
+        <v>64.051</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>18.1</v>
+        <v>26.5</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>35.6</v>
+        <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>12.680638</v>
+        <v>4.3209004</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>1.065</v>
+        <v>1.394</v>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>JSW Steel Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>67</v>
+        <v>61.6</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27</v>
+        <v>18.6</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1165,23 +1161,23 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1281.3</v>
+        <v>2717.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.73</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1269.12</v>
+        <v>2541.75</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1241.54</v>
+        <v>2355.01</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1173.14</v>
+        <v>2280.04</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -1194,103 +1190,101 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>97.51000000000001</v>
+        <v>96.94</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>56.24</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>15.561</v>
+        <v>136.6097</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>17.3691</v>
+        <v>130.6256</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-1.8081</v>
+        <v>5.9841</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>17.96</v>
+        <v>47.68</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>5339554</v>
+        <v>1094843</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1952278</v>
+        <v>2934188</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>2.74</v>
+        <v>0.37</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>313743</v>
+        <v>390678</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.090759</v>
+        <v>38.69772</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.70393</v>
+        <v>50.272556</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>27.26</v>
+        <v>13.66</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>94.155</v>
+        <v>119.56</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AG5" s="4" t="n">
-        <v>991.8</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="AG5" s="4" t="inlineStr"/>
       <c r="AH5" s="4" t="n">
-        <v>3.1359012</v>
+        <v>4.545034</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.491</v>
+        <v>1.035</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/JSWSTEEL/</t>
+          <t>https://www.screener.in/company/ADANIENT/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>65</v>
+        <v>61.2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19</v>
+        <v>25.2</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -1303,19 +1297,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>831.85</v>
+        <v>9263.5</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.79</v>
+        <v>0.76</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>815.54</v>
+        <v>8802.75</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>791.13</v>
+        <v>8298.309999999999</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>750.53</v>
+        <v>7496.56</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1328,83 +1322,83 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>98</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>63.18</v>
+        <v>72.87</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>18.1378</v>
+        <v>361.5424</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>17.909</v>
+        <v>351.7087</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2288</v>
+        <v>9.8338</v>
       </c>
       <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="n">
-        <v>38.41</v>
+        <v>37.41</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>1305803</v>
+        <v>177024</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>1841800</v>
+        <v>449673</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>106832</v>
+        <v>141495</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>60.800148</v>
+        <v>53.11988</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>43.688892</v>
+        <v>38.191982</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>41.39</v>
+        <v>24.58</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>12.394</v>
+        <v>2.558</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>22.1</v>
+        <v>26.9</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>25.187891</v>
+        <v>11.782825</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>1.31</v>
+        <v>1.841</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/POLYCAB/</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Torrent Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1418,13 +1412,13 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>61.8</v>
+        <v>60.4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1437,19 +1431,19 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6858</v>
+        <v>4486.2</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.51</v>
+        <v>0.38</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6670.85</v>
+        <v>4359.3</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6460.47</v>
+        <v>4267.93</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6300.69</v>
+        <v>3940.01</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -1462,124 +1456,128 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>97.42</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>65.33</v>
+        <v>62.17</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>165.4821</v>
+        <v>69.54349999999999</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>158.5065</v>
+        <v>58.2663</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>6.9756</v>
+        <v>11.2772</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>39.2</v>
+        <v>24.98</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>151586</v>
+        <v>205928</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>336947</v>
+        <v>267353</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>182828</v>
+        <v>154758</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>73.83938999999999</v>
+        <v>71.78336</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>58.911552</v>
-      </c>
-      <c r="AD7" s="4" t="inlineStr"/>
+        <v>48.446224</v>
+      </c>
+      <c r="AD7" s="4" t="n">
+        <v>16.98</v>
+      </c>
       <c r="AE7" s="4" t="n">
-        <v>0.584</v>
+        <v>85.44199999999999</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>12.3</v>
+        <v>41.8</v>
       </c>
       <c r="AG7" s="4" t="n">
-        <v>-1</v>
+        <v>-21.8</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>11.854679</v>
+        <v>18.32948</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="AJ7" s="4" t="n">
+        <v>1.126</v>
+      </c>
       <c r="AK7" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/TORNTPHARM/</t>
         </is>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>61.6</v>
+          <t>Household &amp; Personal Products</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>59</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>19</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2697.6</v>
+        <v>824.45</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.89</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2523.27</v>
+        <v>816.39</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2340.23</v>
+        <v>792.4400000000001</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2285.36</v>
+        <v>751.63</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -1592,69 +1590,71 @@
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>96.23999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>70.95</v>
+        <v>58.49</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>138.106</v>
+        <v>16.6141</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>129.1296</v>
+        <v>17.65</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>8.9764</v>
+        <v>-1.0359</v>
       </c>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="2" t="n">
-        <v>46.9</v>
+        <v>38.07</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>1606690</v>
+        <v>998448</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>2993011</v>
+        <v>1765600</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>372527</v>
+        <v>106690</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>36.899784</v>
+        <v>60.540436</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>47.936844</v>
+        <v>43.6306</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>13.66</v>
+        <v>41.39</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>119.56</v>
+        <v>12.394</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AG8" s="2" t="inlineStr"/>
+        <v>22.1</v>
+      </c>
+      <c r="AG8" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="AH8" s="2" t="n">
-        <v>4.333867</v>
+        <v>25.154284</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>1.035</v>
+        <v>1.31</v>
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIENT/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
@@ -1679,18 +1679,18 @@
           <t>Credit Services</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>61.4</v>
+      <c r="E9" s="5" t="n">
+        <v>58.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>322.4</v>
+        <v>324.1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.02</v>
+        <v>0.53</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>303.96</v>
+        <v>305.88</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>291.94</v>
+        <v>293.21</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>280.07</v>
+        <v>279.98</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -1724,41 +1724,41 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>99.37</v>
+        <v>99.13</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>67.06999999999999</v>
+        <v>67.88</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>9.903700000000001</v>
+        <v>10.291</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>9.334199999999999</v>
+        <v>9.525600000000001</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.5695</v>
+        <v>0.7654</v>
       </c>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="n">
-        <v>24.79</v>
+        <v>24.92</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>7531083</v>
+        <v>5037773</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4640929</v>
+        <v>4765980</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>30444</v>
+        <v>30589</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>27.700855</v>
+        <v>27.833334</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>11.036321</v>
+        <v>11.089102</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>6.97</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AG9" s="4" t="inlineStr"/>
       <c r="AH9" s="4" t="n">
-        <v>1.6903098</v>
+        <v>1.6983936</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>62</v>
@@ -1831,19 +1831,19 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1024.65</v>
+        <v>1038.85</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1005.12</v>
+        <v>1008.33</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>939.1900000000001</v>
+        <v>943.1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>802.5599999999999</v>
+        <v>801.9</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1856,41 +1856,41 @@
         </is>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>86.25</v>
+        <v>87.45</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>56.54</v>
+        <v>58.67</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>26.4053</v>
+        <v>26.156</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>39.2697</v>
+        <v>36.647</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>-12.8644</v>
+        <v>-10.491</v>
       </c>
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="2" t="n">
-        <v>36.43</v>
+        <v>36.08</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>1700509</v>
+        <v>1027398</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>1766545</v>
+        <v>1762148</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.96</v>
+        <v>0.58</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>20011</v>
+        <v>20365</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>61.434063</v>
+        <v>62.448315</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>36.52029</v>
+        <v>37.167137</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>14.14</v>
@@ -1905,10 +1905,10 @@
         <v>43.7</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>6.8872356</v>
+        <v>7.0092216</v>
       </c>
       <c r="AI10" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ10" s="2" t="n">
         <v>1.7</v>
@@ -1927,32 +1927,32 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Oil and Natural Gas Corporation Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Integrated</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>15.8</v>
+        <v>18.6</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1965,19 +1965,19 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>295.85</v>
+        <v>1844.6</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.82</v>
+        <v>-2.47</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>292.49</v>
+        <v>1833.9</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>284.49</v>
+        <v>1787.04</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>258.97</v>
+        <v>1726.17</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -1990,99 +1990,103 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>96.20999999999999</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>56.04</v>
+        <v>54.53</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.6242</v>
+        <v>36.6334</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>3.434</v>
+        <v>36.2794</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1902</v>
+        <v>0.354</v>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="n">
-        <v>26.84</v>
+        <v>28.11</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>14084672</v>
+        <v>3610732</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>17739652</v>
+        <v>4944728</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>364828</v>
+        <v>441622</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>9.589947</v>
+        <v>38.522396</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>6.8484125</v>
-      </c>
-      <c r="AD11" s="4" t="inlineStr"/>
+        <v>28.37593</v>
+      </c>
+      <c r="AD11" s="4" t="n">
+        <v>14.72</v>
+      </c>
       <c r="AE11" s="4" t="n">
-        <v>43.805</v>
+        <v>5.517</v>
       </c>
       <c r="AF11" s="4" t="n">
-        <v>0.8</v>
+        <v>12.8</v>
       </c>
       <c r="AG11" s="4" t="n">
-        <v>16.2</v>
+        <v>25.6</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>0.99115145</v>
+        <v>5.6727753</v>
       </c>
       <c r="AI11" s="4" t="n">
-        <v>625</v>
-      </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="AJ11" s="4" t="n">
+        <v>2.824</v>
+      </c>
       <c r="AK11" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ONGC/</t>
+          <t>https://www.screener.in/company/SUNPHARMA/</t>
         </is>
       </c>
       <c r="AL11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ONGC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Limited</t>
+          <t>Bandhan Bank Limited</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>57.8</v>
+        <v>57.4</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>24.8</v>
+        <v>21.4</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -2091,23 +2095,23 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1793.3</v>
+        <v>194.61</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1713.46</v>
+        <v>192.26</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1612.96</v>
+        <v>182.41</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1481.48</v>
+        <v>166.92</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2120,103 +2124,99 @@
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>98.31999999999999</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>66.78</v>
+        <v>55.93</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>65.0986</v>
+        <v>4.1264</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>68.1972</v>
+        <v>6.2448</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>-3.0985</v>
+        <v>-2.1185</v>
       </c>
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="n">
-        <v>29.96</v>
+        <v>23.69</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>1628329</v>
+        <v>11298203</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>3351371</v>
+        <v>17552798</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.49</v>
+        <v>0.64</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>411694</v>
+        <v>31732</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>30.660604</v>
+        <v>25.951252</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>23.039103</v>
+        <v>9.145163999999999</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>15.59</v>
-      </c>
-      <c r="AE12" s="2" t="n">
-        <v>64.051</v>
-      </c>
+        <v>4.88</v>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
       <c r="AF12" s="2" t="n">
-        <v>26.5</v>
+        <v>119.3</v>
       </c>
       <c r="AG12" s="2" t="n">
-        <v>3.6</v>
+        <v>68</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>4.282554</v>
+        <v>1.2390856</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ12" s="2" t="n">
-        <v>1.394</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr"/>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIPORTS/</t>
+          <t>https://www.screener.in/company/BANDHANBNK/</t>
         </is>
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BANDHANBNK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>JSW Steel Limited</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
         <v>57</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -2225,23 +2225,23 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1891.3</v>
+        <v>1285.5</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1832.77</v>
+        <v>1270.68</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1784.7</v>
+        <v>1243.26</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1727.92</v>
+        <v>1166.6</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -2254,67 +2254,71 @@
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>98.68000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>64</v>
+        <v>57.35</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>40.7978</v>
+        <v>15.0185</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>36.1909</v>
+        <v>16.899</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.6069</v>
+        <v>-1.8804</v>
       </c>
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="n">
-        <v>28.89</v>
+        <v>17.19</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1605806</v>
+        <v>588674</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5244498</v>
+        <v>1881873</v>
       </c>
       <c r="Z13" s="4" t="n">
         <v>0.31</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>442581</v>
+        <v>314695</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>40.4695</v>
+        <v>14.1273155</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>28.308376</v>
-      </c>
-      <c r="AD13" s="4" t="inlineStr"/>
+        <v>17.75764</v>
+      </c>
+      <c r="AD13" s="4" t="n">
+        <v>27.26</v>
+      </c>
       <c r="AE13" s="4" t="n">
-        <v>6.675</v>
+        <v>94.155</v>
       </c>
       <c r="AF13" s="4" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="AG13" s="4" t="n">
-        <v>15.7</v>
+        <v>991.8</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>5.685103</v>
+        <v>3.145415</v>
       </c>
       <c r="AI13" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="AJ13" s="4" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AJ13" s="4" t="n">
+        <v>1.491</v>
+      </c>
       <c r="AK13" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/SUNPHARMA/</t>
+          <t>https://www.screener.in/company/JSWSTEEL/</t>
         </is>
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
         </is>
       </c>
     </row>
@@ -2359,19 +2363,19 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1461.8</v>
+        <v>1473</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-0.18</v>
+        <v>0.77</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1261.74</v>
+        <v>1281.86</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1138.5</v>
+        <v>1151.61</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1000.81</v>
+        <v>1003.67</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -2384,41 +2388,41 @@
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>96.66</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>74.26000000000001</v>
+        <v>74.83</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>97.3484</v>
+        <v>102.0446</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>79.27</v>
+        <v>83.8249</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>18.0784</v>
+        <v>18.2197</v>
       </c>
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="n">
-        <v>35.79</v>
+        <v>36.86</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>695194</v>
+        <v>357761</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>890863</v>
+        <v>901540</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>9838</v>
+        <v>10093</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>87.62642</v>
+        <v>90.00595</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>45.035072</v>
+        <v>46.202988</v>
       </c>
       <c r="AD14" s="2" t="n">
         <v>16.94</v>
@@ -2433,7 +2437,7 @@
         <v>69</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>15.092523</v>
+        <v>13.988189</v>
       </c>
       <c r="AI14" s="2" t="n">
         <v>0</v>
@@ -2455,12 +2459,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2470,17 +2474,17 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>11.8</v>
+        <v>19</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -2489,23 +2493,23 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4469.2</v>
+        <v>8362.5</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4345.95</v>
+        <v>7983.06</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4259.02</v>
+        <v>7769.4</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3932.97</v>
+        <v>7464.56</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -2518,67 +2522,71 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>98.11</v>
+        <v>99.08</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>61.21</v>
+        <v>72.61</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>66.76430000000001</v>
+        <v>158.9036</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>55.447</v>
+        <v>129.8027</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>11.3172</v>
+        <v>29.1008</v>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="n">
-        <v>24.61</v>
+        <v>25.65</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>245755</v>
+        <v>564876</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>271204</v>
+        <v>441179</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.91</v>
+        <v>1.28</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>151833</v>
+        <v>120837</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>66.91826</v>
+        <v>62.4183</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>69.271034</v>
-      </c>
-      <c r="AD15" s="4" t="inlineStr"/>
+        <v>39.287693</v>
+      </c>
+      <c r="AD15" s="4" t="n">
+        <v>21.5</v>
+      </c>
       <c r="AE15" s="4" t="n">
-        <v>33.4</v>
+        <v>85.146</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="AG15" s="4" t="n">
-        <v>26.1</v>
+        <v>35.6</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>17.98314</v>
+        <v>12.743567</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="AJ15" s="4" t="n">
+        <v>1.065</v>
+      </c>
       <c r="AK15" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TORNTPHARM/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
@@ -2619,23 +2627,23 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>328.75</v>
+        <v>334.35</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.08</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>328.72</v>
+        <v>329.26</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>321.71</v>
+        <v>322.2</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>295.13</v>
+        <v>295.42</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2648,41 +2656,41 @@
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>93.95999999999999</v>
+        <v>95.56</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>51.31</v>
+        <v>54.83</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>2.9374</v>
+        <v>3.0606</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>4.648</v>
+        <v>4.3305</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>-1.7106</v>
+        <v>-1.27</v>
       </c>
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="2" t="n">
-        <v>18.76</v>
+        <v>17.79</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>2458845</v>
+        <v>3833075</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>6409024</v>
+        <v>5977705</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.38</v>
+        <v>0.64</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>20686</v>
+        <v>21243</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>23.712767</v>
+        <v>24.385654</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>17.617908</v>
+        <v>18.092144</v>
       </c>
       <c r="AD16" s="2" t="inlineStr"/>
       <c r="AE16" s="2" t="inlineStr"/>
@@ -2693,7 +2701,7 @@
         <v>367.9</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>1.2357199</v>
+        <v>1.268983</v>
       </c>
       <c r="AI16" s="2" t="n">
         <v>33</v>
@@ -2751,19 +2759,19 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>490.15</v>
+        <v>480.35</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.55</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>438.07</v>
+        <v>442.09</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>403.11</v>
+        <v>406.14</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>355.97</v>
+        <v>356.67</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
@@ -2776,41 +2784,41 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>98.28</v>
+        <v>96.31</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>80.68000000000001</v>
+        <v>73.67</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>26.9822</v>
+        <v>26.9755</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>21.0034</v>
+        <v>22.1978</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>5.9789</v>
+        <v>4.7777</v>
       </c>
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="n">
-        <v>45.03</v>
+        <v>46.07</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>958244</v>
+        <v>628254</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1503564</v>
+        <v>1521160</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>12591</v>
+        <v>12640</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>30.440432</v>
+        <v>30.522152</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>18.035673</v>
+        <v>18.107012</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>10.66</v>
@@ -2819,16 +2827,16 @@
         <v>40.071</v>
       </c>
       <c r="AF17" s="4" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="AG17" s="4" t="n">
-        <v>5.9</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>3.109766</v>
+        <v>3.1220665</v>
       </c>
       <c r="AI17" s="4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ17" s="4" t="n">
         <v>1.141</v>
@@ -2885,19 +2893,19 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>739</v>
+        <v>775.95</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-1.9</v>
+        <v>5</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>716.74</v>
+        <v>722.38</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>604.59</v>
+        <v>611.3099999999999</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>498.97</v>
+        <v>499.46</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -2910,39 +2918,39 @@
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>83.22</v>
+        <v>87.38</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>57.69</v>
+        <v>61.52</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>71.4462</v>
+        <v>67.58750000000001</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>81.86799999999999</v>
+        <v>79.0119</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>-10.4218</v>
+        <v>-11.4244</v>
       </c>
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="n">
-        <v>42.56</v>
+        <v>40.93</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>276663</v>
+        <v>328037</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>2822101</v>
+        <v>2802911</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>3367</v>
+        <v>3535</v>
       </c>
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="n">
-        <v>27.811829</v>
+        <v>29.200718</v>
       </c>
       <c r="AD18" s="2" t="n">
         <v>-2.82</v>
@@ -2955,7 +2963,7 @@
       </c>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="n">
-        <v>5.663993</v>
+        <v>5.946846</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>0</v>
@@ -2977,32 +2985,32 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CESC Limited</t>
+          <t>Nestlé India Limited</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Packaged Foods</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>32</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -3011,23 +3019,23 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>179.84</v>
+        <v>1423.1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.45</v>
+        <v>1.18</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>180.31</v>
+        <v>1423.65</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>173.17</v>
+        <v>1367.49</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>164.53</v>
+        <v>1274.91</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -3040,103 +3048,103 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>87.94</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>51.7</v>
+        <v>54.63</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.4421</v>
+        <v>23.4138</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>4.1379</v>
+        <v>37.5676</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.6958</v>
+        <v>-14.1538</v>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="n">
-        <v>33.68</v>
+        <v>41.92</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1821751</v>
+        <v>1306017</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>4697031</v>
+        <v>1930722</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>23492</v>
+        <v>272587</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>15.225085</v>
+        <v>77.585075</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>12.359395</v>
+        <v>59.672585</v>
       </c>
       <c r="AD19" s="4" t="n">
-        <v>12.55</v>
+        <v>76.34</v>
       </c>
       <c r="AE19" s="4" t="n">
-        <v>164.311</v>
+        <v>8.613</v>
       </c>
       <c r="AF19" s="4" t="n">
-        <v>5.6</v>
+        <v>23.8</v>
       </c>
       <c r="AG19" s="4" t="n">
-        <v>17.8</v>
+        <v>27.4</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>1.8459456</v>
+        <v>52.858692</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.921</v>
+        <v>0.964</v>
       </c>
       <c r="AK19" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CESC/</t>
+          <t>https://www.screener.in/company/NESTLEIND/</t>
         </is>
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Nestlé India Limited</t>
+          <t>Aurobindo Pharma Limited</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Packaged Foods</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -3145,23 +3153,23 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1406.5</v>
+        <v>1463.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-0.96</v>
+        <v>-5.38</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1423.71</v>
+        <v>1468.91</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1365.22</v>
+        <v>1395.31</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1272.27</v>
+        <v>1249.19</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -3174,83 +3182,83 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>93.89</v>
+        <v>94.42</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>49.69</v>
+        <v>52.81</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>26.4144</v>
+        <v>38.6243</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>41.1061</v>
+        <v>41.4386</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>-14.6917</v>
+        <v>-2.8142</v>
       </c>
       <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="n">
-        <v>44.17</v>
+        <v>27.29</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>2049251</v>
+        <v>3038819</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>2036392</v>
+        <v>1252589</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>1.01</v>
+        <v>2.43</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>274418</v>
+        <v>83694</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>78.450935</v>
+        <v>24.122719</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>60.073612</v>
+        <v>16.41533</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>76.34</v>
+        <v>9.93</v>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>8.613</v>
+        <v>21.31</v>
       </c>
       <c r="AF20" s="2" t="n">
-        <v>23.8</v>
+        <v>5.6</v>
       </c>
       <c r="AG20" s="2" t="n">
-        <v>27.4</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>53.213924</v>
+        <v>2.2299075</v>
       </c>
       <c r="AI20" s="2" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="AJ20" s="2" t="n">
-        <v>0.964</v>
+        <v>1.813</v>
       </c>
       <c r="AK20" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NESTLEIND/</t>
+          <t>https://www.screener.in/company/AUROPHARMA/</t>
         </is>
       </c>
       <c r="AL20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bandhan Bank Limited</t>
+          <t>The Federal Bank Limited</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3264,13 +3272,13 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>49.4</v>
+        <v>50.6</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -3279,23 +3287,23 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>191.08</v>
+        <v>287.2</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>192.01</v>
+        <v>286.81</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>181.91</v>
+        <v>284.16</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>167.05</v>
+        <v>257.72</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
@@ -3308,99 +3316,99 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>89.84999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>52.13</v>
+        <v>50.87</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.4157</v>
+        <v>0.0703</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>6.7745</v>
+        <v>0.7683</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.3588</v>
+        <v>-0.698</v>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="n">
-        <v>24.67</v>
+        <v>12.8</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>7549122</v>
+        <v>6756952</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>17529679</v>
+        <v>8152862</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>31352</v>
+        <v>71273</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>25.640316</v>
+        <v>16.538021</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>9.035591</v>
+        <v>12.173913</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>4.88</v>
+        <v>11.73</v>
       </c>
       <c r="AE21" s="4" t="inlineStr"/>
       <c r="AF21" s="4" t="n">
-        <v>119.3</v>
+        <v>12.3</v>
       </c>
       <c r="AG21" s="4" t="n">
-        <v>68</v>
+        <v>22.2</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>1.2242395</v>
+        <v>1.7806026</v>
       </c>
       <c r="AI21" s="4" t="n">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="AJ21" s="4" t="inlineStr"/>
       <c r="AK21" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BANDHANBNK/</t>
+          <t>https://www.screener.in/company/FEDERALBNK/</t>
         </is>
       </c>
       <c r="AL21" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BANDHANBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>CESC Limited</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>49</v>
+        <v>50.4</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -3409,23 +3417,23 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>460.2</v>
+        <v>177.22</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.33</v>
+        <v>-1.46</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>460.59</v>
+        <v>180.01</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>452.99</v>
+        <v>173.33</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>416.93</v>
+        <v>164.39</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -3438,103 +3446,103 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>93.68000000000001</v>
+        <v>86.66</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>50.78</v>
+        <v>48.36</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>1.6205</v>
+        <v>1.9388</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>3.2312</v>
+        <v>3.6981</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>-1.6108</v>
+        <v>-1.7592</v>
       </c>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="n">
-        <v>14.42</v>
+        <v>31.76</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>7425043</v>
+        <v>5770683</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>10937365</v>
+        <v>4881721</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.68</v>
+        <v>1.18</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>281359</v>
+        <v>24601</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>9.051348000000001</v>
+        <v>15.957867</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>7.983393</v>
+        <v>12.943122</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>28.12</v>
+        <v>12.55</v>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>11.629</v>
+        <v>164.311</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>16.2</v>
+        <v>5.6</v>
       </c>
       <c r="AG22" s="2" t="n">
-        <v>12.9</v>
+        <v>17.8</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>2.362117</v>
+        <v>1.9331285</v>
       </c>
       <c r="AI22" s="2" t="n">
-        <v>478</v>
+        <v>339</v>
       </c>
       <c r="AJ22" s="2" t="n">
-        <v>1.856</v>
+        <v>0.921</v>
       </c>
       <c r="AK22" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/COALINDIA/</t>
+          <t>https://www.screener.in/company/CESC/</t>
         </is>
       </c>
       <c r="AL22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:COALINDIA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>HFCL Limited</t>
+          <t>Larsen &amp; Toubro Limited</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>47</v>
+        <v>48.8</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>10</v>
+        <v>21.8</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -3547,19 +3555,19 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>141.75</v>
+        <v>3926.6</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.73</v>
+        <v>0.93</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>131.4</v>
+        <v>3911.42</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>109.27</v>
+        <v>3900.11</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>85</v>
+        <v>3799.96</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -3572,98 +3580,100 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>91.27</v>
+        <v>89.3</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>67.43000000000001</v>
+        <v>51.68</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>13.2906</v>
+        <v>-3.4272</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>15.0023</v>
+        <v>6.4014</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.7117</v>
+        <v>-9.8286</v>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="n">
-        <v>58.8</v>
+        <v>10.17</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>40951694</v>
+        <v>1330428</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>82063174</v>
+        <v>2463148</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>22680</v>
+        <v>554862</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>423.45718</v>
+        <v>34.47056</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>28.501925</v>
+        <v>21.94283</v>
       </c>
       <c r="AD23" s="4" t="n">
-        <v>7.27</v>
+        <v>16.95</v>
       </c>
       <c r="AE23" s="4" t="n">
-        <v>38.321</v>
+        <v>97.64</v>
       </c>
       <c r="AF23" s="4" t="n">
-        <v>127.8</v>
-      </c>
-      <c r="AG23" s="4" t="inlineStr"/>
+        <v>11.7</v>
+      </c>
+      <c r="AG23" s="4" t="n">
+        <v>-34.5</v>
+      </c>
       <c r="AH23" s="4" t="n">
-        <v>4.4704857</v>
+        <v>5.0768437</v>
       </c>
       <c r="AI23" s="4" t="n">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>1.991</v>
+        <v>1.251</v>
       </c>
       <c r="AK23" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/HFCL/</t>
+          <t>https://www.screener.in/company/LT/</t>
         </is>
       </c>
       <c r="AL23" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Limited</t>
+          <t>HFCL Limited</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>10</v>
@@ -3679,19 +3689,19 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1318.5</v>
+        <v>148.21</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-0.26</v>
+        <v>4.56</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1302.17</v>
+        <v>133</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1284.73</v>
+        <v>110.8</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1257.4</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -3704,71 +3714,69 @@
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>95.83</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>55.2</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>13.5186</v>
+        <v>13.0393</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>11.7532</v>
+        <v>14.6097</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>1.7654</v>
+        <v>-1.5704</v>
       </c>
       <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="2" t="n">
-        <v>14.81</v>
+        <v>57.65</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>2183121</v>
+        <v>44851554</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>2637262</v>
+        <v>82733845</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.83</v>
+        <v>0.54</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>108837</v>
+        <v>24919</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>25.951956</v>
+        <v>452.3333</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>20.26368</v>
+        <v>31.315386</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>11.83</v>
+        <v>7.27</v>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>20.328</v>
+        <v>38.321</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="AG24" s="2" t="n">
-        <v>-86.2</v>
-      </c>
+        <v>127.8</v>
+      </c>
+      <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="n">
-        <v>2.8903089</v>
+        <v>4.9117727</v>
       </c>
       <c r="AI24" s="2" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="AJ24" s="2" t="n">
-        <v>1.802</v>
+        <v>1.991</v>
       </c>
       <c r="AK24" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DRREDDY/</t>
+          <t>https://www.screener.in/company/HFCL/</t>
         </is>
       </c>
       <c r="AL24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DRREDDY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
         </is>
       </c>
     </row>
@@ -3813,19 +3821,19 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1401.9</v>
+        <v>1399.2</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1354.77</v>
+        <v>1359</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1325.86</v>
+        <v>1328.74</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1393.85</v>
+        <v>1389.79</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -3838,41 +3846,41 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>83.8</v>
+        <v>83.63</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>62.62</v>
+        <v>61.93</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>35.851</v>
+        <v>34.8657</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>30.0294</v>
+        <v>30.9967</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.8216</v>
+        <v>3.869</v>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="n">
-        <v>37.25</v>
+        <v>36.62</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1145360</v>
+        <v>917323</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2064837</v>
+        <v>1889337</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>113027</v>
+        <v>114215</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>29.186483</v>
+        <v>29.462387</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>22.172165</v>
+        <v>22.376484</v>
       </c>
       <c r="AD25" s="4" t="n">
         <v>11.74</v>
@@ -3887,7 +3895,7 @@
         <v>-54.6</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>3.4333582</v>
+        <v>3.4694293</v>
       </c>
       <c r="AI25" s="4" t="n">
         <v>93</v>
@@ -3909,32 +3917,32 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
         <v>45</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -3943,23 +3951,23 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1546.7</v>
+        <v>456.55</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1.92</v>
+        <v>-0.79</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1469.48</v>
+        <v>460.21</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1392.53</v>
+        <v>453.13</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1251</v>
+        <v>416.19</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -3972,71 +3980,71 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>99.79000000000001</v>
+        <v>92.94</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>76.70999999999999</v>
+        <v>47.87</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>44.5043</v>
+        <v>1.1373</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>42.1421</v>
+        <v>2.8125</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>2.3621</v>
+        <v>-1.6751</v>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="2" t="n">
-        <v>29.33</v>
+        <v>13.65</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>1013775</v>
+        <v>9201635</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>1149031</v>
+        <v>10575351</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>84207</v>
+        <v>282253</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>24.262268</v>
+        <v>9.078295000000001</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>16.824411</v>
+        <v>8.008748000000001</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>9.93</v>
+        <v>28.12</v>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>21.31</v>
+        <v>11.629</v>
       </c>
       <c r="AF26" s="2" t="n">
-        <v>7</v>
+        <v>16.2</v>
       </c>
       <c r="AG26" s="2" t="n">
-        <v>1.9</v>
+        <v>12.9</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>2.4254427</v>
+        <v>2.3696191</v>
       </c>
       <c r="AI26" s="2" t="n">
-        <v>26</v>
+        <v>482</v>
       </c>
       <c r="AJ26" s="2" t="n">
-        <v>1.813</v>
+        <v>1.856</v>
       </c>
       <c r="AK26" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AUROPHARMA/</t>
+          <t>https://www.screener.in/company/COALINDIA/</t>
         </is>
       </c>
       <c r="AL26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:COALINDIA</t>
         </is>
       </c>
     </row>
@@ -4081,19 +4089,19 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1472.8</v>
+        <v>1478.4</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.18</v>
+        <v>0.38</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1432.59</v>
+        <v>1436.96</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1413.23</v>
+        <v>1415.78</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1441.19</v>
+        <v>1441.48</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -4106,41 +4114,41 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>93.51000000000001</v>
+        <v>93.87</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>60.88</v>
+        <v>61.81</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>23.8957</v>
+        <v>24.538</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>21.1728</v>
+        <v>21.8458</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.7229</v>
+        <v>2.6922</v>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="n">
-        <v>18.65</v>
+        <v>18.29</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>465411</v>
+        <v>533048</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1074352</v>
+        <v>1075683</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>150468</v>
+        <v>150346</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>61.574345</v>
+        <v>61.678493</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>48.76969</v>
+        <v>48.730103</v>
       </c>
       <c r="AD27" s="4" t="n">
         <v>23.52</v>
@@ -4155,7 +4163,7 @@
         <v>37</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>15.753133</v>
+        <v>15.740346</v>
       </c>
       <c r="AI27" s="4" t="n">
         <v>68</v>
@@ -4177,32 +4185,32 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>Trent Limited</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Apparel Retail</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>43.4</v>
+        <v>44.5</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>15</v>
+        <v>25.5</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>28.4</v>
+        <v>19</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
@@ -4211,112 +4219,112 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 💎 High ROE</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3056.6</v>
+        <v>4296.5</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.71</v>
+        <v>3.02</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3132.01</v>
+        <v>4135.22</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3125.18</v>
+        <v>4052.1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>3021.85</v>
+        <v>4292.4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>79.13</v>
+        <v>68.62</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>42.25</v>
+        <v>61.01</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>-52.7758</v>
+        <v>38.0988</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>-26.0231</v>
+        <v>47.4099</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>-26.7528</v>
+        <v>-9.311</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
       <c r="W28" s="2" t="n">
-        <v>17.78</v>
+        <v>16.6</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>949176</v>
+        <v>1087977</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>1492341</v>
+        <v>693351</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.64</v>
+        <v>1.57</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>86223</v>
+        <v>152860</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>26.43298</v>
+        <v>88.56849</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>17.278694</v>
+        <v>57.508495</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>31.57</v>
+        <v>27.13</v>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>21.402</v>
+        <v>36.034</v>
       </c>
       <c r="AF28" s="2" t="n">
-        <v>111.8</v>
+        <v>19.2</v>
       </c>
       <c r="AG28" s="2" t="n">
-        <v>71.2</v>
+        <v>25.8</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>5.9687614</v>
+        <v>21.885735</v>
       </c>
       <c r="AI28" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ28" s="2" t="n">
-        <v>1.383</v>
+        <v>1.264</v>
       </c>
       <c r="AK28" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/WAAREEENER/</t>
+          <t>https://www.screener.in/company/TRENT/</t>
         </is>
       </c>
       <c r="AL28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:WAAREEENER</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TRENT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Asian Paints Limited</t>
+          <t>Berger Paints India Limited</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -4330,13 +4338,13 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>34.5</v>
+        <v>29.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.8</v>
+        <v>14.6</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
@@ -4349,19 +4357,19 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2598.8</v>
+        <v>501.15</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2538.64</v>
+        <v>495.27</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2471.54</v>
+        <v>478.18</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2479.35</v>
+        <v>497.56</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -4374,99 +4382,103 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>87.04000000000001</v>
+        <v>83.39</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>61.73</v>
+        <v>55.34</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>57.3423</v>
+        <v>13.7872</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>57.0371</v>
+        <v>14.9989</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.3052</v>
+        <v>-1.2116</v>
       </c>
       <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="n">
-        <v>27.67</v>
+        <v>31.59</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1031843</v>
+        <v>315514</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>950823</v>
+        <v>986339</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>1.09</v>
+        <v>0.32</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>253063</v>
+        <v>58866</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>65.96202</v>
+        <v>52.20786</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>52.78058</v>
-      </c>
-      <c r="AD29" s="4" t="inlineStr"/>
+        <v>39.75516</v>
+      </c>
+      <c r="AD29" s="4" t="n">
+        <v>17.23</v>
+      </c>
       <c r="AE29" s="4" t="n">
-        <v>17.609</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="AF29" s="4" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="AG29" s="4" t="n">
-        <v>-4.6</v>
+        <v>27.7</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>12.918666</v>
+        <v>8.514495999999999</v>
       </c>
       <c r="AI29" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="AJ29" s="4" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="AJ29" s="4" t="n">
+        <v>2.115</v>
+      </c>
       <c r="AK29" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ASIANPAINT/</t>
+          <t>https://www.screener.in/company/BERGEPAINT/</t>
         </is>
       </c>
       <c r="AL29" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ASIANPAINT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The Federal Bank Limited</t>
+          <t>Power Grid Corporation of India Limited</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>41.6</v>
+        <v>43.4</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>23.6</v>
+        <v>16.4</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -4475,23 +4487,23 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>283.75</v>
+        <v>294.3</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-2.12</v>
+        <v>-1.75</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>286.77</v>
+        <v>305.43</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>284.03</v>
+        <v>303.63</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>257.5</v>
+        <v>288.7</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -4500,103 +4512,107 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>93.95999999999999</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>46.94</v>
+        <v>33.94</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>0.0133</v>
+        <v>-3.1299</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>0.9428</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>-0.9295</v>
+        <v>-2.2897</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="n">
-        <v>13.3</v>
+        <v>25.29</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>6916472</v>
+        <v>15105294</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>8177205</v>
+        <v>9998853</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>0.85</v>
+        <v>1.51</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>70768</v>
+        <v>274693</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>16.430206</v>
+        <v>14.69403</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>12.087634</v>
+        <v>14.827611</v>
       </c>
       <c r="AD30" s="2" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="AE30" s="2" t="inlineStr"/>
+        <v>16.49</v>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>150.993</v>
+      </c>
       <c r="AF30" s="2" t="n">
-        <v>12.3</v>
+        <v>-5</v>
       </c>
       <c r="AG30" s="2" t="n">
-        <v>22.2</v>
+        <v>9.6</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>1.767983</v>
+        <v>2.73242</v>
       </c>
       <c r="AI30" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ30" s="2" t="inlineStr"/>
+        <v>416</v>
+      </c>
+      <c r="AJ30" s="2" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AK30" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/FEDERALBNK/</t>
+          <t>https://www.screener.in/company/POWERGRID/</t>
         </is>
       </c>
       <c r="AL30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Berger Paints India Limited</t>
+          <t>Dr. Reddy's Laboratories Limited</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>41.1</v>
+        <v>43</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>26.5</v>
+        <v>33</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>14.6</v>
+        <v>10</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -4605,27 +4621,27 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>499.35</v>
+        <v>1307.2</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.79</v>
+        <v>-0.86</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>494.65</v>
+        <v>1302.65</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>477.24</v>
+        <v>1285.61</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>497.11</v>
+        <v>1254.13</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -4634,132 +4650,128 @@
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>83.09</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>54.68</v>
+        <v>52.41</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>15.1241</v>
+        <v>12.2401</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>15.3018</v>
+        <v>11.8506</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.1777</v>
+        <v>0.3895</v>
       </c>
       <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="n">
-        <v>31.78</v>
+        <v>14.03</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>440704</v>
+        <v>2002451</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>976222</v>
+        <v>2455449</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>58434</v>
+        <v>110852</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>51.98651</v>
+        <v>26.453407</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>39.4638</v>
+        <v>20.638819</v>
       </c>
       <c r="AD31" s="4" t="n">
-        <v>17.23</v>
+        <v>11.83</v>
       </c>
       <c r="AE31" s="4" t="n">
-        <v>9.164999999999999</v>
+        <v>20.328</v>
       </c>
       <c r="AF31" s="4" t="n">
-        <v>6.1</v>
+        <v>-11.6</v>
       </c>
       <c r="AG31" s="4" t="n">
-        <v>27.7</v>
+        <v>-86.2</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>8.452094000000001</v>
+        <v>2.943817</v>
       </c>
       <c r="AI31" s="4" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>2.115</v>
+        <v>1.802</v>
       </c>
       <c r="AK31" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BERGEPAINT/</t>
+          <t>https://www.screener.in/company/DRREDDY/</t>
         </is>
       </c>
       <c r="AL31" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Limited</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Furnishings, Fixtures &amp; Appliances</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>41</v>
+        <v>42.4</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7</v>
+        <v>21.4</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>📈 EMA Bull Stack | 📊 High Volume</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="n">
-        <v>7537</v>
+        <v>1285.4</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>6.92</v>
+        <v>2.56</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>7842.48</v>
+        <v>1270.73</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7620.45</v>
+        <v>1282.73</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>7273</v>
+        <v>1246.58</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4768,103 +4780,99 @@
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>83.98999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>45.69</v>
+        <v>52.85</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>-19.7644</v>
+        <v>-11.6616</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>156.9902</v>
+        <v>-11.4415</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>-176.7546</v>
+        <v>-0.2201</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="2" t="n">
-        <v>25.53</v>
+        <v>15.25</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>1293057</v>
+        <v>5016900</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>497897</v>
+        <v>7125439</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>25918</v>
+        <v>407731</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>145.72278</v>
+        <v>15.526347</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>38.715847</v>
+        <v>10.406349</v>
       </c>
       <c r="AD32" s="2" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="AE32" s="2" t="n">
-        <v>46.566</v>
-      </c>
+        <v>13.15</v>
+      </c>
+      <c r="AE32" s="2" t="inlineStr"/>
       <c r="AF32" s="2" t="n">
-        <v>10.5</v>
+        <v>-11.2</v>
       </c>
       <c r="AG32" s="2" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>5.9238043</v>
+        <v>1.8944746</v>
       </c>
       <c r="AI32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="2" t="n">
-        <v>1.131</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr"/>
       <c r="AK32" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AMBER/</t>
+          <t>https://www.screener.in/company/AXISBANK/</t>
         </is>
       </c>
       <c r="AL32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AMBER</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Limited</t>
+          <t>Asian Paints Limited</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>40.4</v>
+        <v>42.3</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>24</v>
+        <v>34.5</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>16.4</v>
+        <v>7.8</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -4873,132 +4881,128 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>299.55</v>
+        <v>2639.8</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.12</v>
+        <v>1.58</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>306.6</v>
+        <v>2548.27</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>304.01</v>
+        <v>2478.14</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>288.5</v>
+        <v>2483</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>92.18000000000001</v>
+        <v>88.41</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>39.18</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-2.5086</v>
+        <v>58.4066</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2678</v>
+        <v>57.311</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-2.2408</v>
+        <v>1.0956</v>
       </c>
       <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="n">
-        <v>25.28</v>
+        <v>27.62</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>10353164</v>
+        <v>1556434</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>9742600</v>
+        <v>1006801</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>273717</v>
+        <v>254788</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>14.64179</v>
+        <v>66.24626000000001</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>14.774897</v>
-      </c>
-      <c r="AD33" s="4" t="n">
-        <v>16.49</v>
-      </c>
+        <v>53.140472</v>
+      </c>
+      <c r="AD33" s="4" t="inlineStr"/>
       <c r="AE33" s="4" t="n">
-        <v>150.993</v>
+        <v>17.609</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>-5</v>
+        <v>3.7</v>
       </c>
       <c r="AG33" s="4" t="n">
-        <v>9.6</v>
+        <v>-4.6</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>2.762576</v>
+        <v>13.006754</v>
       </c>
       <c r="AI33" s="4" t="n">
-        <v>409</v>
-      </c>
-      <c r="AJ33" s="4" t="n">
-        <v>0.625</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr"/>
       <c r="AK33" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POWERGRID/</t>
+          <t>https://www.screener.in/company/ASIANPAINT/</t>
         </is>
       </c>
       <c r="AL33" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERGRID</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Limited</t>
+          <t>Oil and Natural Gas Corporation Limited</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Oil &amp; Gas Integrated</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
         <v>39.8</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>21.8</v>
+        <v>15.8</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
@@ -5011,19 +5015,19 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>3890.5</v>
+        <v>290</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.46</v>
+        <v>-1.98</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3909.82</v>
+        <v>292.25</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3899.04</v>
+        <v>284.7</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3819.98</v>
+        <v>257.51</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -5036,103 +5040,99 @@
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>88.48</v>
+        <v>94.31</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>48.43</v>
+        <v>49.29</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>-5.814</v>
+        <v>2.9911</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>8.858599999999999</v>
+        <v>3.3455</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>-14.6726</v>
+        <v>-0.3543</v>
       </c>
       <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="2" t="n">
-        <v>10.76</v>
+        <v>25.82</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>1624945</v>
+        <v>11563330</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>2504737</v>
+        <v>17728322</v>
       </c>
       <c r="Z34" s="2" t="n">
         <v>0.65</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>540170</v>
+        <v>358475</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>33.54062</v>
+        <v>9.419835000000001</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>21.401329</v>
-      </c>
-      <c r="AD34" s="2" t="n">
-        <v>16.95</v>
-      </c>
+        <v>6.729156</v>
+      </c>
+      <c r="AD34" s="2" t="inlineStr"/>
       <c r="AE34" s="2" t="n">
-        <v>97.64</v>
+        <v>43.805</v>
       </c>
       <c r="AF34" s="2" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="AG34" s="2" t="n">
-        <v>-34.5</v>
+        <v>16.2</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>4.9424148</v>
+        <v>0.9738918</v>
       </c>
       <c r="AI34" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="AJ34" s="2" t="n">
-        <v>1.251</v>
-      </c>
+        <v>638</v>
+      </c>
+      <c r="AJ34" s="2" t="inlineStr"/>
       <c r="AK34" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/LT/</t>
+          <t>https://www.screener.in/company/ONGC/</t>
         </is>
       </c>
       <c r="AL34" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ONGC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Limited</t>
+          <t>NTPC Limited</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Discount Stores</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>39.4</v>
+        <v>38.8</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>15.4</v>
+        <v>17.8</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -5141,23 +5141,23 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4137.2</v>
+        <v>388.65</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.17</v>
+        <v>-0.04</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>4330.45</v>
+        <v>392.89</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4263.34</v>
+        <v>386.86</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4132.53</v>
+        <v>359.65</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
@@ -5166,107 +5166,107 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>83.59</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>34.81</v>
+        <v>45.97</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-34.2653</v>
+        <v>0.0279</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>11.2351</v>
+        <v>1.761</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-45.5004</v>
+        <v>-1.7331</v>
       </c>
       <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="n">
-        <v>25.56</v>
+        <v>14.99</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>498131</v>
+        <v>11755213</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>355027</v>
+        <v>8411840</v>
       </c>
       <c r="Z35" s="4" t="n">
         <v>1.4</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>268496</v>
+        <v>378218</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>90.46364</v>
+        <v>21.5855</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>58.061115</v>
+        <v>13.747597</v>
       </c>
       <c r="AD35" s="4" t="n">
-        <v>12.94</v>
+        <v>13.69</v>
       </c>
       <c r="AE35" s="4" t="n">
-        <v>9.913</v>
+        <v>118.127</v>
       </c>
       <c r="AF35" s="4" t="n">
-        <v>18.9</v>
+        <v>8</v>
       </c>
       <c r="AG35" s="4" t="n">
-        <v>19.6</v>
+        <v>-1.6</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>10.950983</v>
+        <v>1.8623116</v>
       </c>
       <c r="AI35" s="4" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>1.977</v>
+        <v>0.825</v>
       </c>
       <c r="AK35" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DMART/</t>
+          <t>https://www.screener.in/company/NTPC/</t>
         </is>
       </c>
       <c r="AL35" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DMART</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NTPC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>Tata Steel Limited</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
@@ -5275,23 +5275,23 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 💎 High ROE</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>431</v>
+        <v>209.19</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>443.87</v>
+        <v>211.41</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>434.37</v>
+        <v>207.15</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>403.93</v>
+        <v>186.41</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -5304,103 +5304,103 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>88.59</v>
+        <v>93.22</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>42.68</v>
+        <v>47.74</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>-1.9433</v>
+        <v>0.7791</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>2.7069</v>
+        <v>2.1165</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>-4.6502</v>
+        <v>-1.3374</v>
       </c>
       <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="n">
-        <v>15.69</v>
+        <v>19.01</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>6959709</v>
+        <v>22023114</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>6585962</v>
+        <v>30062214</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>1.06</v>
+        <v>0.73</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>142086</v>
+        <v>262183</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>5.485412</v>
+        <v>28.640327</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>6.613924</v>
+        <v>11.181915</v>
       </c>
       <c r="AD36" s="2" t="n">
-        <v>20.47</v>
+        <v>11.16</v>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>586.0170000000001</v>
+        <v>89.01600000000001</v>
       </c>
       <c r="AF36" s="2" t="n">
-        <v>-15.4</v>
+        <v>12.5</v>
       </c>
       <c r="AG36" s="2" t="n">
-        <v>10.8</v>
+        <v>125.4</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>1.0693519</v>
+        <v>2.7580326</v>
       </c>
       <c r="AI36" s="2" t="n">
-        <v>339</v>
+        <v>191</v>
       </c>
       <c r="AJ36" s="2" t="n">
-        <v>287.366</v>
+        <v>0.748</v>
       </c>
       <c r="AK36" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/PFC/</t>
+          <t>https://www.screener.in/company/TATASTEEL/</t>
         </is>
       </c>
       <c r="AL36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PFC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NTPC Limited</t>
+          <t>Power Finance Corporation Limited</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>14.2</v>
+        <v>20</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
@@ -5409,23 +5409,23 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>📈 EMA Bull Stack | 💎 High ROE</t>
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>388.8</v>
+        <v>430.55</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-0.93</v>
+        <v>-0.1</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>393.34</v>
+        <v>442.61</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>386.79</v>
+        <v>434.22</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>359.48</v>
+        <v>402.97</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
@@ -5434,103 +5434,107 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>93.81999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>46.12</v>
+        <v>42.44</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.4056</v>
+        <v>-2.6578</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>2.1942</v>
+        <v>1.6339</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>-1.7887</v>
+        <v>-4.2917</v>
       </c>
       <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="n">
-        <v>14.95</v>
+        <v>15.43</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>10596954</v>
+        <v>3609645</v>
       </c>
       <c r="Y37" s="4" t="n">
-        <v>8137413</v>
+        <v>6358988</v>
       </c>
       <c r="Z37" s="4" t="n">
-        <v>1.3</v>
+        <v>0.57</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>376861</v>
+        <v>144841</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>21.496128</v>
+        <v>5.5917954</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>14.516919</v>
-      </c>
-      <c r="AD37" s="4" t="inlineStr"/>
+        <v>6.742193</v>
+      </c>
+      <c r="AD37" s="4" t="n">
+        <v>20.47</v>
+      </c>
       <c r="AE37" s="4" t="n">
-        <v>118.127</v>
+        <v>586.0170000000001</v>
       </c>
       <c r="AF37" s="4" t="n">
-        <v>8</v>
+        <v>-15.4</v>
       </c>
       <c r="AG37" s="4" t="n">
-        <v>-1.6</v>
+        <v>10.8</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>1.9606904</v>
+        <v>1.0900908</v>
       </c>
       <c r="AI37" s="4" t="n">
-        <v>292</v>
-      </c>
-      <c r="AJ37" s="4" t="inlineStr"/>
+        <v>339</v>
+      </c>
+      <c r="AJ37" s="4" t="n">
+        <v>287.366</v>
+      </c>
       <c r="AK37" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NTPC/</t>
+          <t>https://www.screener.in/company/PFC/</t>
         </is>
       </c>
       <c r="AL37" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NTPC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PFC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Tata Steel Limited</t>
+          <t>Muthoot Finance Limited</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -5539,27 +5543,27 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>💎 High ROE</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>208.58</v>
+        <v>3296.7</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>211.64</v>
+        <v>3395.12</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>207.07</v>
+        <v>3429.02</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>187.7</v>
+        <v>3287.21</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5568,103 +5572,103 @@
         </is>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>92.95</v>
+        <v>80.12</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>46.79</v>
+        <v>42.52</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>1.0793</v>
+        <v>-40.0488</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>2.4509</v>
+        <v>-15.0266</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>-1.3716</v>
+        <v>-25.0223</v>
       </c>
       <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="n">
-        <v>19.73</v>
+        <v>14.43</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>24385712</v>
+        <v>367680</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>30080012</v>
+        <v>822369</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>260899</v>
+        <v>134669</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>28.5</v>
+        <v>12.718587</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>11.127129</v>
+        <v>9.696198000000001</v>
       </c>
       <c r="AD38" s="2" t="n">
-        <v>11.16</v>
+        <v>30.41</v>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>89.01600000000001</v>
+        <v>379.707</v>
       </c>
       <c r="AF38" s="2" t="n">
-        <v>12.5</v>
+        <v>53.7</v>
       </c>
       <c r="AG38" s="2" t="n">
-        <v>125.4</v>
+        <v>126.7</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>2.7445192</v>
+        <v>3.7805638</v>
       </c>
       <c r="AI38" s="2" t="n">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="AJ38" s="2" t="n">
-        <v>0.748</v>
+        <v>128.286</v>
       </c>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TATASTEEL/</t>
+          <t>https://www.screener.in/company/MUTHOOTFIN/</t>
         </is>
       </c>
       <c r="AL38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Limited</t>
+          <t>Astral Limited</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Textile Manufacturing</t>
+          <t>Building Products &amp; Equipment</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>33.5</v>
+        <v>33.9</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>8</v>
+        <v>15.4</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -5673,19 +5677,19 @@
       </c>
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="4" t="n">
-        <v>951.7</v>
+        <v>1541.7</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-0.71</v>
+        <v>4.17</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>931.17</v>
+        <v>1534.06</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>913.6900000000001</v>
+        <v>1555.2</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>949.7</v>
+        <v>1503.63</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
@@ -5698,99 +5702,103 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>75.92</v>
+        <v>87.17</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>57.23</v>
+        <v>49.83</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>11.2359</v>
+        <v>-21.2589</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>12.3506</v>
+        <v>-17.3065</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>-1.1147</v>
+        <v>-3.9525</v>
       </c>
       <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="n">
-        <v>25.06</v>
+        <v>13.19</v>
       </c>
       <c r="X39" s="4" t="n">
-        <v>179112</v>
+        <v>1094826</v>
       </c>
       <c r="Y39" s="4" t="n">
-        <v>226792</v>
+        <v>607877</v>
       </c>
       <c r="Z39" s="4" t="n">
-        <v>0.79</v>
+        <v>1.8</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>32255</v>
+        <v>41703</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>37.191944</v>
+        <v>77.460075</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>26.112999</v>
-      </c>
-      <c r="AD39" s="4" t="inlineStr"/>
+        <v>45.972458</v>
+      </c>
+      <c r="AD39" s="4" t="n">
+        <v>13.8</v>
+      </c>
       <c r="AE39" s="4" t="n">
-        <v>6.46</v>
+        <v>6.168</v>
       </c>
       <c r="AF39" s="4" t="n">
-        <v>-4</v>
+        <v>24.2</v>
       </c>
       <c r="AG39" s="4" t="n">
-        <v>3</v>
+        <v>18.9</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>6.018329</v>
+        <v>10.274961</v>
       </c>
       <c r="AI39" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="AJ39" s="4" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="AJ39" s="4" t="n">
+        <v>1.762</v>
+      </c>
       <c r="AK39" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/KPRMILL/</t>
+          <t>https://www.screener.in/company/ASTRAL/</t>
         </is>
       </c>
       <c r="AL39" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:KPRMILL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ASTRAL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Tata Power Company Limited</t>
+          <t>Eicher Motors Limited</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Independent Power Producers</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>31</v>
+        <v>32.7</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>10</v>
+        <v>22.2</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
@@ -5799,27 +5807,27 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>💎 High ROE</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>410.5</v>
+        <v>6981.5</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-0.73</v>
+        <v>1.3</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>420.36</v>
+        <v>7048.35</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>412.84</v>
+        <v>7121.11</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>394.31</v>
+        <v>6866.33</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5828,83 +5836,83 @@
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>88.3</v>
+        <v>84.83</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>43.16</v>
+        <v>45.69</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>-2.2566</v>
+        <v>-61.6243</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>1.937</v>
+        <v>-31.8596</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>-4.1935</v>
+        <v>-29.7647</v>
       </c>
       <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="2" t="n">
-        <v>24.93</v>
+        <v>18.25</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>5013888</v>
+        <v>512596</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>7165231</v>
+        <v>434501</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>0.7</v>
+        <v>1.18</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>130657</v>
+        <v>203512</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>34.94872</v>
+        <v>36.87273</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>22.907728</v>
+        <v>27.911718</v>
       </c>
       <c r="AD40" s="2" t="n">
-        <v>11.34</v>
+        <v>23.77</v>
       </c>
       <c r="AE40" s="2" t="n">
-        <v>167.811</v>
+        <v>2.048</v>
       </c>
       <c r="AF40" s="2" t="n">
-        <v>-12.8</v>
+        <v>19.1</v>
       </c>
       <c r="AG40" s="2" t="n">
-        <v>-4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>3.4511862</v>
+        <v>9.20701</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="AJ40" s="2" t="n">
-        <v>0.806</v>
+        <v>1.902</v>
       </c>
       <c r="AK40" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TATAPOWER/</t>
+          <t>https://www.screener.in/company/EICHERMOT/</t>
         </is>
       </c>
       <c r="AL40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Titan Company Limited</t>
+          <t>Amber Enterprises India Limited</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -5914,17 +5922,17 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Luxury Goods</t>
+          <t>Furnishings, Fixtures &amp; Appliances</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>26.5</v>
+        <v>31</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4.5</v>
+        <v>24</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -5933,27 +5941,27 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>💎 High ROE</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>4083.1</v>
+        <v>7359</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-0.57</v>
+        <v>-2.36</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>4227.42</v>
+        <v>7796.43</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>4244.1</v>
+        <v>7610.18</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>3974.84</v>
+        <v>7222.26</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -5962,103 +5970,103 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>88.67</v>
+        <v>82</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>39.28</v>
+        <v>43.2</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>-62.3227</v>
+        <v>-52.8406</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-33.5918</v>
+        <v>115.0241</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>-28.7309</v>
+        <v>-167.8646</v>
       </c>
       <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="n">
-        <v>9.31</v>
+        <v>24.44</v>
       </c>
       <c r="X41" s="4" t="n">
-        <v>863060</v>
+        <v>722523</v>
       </c>
       <c r="Y41" s="4" t="n">
-        <v>1454502</v>
+        <v>524323</v>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>0.59</v>
+        <v>1.38</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>361897</v>
+        <v>26279</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>71.37509</v>
+        <v>149.1107</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>47.52608</v>
+        <v>39.2551</v>
       </c>
       <c r="AD41" s="4" t="n">
-        <v>37.13</v>
+        <v>5.58</v>
       </c>
       <c r="AE41" s="4" t="n">
-        <v>195.001</v>
+        <v>46.566</v>
       </c>
       <c r="AF41" s="4" t="n">
-        <v>80.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG41" s="4" t="n">
-        <v>35.1</v>
+        <v>11</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>28.257963</v>
+        <v>6.0063143</v>
       </c>
       <c r="AI41" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>1.276</v>
+        <v>1.131</v>
       </c>
       <c r="AK41" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TITAN/</t>
+          <t>https://www.screener.in/company/AMBER/</t>
         </is>
       </c>
       <c r="AL41" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AMBER</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>One97 Communications Limited</t>
+          <t>Tata Power Company Limited</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
@@ -6067,151 +6075,157 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1155.6</v>
+        <v>408.9</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.39</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1134.39</v>
+        <v>419.27</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1125.87</v>
+        <v>412.68</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1130.21</v>
+        <v>393.03</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>83.63</v>
+        <v>87.95</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>54.62</v>
+        <v>42.16</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>9.1768</v>
+        <v>-2.7883</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>11.0402</v>
+        <v>0.9919</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>-1.8633</v>
+        <v>-3.7803</v>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
       <c r="W42" s="2" t="n">
-        <v>15.88</v>
+        <v>25.07</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>1233342</v>
+        <v>4398760</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>3381646</v>
+        <v>7046142</v>
       </c>
       <c r="Z42" s="2" t="n">
-        <v>0.36</v>
+        <v>0.62</v>
       </c>
       <c r="AA42" s="2" t="n">
-        <v>71214</v>
+        <v>132143</v>
       </c>
       <c r="AB42" s="2" t="n">
-        <v>130.10527</v>
+        <v>35.37639</v>
       </c>
       <c r="AC42" s="2" t="n">
-        <v>35.164474</v>
+        <v>23.168234</v>
       </c>
       <c r="AD42" s="2" t="n">
-        <v>3.56</v>
+        <v>11.34</v>
       </c>
       <c r="AE42" s="2" t="n">
-        <v>1.073</v>
+        <v>167.811</v>
       </c>
       <c r="AF42" s="2" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="AG42" s="2" t="inlineStr"/>
+        <v>-12.8</v>
+      </c>
+      <c r="AG42" s="2" t="n">
+        <v>-4.6</v>
+      </c>
       <c r="AH42" s="2" t="n">
-        <v>4.4501166</v>
+        <v>3.490433</v>
       </c>
       <c r="AI42" s="2" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AJ42" s="2" t="n">
-        <v>2.546</v>
+        <v>0.806</v>
       </c>
       <c r="AK42" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/PAYTM/</t>
+          <t>https://www.screener.in/company/TATAPOWER/</t>
         </is>
       </c>
       <c r="AL42" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PAYTM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>Titan Company Limited</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Luxury Goods</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>25.9</v>
+        <v>26.5</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>4.5</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>💎 High ROE</t>
+        </is>
+      </c>
       <c r="J43" s="4" t="n">
-        <v>1253.3</v>
+        <v>4079.8</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.28</v>
+        <v>-0.08</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>1269.19</v>
+        <v>4213.36</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>1282.63</v>
+        <v>4237.65</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>1248.46</v>
+        <v>3971.21</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
@@ -6224,198 +6238,76 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>88.37</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>43.25</v>
+        <v>39.11</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>-14.8622</v>
+        <v>-65.7901</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>-11.3865</v>
+        <v>-40.0314</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>-3.4757</v>
+        <v>-25.7586</v>
       </c>
       <c r="V43" s="4" t="inlineStr"/>
       <c r="W43" s="4" t="n">
-        <v>16.35</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="X43" s="4" t="n">
-        <v>5171528</v>
+        <v>768112</v>
       </c>
       <c r="Y43" s="4" t="n">
-        <v>7057010</v>
+        <v>1444981</v>
       </c>
       <c r="Z43" s="4" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>399709</v>
+        <v>368940</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>15.2172365</v>
+        <v>72.81513</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>10.201588</v>
+        <v>48.451023</v>
       </c>
       <c r="AD43" s="4" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="AE43" s="4" t="inlineStr"/>
+        <v>37.13</v>
+      </c>
+      <c r="AE43" s="4" t="n">
+        <v>195.001</v>
+      </c>
       <c r="AF43" s="4" t="n">
-        <v>-11.2</v>
+        <v>80.5</v>
       </c>
       <c r="AG43" s="4" t="n">
-        <v>6.4</v>
+        <v>35.1</v>
       </c>
       <c r="AH43" s="4" t="n">
-        <v>1.8571979</v>
+        <v>28.807915</v>
       </c>
       <c r="AI43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ43" s="4" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AJ43" s="4" t="n">
+        <v>1.276</v>
+      </c>
       <c r="AK43" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AXISBANK/</t>
+          <t>https://www.screener.in/company/TITAN/</t>
         </is>
       </c>
       <c r="AL43" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Eicher Motors Limited</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Auto Manufacturers</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
-        <v>6892</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>7055.39</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>7126.81</v>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>6882.89</v>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>83.73999999999999</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>40.91</v>
-      </c>
-      <c r="S44" s="2" t="n">
-        <v>-64.0885</v>
-      </c>
-      <c r="T44" s="2" t="n">
-        <v>-24.4184</v>
-      </c>
-      <c r="U44" s="2" t="n">
-        <v>-39.67</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
-      <c r="W44" s="2" t="n">
-        <v>18.03</v>
-      </c>
-      <c r="X44" s="2" t="n">
-        <v>491206</v>
-      </c>
-      <c r="Y44" s="2" t="n">
-        <v>429558</v>
-      </c>
-      <c r="Z44" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA44" s="2" t="n">
-        <v>191512</v>
-      </c>
-      <c r="AB44" s="2" t="n">
-        <v>35.795223</v>
-      </c>
-      <c r="AC44" s="2" t="n">
-        <v>30.332722</v>
-      </c>
-      <c r="AD44" s="2" t="inlineStr"/>
-      <c r="AE44" s="2" t="n">
-        <v>2.018</v>
-      </c>
-      <c r="AF44" s="2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AG44" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="AH44" s="2" t="n">
-        <v>8.669914</v>
-      </c>
-      <c r="AI44" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="AJ44" s="2" t="inlineStr"/>
-      <c r="AK44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/EICHERMOT/</t>
-        </is>
-      </c>
-      <c r="AL44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL44"/>
+  <autoFilter ref="A1:AL43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6673,12 +6565,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL9"/>
+  <dimension ref="A1:AL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -6699,7 +6591,7 @@
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
@@ -6945,23 +6837,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>274.5</v>
+        <v>277.25</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>268.53</v>
+        <v>269.36</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>262.9</v>
+        <v>263.46</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>247.57</v>
+        <v>247.34</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -6974,45 +6866,41 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>96.11</v>
+        <v>97.08</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>59.8</v>
+        <v>62.41</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>3.7145</v>
+        <v>3.9607</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>3.7075</v>
+        <v>3.7581</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2026</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>21.42</v>
+        <v>21.99</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>5838024</v>
+        <v>31687149</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>3213435</v>
+        <v>4585803</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>1.82</v>
+        <v>6.91</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>79391</v>
+        <v>77329</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>390.49298</v>
+        <v>391.3768</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>104.479126</v>
+        <v>101.846466</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>14.34</v>
@@ -7027,7 +6915,7 @@
         <v>290.2</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>57.31859</v>
+        <v>55.83006</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
@@ -7049,32 +6937,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Polycab India Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>68.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>25.2</v>
+        <v>21.4</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -7083,23 +6971,23 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9193.5</v>
+        <v>6887</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-0.06</v>
+        <v>0.42</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>8754.25</v>
+        <v>6691.44</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>8258.92</v>
+        <v>6477.2</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>7500.27</v>
+        <v>6281.44</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -7112,103 +7000,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>98.75</v>
+        <v>97.83</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>71.51000000000001</v>
+        <v>66.47</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>365.9882</v>
+        <v>162.3304</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>349.2502</v>
+        <v>159.2713</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>16.738</v>
+        <v>3.0591</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>37.17</v>
+        <v>38.27</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>231631</v>
+        <v>354149</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>471656</v>
+        <v>334396</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.49</v>
+        <v>1.06</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>139462</v>
+        <v>179364</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>52.47847</v>
+        <v>72.13858</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>37.64339</v>
+        <v>47.168694</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>24.58</v>
+        <v>16.19</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>2.558</v>
+        <v>0.042</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>26.9</v>
+        <v>9.5</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>8</v>
+        <v>13.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.613577</v>
+        <v>11.630048</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>1.841</v>
+        <v>5.431</v>
       </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POLYCAB/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>Adani Ports and Special Economic Zone Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Marine Shipping</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>68</v>
+        <v>61.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>19</v>
+        <v>24.8</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -7217,23 +7105,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8308.5</v>
+        <v>1786.9</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.85</v>
+        <v>-0.36</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7943.12</v>
+        <v>1720.46</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7745.19</v>
+        <v>1619.78</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>7458.51</v>
+        <v>1479.36</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -7246,103 +7134,103 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>99.05</v>
+        <v>97.97</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>71.14</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>143.2305</v>
+        <v>63.0954</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>122.5275</v>
+        <v>67.1768</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>20.703</v>
+        <v>-4.0814</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>24.91</v>
+        <v>30.09</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1425124</v>
+        <v>1487044</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>433308</v>
+        <v>3311212</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>3.29</v>
+        <v>0.45</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>120240</v>
+        <v>415381</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>61.74777</v>
+        <v>30.951073</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>39.105675</v>
+        <v>23.245396</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>21.5</v>
+        <v>15.59</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>85.146</v>
+        <v>64.051</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>18.1</v>
+        <v>26.5</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>35.6</v>
+        <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>12.680638</v>
+        <v>4.3209004</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>1.065</v>
+        <v>1.394</v>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>JSW Steel Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>67</v>
+        <v>61.6</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27</v>
+        <v>18.6</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -7351,23 +7239,23 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1281.3</v>
+        <v>2717.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.73</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1269.12</v>
+        <v>2541.75</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1241.54</v>
+        <v>2355.01</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1173.14</v>
+        <v>2280.04</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -7380,103 +7268,101 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>97.51000000000001</v>
+        <v>96.94</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>56.24</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>15.561</v>
+        <v>136.6097</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>17.3691</v>
+        <v>130.6256</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-1.8081</v>
+        <v>5.9841</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>17.96</v>
+        <v>47.68</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>5339554</v>
+        <v>1094843</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1952278</v>
+        <v>2934188</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>2.74</v>
+        <v>0.37</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>313743</v>
+        <v>390678</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.090759</v>
+        <v>38.69772</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.70393</v>
+        <v>50.272556</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>27.26</v>
+        <v>13.66</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>94.155</v>
+        <v>119.56</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AG5" s="4" t="n">
-        <v>991.8</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="AG5" s="4" t="inlineStr"/>
       <c r="AH5" s="4" t="n">
-        <v>3.1359012</v>
+        <v>4.545034</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.491</v>
+        <v>1.035</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/JSWSTEEL/</t>
+          <t>https://www.screener.in/company/ADANIENT/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>65</v>
+        <v>61.2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19</v>
+        <v>25.2</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -7489,19 +7375,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>831.85</v>
+        <v>9263.5</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.79</v>
+        <v>0.76</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>815.54</v>
+        <v>8802.75</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>791.13</v>
+        <v>8298.309999999999</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>750.53</v>
+        <v>7496.56</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -7514,83 +7400,83 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>98</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>63.18</v>
+        <v>72.87</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>18.1378</v>
+        <v>361.5424</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>17.909</v>
+        <v>351.7087</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2288</v>
+        <v>9.8338</v>
       </c>
       <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="n">
-        <v>38.41</v>
+        <v>37.41</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>1305803</v>
+        <v>177024</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>1841800</v>
+        <v>449673</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>106832</v>
+        <v>141495</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>60.800148</v>
+        <v>53.11988</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>43.688892</v>
+        <v>38.191982</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>41.39</v>
+        <v>24.58</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>12.394</v>
+        <v>2.558</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>22.1</v>
+        <v>26.9</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>25.187891</v>
+        <v>11.782825</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>1.31</v>
+        <v>1.841</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/POLYCAB/</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Torrent Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -7604,13 +7490,13 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>61.8</v>
+        <v>60.4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -7623,19 +7509,19 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6858</v>
+        <v>4486.2</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.51</v>
+        <v>0.38</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6670.85</v>
+        <v>4359.3</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6460.47</v>
+        <v>4267.93</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6300.69</v>
+        <v>3940.01</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -7648,336 +7534,76 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>97.42</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>65.33</v>
+        <v>62.17</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>165.4821</v>
+        <v>69.54349999999999</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>158.5065</v>
+        <v>58.2663</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>6.9756</v>
+        <v>11.2772</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>39.2</v>
+        <v>24.98</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>151586</v>
+        <v>205928</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>336947</v>
+        <v>267353</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>182828</v>
+        <v>154758</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>73.83938999999999</v>
+        <v>71.78336</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>58.911552</v>
-      </c>
-      <c r="AD7" s="4" t="inlineStr"/>
+        <v>48.446224</v>
+      </c>
+      <c r="AD7" s="4" t="n">
+        <v>16.98</v>
+      </c>
       <c r="AE7" s="4" t="n">
-        <v>0.584</v>
+        <v>85.44199999999999</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>12.3</v>
+        <v>41.8</v>
       </c>
       <c r="AG7" s="4" t="n">
-        <v>-1</v>
+        <v>-21.8</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>11.854679</v>
+        <v>18.32948</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="AJ7" s="4" t="n">
+        <v>1.126</v>
+      </c>
       <c r="AK7" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/TORNTPHARM/</t>
         </is>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Adani Enterprises Limited</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Thermal Coal</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>2697.6</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>2523.27</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>2340.23</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>2285.36</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>96.23999999999999</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>138.106</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>129.1296</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>8.9764</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>1606690</v>
-      </c>
-      <c r="Y8" s="2" t="n">
-        <v>2993011</v>
-      </c>
-      <c r="Z8" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AA8" s="2" t="n">
-        <v>372527</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>36.899784</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>47.936844</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>119.56</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="n">
-        <v>4.333867</v>
-      </c>
-      <c r="AI8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ8" s="2" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="AK8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/ADANIENT/</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>MANAPPURAM</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Manappuram Finance Limited</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Credit Services</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>322.4</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>303.96</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>291.94</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>280.07</v>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>99.37</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>67.06999999999999</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>9.903700000000001</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>9.334199999999999</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0.5695</v>
-      </c>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="X9" s="4" t="n">
-        <v>7531083</v>
-      </c>
-      <c r="Y9" s="4" t="n">
-        <v>4640929</v>
-      </c>
-      <c r="Z9" s="4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA9" s="4" t="n">
-        <v>30444</v>
-      </c>
-      <c r="AB9" s="4" t="n">
-        <v>27.700855</v>
-      </c>
-      <c r="AC9" s="4" t="n">
-        <v>11.036321</v>
-      </c>
-      <c r="AD9" s="4" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="AE9" s="4" t="n">
-        <v>360.191</v>
-      </c>
-      <c r="AF9" s="4" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="n">
-        <v>1.6903098</v>
-      </c>
-      <c r="AI9" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="AJ9" s="4" t="n">
-        <v>94.116</v>
-      </c>
-      <c r="AK9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/MANAPPURAM/</t>
-        </is>
-      </c>
-      <c r="AL9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL9"/>
+  <autoFilter ref="A1:AL7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7988,12 +7614,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL9"/>
+  <dimension ref="A1:AL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -8014,7 +7640,7 @@
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
@@ -8260,23 +7886,23 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>274.5</v>
+        <v>277.25</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>268.53</v>
+        <v>269.36</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>262.9</v>
+        <v>263.46</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>247.57</v>
+        <v>247.34</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -8289,45 +7915,41 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>96.11</v>
+        <v>97.08</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>59.8</v>
+        <v>62.41</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>3.7145</v>
+        <v>3.9607</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>3.7075</v>
+        <v>3.7581</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2026</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
-        <v>21.42</v>
+        <v>21.99</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>5838024</v>
+        <v>31687149</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>3213435</v>
+        <v>4585803</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>1.82</v>
+        <v>6.91</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>79391</v>
+        <v>77329</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>390.49298</v>
+        <v>391.3768</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>104.479126</v>
+        <v>101.846466</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>14.34</v>
@@ -8342,7 +7964,7 @@
         <v>290.2</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>57.31859</v>
+        <v>55.83006</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
@@ -8364,32 +7986,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Polycab India Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>68.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>25.2</v>
+        <v>21.4</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -8398,23 +8020,23 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9193.5</v>
+        <v>6887</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-0.06</v>
+        <v>0.42</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>8754.25</v>
+        <v>6691.44</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>8258.92</v>
+        <v>6477.2</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>7500.27</v>
+        <v>6281.44</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -8427,103 +8049,103 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>98.75</v>
+        <v>97.83</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>71.51000000000001</v>
+        <v>66.47</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>365.9882</v>
+        <v>162.3304</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>349.2502</v>
+        <v>159.2713</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>16.738</v>
+        <v>3.0591</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>37.17</v>
+        <v>38.27</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>231631</v>
+        <v>354149</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>471656</v>
+        <v>334396</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.49</v>
+        <v>1.06</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>139462</v>
+        <v>179364</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>52.47847</v>
+        <v>72.13858</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>37.64339</v>
+        <v>47.168694</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>24.58</v>
+        <v>16.19</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>2.558</v>
+        <v>0.042</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>26.9</v>
+        <v>9.5</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>8</v>
+        <v>13.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>11.613577</v>
+        <v>11.630048</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>1.841</v>
+        <v>5.431</v>
       </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/POLYCAB/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>Adani Ports and Special Economic Zone Limited</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Marine Shipping</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>68</v>
+        <v>61.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>19</v>
+        <v>24.8</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -8532,23 +8154,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8308.5</v>
+        <v>1786.9</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.85</v>
+        <v>-0.36</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7943.12</v>
+        <v>1720.46</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7745.19</v>
+        <v>1619.78</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>7458.51</v>
+        <v>1479.36</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -8561,103 +8183,103 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>99.05</v>
+        <v>97.97</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>71.14</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>143.2305</v>
+        <v>63.0954</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>122.5275</v>
+        <v>67.1768</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>20.703</v>
+        <v>-4.0814</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="n">
-        <v>24.91</v>
+        <v>30.09</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1425124</v>
+        <v>1487044</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>433308</v>
+        <v>3311212</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>3.29</v>
+        <v>0.45</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>120240</v>
+        <v>415381</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>61.74777</v>
+        <v>30.951073</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>39.105675</v>
+        <v>23.245396</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>21.5</v>
+        <v>15.59</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>85.146</v>
+        <v>64.051</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>18.1</v>
+        <v>26.5</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>35.6</v>
+        <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>12.680638</v>
+        <v>4.3209004</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>1.065</v>
+        <v>1.394</v>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/ADANIPORTS/</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>JSW Steel Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>67</v>
+        <v>61.6</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27</v>
+        <v>18.6</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -8666,23 +8288,23 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📊 High Volume | 🏆 Near 52W High | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1281.3</v>
+        <v>2717.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.73</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1269.12</v>
+        <v>2541.75</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1241.54</v>
+        <v>2355.01</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1173.14</v>
+        <v>2280.04</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -8695,103 +8317,101 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>97.51000000000001</v>
+        <v>96.94</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>56.24</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>15.561</v>
+        <v>136.6097</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>17.3691</v>
+        <v>130.6256</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-1.8081</v>
+        <v>5.9841</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>17.96</v>
+        <v>47.68</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>5339554</v>
+        <v>1094843</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1952278</v>
+        <v>2934188</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>2.74</v>
+        <v>0.37</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>313743</v>
+        <v>390678</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>14.090759</v>
+        <v>38.69772</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>17.70393</v>
+        <v>50.272556</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>27.26</v>
+        <v>13.66</v>
       </c>
       <c r="AE5" s="4" t="n">
-        <v>94.155</v>
+        <v>119.56</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AG5" s="4" t="n">
-        <v>991.8</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="AG5" s="4" t="inlineStr"/>
       <c r="AH5" s="4" t="n">
-        <v>3.1359012</v>
+        <v>4.545034</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>1.491</v>
+        <v>1.035</v>
       </c>
       <c r="AK5" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/JSWSTEEL/</t>
+          <t>https://www.screener.in/company/ADANIENT/</t>
         </is>
       </c>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>65</v>
+        <v>61.2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19</v>
+        <v>25.2</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -8804,19 +8424,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>831.85</v>
+        <v>9263.5</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.79</v>
+        <v>0.76</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>815.54</v>
+        <v>8802.75</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>791.13</v>
+        <v>8298.309999999999</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>750.53</v>
+        <v>7496.56</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -8829,83 +8449,83 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>98</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>63.18</v>
+        <v>72.87</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>18.1378</v>
+        <v>361.5424</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>17.909</v>
+        <v>351.7087</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2288</v>
+        <v>9.8338</v>
       </c>
       <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="n">
-        <v>38.41</v>
+        <v>37.41</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>1305803</v>
+        <v>177024</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>1841800</v>
+        <v>449673</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>106832</v>
+        <v>141495</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>60.800148</v>
+        <v>53.11988</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>43.688892</v>
+        <v>38.191982</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>41.39</v>
+        <v>24.58</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>12.394</v>
+        <v>2.558</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>22.1</v>
+        <v>26.9</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>25.187891</v>
+        <v>11.782825</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>1.31</v>
+        <v>1.841</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/POLYCAB/</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Torrent Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -8919,13 +8539,13 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>61.8</v>
+        <v>60.4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -8938,19 +8558,19 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6858</v>
+        <v>4486.2</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.51</v>
+        <v>0.38</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6670.85</v>
+        <v>4359.3</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6460.47</v>
+        <v>4267.93</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6300.69</v>
+        <v>3940.01</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -8963,336 +8583,76 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>97.42</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>65.33</v>
+        <v>62.17</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>165.4821</v>
+        <v>69.54349999999999</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>158.5065</v>
+        <v>58.2663</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>6.9756</v>
+        <v>11.2772</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>39.2</v>
+        <v>24.98</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>151586</v>
+        <v>205928</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>336947</v>
+        <v>267353</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>182828</v>
+        <v>154758</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>73.83938999999999</v>
+        <v>71.78336</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>58.911552</v>
-      </c>
-      <c r="AD7" s="4" t="inlineStr"/>
+        <v>48.446224</v>
+      </c>
+      <c r="AD7" s="4" t="n">
+        <v>16.98</v>
+      </c>
       <c r="AE7" s="4" t="n">
-        <v>0.584</v>
+        <v>85.44199999999999</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>12.3</v>
+        <v>41.8</v>
       </c>
       <c r="AG7" s="4" t="n">
-        <v>-1</v>
+        <v>-21.8</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>11.854679</v>
+        <v>18.32948</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="AJ7" s="4" t="n">
+        <v>1.126</v>
+      </c>
       <c r="AK7" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/TORNTPHARM/</t>
         </is>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Adani Enterprises Limited</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Thermal Coal</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>2697.6</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>2523.27</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>2340.23</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>2285.36</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>96.23999999999999</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>138.106</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>129.1296</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>8.9764</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>1606690</v>
-      </c>
-      <c r="Y8" s="2" t="n">
-        <v>2993011</v>
-      </c>
-      <c r="Z8" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AA8" s="2" t="n">
-        <v>372527</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>36.899784</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>47.936844</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>119.56</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="n">
-        <v>4.333867</v>
-      </c>
-      <c r="AI8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ8" s="2" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="AK8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/ADANIENT/</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>MANAPPURAM</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Manappuram Finance Limited</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Credit Services</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>322.4</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>303.96</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>291.94</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>280.07</v>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>99.37</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>67.06999999999999</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>9.903700000000001</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>9.334199999999999</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0.5695</v>
-      </c>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="X9" s="4" t="n">
-        <v>7531083</v>
-      </c>
-      <c r="Y9" s="4" t="n">
-        <v>4640929</v>
-      </c>
-      <c r="Z9" s="4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA9" s="4" t="n">
-        <v>30444</v>
-      </c>
-      <c r="AB9" s="4" t="n">
-        <v>27.700855</v>
-      </c>
-      <c r="AC9" s="4" t="n">
-        <v>11.036321</v>
-      </c>
-      <c r="AD9" s="4" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="AE9" s="4" t="n">
-        <v>360.191</v>
-      </c>
-      <c r="AF9" s="4" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="n">
-        <v>1.6903098</v>
-      </c>
-      <c r="AI9" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="AJ9" s="4" t="n">
-        <v>94.116</v>
-      </c>
-      <c r="AK9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.screener.in/company/MANAPPURAM/</t>
-        </is>
-      </c>
-      <c r="AL9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL9"/>
+  <autoFilter ref="A1:AL7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9317,7 +8677,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 22-May-2026 17:28 IST</t>
+          <t>Run Date: 25-May-2026 16:56 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -9345,7 +8705,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -9375,7 +8735,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9385,7 +8745,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -9395,7 +8755,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -9421,7 +8781,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="14">
@@ -9441,7 +8801,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="16">
@@ -9473,41 +8833,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>68.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>68</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>67</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>65</v>
+        <v>61.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -775,7 +775,7 @@
         <v>324.82</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>296.89</v>
+        <v>296.83</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -816,13 +816,13 @@
         <v>1.01</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>21540</v>
+        <v>21360</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>24.673758</v>
+        <v>24.468084</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>18.331898</v>
+        <v>18.179089</v>
       </c>
       <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>367.9</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>1.2857991</v>
+        <v>1.2750812</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>33</v>
@@ -903,7 +903,7 @@
         <v>453.89</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>417.78</v>
+        <v>417.31</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -944,13 +944,13 @@
         <v>7.74</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>285704</v>
+        <v>282191</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>9.185655000000001</v>
+        <v>9.072716</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>8.106672</v>
+        <v>8.007</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>28.12</v>
@@ -965,7 +965,7 @@
         <v>12.9</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>2.3985927</v>
+        <v>2.3691018</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>475</v>
@@ -1037,7 +1037,7 @@
         <v>1641.65</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1490.46</v>
+        <v>1490.49</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1078,13 +1078,13 @@
         <v>0.66</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>420012</v>
+        <v>415772</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>31.323023</v>
+        <v>31.006872</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>23.50455</v>
+        <v>23.267313</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.59</v>
@@ -1099,7 +1099,7 @@
         <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.369073</v>
+        <v>4.3249745</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>41</v>
@@ -1171,7 +1171,7 @@
         <v>6510.26</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>6303.62</v>
+        <v>6303.55</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -1212,13 +1212,13 @@
         <v>0.43</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>180280</v>
+        <v>176988</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>70.358475</v>
+        <v>69.07377</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>48.03056</v>
+        <v>47.15355</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>16.19</v>
@@ -1233,7 +1233,7 @@
         <v>13.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>11.689433</v>
+        <v>11.47599</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>44</v>
@@ -1305,7 +1305,7 @@
         <v>1189.85</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1017.63</v>
+        <v>1017.19</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1346,13 +1346,13 @@
         <v>0.35</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>9965</v>
+        <v>10155</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>88.17967</v>
+        <v>89.86407</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>45.615974</v>
+        <v>46.487324</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>16.94</v>
@@ -1367,7 +1367,7 @@
         <v>69</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>13.810468</v>
+        <v>14.074273</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>8441.25</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7560.62</v>
+        <v>7561.76</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -1480,13 +1480,13 @@
         <v>0.49</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>145462</v>
+        <v>142684</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>54.63387</v>
+        <v>53.59061</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>39.262745</v>
+        <v>38.51301</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>24.58</v>
@@ -1501,7 +1501,7 @@
         <v>8</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>12.1131735</v>
+        <v>11.881867</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>36</v>
@@ -1573,7 +1573,7 @@
         <v>7830.53</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>7493.93</v>
+        <v>7498.69</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -1614,13 +1614,13 @@
         <v>0.67</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>119047</v>
+        <v>117566</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>61.402405</v>
+        <v>60.638535</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>38.752354</v>
+        <v>38.27026</v>
       </c>
       <c r="AD8" s="2" t="n">
         <v>21.5</v>
@@ -1635,7 +1635,7 @@
         <v>35.6</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>12.554779</v>
+        <v>12.398593</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>24</v>
@@ -1707,7 +1707,7 @@
         <v>4296.48</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3957.95</v>
+        <v>3950.73</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -1748,13 +1748,13 @@
         <v>0.7</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>153285</v>
+        <v>149282</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>70.789314</v>
+        <v>68.94029</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>47.70262</v>
+        <v>46.456627</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>16.98</v>
@@ -1769,7 +1769,7 @@
         <v>-21.8</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>18.155107</v>
+        <v>17.680895</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>84</v>
@@ -1841,7 +1841,7 @@
         <v>1249.42</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1171.93</v>
+        <v>1171.38</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1882,13 +1882,13 @@
         <v>1.14</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>319723</v>
+        <v>311913</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>14.354591</v>
+        <v>14.003944</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>18.041344</v>
+        <v>17.60064</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>27.26</v>
@@ -1903,7 +1903,7 @@
         <v>991.8</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>3.1956675</v>
+        <v>3.1176054</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>54</v>
@@ -1975,7 +1975,7 @@
         <v>415.21</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>360.58</v>
+        <v>360.33</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -2016,13 +2016,13 @@
         <v>0.16</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>12713</v>
+        <v>12407</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>30.676786</v>
+        <v>29.93991</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>18.210266</v>
+        <v>17.772844</v>
       </c>
       <c r="AD11" s="4" t="n">
         <v>10.66</v>
@@ -2037,7 +2037,7 @@
         <v>-85.59999999999999</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>3.13987</v>
+        <v>22.567343</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>77</v>
@@ -2109,7 +2109,7 @@
         <v>174.62</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>165.04</v>
+        <v>165.02</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         <v>0.98</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>24698</v>
+        <v>24137</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>16.006872</v>
+        <v>15.64347</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>12.994033</v>
+        <v>12.69903</v>
       </c>
       <c r="AD12" s="2" t="n">
         <v>12.55</v>
@@ -2171,7 +2171,7 @@
         <v>17.8</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>1.9407324</v>
+        <v>1.896672</v>
       </c>
       <c r="AI12" s="2" t="n">
         <v>323</v>
@@ -2243,7 +2243,7 @@
         <v>1373.82</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1280.08</v>
+        <v>1282.17</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         <v>0.66</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>275286</v>
+        <v>274110</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>78.74242</v>
+        <v>78.40595999999999</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>60.26357</v>
+        <v>60.00607</v>
       </c>
       <c r="AD13" s="4" t="n">
         <v>76.34</v>
@@ -2305,7 +2305,7 @@
         <v>27.4</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>53.38219</v>
+        <v>53.154095</v>
       </c>
       <c r="AI13" s="4" t="n">
         <v>84</v>
@@ -2377,7 +2377,7 @@
         <v>796.6</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>754.84</v>
+        <v>755.76</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -2418,13 +2418,13 @@
         <v>0.53</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>108329</v>
+        <v>106477</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>61.51582</v>
+        <v>60.463577</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>44.300945</v>
+        <v>43.543167</v>
       </c>
       <c r="AD14" s="2" t="n">
         <v>41.39</v>
@@ -2439,7 +2439,7 @@
         <v>14.5</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>25.540756</v>
+        <v>25.103876</v>
       </c>
       <c r="AI14" s="2" t="n">
         <v>48</v>
@@ -2511,7 +2511,7 @@
         <v>955.88</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>810.47</v>
+        <v>810.38</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -2552,13 +2552,13 @@
         <v>0.31</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>20322</v>
+        <v>20968</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>62.168533</v>
+        <v>64.14555</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>37.08804</v>
+        <v>38.267475</v>
       </c>
       <c r="AD15" s="4" t="n">
         <v>14.14</v>
@@ -2573,7 +2573,7 @@
         <v>43.7</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>6.9943047</v>
+        <v>7.2167306</v>
       </c>
       <c r="AI15" s="4" t="n">
         <v>14</v>
@@ -2645,7 +2645,7 @@
         <v>3915.91</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3812.51</v>
+        <v>3806.13</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2686,13 +2686,13 @@
         <v>0.66</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>557146</v>
+        <v>560791</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>34.624264</v>
+        <v>34.850815</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>22.066845</v>
+        <v>22.211233</v>
       </c>
       <c r="AD16" s="2" t="n">
         <v>16.95</v>
@@ -2707,7 +2707,7 @@
         <v>-34.5</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>5.0977383</v>
+        <v>5.131094</v>
       </c>
       <c r="AI16" s="2" t="n">
         <v>94</v>
@@ -2779,7 +2779,7 @@
         <v>2420.31</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2303.67</v>
+        <v>2300.71</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
@@ -2820,13 +2820,13 @@
         <v>1.27</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>407554</v>
+        <v>402701</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>40.320087</v>
+        <v>39.839954</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>52.44421</v>
+        <v>51.819702</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>13.66</v>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AG17" s="4" t="inlineStr"/>
       <c r="AH17" s="4" t="n">
-        <v>4.7413683</v>
+        <v>4.684908</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>4</v>
@@ -2911,7 +2911,7 @@
         <v>184.53</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>168.23</v>
+        <v>168.04</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -2952,13 +2952,13 @@
         <v>1.04</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>33187</v>
+        <v>33558</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>27.105263</v>
+        <v>27.407896</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>9.550098</v>
+        <v>9.656726000000001</v>
       </c>
       <c r="AD18" s="2" t="n">
         <v>4.88</v>
@@ -2971,7 +2971,7 @@
         <v>68</v>
       </c>
       <c r="AH18" s="2" t="n">
-        <v>1.2958908</v>
+        <v>1.3103596</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>73</v>
@@ -3041,7 +3041,7 @@
         <v>387.53</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>360.81</v>
+        <v>360.6</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -3082,13 +3082,13 @@
         <v>1.7</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>385782</v>
+        <v>375164</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>13.061393</v>
+        <v>12.701904</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>14.062249</v>
+        <v>13.675214</v>
       </c>
       <c r="AD19" s="4" t="n">
         <v>13.69</v>
@@ -3103,7 +3103,7 @@
         <v>-1.6</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>1.8995532</v>
+        <v>1.8472718</v>
       </c>
       <c r="AI19" s="4" t="n">
         <v>285</v>
@@ -3175,7 +3175,7 @@
         <v>297.17</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>281.61</v>
+        <v>281.36</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -3216,13 +3216,13 @@
         <v>0.37</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>30904</v>
+        <v>30566</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>28.11966</v>
+        <v>27.811966</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>11.2031765</v>
+        <v>11.080588</v>
       </c>
       <c r="AD20" s="2" t="n">
         <v>6.97</v>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="n">
-        <v>1.7158651</v>
+        <v>1.6970897</v>
       </c>
       <c r="AI20" s="2" t="n">
         <v>61</v>
@@ -3303,7 +3303,7 @@
         <v>1285.23</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1250.1</v>
+        <v>1249.12</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
@@ -3344,13 +3344,13 @@
         <v>1.07</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>405691</v>
+        <v>400124</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>15.436043</v>
+        <v>15.224233</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>10.353174</v>
+        <v>10.211111</v>
       </c>
       <c r="AD21" s="4" t="n">
         <v>13.15</v>
@@ -3363,7 +3363,7 @@
         <v>6.4</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>1.8847942</v>
+        <v>1.8589315</v>
       </c>
       <c r="AI21" s="4" t="n">
         <v>8</v>
@@ -3383,12 +3383,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Canara Bank</t>
+          <t>Union Bank of India</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3405,10 +3405,10 @@
         <v>53.9</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>25.5</v>
+        <v>28.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>28.4</v>
+        <v>25.4</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -3417,19 +3417,19 @@
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="n">
-        <v>134.16</v>
+        <v>168.72</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>132</v>
+        <v>166.16</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>135.46</v>
+        <v>170.92</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>133</v>
+        <v>161.51</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -3442,120 +3442,120 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>82.36</v>
+        <v>82.11</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>52.71</v>
+        <v>51.67</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>-1.5506</v>
+        <v>-2.6548</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>-2.2398</v>
+        <v>-3.9353</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>0.6892</v>
+        <v>1.2805</v>
       </c>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="n">
-        <v>14.83</v>
+        <v>20.05</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>26115218</v>
+        <v>7569728</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>23758342</v>
+        <v>11278254</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>1.1</v>
+        <v>0.67</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>121819</v>
+        <v>128153</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>6.180396</v>
+        <v>6.5990567</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>5.813008</v>
+        <v>6.5414696</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>17.57</v>
+        <v>15.71</v>
       </c>
       <c r="AE22" s="2" t="inlineStr"/>
-      <c r="AF22" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AG22" s="2" t="n">
-        <v>-9.800000000000001</v>
-      </c>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
       <c r="AH22" s="2" t="n">
-        <v>1.0355463</v>
+        <v>0.9779855</v>
       </c>
       <c r="AI22" s="2" t="n">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="AJ22" s="2" t="inlineStr"/>
       <c r="AK22" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CANBK/</t>
+          <t>https://www.screener.in/company/UNIONBANK/</t>
         </is>
       </c>
       <c r="AL22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CANBK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Union Bank of India</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>53.9</v>
+        <v>52.4</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>28.5</v>
+        <v>24</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>25.4</v>
+        <v>28.4</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>💎 High ROE</t>
+        </is>
+      </c>
       <c r="J23" s="4" t="n">
-        <v>168.72</v>
+        <v>3129.1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>166.16</v>
+        <v>3106.94</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>170.92</v>
+        <v>3114.39</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>161.75</v>
+        <v>3015.33</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -3568,95 +3568,103 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>82.11</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>51.67</v>
+        <v>50.67</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.6548</v>
+        <v>-44.04</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.9353</v>
+        <v>-41.3219</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.2805</v>
+        <v>-2.7181</v>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="n">
-        <v>20.05</v>
+        <v>15.59</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>7569728</v>
+        <v>1978239</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>11278254</v>
+        <v>1420556</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.67</v>
+        <v>1.39</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>128817</v>
+        <v>90346</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>6.6332545</v>
+        <v>27.650322</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>6.575369</v>
+        <v>18.104729</v>
       </c>
       <c r="AD23" s="4" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="4" t="inlineStr"/>
-      <c r="AG23" s="4" t="inlineStr"/>
+        <v>31.57</v>
+      </c>
+      <c r="AE23" s="4" t="n">
+        <v>21.402</v>
+      </c>
+      <c r="AF23" s="4" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="AG23" s="4" t="n">
+        <v>71.2</v>
+      </c>
       <c r="AH23" s="4" t="n">
-        <v>0.9830536</v>
+        <v>6.254107</v>
       </c>
       <c r="AI23" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="AJ23" s="4" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="AJ23" s="4" t="n">
+        <v>1.383</v>
+      </c>
       <c r="AK23" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/UNIONBANK/</t>
+          <t>https://www.screener.in/company/WAAREEENER/</t>
         </is>
       </c>
       <c r="AL23" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:WAAREEENER</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>Eicher Motors Limited</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>28.4</v>
+        <v>22.2</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -3665,23 +3673,23 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>💎 High ROE</t>
+          <t>✅ Supertrend Buy | 💎 High ROE</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3129.1</v>
+        <v>7419</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1.33</v>
+        <v>0.58</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3106.94</v>
+        <v>7140.39</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3114.39</v>
+        <v>7153</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3013.23</v>
+        <v>6893.68</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -3690,107 +3698,107 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>81.01000000000001</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>50.67</v>
+        <v>61.37</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>-44.04</v>
+        <v>25.8987</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>-41.3219</v>
+        <v>-13.9708</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>-2.7181</v>
+        <v>39.8696</v>
       </c>
       <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="2" t="n">
-        <v>15.59</v>
+        <v>16.72</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>1978239</v>
+        <v>283327</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>1420556</v>
+        <v>464892</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>1.39</v>
+        <v>0.61</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>90466</v>
+        <v>197007</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>27.687298</v>
+        <v>35.697586</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>18.128939</v>
+        <v>27.068094</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>31.57</v>
+        <v>23.77</v>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>21.402</v>
+        <v>2.048</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>111.8</v>
+        <v>19.1</v>
       </c>
       <c r="AG24" s="2" t="n">
-        <v>71.2</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" s="2" t="n">
-        <v>6.2624702</v>
+        <v>7.8434587</v>
       </c>
       <c r="AI24" s="2" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="AJ24" s="2" t="n">
-        <v>1.383</v>
+        <v>1.902</v>
       </c>
       <c r="AK24" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/WAAREEENER/</t>
+          <t>https://www.screener.in/company/EICHERMOT/</t>
         </is>
       </c>
       <c r="AL24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:WAAREEENER</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Eicher Motors Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>52.2</v>
+        <v>51.6</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>22.2</v>
+        <v>18.6</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -3799,27 +3807,27 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7419</v>
+        <v>1844.3</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.58</v>
+        <v>0.19</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7140.39</v>
+        <v>1836.01</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7153</v>
+        <v>1793.25</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6892.06</v>
+        <v>1728.73</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -3828,103 +3836,103 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>90.15000000000001</v>
+        <v>96.23</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>61.37</v>
+        <v>54.45</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>25.8987</v>
+        <v>26.3583</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-13.9708</v>
+        <v>32.6871</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>39.8696</v>
+        <v>-6.3288</v>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="n">
-        <v>16.72</v>
+        <v>25.63</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>283327</v>
+        <v>1385752</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>464892</v>
+        <v>2613156</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>203842</v>
+        <v>431688</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>36.936085</v>
+        <v>37.663803</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>28.007198</v>
+        <v>27.768585</v>
       </c>
       <c r="AD25" s="4" t="n">
-        <v>23.77</v>
+        <v>14.72</v>
       </c>
       <c r="AE25" s="4" t="n">
-        <v>2.048</v>
+        <v>5.517</v>
       </c>
       <c r="AF25" s="4" t="n">
-        <v>19.1</v>
+        <v>12.8</v>
       </c>
       <c r="AG25" s="4" t="n">
-        <v>11.5</v>
+        <v>25.6</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>8.115581000000001</v>
+        <v>5.5451794</v>
       </c>
       <c r="AI25" s="4" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>1.902</v>
+        <v>2.824</v>
       </c>
       <c r="AK25" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/EICHERMOT/</t>
+          <t>https://www.screener.in/company/SUNPHARMA/</t>
         </is>
       </c>
       <c r="AL25" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>The Federal Bank Limited</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>51.6</v>
+        <v>50.6</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>18.6</v>
+        <v>23.6</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -3937,19 +3945,19 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1844.3</v>
+        <v>288.9</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.19</v>
+        <v>-0.45</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1836.01</v>
+        <v>287.49</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1793.25</v>
+        <v>284.75</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1730.9</v>
+        <v>258.6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -3962,103 +3970,99 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>96.23</v>
+        <v>95.66</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>54.45</v>
+        <v>52.42</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>26.3583</v>
+        <v>0.5874</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>32.6871</v>
+        <v>0.6284</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>-6.3288</v>
+        <v>-0.041</v>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="2" t="n">
-        <v>25.63</v>
+        <v>13.62</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>1385752</v>
+        <v>3869975</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>2613156</v>
+        <v>7776210</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>441478</v>
+        <v>71207</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>38.5179</v>
+        <v>16.530321</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>28.398287</v>
+        <v>12.161287</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="AE26" s="2" t="n">
-        <v>5.517</v>
-      </c>
+        <v>11.73</v>
+      </c>
+      <c r="AE26" s="2" t="inlineStr"/>
       <c r="AF26" s="2" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="AG26" s="2" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>5.670926</v>
+        <v>1.7787559</v>
       </c>
       <c r="AI26" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="AJ26" s="2" t="n">
-        <v>2.824</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr"/>
       <c r="AK26" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/SUNPHARMA/</t>
+          <t>https://www.screener.in/company/FEDERALBNK/</t>
         </is>
       </c>
       <c r="AL26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>The Federal Bank Limited</t>
+          <t>Tata Steel Limited</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>23.6</v>
+        <v>17</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -4067,23 +4071,23 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>288.9</v>
+        <v>214.7</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.45</v>
+        <v>2.01</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>287.49</v>
+        <v>211.55</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>284.75</v>
+        <v>207.68</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>258.64</v>
+        <v>187.02</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -4092,103 +4096,107 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>95.66</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>52.42</v>
+        <v>56.32</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.5874</v>
+        <v>0.7458</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.6284</v>
+        <v>1.3924</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.041</v>
+        <v>-0.6466</v>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="n">
-        <v>13.62</v>
+        <v>17.08</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3869975</v>
+        <v>39110042</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7776210</v>
+        <v>29021368</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.5</v>
+        <v>1.35</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>71207</v>
+        <v>259439</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>16.530321</v>
+        <v>28.3406</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>12.161287</v>
+        <v>11.064895</v>
       </c>
       <c r="AD27" s="4" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="AE27" s="4" t="inlineStr"/>
+        <v>11.16</v>
+      </c>
+      <c r="AE27" s="4" t="n">
+        <v>89.01600000000001</v>
+      </c>
       <c r="AF27" s="4" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="AG27" s="4" t="n">
-        <v>22.2</v>
+        <v>125.4</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>1.7787559</v>
+        <v>2.7291691</v>
       </c>
       <c r="AI27" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ27" s="4" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="AJ27" s="4" t="n">
+        <v>0.748</v>
+      </c>
       <c r="AK27" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/FEDERALBNK/</t>
+          <t>https://www.screener.in/company/TATASTEEL/</t>
         </is>
       </c>
       <c r="AL27" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tata Steel Limited</t>
+          <t>HFCL Limited</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
         <v>50</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -4197,23 +4205,23 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>214.7</v>
+        <v>173.92</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2.01</v>
+        <v>7.49</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>211.55</v>
+        <v>141.7</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>207.68</v>
+        <v>117.08</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>187.21</v>
+        <v>87.62</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -4222,87 +4230,89 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>95.68000000000001</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>56.32</v>
+        <v>80.47</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>0.7458</v>
+        <v>15.3836</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1.3924</v>
+        <v>14.6133</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>-0.6466</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr"/>
+        <v>0.7703</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W28" s="2" t="n">
-        <v>17.08</v>
+        <v>58.37</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>39110042</v>
+        <v>79961509</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>29021368</v>
+        <v>90025183</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>1.35</v>
+        <v>0.89</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>267534</v>
+        <v>27536</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>29.224794</v>
+        <v>486.3243</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>11.410107</v>
+        <v>34.603848</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>11.16</v>
+        <v>7.27</v>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>89.01600000000001</v>
+        <v>38.321</v>
       </c>
       <c r="AF28" s="2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG28" s="2" t="n">
-        <v>125.4</v>
-      </c>
+        <v>127.8</v>
+      </c>
+      <c r="AG28" s="2" t="inlineStr"/>
       <c r="AH28" s="2" t="n">
-        <v>2.8143163</v>
+        <v>5.427563</v>
       </c>
       <c r="AI28" s="2" t="n">
-        <v>186</v>
+        <v>6</v>
       </c>
       <c r="AJ28" s="2" t="n">
-        <v>0.748</v>
+        <v>1.991</v>
       </c>
       <c r="AK28" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TATASTEEL/</t>
+          <t>https://www.screener.in/company/HFCL/</t>
         </is>
       </c>
       <c r="AL28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>HFCL Limited</t>
+          <t>ideaForge Technology Limited</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -4312,17 +4322,17 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>50</v>
+        <v>49.4</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10</v>
+        <v>12.4</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -4331,23 +4341,23 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>🔥 Fresh MACD Cross | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>173.92</v>
+        <v>845.3</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.49</v>
+        <v>-1.18</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>141.7</v>
+        <v>752.75</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>117.08</v>
+        <v>637.05</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>87.67</v>
+        <v>509.38</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -4360,203 +4370,193 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>98.56999999999999</v>
+        <v>95.19</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>80.47</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>15.3836</v>
+        <v>68.745</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>14.6133</v>
+        <v>73.77549999999999</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.7703</v>
-      </c>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>-5.0305</v>
+      </c>
+      <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="n">
-        <v>58.37</v>
+        <v>39.81</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>79961509</v>
+        <v>579560</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>90025183</v>
+        <v>2450705</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.89</v>
+        <v>0.24</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>26504</v>
-      </c>
-      <c r="AB29" s="4" t="n">
-        <v>468.1081</v>
-      </c>
+        <v>3666</v>
+      </c>
+      <c r="AB29" s="4" t="inlineStr"/>
       <c r="AC29" s="4" t="n">
-        <v>33.307693</v>
+        <v>30.28674</v>
       </c>
       <c r="AD29" s="4" t="n">
-        <v>7.27</v>
+        <v>-2.82</v>
       </c>
       <c r="AE29" s="4" t="n">
-        <v>38.321</v>
+        <v>13.974</v>
       </c>
       <c r="AF29" s="4" t="n">
-        <v>127.8</v>
+        <v>594.4</v>
       </c>
       <c r="AG29" s="4" t="inlineStr"/>
       <c r="AH29" s="4" t="n">
-        <v>5.224263</v>
+        <v>6.1680183</v>
       </c>
       <c r="AI29" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>1.991</v>
+        <v>2.622</v>
       </c>
       <c r="AK29" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/HFCL/</t>
+          <t>https://www.screener.in/company/IDEAFORGE/</t>
         </is>
       </c>
       <c r="AL29" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEAFORGE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ideaForge Technology Limited</t>
+          <t>Canara Bank</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>49.4</v>
+        <v>46.9</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>37</v>
+        <v>25.5</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>12.4</v>
+        <v>21.4</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
-        </is>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="n">
-        <v>845.3</v>
+        <v>134.16</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-1.18</v>
+        <v>0.76</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>752.75</v>
+        <v>132</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>637.05</v>
+        <v>135.46</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>509.74</v>
+        <v>132.94</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>95.19</v>
+        <v>82.36</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>66.70999999999999</v>
+        <v>52.71</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>68.745</v>
+        <v>-1.5506</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>73.77549999999999</v>
+        <v>-2.2398</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>-5.0305</v>
+        <v>0.6892</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="n">
-        <v>39.81</v>
+        <v>14.83</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>579560</v>
+        <v>26115218</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>2450705</v>
+        <v>23758342</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>0.24</v>
+        <v>1.1</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>3645</v>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+        <v>118644</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>6.0193286</v>
+      </c>
       <c r="AC30" s="2" t="n">
-        <v>30.107527</v>
+        <v>5.6615143</v>
       </c>
       <c r="AD30" s="2" t="n">
-        <v>-2.82</v>
-      </c>
-      <c r="AE30" s="2" t="n">
-        <v>13.974</v>
-      </c>
+        <v>15.94</v>
+      </c>
+      <c r="AE30" s="2" t="inlineStr"/>
       <c r="AF30" s="2" t="n">
-        <v>594.4</v>
-      </c>
-      <c r="AG30" s="2" t="inlineStr"/>
+        <v>-46.7</v>
+      </c>
+      <c r="AG30" s="2" t="n">
+        <v>-9.800000000000001</v>
+      </c>
       <c r="AH30" s="2" t="n">
-        <v>6.131521</v>
+        <v>1.0085589</v>
       </c>
       <c r="AI30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="2" t="n">
-        <v>2.622</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr"/>
       <c r="AK30" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/IDEAFORGE/</t>
+          <t>https://www.screener.in/company/CANBK/</t>
         </is>
       </c>
       <c r="AL30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEAFORGE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CANBK</t>
         </is>
       </c>
     </row>
@@ -4610,10 +4610,10 @@
         <v>2577.09</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2498.6</v>
+        <v>2498.61</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2491.34</v>
+        <v>2492.36</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
@@ -4654,13 +4654,13 @@
         <v>0.83</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>256437</v>
+        <v>256111</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>66.741516</v>
+        <v>66.656685</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>53.48437</v>
+        <v>53.416393</v>
       </c>
       <c r="AD31" s="4" t="inlineStr"/>
       <c r="AE31" s="4" t="n">
@@ -4673,7 +4673,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>13.090927</v>
+        <v>13.074288</v>
       </c>
       <c r="AI31" s="4" t="n">
         <v>94</v>
@@ -4743,7 +4743,7 @@
         <v>284.4</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>258.62</v>
+        <v>258.35</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -4784,13 +4784,13 @@
         <v>1.81</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>343819</v>
+        <v>333881</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>8.296904</v>
+        <v>8.057074</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>6.3727264</v>
+        <v>6.097757</v>
       </c>
       <c r="AD32" s="2" t="n">
         <v>12.7</v>
@@ -4805,7 +4805,7 @@
         <v>47.8</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>0.92487305</v>
+        <v>0.8981387</v>
       </c>
       <c r="AI32" s="2" t="n">
         <v>675</v>
@@ -4877,7 +4877,7 @@
         <v>1338.68</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1393.43</v>
+        <v>1392.41</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
@@ -4918,13 +4918,13 @@
         <v>0.52</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>114869</v>
+        <v>113173</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>29.662079</v>
+        <v>29.224031</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>22.504675</v>
+        <v>22.172327</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>11.74</v>
@@ -4939,7 +4939,7 @@
         <v>-54.6</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>3.489305</v>
+        <v>3.4377751</v>
       </c>
       <c r="AI33" s="4" t="n">
         <v>92</v>
@@ -5007,7 +5007,7 @@
         <v>1557.69</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1504.69</v>
+        <v>1504.48</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -5048,13 +5048,13 @@
         <v>0.8</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>43038</v>
+        <v>42398</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>80.18017999999999</v>
+        <v>78.98899</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>47.548252</v>
+        <v>46.841854</v>
       </c>
       <c r="AD34" s="2" t="n">
         <v>13.8</v>
@@ -5069,7 +5069,7 @@
         <v>18.9</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>10.603934</v>
+        <v>10.446397</v>
       </c>
       <c r="AI34" s="2" t="n">
         <v>23</v>
@@ -5141,7 +5141,7 @@
         <v>263.8</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>248.23</v>
+        <v>248.25</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
@@ -5182,13 +5182,13 @@
         <v>1.07</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>75511</v>
+        <v>75110</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>371.40848</v>
+        <v>369.4366</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>98.707115</v>
+        <v>98.18307</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>14.34</v>
@@ -5203,7 +5203,7 @@
         <v>290.2</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>53.240463</v>
+        <v>52.9578</v>
       </c>
       <c r="AI35" s="4" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>1422.92</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1445.04</v>
+        <v>1445.31</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -5316,13 +5316,13 @@
         <v>0.3</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>150529</v>
+        <v>150916</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>61.65069</v>
+        <v>61.80909</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>48.77452</v>
+        <v>48.899837</v>
       </c>
       <c r="AD36" s="2" t="n">
         <v>23.52</v>
@@ -5337,7 +5337,7 @@
         <v>37</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>15.759526</v>
+        <v>15.800017</v>
       </c>
       <c r="AI36" s="2" t="n">
         <v>68</v>
@@ -5409,7 +5409,7 @@
         <v>482.46</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>499.51</v>
+        <v>499.64</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
@@ -5450,13 +5450,13 @@
         <v>0.25</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>61553</v>
+        <v>58370</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>54.76141</v>
+        <v>51.92946</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>41.57027</v>
+        <v>39.420486</v>
       </c>
       <c r="AD37" s="4" t="n">
         <v>17.23</v>
@@ -5471,7 +5471,7 @@
         <v>27.7</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>8.903244000000001</v>
+        <v>8.442818000000001</v>
       </c>
       <c r="AI37" s="4" t="n">
         <v>72</v>
@@ -5543,7 +5543,7 @@
         <v>173.31</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>179.44</v>
+        <v>179.1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -5584,13 +5584,13 @@
         <v>16.67</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>11954</v>
+        <v>11514</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>19.951498</v>
+        <v>19.21775</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>17.339014</v>
+        <v>16.701345</v>
       </c>
       <c r="AD38" s="2" t="n">
         <v>9.73</v>
@@ -5605,7 +5605,7 @@
         <v>59</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>2.0198083</v>
+        <v>1.9455268</v>
       </c>
       <c r="AI38" s="2" t="n">
         <v>104</v>
@@ -5677,7 +5677,7 @@
         <v>302.77</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>288.89</v>
+        <v>289.15</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
@@ -5718,13 +5718,13 @@
         <v>1.03</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>279530</v>
+        <v>270229</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>14.9453</v>
+        <v>14.448034</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>15.088669</v>
+        <v>14.586634</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>16.49</v>
@@ -5739,7 +5739,7 @@
         <v>9.6</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>2.7805274</v>
+        <v>2.6880126</v>
       </c>
       <c r="AI39" s="4" t="n">
         <v>408</v>
@@ -5811,7 +5811,7 @@
         <v>1290.17</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1257.45</v>
+        <v>1256.61</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0.4</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>109903</v>
+        <v>108529</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>26.195675</v>
+        <v>25.868229</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>20.462101</v>
+        <v>20.206324</v>
       </c>
       <c r="AD40" s="2" t="n">
         <v>11.83</v>
@@ -5873,7 +5873,7 @@
         <v>-86.2</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>2.9186106</v>
+        <v>2.882128</v>
       </c>
       <c r="AI40" s="2" t="n">
         <v>61</v>
@@ -5945,7 +5945,7 @@
         <v>413.54</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>394.12</v>
+        <v>394.03</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
@@ -5986,13 +5986,13 @@
         <v>1.03</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>136729</v>
+        <v>134444</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>36.541416</v>
+        <v>35.93083</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>23.972162</v>
+        <v>23.5716</v>
       </c>
       <c r="AD41" s="4" t="n">
         <v>11.34</v>
@@ -6007,7 +6007,7 @@
         <v>-4.6</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>3.6115494</v>
+        <v>3.5512023</v>
       </c>
       <c r="AI41" s="4" t="n">
         <v>59</v>
@@ -6075,7 +6075,7 @@
         <v>79.15000000000001</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -6116,13 +6116,13 @@
         <v>1.61</v>
       </c>
       <c r="AA42" s="2" t="n">
-        <v>81325</v>
+        <v>79225</v>
       </c>
       <c r="AB42" s="2" t="n">
-        <v>29.227436</v>
+        <v>28.472925</v>
       </c>
       <c r="AC42" s="2" t="n">
-        <v>12.65</v>
+        <v>12.323438</v>
       </c>
       <c r="AD42" s="2" t="n">
         <v>9.02</v>
@@ -6137,7 +6137,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="AH42" s="2" t="n">
-        <v>1.9659075</v>
+        <v>1.9151572</v>
       </c>
       <c r="AI42" s="2" t="n">
         <v>237</v>
@@ -6209,7 +6209,7 @@
         <v>434.34</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>404.13</v>
+        <v>403.86</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>143092</v>
+        <v>141442</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>5.5228634</v>
+        <v>5.459177</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>6.660777</v>
+        <v>6.583969</v>
       </c>
       <c r="AD43" s="4" t="n">
         <v>20.47</v>
@@ -6271,7 +6271,7 @@
         <v>10.8</v>
       </c>
       <c r="AH43" s="4" t="n">
-        <v>1.0769273</v>
+        <v>1.0645088</v>
       </c>
       <c r="AI43" s="4" t="n">
         <v>337</v>
@@ -6343,7 +6343,7 @@
         <v>1401.53</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1255.32</v>
+        <v>1252.93</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -6384,13 +6384,13 @@
         <v>0.61</v>
       </c>
       <c r="AA44" s="2" t="n">
-        <v>82388</v>
+        <v>82072</v>
       </c>
       <c r="AB44" s="2" t="n">
-        <v>23.74233</v>
+        <v>23.651136</v>
       </c>
       <c r="AC44" s="2" t="n">
-        <v>16.172697</v>
+        <v>16.110577</v>
       </c>
       <c r="AD44" s="2" t="n">
         <v>9.93</v>
@@ -6405,7 +6405,7 @@
         <v>1.9</v>
       </c>
       <c r="AH44" s="2" t="n">
-        <v>2.1951084</v>
+        <v>2.186677</v>
       </c>
       <c r="AI44" s="2" t="n">
         <v>28</v>
@@ -6477,7 +6477,7 @@
         <v>3417.85</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>3290.76</v>
+        <v>3281.67</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
@@ -6518,13 +6518,13 @@
         <v>0.21</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>132926</v>
+        <v>134207</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>12.546894</v>
+        <v>12.667777</v>
       </c>
       <c r="AC45" s="4" t="n">
-        <v>9.570746</v>
+        <v>9.662955999999999</v>
       </c>
       <c r="AD45" s="4" t="n">
         <v>30.41</v>
@@ -6539,7 +6539,7 @@
         <v>126.7</v>
       </c>
       <c r="AH45" s="4" t="n">
-        <v>3.73165</v>
+        <v>3.767603</v>
       </c>
       <c r="AI45" s="4" t="n">
         <v>91</v>
@@ -6608,10 +6608,10 @@
         <v>7701.87</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7589.88</v>
+        <v>7589.87</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>7246.86</v>
+        <v>7228.7</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -6652,13 +6652,13 @@
         <v>0.75</v>
       </c>
       <c r="AA46" s="2" t="n">
-        <v>26541</v>
+        <v>26856</v>
       </c>
       <c r="AB46" s="2" t="n">
-        <v>149.43407</v>
+        <v>151.21127</v>
       </c>
       <c r="AC46" s="2" t="n">
-        <v>39.591805</v>
+        <v>40.062668</v>
       </c>
       <c r="AD46" s="2" t="n">
         <v>5.58</v>
@@ -6673,7 +6673,7 @@
         <v>11</v>
       </c>
       <c r="AH46" s="2" t="n">
-        <v>6.0578327</v>
+        <v>6.1298776</v>
       </c>
       <c r="AI46" s="2" t="n">
         <v>0</v>
@@ -6745,7 +6745,7 @@
         <v>4225.94</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>3982.04</v>
+        <v>3985.18</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
@@ -6786,13 +6786,13 @@
         <v>0.33</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>368567</v>
+        <v>361462</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>72.76707500000001</v>
+        <v>71.36427</v>
       </c>
       <c r="AC47" s="4" t="n">
-        <v>48.402096</v>
+        <v>47.468998</v>
       </c>
       <c r="AD47" s="4" t="n">
         <v>37.13</v>
@@ -6807,7 +6807,7 @@
         <v>35.1</v>
       </c>
       <c r="AH47" s="4" t="n">
-        <v>28.778822</v>
+        <v>23.038303</v>
       </c>
       <c r="AI47" s="4" t="n">
         <v>27</v>
@@ -7373,7 +7373,7 @@
         <v>324.82</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>296.89</v>
+        <v>296.83</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -7414,13 +7414,13 @@
         <v>1.01</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>21540</v>
+        <v>21360</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>24.673758</v>
+        <v>24.468084</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>18.331898</v>
+        <v>18.179089</v>
       </c>
       <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="inlineStr"/>
@@ -7431,7 +7431,7 @@
         <v>367.9</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>1.2857991</v>
+        <v>1.2750812</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>33</v>
@@ -7501,7 +7501,7 @@
         <v>453.89</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>417.78</v>
+        <v>417.31</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -7542,13 +7542,13 @@
         <v>7.74</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>285704</v>
+        <v>282191</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>9.185655000000001</v>
+        <v>9.072716</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>8.106672</v>
+        <v>8.007</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>28.12</v>
@@ -7563,7 +7563,7 @@
         <v>12.9</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>2.3985927</v>
+        <v>2.3691018</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>475</v>
@@ -7635,7 +7635,7 @@
         <v>1641.65</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1490.46</v>
+        <v>1490.49</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -7676,13 +7676,13 @@
         <v>0.66</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>420012</v>
+        <v>415772</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>31.323023</v>
+        <v>31.006872</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>23.50455</v>
+        <v>23.267313</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.59</v>
@@ -7697,7 +7697,7 @@
         <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.369073</v>
+        <v>4.3249745</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>41</v>
@@ -7769,7 +7769,7 @@
         <v>6510.26</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>6303.62</v>
+        <v>6303.55</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -7810,13 +7810,13 @@
         <v>0.43</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>180280</v>
+        <v>176988</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>70.358475</v>
+        <v>69.07377</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>48.03056</v>
+        <v>47.15355</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>16.19</v>
@@ -7831,7 +7831,7 @@
         <v>13.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>11.689433</v>
+        <v>11.47599</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>44</v>
@@ -7903,7 +7903,7 @@
         <v>1189.85</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1017.63</v>
+        <v>1017.19</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -7944,13 +7944,13 @@
         <v>0.35</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>9965</v>
+        <v>10155</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>88.17967</v>
+        <v>89.86407</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>45.615974</v>
+        <v>46.487324</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>16.94</v>
@@ -7965,7 +7965,7 @@
         <v>69</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>13.810468</v>
+        <v>14.074273</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>0</v>
@@ -8037,7 +8037,7 @@
         <v>8441.25</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7560.62</v>
+        <v>7561.76</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0.49</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>145462</v>
+        <v>142684</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>54.63387</v>
+        <v>53.59061</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>39.262745</v>
+        <v>38.51301</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>24.58</v>
@@ -8099,7 +8099,7 @@
         <v>8</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>12.1131735</v>
+        <v>11.881867</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>36</v>
@@ -8171,7 +8171,7 @@
         <v>7830.53</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>7493.93</v>
+        <v>7498.69</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -8212,13 +8212,13 @@
         <v>0.67</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>119047</v>
+        <v>117566</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>61.402405</v>
+        <v>60.638535</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>38.752354</v>
+        <v>38.27026</v>
       </c>
       <c r="AD8" s="2" t="n">
         <v>21.5</v>
@@ -8233,7 +8233,7 @@
         <v>35.6</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>12.554779</v>
+        <v>12.398593</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>24</v>
@@ -8305,7 +8305,7 @@
         <v>4296.48</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3957.95</v>
+        <v>3950.73</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -8346,13 +8346,13 @@
         <v>0.7</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>153285</v>
+        <v>149282</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>70.789314</v>
+        <v>68.94029</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>47.70262</v>
+        <v>46.456627</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>16.98</v>
@@ -8367,7 +8367,7 @@
         <v>-21.8</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>18.155107</v>
+        <v>17.680895</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>84</v>
@@ -8439,7 +8439,7 @@
         <v>1249.42</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1171.93</v>
+        <v>1171.38</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -8480,13 +8480,13 @@
         <v>1.14</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>319723</v>
+        <v>311913</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>14.354591</v>
+        <v>14.003944</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>18.041344</v>
+        <v>17.60064</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>27.26</v>
@@ -8501,7 +8501,7 @@
         <v>991.8</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>3.1956675</v>
+        <v>3.1176054</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>54</v>
@@ -8573,7 +8573,7 @@
         <v>415.21</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>360.58</v>
+        <v>360.33</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -8614,13 +8614,13 @@
         <v>0.16</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>12713</v>
+        <v>12407</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>30.676786</v>
+        <v>29.93991</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>18.210266</v>
+        <v>17.772844</v>
       </c>
       <c r="AD11" s="4" t="n">
         <v>10.66</v>
@@ -8635,7 +8635,7 @@
         <v>-85.59999999999999</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>3.13987</v>
+        <v>22.567343</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>77</v>
@@ -8954,7 +8954,7 @@
         <v>324.82</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>296.89</v>
+        <v>296.83</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -8995,13 +8995,13 @@
         <v>1.01</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>21540</v>
+        <v>21360</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>24.673758</v>
+        <v>24.468084</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>18.331898</v>
+        <v>18.179089</v>
       </c>
       <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="inlineStr"/>
@@ -9012,7 +9012,7 @@
         <v>367.9</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>1.2857991</v>
+        <v>1.2750812</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>33</v>
@@ -9082,7 +9082,7 @@
         <v>453.89</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>417.78</v>
+        <v>417.31</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -9123,13 +9123,13 @@
         <v>7.74</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>285704</v>
+        <v>282191</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>9.185655000000001</v>
+        <v>9.072716</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>8.106672</v>
+        <v>8.007</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>28.12</v>
@@ -9144,7 +9144,7 @@
         <v>12.9</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>2.3985927</v>
+        <v>2.3691018</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>475</v>
@@ -9216,7 +9216,7 @@
         <v>1641.65</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1490.46</v>
+        <v>1490.49</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -9257,13 +9257,13 @@
         <v>0.66</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>420012</v>
+        <v>415772</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>31.323023</v>
+        <v>31.006872</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>23.50455</v>
+        <v>23.267313</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.59</v>
@@ -9278,7 +9278,7 @@
         <v>3.6</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>4.369073</v>
+        <v>4.3249745</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>41</v>
@@ -9350,7 +9350,7 @@
         <v>6510.26</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>6303.62</v>
+        <v>6303.55</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -9391,13 +9391,13 @@
         <v>0.43</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>180280</v>
+        <v>176988</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>70.358475</v>
+        <v>69.07377</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>48.03056</v>
+        <v>47.15355</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>16.19</v>
@@ -9412,7 +9412,7 @@
         <v>13.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>11.689433</v>
+        <v>11.47599</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>44</v>
@@ -9484,7 +9484,7 @@
         <v>1189.85</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1017.63</v>
+        <v>1017.19</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -9525,13 +9525,13 @@
         <v>0.35</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>9965</v>
+        <v>10155</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>88.17967</v>
+        <v>89.86407</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>45.615974</v>
+        <v>46.487324</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>16.94</v>
@@ -9546,7 +9546,7 @@
         <v>69</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>13.810468</v>
+        <v>14.074273</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
         <v>8441.25</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7560.62</v>
+        <v>7561.76</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -9659,13 +9659,13 @@
         <v>0.49</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>145462</v>
+        <v>142684</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>54.63387</v>
+        <v>53.59061</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>39.262745</v>
+        <v>38.51301</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>24.58</v>
@@ -9680,7 +9680,7 @@
         <v>8</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>12.1131735</v>
+        <v>11.881867</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>36</v>
@@ -9752,7 +9752,7 @@
         <v>7830.53</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>7493.93</v>
+        <v>7498.69</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -9793,13 +9793,13 @@
         <v>0.67</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>119047</v>
+        <v>117566</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>61.402405</v>
+        <v>60.638535</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>38.752354</v>
+        <v>38.27026</v>
       </c>
       <c r="AD8" s="2" t="n">
         <v>21.5</v>
@@ -9814,7 +9814,7 @@
         <v>35.6</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>12.554779</v>
+        <v>12.398593</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>24</v>
@@ -9886,7 +9886,7 @@
         <v>4296.48</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3957.95</v>
+        <v>3950.73</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -9927,13 +9927,13 @@
         <v>0.7</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>153285</v>
+        <v>149282</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>70.789314</v>
+        <v>68.94029</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>47.70262</v>
+        <v>46.456627</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>16.98</v>
@@ -9948,7 +9948,7 @@
         <v>-21.8</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>18.155107</v>
+        <v>17.680895</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>84</v>
@@ -10020,7 +10020,7 @@
         <v>1249.42</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1171.93</v>
+        <v>1171.38</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -10061,13 +10061,13 @@
         <v>1.14</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>319723</v>
+        <v>311913</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>14.354591</v>
+        <v>14.003944</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>18.041344</v>
+        <v>17.60064</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>27.26</v>
@@ -10082,7 +10082,7 @@
         <v>991.8</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>3.1956675</v>
+        <v>3.1176054</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>54</v>
@@ -10154,7 +10154,7 @@
         <v>415.21</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>360.58</v>
+        <v>360.33</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -10195,13 +10195,13 @@
         <v>0.16</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>12713</v>
+        <v>12407</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>30.676786</v>
+        <v>29.93991</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>18.210266</v>
+        <v>17.772844</v>
       </c>
       <c r="AD11" s="4" t="n">
         <v>10.66</v>
@@ -10216,7 +10216,7 @@
         <v>-85.59999999999999</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>3.13987</v>
+        <v>22.567343</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>77</v>
@@ -10261,7 +10261,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 28-May-2026 18:44 IST</t>
+          <t>Run Date: 29-May-2026 18:43 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">

--- a/output/swing_screener_report.xlsx
+++ b/output/swing_screener_report.xlsx
@@ -517,7 +517,7 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="8" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
@@ -775,7 +775,7 @@
         <v>3765.73</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>3091.23</v>
+        <v>3092.67</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -816,13 +816,13 @@
         <v>0.73</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>164121</v>
+        <v>167569</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>67.11676</v>
+        <v>68.526825</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>40.356247</v>
+        <v>41.204098</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>36</v>
@@ -837,7 +837,7 @@
         <v>64</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>20.873882</v>
+        <v>21.312424</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>25</v>
@@ -909,7 +909,7 @@
         <v>981.77</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>922.16</v>
+        <v>922.6</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         <v>2.35</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>75996</v>
+        <v>77350</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>28.989439</v>
+        <v>29.506138</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>16.740313</v>
+        <v>17.038687</v>
       </c>
       <c r="AD3" s="4" t="inlineStr"/>
       <c r="AE3" s="4" t="inlineStr"/>
@@ -971,7 +971,7 @@
         <v>62.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>3.800012</v>
+        <v>3.8677423</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>10</v>
@@ -1041,7 +1041,7 @@
         <v>730.51</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>720.17</v>
+        <v>720.5</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>5.69</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>33148</v>
+        <v>34549</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>36.90504</v>
+        <v>38.464245</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>27.03451</v>
+        <v>28.176691</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.26</v>
@@ -1103,7 +1103,7 @@
         <v>45.8</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>5.5767155</v>
+        <v>5.812326</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>85</v>
@@ -1175,7 +1175,7 @@
         <v>9027.620000000001</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>8158.75</v>
+        <v>8158.26</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -1216,13 +1216,13 @@
         <v>0.53</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>81209</v>
+        <v>81605</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>30.8643</v>
+        <v>31.014858</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>24.328379</v>
+        <v>24.447054</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>32.61</v>
@@ -1237,7 +1237,7 @@
         <v>30.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>10.371437</v>
+        <v>10.4220295</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>713</v>
@@ -1309,7 +1309,7 @@
         <v>4045.71</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3383.54</v>
+        <v>3380.7</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1350,13 +1350,13 @@
         <v>1.78</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>26121</v>
+        <v>26263</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>126.58388</v>
+        <v>127.27096</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>63.013733</v>
+        <v>63.355762</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>32.83</v>
@@ -1371,7 +1371,7 @@
         <v>64.3</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>36.019722</v>
+        <v>36.215233</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>5</v>
@@ -1443,7 +1443,7 @@
         <v>2622.28</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2384.78</v>
+        <v>2380.51</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -1484,13 +1484,13 @@
         <v>0.99</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>400840</v>
+        <v>403707</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>39.684868</v>
+        <v>39.968758</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>51.63206</v>
+        <v>52.001415</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>13.66</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
-        <v>4.6668615</v>
+        <v>4.7002463</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>4</v>
@@ -1575,7 +1575,7 @@
         <v>335.31</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>304.69</v>
+        <v>305.22</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -1616,13 +1616,13 @@
         <v>1.95</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>22662</v>
+        <v>23083</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>25.965223</v>
+        <v>26.447834</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>19.23719</v>
+        <v>19.594748</v>
       </c>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
         <v>367.9</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>1.3521404</v>
+        <v>1.3772724</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>33</v>
@@ -1703,7 +1703,7 @@
         <v>469.61</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>423.29</v>
+        <v>424.55</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -1744,13 +1744,13 @@
         <v>0.73</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>8418</v>
+        <v>8525</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>51.80216</v>
+        <v>52.45837</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>38.747257</v>
+        <v>39.238094</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>28.75</v>
@@ -1765,7 +1765,7 @@
         <v>116.3</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>15.739199</v>
+        <v>15.938578</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>309</v>
@@ -1837,7 +1837,7 @@
         <v>506.37</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>372.46</v>
+        <v>372.1</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1878,13 +1878,13 @@
         <v>0.76</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>7728</v>
+        <v>7738</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>41.665497</v>
+        <v>41.71831</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>28.686062</v>
+        <v>28.722425</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>25.31</v>
@@ -1899,7 +1899,7 @@
         <v>113</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>10.492109</v>
+        <v>10.505409</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>1698.35</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1525.77</v>
+        <v>1524.23</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -2012,13 +2012,13 @@
         <v>1.17</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>417685</v>
+        <v>415819</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>31.154839</v>
+        <v>31.01564</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>23.459633</v>
+        <v>23.291836</v>
       </c>
       <c r="AD11" s="4" t="n">
         <v>15.59</v>
@@ -2033,7 +2033,7 @@
         <v>3.6</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>4.3527536</v>
+        <v>4.3333054</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>41</v>
@@ -2105,7 +2105,7 @@
         <v>5344.79</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>4596.45</v>
+        <v>4595.6</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2146,13 +2146,13 @@
         <v>0.49</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>155828</v>
+        <v>159501</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>65.78701</v>
+        <v>67.33762</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>47.24181</v>
+        <v>48.35531</v>
       </c>
       <c r="AD12" s="2" t="n">
         <v>29.45</v>
@@ -2167,7 +2167,7 @@
         <v>22.7</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>18.385876</v>
+        <v>18.819235</v>
       </c>
       <c r="AI12" s="2" t="n">
         <v>117</v>
@@ -2239,7 +2239,7 @@
         <v>1004.25</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>976.09</v>
+        <v>976.33</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -2280,13 +2280,13 @@
         <v>0.75</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>938892</v>
+        <v>942308</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>11.160303</v>
+        <v>11.200899</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>9.954886999999999</v>
+        <v>9.991097999999999</v>
       </c>
       <c r="AD13" s="4" t="n">
         <v>15.48</v>
@@ -2299,7 +2299,7 @@
         <v>-3.1</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>1.5859243</v>
+        <v>1.5916932</v>
       </c>
       <c r="AI13" s="4" t="n">
         <v>171</v>
@@ -2369,7 +2369,7 @@
         <v>291.71</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>264.18</v>
+        <v>264.06</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -2410,13 +2410,13 @@
         <v>0.45</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>77820</v>
+        <v>78165</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>18.050316</v>
+        <v>18.130362</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>13.287138</v>
+        <v>13.346061</v>
       </c>
       <c r="AD14" s="2" t="n">
         <v>11.73</v>
@@ -2429,7 +2429,7 @@
         <v>22.2</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>1.943427</v>
+        <v>1.9520452</v>
       </c>
       <c r="AI14" s="2" t="n">
         <v>38</v>
@@ -2499,7 +2499,7 @@
         <v>963.76</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>963.16</v>
+        <v>962.66</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -2540,13 +2540,13 @@
         <v>1.13</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>36506</v>
+        <v>36152</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>42.01025</v>
+        <v>41.602283</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>29.642149</v>
+        <v>29.354292</v>
       </c>
       <c r="AD15" s="4" t="n">
         <v>16.2</v>
@@ -2561,7 +2561,7 @@
         <v>11.2</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>6.8114424</v>
+        <v>6.745296</v>
       </c>
       <c r="AI15" s="4" t="n">
         <v>47</v>
@@ -2633,7 +2633,7 @@
         <v>8866.040000000001</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>7815.57</v>
+        <v>7820.65</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2674,13 +2674,13 @@
         <v>0.64</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>143836</v>
+        <v>143866</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>53.937786</v>
+        <v>54.065063</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>38.688198</v>
+        <v>38.696297</v>
       </c>
       <c r="AD16" s="2" t="n">
         <v>24.58</v>
@@ -2695,7 +2695,7 @@
         <v>8</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>11.977775</v>
+        <v>11.980282</v>
       </c>
       <c r="AI16" s="2" t="n">
         <v>49</v>
@@ -2767,7 +2767,7 @@
         <v>723.27</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>620.64</v>
+        <v>619.84</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
@@ -2808,13 +2808,13 @@
         <v>0.28</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>18992</v>
+        <v>18548</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>31.347649</v>
+        <v>30.613497</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>19.677792</v>
+        <v>19.216944</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>13.52</v>
@@ -2829,7 +2829,7 @@
         <v>31.3</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>3.6916</v>
+        <v>3.605144</v>
       </c>
       <c r="AI17" s="4" t="n">
         <v>23</v>
@@ -2901,7 +2901,7 @@
         <v>88.53</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>80.47</v>
+        <v>80.34</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -2942,13 +2942,13 @@
         <v>0.58</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>79944</v>
+        <v>77781</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>10.735537</v>
+        <v>10.4451</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>9.03233</v>
+        <v>8.787971499999999</v>
       </c>
       <c r="AD18" s="2" t="n">
         <v>23.36</v>
@@ -2963,7 +2963,7 @@
         <v>37.7</v>
       </c>
       <c r="AH18" s="2" t="n">
-        <v>2.3427114</v>
+        <v>2.2793322</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>385</v>
@@ -3035,7 +3035,7 @@
         <v>4346.79</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4009.82</v>
+        <v>4010.45</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -3076,13 +3076,13 @@
         <v>0.76</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>154710</v>
+        <v>152436</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>71.425</v>
+        <v>70.375</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>48.239807</v>
+        <v>47.530643</v>
       </c>
       <c r="AD19" s="4" t="n">
         <v>16.99</v>
@@ -3097,7 +3097,7 @@
         <v>-21.7</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>18.323868</v>
+        <v>18.054493</v>
       </c>
       <c r="AI19" s="4" t="n">
         <v>83</v>
@@ -3169,7 +3169,7 @@
         <v>7161.85</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>6946.7</v>
+        <v>6945.07</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -3210,13 +3210,13 @@
         <v>0.59</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>200713</v>
+        <v>209291</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>36.363636</v>
+        <v>37.917744</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>27.577248</v>
+        <v>28.755842</v>
       </c>
       <c r="AD20" s="2" t="n">
         <v>23.77</v>
@@ -3231,7 +3231,7 @@
         <v>11.5</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>7.9909945</v>
+        <v>8.332514</v>
       </c>
       <c r="AI20" s="2" t="n">
         <v>96</v>
@@ -3303,7 +3303,7 @@
         <v>4302.64</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3635.99</v>
+        <v>3622.58</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
@@ -3344,13 +3344,13 @@
         <v>0.75</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>53241</v>
+        <v>53407</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>74.06832</v>
+        <v>74.2987</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>48.96844</v>
+        <v>49.12075</v>
       </c>
       <c r="AD21" s="4" t="n">
         <v>13.69</v>
@@ -3365,7 +3365,7 @@
         <v>18.7</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>9.595321</v>
+        <v>9.625165000000001</v>
       </c>
       <c r="AI21" s="4" t="n">
         <v>30</v>
@@ -3437,7 +3437,7 @@
         <v>1264.05</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1190.12</v>
+        <v>1190.72</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>0.65</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>316722</v>
+        <v>316453</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>14.22495</v>
+        <v>14.212892</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>18.055002</v>
+        <v>18.039698</v>
       </c>
       <c r="AD22" s="2" t="n">
         <v>27.26</v>
@@ -3499,7 +3499,7 @@
         <v>991.8</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>3.1654184</v>
+        <v>3.1627352</v>
       </c>
       <c r="AI22" s="2" t="n">
         <v>55</v>
@@ -3571,7 +3571,7 @@
         <v>839.24</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>804.6</v>
+        <v>805.3</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -3612,13 +3612,13 @@
         <v>0.77</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>113886</v>
+        <v>114438</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>9.727335999999999</v>
+        <v>9.774506000000001</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>7.878552</v>
+        <v>7.9167566</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>15.44</v>
@@ -3631,7 +3631,7 @@
         <v>6.4</v>
       </c>
       <c r="AH23" s="4" t="n">
-        <v>1.4226319</v>
+        <v>1.4295305</v>
       </c>
       <c r="AI23" s="4" t="n">
         <v>216</v>
@@ -3701,7 +3701,7 @@
         <v>1281.37</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1334.86</v>
+        <v>1336.4</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -3742,13 +3742,13 @@
         <v>1.02</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>961543</v>
+        <v>952076</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>17.920343</v>
+        <v>17.74392</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>14.74152</v>
+        <v>14.596391</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>16.36</v>
@@ -3761,7 +3761,7 @@
         <v>8.4</v>
       </c>
       <c r="AH24" s="2" t="n">
-        <v>2.644649</v>
+        <v>2.6186128</v>
       </c>
       <c r="AI24" s="2" t="n">
         <v>82</v>
@@ -3831,7 +3831,7 @@
         <v>2280.77</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2188.54</v>
+        <v>2188.67</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         <v>0.64</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>104857</v>
+        <v>103934</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>19.684978</v>
+        <v>19.51159</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>22.518625</v>
+        <v>22.320276</v>
       </c>
       <c r="AD25" s="4" t="n">
         <v>26.91</v>
@@ -3893,7 +3893,7 @@
         <v>89</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>4.667944</v>
+        <v>4.6268272</v>
       </c>
       <c r="AI25" s="4" t="n">
         <v>52</v>
@@ -3965,7 +3965,7 @@
         <v>192.03</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>173.48</v>
+        <v>173.11</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -4006,13 +4006,13 @@
         <v>1.18</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>32963</v>
+        <v>33974</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>26.956522</v>
+        <v>27.783926</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>9.467454</v>
+        <v>9.758048</v>
       </c>
       <c r="AD26" s="2" t="n">
         <v>4.88</v>
@@ -4025,7 +4025,7 @@
         <v>68</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>1.2870839</v>
+        <v>1.3265897</v>
       </c>
       <c r="AI26" s="2" t="n">
         <v>73</v>
@@ -4095,7 +4095,7 @@
         <v>1047.14</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>858.09</v>
+        <v>855.77</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -4136,13 +4136,13 @@
         <v>0.71</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>24400</v>
+        <v>25062</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>74.643486</v>
+        <v>76.67059</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>44.229</v>
+        <v>45.430134</v>
       </c>
       <c r="AD27" s="4" t="n">
         <v>14.14</v>
@@ -4157,7 +4157,7 @@
         <v>43.7</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>8.465944</v>
+        <v>8.695855</v>
       </c>
       <c r="AI27" s="4" t="n">
         <v>12</v>
@@ -4229,7 +4229,7 @@
         <v>2569.22</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2516.72</v>
+        <v>2516.02</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -4270,13 +4270,13 @@
         <v>0.84</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>263378</v>
+        <v>262601</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>60.972034</v>
+        <v>60.792274</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>46.898796</v>
+        <v>46.76053</v>
       </c>
       <c r="AD28" s="2" t="n">
         <v>20.89</v>
@@ -4291,7 +4291,7 @@
         <v>69.2</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>12.320566</v>
+        <v>12.294497</v>
       </c>
       <c r="AI28" s="2" t="n">
         <v>100</v>
@@ -4363,7 +4363,7 @@
         <v>255.18</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>269.17</v>
+        <v>268.81</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -4404,13 +4404,13 @@
         <v>3.06</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>13605</v>
+        <v>13655</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>14.429103</v>
+        <v>14.48221</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>10.495641</v>
+        <v>10.53427</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>20.11</v>
@@ -4425,7 +4425,7 @@
         <v>25.9</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>2.6843052</v>
+        <v>2.6941848</v>
       </c>
       <c r="AI29" s="4" t="n">
         <v>184</v>
@@ -4497,7 +4497,7 @@
         <v>2907.76</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2393.81</v>
+        <v>2393.19</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -4538,13 +4538,13 @@
         <v>0.52</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>72613</v>
+        <v>73697</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>54.644707</v>
+        <v>55.460644</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>34.01346</v>
+        <v>34.521336</v>
       </c>
       <c r="AD30" s="2" t="n">
         <v>37.88</v>
@@ -4559,7 +4559,7 @@
         <v>291.2</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>17.255247</v>
+        <v>17.512897</v>
       </c>
       <c r="AI30" s="2" t="n">
         <v>21</v>
@@ -4672,13 +4672,13 @@
         <v>1.02</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>129809</v>
+        <v>130764</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>6.679105</v>
+        <v>6.7282014</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>6.626024</v>
+        <v>6.6747303</v>
       </c>
       <c r="AD31" s="4" t="n">
         <v>15.71</v>
@@ -4687,7 +4687,7 @@
       <c r="AF31" s="4" t="inlineStr"/>
       <c r="AG31" s="4" t="inlineStr"/>
       <c r="AH31" s="4" t="n">
-        <v>0.97269815</v>
+        <v>0.9798481999999999</v>
       </c>
       <c r="AI31" s="4" t="n">
         <v>294</v>
@@ -4757,7 +4757,7 @@
         <v>440.85</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>436.6</v>
+        <v>436.41</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -4798,13 +4798,13 @@
         <v>0.24</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>6314</v>
+        <v>6424</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>34.60902</v>
+        <v>35.214287</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>19.099585</v>
+        <v>19.433609</v>
       </c>
       <c r="AD32" s="2" t="n">
         <v>13.45</v>
@@ -4819,7 +4819,7 @@
         <v>162</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>4.3976727</v>
+        <v>4.4745817</v>
       </c>
       <c r="AI32" s="2" t="n">
         <v>65</v>
@@ -4891,7 +4891,7 @@
         <v>4186.03</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4012.11</v>
+        <v>4011.32</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
@@ -4936,13 +4936,13 @@
         <v>1.28</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>371140</v>
+        <v>379966</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>72.99372</v>
+        <v>74.72959</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>48.837673</v>
+        <v>49.999084</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>37.13</v>
@@ -4957,7 +4957,7 @@
         <v>35.1</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>23.655123</v>
+        <v>24.217669</v>
       </c>
       <c r="AI33" s="4" t="n">
         <v>26</v>
@@ -5029,7 +5029,7 @@
         <v>3932.96</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3837.43</v>
+        <v>3839.01</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -5070,13 +5070,13 @@
         <v>1.63</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>557049</v>
+        <v>573626</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>34.60349</v>
+        <v>35.633224</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>22.07506</v>
+        <v>22.729342</v>
       </c>
       <c r="AD34" s="2" t="n">
         <v>16.95</v>
@@ -5091,7 +5091,7 @@
         <v>-34.5</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>5.096857</v>
+        <v>5.2485304</v>
       </c>
       <c r="AI34" s="2" t="n">
         <v>94</v>
@@ -5113,32 +5113,32 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Limited</t>
+          <t>Adani Total Gas Limited</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Auto Parts</t>
+          <t>Utilities - Regulated Gas</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
         <v>53.3</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>35.4</v>
+        <v>33</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>17.9</v>
+        <v>20.3</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -5147,23 +5147,23 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 👤 High Promoter</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>143.4</v>
+        <v>728.5</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>139.34</v>
+        <v>712.59</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>132.46</v>
+        <v>661.8</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>118.76</v>
+        <v>609.5599999999999</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
@@ -5176,103 +5176,101 @@
         </is>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>94.48999999999999</v>
+        <v>84.75</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>59.43</v>
+        <v>55.72</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.9167</v>
+        <v>27.2342</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>4.4471</v>
+        <v>32.2057</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.5304</v>
+        <v>-4.9716</v>
       </c>
       <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="n">
-        <v>42.82</v>
+        <v>40.34</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>12743045</v>
+        <v>3246129</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>27910871</v>
+        <v>12445473</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>151018</v>
+        <v>79192</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>39.180325</v>
-      </c>
-      <c r="AC35" s="4" t="n">
-        <v>21.973038</v>
-      </c>
+        <v>120.61139</v>
+      </c>
+      <c r="AC35" s="4" t="inlineStr"/>
       <c r="AD35" s="4" t="n">
-        <v>10.11</v>
+        <v>14.46</v>
       </c>
       <c r="AE35" s="4" t="n">
-        <v>43.908</v>
+        <v>58.65</v>
       </c>
       <c r="AF35" s="4" t="n">
-        <v>14.9</v>
+        <v>16.1</v>
       </c>
       <c r="AG35" s="4" t="n">
-        <v>43</v>
+        <v>8.5</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>4.094569</v>
+        <v>16.27857</v>
       </c>
       <c r="AI35" s="4" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>1.06</v>
+        <v>0.638</v>
       </c>
       <c r="AK35" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MOTHERSON/</t>
+          <t>https://www.screener.in/company/ATGL/</t>
         </is>
       </c>
       <c r="AL35" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ATGL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Adani Total Gas Limited</t>
+          <t>Marico Limited</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Gas</t>
+          <t>Household &amp; Personal Products</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>53.3</v>
+        <v>52.4</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>20.3</v>
+        <v>27.4</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
@@ -5281,23 +5279,23 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 👤 High Promoter</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base | 💎 High ROE</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>728.5</v>
+        <v>819.05</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>712.59</v>
+        <v>816.29</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>661.8</v>
+        <v>803.62</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>610.02</v>
+        <v>763.6900000000001</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -5310,101 +5308,103 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>84.75</v>
+        <v>96.5</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>55.72</v>
+        <v>53.02</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>27.2342</v>
+        <v>2.0542</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>32.2057</v>
+        <v>4.4612</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>-4.9716</v>
+        <v>-2.4071</v>
       </c>
       <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="n">
-        <v>40.34</v>
+        <v>19.91</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>3246129</v>
+        <v>1184514</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>12445473</v>
+        <v>1724772</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>80121</v>
+        <v>104920</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>122.0268</v>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+        <v>59.53309</v>
+      </c>
+      <c r="AC36" s="2" t="n">
+        <v>42.862484</v>
+      </c>
       <c r="AD36" s="2" t="n">
-        <v>14.46</v>
+        <v>41.39</v>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>58.65</v>
+        <v>12.394</v>
       </c>
       <c r="AF36" s="2" t="n">
-        <v>16.1</v>
+        <v>22.1</v>
       </c>
       <c r="AG36" s="2" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>16.476309</v>
+        <v>24.735735</v>
       </c>
       <c r="AI36" s="2" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="AJ36" s="2" t="n">
-        <v>0.638</v>
+        <v>1.31</v>
       </c>
       <c r="AK36" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ATGL/</t>
+          <t>https://www.screener.in/company/MARICO/</t>
         </is>
       </c>
       <c r="AL36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ATGL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Marico Limited</t>
+          <t>Pidilite Industries Limited</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Household &amp; Personal Products</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>25</v>
+        <v>28.5</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>27.4</v>
+        <v>23.6</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -5413,132 +5413,136 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base | 💎 High ROE</t>
+          <t>⚡ Fresh MACD Cross | ✅ Supertrend Buy | 🏆 Near 52W High | 📉 Tight Base | 💎 High ROE</t>
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>819.05</v>
+        <v>1535.5</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1.02</v>
+        <v>2.45</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>816.29</v>
+        <v>1475.11</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>803.62</v>
+        <v>1445.95</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>763.53</v>
+        <v>1452.26</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>68.51000000000001</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>20.3577</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>17.8994</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>2.4583</v>
+      </c>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="R37" s="4" t="n">
-        <v>53.02</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>2.0542</v>
-      </c>
-      <c r="T37" s="4" t="n">
-        <v>4.4612</v>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>-2.4071</v>
-      </c>
-      <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="n">
-        <v>19.91</v>
+        <v>19.57</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>1184514</v>
+        <v>1254231</v>
       </c>
       <c r="Y37" s="4" t="n">
-        <v>1724772</v>
+        <v>836847</v>
       </c>
       <c r="Z37" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>106139</v>
+        <v>159893</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>60.224262</v>
+        <v>65.59498600000001</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>43.36011</v>
+        <v>51.689976</v>
       </c>
       <c r="AD37" s="4" t="n">
-        <v>41.39</v>
+        <v>23.52</v>
       </c>
       <c r="AE37" s="4" t="n">
-        <v>12.394</v>
+        <v>3.776</v>
       </c>
       <c r="AF37" s="4" t="n">
-        <v>22.1</v>
+        <v>14.1</v>
       </c>
       <c r="AG37" s="4" t="n">
-        <v>14.5</v>
+        <v>37</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>25.022915</v>
+        <v>14.764898</v>
       </c>
       <c r="AI37" s="4" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>1.31</v>
+        <v>2.38</v>
       </c>
       <c r="AK37" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MARICO/</t>
+          <t>https://www.screener.in/company/PIDILITIND/</t>
         </is>
       </c>
       <c r="AL37" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MARICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Pidilite Industries Limited</t>
+          <t>RateGain Travel Technologies Limited</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>23.6</v>
+        <v>19</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -5547,27 +5551,27 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>⚡ Fresh MACD Cross | ✅ Supertrend Buy | 🏆 Near 52W High | 📉 Tight Base | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1535.5</v>
+        <v>783.05</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1475.11</v>
+        <v>733.26</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1445.95</v>
+        <v>669.67</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1453.24</v>
+        <v>602.49</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5576,107 +5580,103 @@
         </is>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>97.5</v>
+        <v>97.64</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>68.51000000000001</v>
+        <v>69.27</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>20.3577</v>
+        <v>39.1958</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>17.8994</v>
+        <v>40.6626</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>2.4583</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>-1.4668</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="n">
-        <v>19.57</v>
+        <v>58.38</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>1254231</v>
+        <v>327158</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>836847</v>
+        <v>1177141</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>1.5</v>
+        <v>0.28</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>156279</v>
+        <v>9738</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>64.11273</v>
+        <v>50.155106</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>50.521935</v>
+        <v>24.923134</v>
       </c>
       <c r="AD38" s="2" t="n">
-        <v>23.52</v>
+        <v>10.54</v>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>3.776</v>
+        <v>47.296</v>
       </c>
       <c r="AF38" s="2" t="n">
-        <v>14.1</v>
+        <v>174.5</v>
       </c>
       <c r="AG38" s="2" t="n">
-        <v>37</v>
+        <v>27.1</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>14.431255</v>
+        <v>4.8546634</v>
       </c>
       <c r="AI38" s="2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ38" s="2" t="n">
-        <v>2.38</v>
+        <v>1.412</v>
       </c>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/PIDILITIND/</t>
+          <t>https://www.screener.in/company/RATEGAIN/</t>
         </is>
       </c>
       <c r="AL38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RATEGAIN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>RateGain Travel Technologies Limited</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Banks - Regional</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
@@ -5685,23 +5685,23 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>📤 20D Breakout | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>783.05</v>
+        <v>1356.3</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1.33</v>
+        <v>2.96</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>733.26</v>
+        <v>1289.73</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>669.67</v>
+        <v>1286.96</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>603.2</v>
+        <v>1260.73</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
@@ -5714,103 +5714,99 @@
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>97.64</v>
+        <v>95.63</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>69.27</v>
+        <v>67.98</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>39.1958</v>
+        <v>8.9633</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>40.6626</v>
+        <v>0.4413</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>-1.4668</v>
+        <v>8.522</v>
       </c>
       <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="n">
-        <v>58.38</v>
+        <v>15.68</v>
       </c>
       <c r="X39" s="4" t="n">
-        <v>327158</v>
+        <v>8535670</v>
       </c>
       <c r="Y39" s="4" t="n">
-        <v>1177141</v>
+        <v>7175943</v>
       </c>
       <c r="Z39" s="4" t="n">
-        <v>0.28</v>
+        <v>1.19</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>9248</v>
+        <v>425576</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>47.630775</v>
+        <v>16.1929</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>23.797924</v>
+        <v>11.445203</v>
       </c>
       <c r="AD39" s="4" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="AE39" s="4" t="n">
-        <v>47.296</v>
-      </c>
+        <v>13.15</v>
+      </c>
+      <c r="AE39" s="4" t="inlineStr"/>
       <c r="AF39" s="4" t="n">
-        <v>174.5</v>
+        <v>-11.2</v>
       </c>
       <c r="AG39" s="4" t="n">
-        <v>27.1</v>
+        <v>6.4</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>4.610326</v>
+        <v>1.9769752</v>
       </c>
       <c r="AI39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="4" t="n">
-        <v>1.412</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="AJ39" s="4" t="inlineStr"/>
       <c r="AK39" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/RATEGAIN/</t>
+          <t>https://www.screener.in/company/AXISBANK/</t>
         </is>
       </c>
       <c r="AL39" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RATEGAIN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
@@ -5819,23 +5815,23 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>📤 20D Breakout | ✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1356.3</v>
+        <v>273.5</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.96</v>
+        <v>5.09</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1289.73</v>
+        <v>266.41</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1286.96</v>
+        <v>264.41</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1261.56</v>
+        <v>251.14</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -5848,99 +5844,103 @@
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>95.63</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>67.98</v>
+        <v>57.22</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>8.9633</v>
+        <v>-0.1248</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>0.4413</v>
+        <v>0.1225</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>8.522</v>
+        <v>-0.2473</v>
       </c>
       <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="2" t="n">
-        <v>15.68</v>
+        <v>13.22</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>8535670</v>
+        <v>12127542</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>7175943</v>
+        <v>7300388</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>1.19</v>
+        <v>1.66</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>421843</v>
+        <v>78125</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>16.050888</v>
+        <v>384.22534</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>11.344829</v>
+        <v>102.11033</v>
       </c>
       <c r="AD40" s="2" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="AE40" s="2" t="inlineStr"/>
+        <v>14.34</v>
+      </c>
+      <c r="AE40" s="2" t="n">
+        <v>82.405</v>
+      </c>
       <c r="AF40" s="2" t="n">
-        <v>-11.2</v>
+        <v>28.4</v>
       </c>
       <c r="AG40" s="2" t="n">
-        <v>6.4</v>
+        <v>290.2</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>1.959637</v>
+        <v>55.07773</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ40" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="2" t="n">
+        <v>1.156</v>
+      </c>
       <c r="AK40" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AXISBANK/</t>
+          <t>https://www.screener.in/company/NYKAA/</t>
         </is>
       </c>
       <c r="AL40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Limited</t>
+          <t>Radico Khaitan Limited</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Beverages - Wineries &amp; Distilleries</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>32.2</v>
+        <v>34.6</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>19.6</v>
+        <v>16.7</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
@@ -5953,19 +5953,19 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>273.5</v>
+        <v>3541.7</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>5.09</v>
+        <v>2.66</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>266.41</v>
+        <v>3476.82</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>264.41</v>
+        <v>3334.51</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>251.15</v>
+        <v>3046.98</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
@@ -5978,103 +5978,99 @@
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>95.76000000000001</v>
+        <v>96.27</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>57.22</v>
+        <v>59.22</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>-0.1248</v>
+        <v>40.6117</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>0.1225</v>
+        <v>56.9006</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>-0.2473</v>
+        <v>-16.2889</v>
       </c>
       <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="n">
-        <v>13.22</v>
+        <v>27.85</v>
       </c>
       <c r="X41" s="4" t="n">
-        <v>12127542</v>
+        <v>302638</v>
       </c>
       <c r="Y41" s="4" t="n">
-        <v>7300388</v>
+        <v>246481</v>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>78326</v>
+        <v>48108</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>385.21127</v>
+        <v>79.85771</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>102.372345</v>
-      </c>
-      <c r="AD41" s="4" t="n">
-        <v>14.34</v>
-      </c>
+        <v>49.755047</v>
+      </c>
+      <c r="AD41" s="4" t="inlineStr"/>
       <c r="AE41" s="4" t="n">
-        <v>82.405</v>
+        <v>20.939</v>
       </c>
       <c r="AF41" s="4" t="n">
-        <v>28.4</v>
+        <v>19.5</v>
       </c>
       <c r="AG41" s="4" t="n">
-        <v>290.2</v>
+        <v>62.1</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>55.21906</v>
+        <v>14.497959</v>
       </c>
       <c r="AI41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" s="4" t="n">
-        <v>1.156</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="AJ41" s="4" t="inlineStr"/>
       <c r="AK41" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NYKAA/</t>
+          <t>https://www.screener.in/company/RADICO/</t>
         </is>
       </c>
       <c r="AL41" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RADICO</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Radico Khaitan Limited</t>
+          <t>Arvind Limited</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Beverages - Wineries &amp; Distilleries</t>
+          <t>Textile Manufacturing</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>34.6</v>
+        <v>35.4</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>16.7</v>
+        <v>15.8</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -6083,23 +6079,23 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3541.7</v>
+        <v>494.5</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.66</v>
+        <v>0.25</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3476.82</v>
+        <v>480.76</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3334.51</v>
+        <v>444.34</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>3047</v>
+        <v>378.73</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -6112,99 +6108,103 @@
         </is>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>96.27</v>
+        <v>96.05</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>59.22</v>
+        <v>62.05</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>40.6117</v>
+        <v>17.2427</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>56.9006</v>
+        <v>20.0992</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>-16.2889</v>
+        <v>-2.8565</v>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
       <c r="W42" s="2" t="n">
-        <v>27.85</v>
+        <v>42.84</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>302638</v>
+        <v>473209</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>246481</v>
+        <v>984016</v>
       </c>
       <c r="Z42" s="2" t="n">
-        <v>1.23</v>
+        <v>0.48</v>
       </c>
       <c r="AA42" s="2" t="n">
-        <v>47434</v>
+        <v>13072</v>
       </c>
       <c r="AB42" s="2" t="n">
-        <v>78.73944</v>
+        <v>31.623335</v>
       </c>
       <c r="AC42" s="2" t="n">
-        <v>49.05831</v>
-      </c>
-      <c r="AD42" s="2" t="inlineStr"/>
+        <v>18.56862</v>
+      </c>
+      <c r="AD42" s="2" t="n">
+        <v>10.66</v>
+      </c>
       <c r="AE42" s="2" t="n">
-        <v>20.939</v>
+        <v>40.071</v>
       </c>
       <c r="AF42" s="2" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AG42" s="2" t="n">
-        <v>62.1</v>
+        <v>5.9</v>
       </c>
       <c r="AH42" s="2" t="n">
-        <v>14.294939</v>
+        <v>3.2285633</v>
       </c>
       <c r="AI42" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ42" s="2" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>1.141</v>
+      </c>
       <c r="AK42" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/RADICO/</t>
+          <t>https://www.screener.in/company/ARVIND/</t>
         </is>
       </c>
       <c r="AL42" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RADICO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ARVIND</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Arvind Limited</t>
+          <t>Angel One Limited</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Textile Manufacturing</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>35.4</v>
+        <v>27.4</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>15.8</v>
+        <v>23.6</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
@@ -6213,23 +6213,23 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>494.5</v>
+        <v>339.5</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.25</v>
+        <v>4.86</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>480.76</v>
+        <v>330.11</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>444.34</v>
+        <v>312.19</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>379.32</v>
+        <v>273.39</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
@@ -6242,103 +6242,103 @@
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>96.05</v>
+        <v>96.72</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>62.05</v>
+        <v>57.43</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>17.2427</v>
+        <v>5.8808</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>20.0992</v>
+        <v>7.9982</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>-2.8565</v>
+        <v>-2.1174</v>
       </c>
       <c r="V43" s="4" t="inlineStr"/>
       <c r="W43" s="4" t="n">
-        <v>42.84</v>
+        <v>19.99</v>
       </c>
       <c r="X43" s="4" t="n">
-        <v>473209</v>
+        <v>7318502</v>
       </c>
       <c r="Y43" s="4" t="n">
-        <v>984016</v>
+        <v>7826469</v>
       </c>
       <c r="Z43" s="4" t="n">
-        <v>0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>12962</v>
+        <v>32177</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>31.357006</v>
+        <v>35.766495</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>18.412237</v>
+        <v>20.313564</v>
       </c>
       <c r="AD43" s="4" t="n">
-        <v>10.66</v>
+        <v>15.53</v>
       </c>
       <c r="AE43" s="4" t="n">
-        <v>40.071</v>
+        <v>129.314</v>
       </c>
       <c r="AF43" s="4" t="n">
-        <v>15</v>
+        <v>33.5</v>
       </c>
       <c r="AG43" s="4" t="n">
-        <v>5.9</v>
+        <v>82.7</v>
       </c>
       <c r="AH43" s="4" t="n">
-        <v>3.2013726</v>
+        <v>5.245291</v>
       </c>
       <c r="AI43" s="4" t="n">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="AJ43" s="4" t="n">
-        <v>1.141</v>
+        <v>1.324</v>
       </c>
       <c r="AK43" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ARVIND/</t>
+          <t>https://www.screener.in/company/ANGELONE/</t>
         </is>
       </c>
       <c r="AL43" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ARVIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ANGELONE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Angel One Limited</t>
+          <t>Divi's Laboratories Limited</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
         <v>51</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>27.4</v>
+        <v>24.8</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>23.6</v>
+        <v>26.2</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
@@ -6347,23 +6347,23 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base | 🏦 Zero Debt</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>339.5</v>
+        <v>6638</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4.86</v>
+        <v>-0.26</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>330.11</v>
+        <v>6654.8</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>312.19</v>
+        <v>6555.64</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>274.22</v>
+        <v>6376.34</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -6376,103 +6376,103 @@
         </is>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>96.72</v>
+        <v>94.3</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>57.43</v>
+        <v>50.03</v>
       </c>
       <c r="S44" s="2" t="n">
-        <v>5.8808</v>
+        <v>11.9844</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>7.9982</v>
+        <v>32.2234</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>-2.1174</v>
+        <v>-20.239</v>
       </c>
       <c r="V44" s="2" t="inlineStr"/>
       <c r="W44" s="2" t="n">
-        <v>19.99</v>
+        <v>21.28</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>7318502</v>
+        <v>162810</v>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>7826469</v>
+        <v>392123</v>
       </c>
       <c r="Z44" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="AA44" s="2" t="n">
-        <v>31008</v>
+        <v>175435</v>
       </c>
       <c r="AB44" s="2" t="n">
-        <v>34.467003</v>
+        <v>68.19213000000001</v>
       </c>
       <c r="AC44" s="2" t="n">
-        <v>19.57552</v>
+        <v>46.85123</v>
       </c>
       <c r="AD44" s="2" t="n">
-        <v>15.53</v>
+        <v>16.19</v>
       </c>
       <c r="AE44" s="2" t="n">
-        <v>129.314</v>
+        <v>0.042</v>
       </c>
       <c r="AF44" s="2" t="n">
-        <v>33.5</v>
+        <v>9.5</v>
       </c>
       <c r="AG44" s="2" t="n">
-        <v>82.7</v>
+        <v>13.6</v>
       </c>
       <c r="AH44" s="2" t="n">
-        <v>5.054716</v>
+        <v>10.459317</v>
       </c>
       <c r="AI44" s="2" t="n">
-        <v>206</v>
+        <v>45</v>
       </c>
       <c r="AJ44" s="2" t="n">
-        <v>1.324</v>
+        <v>5.431</v>
       </c>
       <c r="AK44" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ANGELONE/</t>
+          <t>https://www.screener.in/company/DIVISLAB/</t>
         </is>
       </c>
       <c r="AL44" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ANGELONE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Limited</t>
+          <t>Avalon Technologies Limited</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>51</v>
+        <v>50.90000000000001</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>24.8</v>
+        <v>29.8</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>26.2</v>
+        <v>21.1</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
@@ -6481,23 +6481,23 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base | 🏦 Zero Debt</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 At 52W High</t>
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>6638</v>
+        <v>1687</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-0.26</v>
+        <v>7.58</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>6654.8</v>
+        <v>1506.77</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>6555.64</v>
+        <v>1335.21</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>6387.54</v>
+        <v>1082.9</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
@@ -6510,103 +6510,103 @@
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>94.3</v>
+        <v>99.47</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>50.03</v>
+        <v>68.41</v>
       </c>
       <c r="S45" s="4" t="n">
-        <v>11.9844</v>
+        <v>99.502</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>32.2234</v>
+        <v>101.0941</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>-20.239</v>
+        <v>-1.5921</v>
       </c>
       <c r="V45" s="4" t="inlineStr"/>
       <c r="W45" s="4" t="n">
-        <v>21.28</v>
+        <v>25.83</v>
       </c>
       <c r="X45" s="4" t="n">
-        <v>162810</v>
+        <v>476593</v>
       </c>
       <c r="Y45" s="4" t="n">
-        <v>392123</v>
+        <v>675422</v>
       </c>
       <c r="Z45" s="4" t="n">
-        <v>0.42</v>
+        <v>0.71</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>176218</v>
+        <v>11755</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>68.496544</v>
+        <v>104.3272</v>
       </c>
       <c r="AC45" s="4" t="n">
-        <v>47.06037</v>
+        <v>53.80973</v>
       </c>
       <c r="AD45" s="4" t="n">
-        <v>16.19</v>
+        <v>16.94</v>
       </c>
       <c r="AE45" s="4" t="n">
-        <v>0.042</v>
+        <v>29.503</v>
       </c>
       <c r="AF45" s="4" t="n">
-        <v>9.5</v>
+        <v>40</v>
       </c>
       <c r="AG45" s="4" t="n">
-        <v>13.6</v>
+        <v>69</v>
       </c>
       <c r="AH45" s="4" t="n">
-        <v>10.506007</v>
+        <v>16.291168</v>
       </c>
       <c r="AI45" s="4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AJ45" s="4" t="n">
-        <v>5.431</v>
+        <v>2.052</v>
       </c>
       <c r="AK45" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/DIVISLAB/</t>
+          <t>https://www.screener.in/company/AVALON/</t>
         </is>
       </c>
       <c r="AL45" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>Samvardhana Motherson International Limited</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Auto Parts</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>50.90000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>29.8</v>
+        <v>35.4</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>21.1</v>
+        <v>15.5</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
@@ -6615,23 +6615,23 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 At 52W High</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1687</v>
+        <v>143.4</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>7.58</v>
+        <v>1.89</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1506.77</v>
+        <v>139.34</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1335.21</v>
+        <v>132.46</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1085</v>
+        <v>118.71</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -6644,71 +6644,71 @@
         </is>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>99.47</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>68.41</v>
+        <v>59.43</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>99.502</v>
+        <v>3.9167</v>
       </c>
       <c r="T46" s="2" t="n">
-        <v>101.0941</v>
+        <v>4.4471</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>-1.5921</v>
+        <v>-0.5304</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
       <c r="W46" s="2" t="n">
-        <v>25.83</v>
+        <v>42.82</v>
       </c>
       <c r="X46" s="2" t="n">
-        <v>476593</v>
+        <v>12743045</v>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>675422</v>
+        <v>27910871</v>
       </c>
       <c r="Z46" s="2" t="n">
-        <v>0.71</v>
+        <v>0.46</v>
       </c>
       <c r="AA46" s="2" t="n">
-        <v>11267</v>
+        <v>155989</v>
       </c>
       <c r="AB46" s="2" t="n">
-        <v>99.99999</v>
+        <v>40.469944</v>
       </c>
       <c r="AC46" s="2" t="n">
-        <v>51.577847</v>
+        <v>22.61854</v>
       </c>
       <c r="AD46" s="2" t="n">
-        <v>16.94</v>
+        <v>10.11</v>
       </c>
       <c r="AE46" s="2" t="n">
-        <v>29.503</v>
+        <v>43.908</v>
       </c>
       <c r="AF46" s="2" t="n">
-        <v>40</v>
+        <v>14.9</v>
       </c>
       <c r="AG46" s="2" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="AH46" s="2" t="n">
-        <v>15.615455</v>
+        <v>4.2293415</v>
       </c>
       <c r="AI46" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AJ46" s="2" t="n">
-        <v>2.052</v>
+        <v>1.06</v>
       </c>
       <c r="AK46" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/AVALON/</t>
+          <t>https://www.screener.in/company/MOTHERSON/</t>
         </is>
       </c>
       <c r="AL46" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AVALON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
         <v>263.96</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>264.73</v>
+        <v>264.77</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>1.87</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>142083</v>
+        <v>142755</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>7.158676</v>
+        <v>7.192548</v>
       </c>
       <c r="AC47" s="4" t="n">
-        <v>6.380421</v>
+        <v>6.41061</v>
       </c>
       <c r="AD47" s="4" t="n">
         <v>12.74</v>
@@ -6825,7 +6825,7 @@
         <v>7.1</v>
       </c>
       <c r="AH47" s="4" t="n">
-        <v>0.8566022</v>
+        <v>0.86065525</v>
       </c>
       <c r="AI47" s="4" t="n">
         <v>309</v>
@@ -6845,32 +6845,32 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Adani Energy Solutions Limited</t>
+          <t>Apollo Hospitals Enterprise Limited</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Independent Power Producers</t>
+          <t>Medical Care Facilities</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>50.40000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>32.2</v>
+        <v>29.8</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
@@ -6879,23 +6879,23 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 👤 High Promoter</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 At 52W High | 📉 Tight Base | 💎 High ROE</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1489.6</v>
+        <v>8498</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.56</v>
+        <v>0.06</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1476.19</v>
+        <v>8275.200000000001</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1361.02</v>
+        <v>8024.24</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1116.47</v>
+        <v>7603.71</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -6908,103 +6908,103 @@
         </is>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>92.25</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>55.22</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>53.1541</v>
+        <v>146.6478</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>61.8999</v>
+        <v>135.9964</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>-8.745799999999999</v>
+        <v>10.6513</v>
       </c>
       <c r="V48" s="2" t="inlineStr"/>
       <c r="W48" s="2" t="n">
-        <v>27.84</v>
+        <v>17.08</v>
       </c>
       <c r="X48" s="2" t="n">
-        <v>1607528</v>
+        <v>276444</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>3514227</v>
+        <v>484048</v>
       </c>
       <c r="Z48" s="2" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="AA48" s="2" t="n">
-        <v>178943</v>
+        <v>121764</v>
       </c>
       <c r="AB48" s="2" t="n">
-        <v>79.99999</v>
+        <v>62.673923</v>
       </c>
       <c r="AC48" s="2" t="n">
-        <v>43.776134</v>
+        <v>39.613438</v>
       </c>
       <c r="AD48" s="2" t="n">
-        <v>9.66</v>
+        <v>21.5</v>
       </c>
       <c r="AE48" s="2" t="n">
-        <v>194.5</v>
+        <v>85.146</v>
       </c>
       <c r="AF48" s="2" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="AG48" s="2" t="n">
-        <v>3.5</v>
+        <v>35.6</v>
       </c>
       <c r="AH48" s="2" t="n">
-        <v>7.0373693</v>
+        <v>12.841373</v>
       </c>
       <c r="AI48" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AJ48" s="2" t="n">
-        <v>1.154</v>
+        <v>1.065</v>
       </c>
       <c r="AK48" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ADANIENSOL/</t>
+          <t>https://www.screener.in/company/APOLLOHOSP/</t>
         </is>
       </c>
       <c r="AL48" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited</t>
+          <t>Nestlé India Limited</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Packaged Foods</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>49.8</v>
+        <v>49</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>29.8</v>
+        <v>21.6</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>20</v>
+        <v>27.4</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
@@ -7013,23 +7013,23 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 At 52W High | 📉 Tight Base | 💎 High ROE</t>
+          <t>📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base | 💎 High ROE</t>
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>8498</v>
+        <v>1375.7</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0.06</v>
+        <v>-3.29</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>8275.200000000001</v>
+        <v>1409.55</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>8024.24</v>
+        <v>1385.18</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>7610.4</v>
+        <v>1297.58</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
@@ -7038,107 +7038,107 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>98.54000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>67.20999999999999</v>
+        <v>41.76</v>
       </c>
       <c r="S49" s="4" t="n">
-        <v>146.6478</v>
+        <v>-0.4199</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>135.9964</v>
+        <v>3.6205</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>10.6513</v>
+        <v>-4.0404</v>
       </c>
       <c r="V49" s="4" t="inlineStr"/>
       <c r="W49" s="4" t="n">
-        <v>17.08</v>
+        <v>22.75</v>
       </c>
       <c r="X49" s="4" t="n">
-        <v>276444</v>
+        <v>2380729</v>
       </c>
       <c r="Y49" s="4" t="n">
-        <v>484048</v>
+        <v>2062875</v>
       </c>
       <c r="Z49" s="4" t="n">
-        <v>0.57</v>
+        <v>1.15</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>122188</v>
+        <v>265085</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>62.892246</v>
+        <v>75.69934000000001</v>
       </c>
       <c r="AC49" s="4" t="n">
-        <v>39.751434</v>
+        <v>57.906826</v>
       </c>
       <c r="AD49" s="4" t="n">
-        <v>21.5</v>
+        <v>76.34</v>
       </c>
       <c r="AE49" s="4" t="n">
-        <v>85.146</v>
+        <v>8.621</v>
       </c>
       <c r="AF49" s="4" t="n">
-        <v>18.1</v>
+        <v>23</v>
       </c>
       <c r="AG49" s="4" t="n">
-        <v>35.6</v>
+        <v>27.4</v>
       </c>
       <c r="AH49" s="4" t="n">
-        <v>12.8861065</v>
+        <v>51.404102</v>
       </c>
       <c r="AI49" s="4" t="n">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="AJ49" s="4" t="n">
-        <v>1.065</v>
+        <v>0.964</v>
       </c>
       <c r="AK49" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/APOLLOHOSP/</t>
+          <t>https://www.screener.in/company/NESTLEIND/</t>
         </is>
       </c>
       <c r="AL49" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Nestlé India Limited</t>
+          <t>ideaForge Technology Limited</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Packaged Foods</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>21.6</v>
+        <v>35.4</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>27.4</v>
+        <v>13.3</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
@@ -7147,23 +7147,23 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base | 💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1375.7</v>
+        <v>869.1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>-3.29</v>
+        <v>-0.21</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1409.55</v>
+        <v>848.8200000000001</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1385.18</v>
+        <v>731.89</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1298.38</v>
+        <v>554.4299999999999</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -7172,107 +7172,103 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>91.83</v>
+        <v>87.59</v>
       </c>
       <c r="R50" s="2" t="n">
-        <v>41.76</v>
+        <v>57</v>
       </c>
       <c r="S50" s="2" t="n">
-        <v>-0.4199</v>
+        <v>56.8073</v>
       </c>
       <c r="T50" s="2" t="n">
-        <v>3.6205</v>
+        <v>64.0153</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>-4.0404</v>
+        <v>-7.208</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
       <c r="W50" s="2" t="n">
-        <v>22.75</v>
+        <v>41.33</v>
       </c>
       <c r="X50" s="2" t="n">
-        <v>2380729</v>
+        <v>335109</v>
       </c>
       <c r="Y50" s="2" t="n">
-        <v>2062875</v>
+        <v>447571</v>
       </c>
       <c r="Z50" s="2" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="AA50" s="2" t="n">
-        <v>265278</v>
-      </c>
-      <c r="AB50" s="2" t="n">
-        <v>75.7544</v>
-      </c>
+        <v>3752</v>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="n">
-        <v>57.948948</v>
+        <v>30.998207</v>
       </c>
       <c r="AD50" s="2" t="n">
-        <v>76.34</v>
+        <v>-2.82</v>
       </c>
       <c r="AE50" s="2" t="n">
-        <v>8.621</v>
+        <v>13.974</v>
       </c>
       <c r="AF50" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG50" s="2" t="n">
-        <v>27.4</v>
-      </c>
+        <v>594.4</v>
+      </c>
+      <c r="AG50" s="2" t="inlineStr"/>
       <c r="AH50" s="2" t="n">
-        <v>51.441498</v>
+        <v>6.312912</v>
       </c>
       <c r="AI50" s="2" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="AJ50" s="2" t="n">
-        <v>0.964</v>
+        <v>2.622</v>
       </c>
       <c r="AK50" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NESTLEIND/</t>
+          <t>https://www.screener.in/company/IDEAFORGE/</t>
         </is>
       </c>
       <c r="AL50" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEAFORGE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ideaForge Technology Limited</t>
+          <t>Adani Energy Solutions Limited</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>48.7</v>
+        <v>48.3</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>35.4</v>
+        <v>32.2</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>13.3</v>
+        <v>16.1</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -7281,23 +7277,23 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 👤 High Promoter</t>
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>869.1</v>
+        <v>1489.6</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-0.21</v>
+        <v>1.56</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>848.8200000000001</v>
+        <v>1476.19</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>731.89</v>
+        <v>1361.02</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>554.45</v>
+        <v>1114.32</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
@@ -7310,67 +7306,71 @@
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>87.59</v>
+        <v>92.25</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>57</v>
+        <v>55.22</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>56.8073</v>
+        <v>53.1541</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>64.0153</v>
+        <v>61.8999</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>-7.208</v>
+        <v>-8.745799999999999</v>
       </c>
       <c r="V51" s="4" t="inlineStr"/>
       <c r="W51" s="4" t="n">
-        <v>41.33</v>
+        <v>27.84</v>
       </c>
       <c r="X51" s="4" t="n">
-        <v>335109</v>
+        <v>1607528</v>
       </c>
       <c r="Y51" s="4" t="n">
-        <v>447571</v>
+        <v>3514227</v>
       </c>
       <c r="Z51" s="4" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>3771</v>
-      </c>
-      <c r="AB51" s="4" t="inlineStr"/>
+        <v>179219</v>
+      </c>
+      <c r="AB51" s="4" t="n">
+        <v>80.12352</v>
+      </c>
       <c r="AC51" s="4" t="n">
-        <v>31.150537</v>
+        <v>43.84373</v>
       </c>
       <c r="AD51" s="4" t="n">
-        <v>-2.82</v>
+        <v>9.66</v>
       </c>
       <c r="AE51" s="4" t="n">
-        <v>13.974</v>
+        <v>194.5</v>
       </c>
       <c r="AF51" s="4" t="n">
-        <v>594.4</v>
-      </c>
-      <c r="AG51" s="4" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="AG51" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="AH51" s="4" t="n">
-        <v>6.3439345</v>
+        <v>7.0482354</v>
       </c>
       <c r="AI51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" s="4" t="n">
-        <v>2.622</v>
+        <v>1.154</v>
       </c>
       <c r="AK51" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/IDEAFORGE/</t>
+          <t>https://www.screener.in/company/ADANIENSOL/</t>
         </is>
       </c>
       <c r="AL51" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:IDEAFORGE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7427,7 @@
         <v>168.75</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>160.07</v>
+        <v>160.02</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       <c r="AF52" s="2" t="inlineStr"/>
       <c r="AG52" s="2" t="inlineStr"/>
       <c r="AH52" s="2" t="n">
-        <v>2.197054</v>
+        <v>2.5366755</v>
       </c>
       <c r="AI52" s="2" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
         <v>939.36</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>896.27</v>
+        <v>896.6900000000001</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
@@ -7592,13 +7592,13 @@
         <v>0.67</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>74767</v>
+        <v>73997</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>71.92084</v>
+        <v>71.1801</v>
       </c>
       <c r="AC53" s="4" t="n">
-        <v>42.310715</v>
+        <v>41.920452</v>
       </c>
       <c r="AD53" s="4" t="n">
         <v>11.01</v>
@@ -7613,7 +7613,7 @@
         <v>44.3</v>
       </c>
       <c r="AH53" s="4" t="n">
-        <v>7.555655</v>
+        <v>7.4778366</v>
       </c>
       <c r="AI53" s="4" t="n">
         <v>10</v>
@@ -7685,7 +7685,7 @@
         <v>1267.59</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1059.75</v>
+        <v>1058.63</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -7726,13 +7726,13 @@
         <v>0.71</v>
       </c>
       <c r="AA54" s="2" t="n">
-        <v>75327</v>
+        <v>75046</v>
       </c>
       <c r="AB54" s="2" t="n">
-        <v>84.75988</v>
+        <v>84.44376</v>
       </c>
       <c r="AC54" s="2" t="n">
-        <v>58.113583</v>
+        <v>57.896847</v>
       </c>
       <c r="AD54" s="2" t="n">
         <v>17.74</v>
@@ -7747,7 +7747,7 @@
         <v>19.4</v>
       </c>
       <c r="AH54" s="2" t="n">
-        <v>14.203926</v>
+        <v>14.150952</v>
       </c>
       <c r="AI54" s="2" t="n">
         <v>17</v>
@@ -7819,7 +7819,7 @@
         <v>1793.5</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1744.63</v>
+        <v>1746.87</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
@@ -7860,13 +7860,13 @@
         <v>0.45</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>433728</v>
+        <v>433320</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>37.88139</v>
+        <v>37.845764</v>
       </c>
       <c r="AC55" s="4" t="n">
-        <v>27.910172</v>
+        <v>27.883924</v>
       </c>
       <c r="AD55" s="4" t="n">
         <v>14.72</v>
@@ -7881,7 +7881,7 @@
         <v>25.6</v>
       </c>
       <c r="AH55" s="4" t="n">
-        <v>5.1953163</v>
+        <v>5.1904306</v>
       </c>
       <c r="AI55" s="4" t="n">
         <v>89</v>
@@ -7953,7 +7953,7 @@
         <v>130.21</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>129.25</v>
+        <v>129.2</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -7994,13 +7994,13 @@
         <v>0.83</v>
       </c>
       <c r="AA56" s="2" t="n">
-        <v>119433</v>
+        <v>119914</v>
       </c>
       <c r="AB56" s="2" t="n">
-        <v>6.059365</v>
+        <v>6.083755</v>
       </c>
       <c r="AC56" s="2" t="n">
-        <v>5.699171</v>
+        <v>5.7221117</v>
       </c>
       <c r="AD56" s="2" t="n">
         <v>15.94</v>
@@ -8013,7 +8013,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AH56" s="2" t="n">
-        <v>1.0146881</v>
+        <v>1.0187725</v>
       </c>
       <c r="AI56" s="2" t="n">
         <v>319</v>
@@ -8083,7 +8083,7 @@
         <v>730.72</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>693.6799999999999</v>
+        <v>693.92</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
@@ -8124,13 +8124,13 @@
         <v>0.84</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>31415</v>
+        <v>30805</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>129.76859</v>
+        <v>127.247925</v>
       </c>
       <c r="AC57" s="4" t="n">
-        <v>45.782616</v>
+        <v>44.893322</v>
       </c>
       <c r="AD57" s="4" t="n">
         <v>9.720000000000001</v>
@@ -8145,7 +8145,7 @@
         <v>-58.3</v>
       </c>
       <c r="AH57" s="4" t="n">
-        <v>14.006386</v>
+        <v>13.734323</v>
       </c>
       <c r="AI57" s="4" t="n">
         <v>0</v>
@@ -8217,7 +8217,7 @@
         <v>1313.36</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>1103.66</v>
+        <v>1102.02</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -8258,13 +8258,13 @@
         <v>0.5</v>
       </c>
       <c r="AA58" s="2" t="n">
-        <v>244721</v>
+        <v>244210</v>
       </c>
       <c r="AB58" s="2" t="n">
-        <v>153.79916</v>
+        <v>153.47826</v>
       </c>
       <c r="AC58" s="2" t="n">
-        <v>48.621723</v>
+        <v>48.52027</v>
       </c>
       <c r="AD58" s="2" t="n">
         <v>7.58</v>
@@ -8279,7 +8279,7 @@
         <v>209.8</v>
       </c>
       <c r="AH58" s="2" t="n">
-        <v>12.686363</v>
+        <v>12.659892</v>
       </c>
       <c r="AI58" s="2" t="n">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>2649.66</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>2528.33</v>
+        <v>2529.6</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
@@ -8392,13 +8392,13 @@
         <v>0.99</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>30341</v>
+        <v>30576</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>44.049557</v>
+        <v>44.390484</v>
       </c>
       <c r="AC59" s="4" t="n">
-        <v>31.532143</v>
+        <v>31.77619</v>
       </c>
       <c r="AD59" s="4" t="n">
         <v>31.79</v>
@@ -8413,7 +8413,7 @@
         <v>24.2</v>
       </c>
       <c r="AH59" s="4" t="n">
-        <v>11.552956</v>
+        <v>11.642371</v>
       </c>
       <c r="AI59" s="4" t="n">
         <v>101</v>
@@ -8435,32 +8435,32 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>NIIT Limited</t>
+          <t>CreditAccess Grameen Limited</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Education &amp; Training Services</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>45.59999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>29.4</v>
+        <v>22.6</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>16.2</v>
+        <v>22.9</v>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
@@ -8469,130 +8469,132 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>87.27</v>
+        <v>1310.4</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.61</v>
+        <v>3.47</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>82.26000000000001</v>
+        <v>1290.75</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>75.7</v>
+        <v>1290.2</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>86.23</v>
+        <v>1276</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>60.34</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="R60" s="2" t="n">
-        <v>59.94</v>
+        <v>53.48</v>
       </c>
       <c r="S60" s="2" t="n">
-        <v>6.2609</v>
+        <v>-9.6187</v>
       </c>
       <c r="T60" s="2" t="n">
-        <v>5.4083</v>
+        <v>-8.417</v>
       </c>
       <c r="U60" s="2" t="n">
-        <v>0.8526</v>
+        <v>-1.2017</v>
       </c>
       <c r="V60" s="2" t="inlineStr"/>
       <c r="W60" s="2" t="n">
-        <v>34.85</v>
+        <v>16.12</v>
       </c>
       <c r="X60" s="2" t="n">
-        <v>811591</v>
+        <v>191339</v>
       </c>
       <c r="Y60" s="2" t="n">
-        <v>3473085</v>
+        <v>201484</v>
       </c>
       <c r="Z60" s="2" t="n">
-        <v>0.23</v>
+        <v>0.95</v>
       </c>
       <c r="AA60" s="2" t="n">
-        <v>1191</v>
+        <v>22027</v>
       </c>
       <c r="AB60" s="2" t="n">
-        <v>218.17499</v>
+        <v>28.362211</v>
       </c>
       <c r="AC60" s="2" t="n">
-        <v>27.271873</v>
+        <v>11.16597</v>
       </c>
       <c r="AD60" s="2" t="n">
-        <v>0.57</v>
+        <v>10.51</v>
       </c>
       <c r="AE60" s="2" t="n">
-        <v>0.65</v>
+        <v>302.873</v>
       </c>
       <c r="AF60" s="2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AG60" s="2" t="inlineStr"/>
+        <v>125.9</v>
+      </c>
+      <c r="AG60" s="2" t="n">
+        <v>616.2</v>
+      </c>
       <c r="AH60" s="2" t="n">
-        <v>1.126108</v>
+        <v>2.8082142</v>
       </c>
       <c r="AI60" s="2" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="AJ60" s="2" t="n">
-        <v>5.709</v>
+        <v>286.649</v>
       </c>
       <c r="AK60" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NIITLTD/</t>
+          <t>https://www.screener.in/company/CREDITACC/</t>
         </is>
       </c>
       <c r="AL60" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NIITLTD</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CREDITACC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CreditAccess Grameen Limited</t>
+          <t>Gabriel India Limited</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Auto Parts</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
@@ -8601,23 +8603,23 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J61" s="4" t="n">
-        <v>1310.4</v>
+        <v>1040.6</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>1290.75</v>
+        <v>1051.29</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>1290.2</v>
+        <v>1034.95</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1279.18</v>
+        <v>985.54</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
@@ -8630,237 +8632,237 @@
         </is>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>83.56999999999999</v>
+        <v>75.11</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>53.48</v>
+        <v>48.27</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>-9.6187</v>
+        <v>-9.307499999999999</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>-8.417</v>
+        <v>1.1336</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>-1.2017</v>
+        <v>-10.4411</v>
       </c>
       <c r="V61" s="4" t="inlineStr"/>
       <c r="W61" s="4" t="n">
-        <v>16.12</v>
+        <v>20.15</v>
       </c>
       <c r="X61" s="4" t="n">
-        <v>191339</v>
+        <v>315963</v>
       </c>
       <c r="Y61" s="4" t="n">
-        <v>201484</v>
+        <v>267913</v>
       </c>
       <c r="Z61" s="4" t="n">
-        <v>0.95</v>
+        <v>1.18</v>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>20992</v>
+        <v>20316</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>27.029703</v>
+        <v>65.16771</v>
       </c>
       <c r="AC61" s="4" t="n">
-        <v>10.641373</v>
+        <v>31.871174</v>
       </c>
       <c r="AD61" s="4" t="n">
-        <v>10.51</v>
+        <v>19.58</v>
       </c>
       <c r="AE61" s="4" t="n">
-        <v>302.873</v>
+        <v>10.642</v>
       </c>
       <c r="AF61" s="4" t="n">
-        <v>125.9</v>
+        <v>12.7</v>
       </c>
       <c r="AG61" s="4" t="n">
-        <v>616.2</v>
+        <v>3.3</v>
       </c>
       <c r="AH61" s="4" t="n">
-        <v>2.6762793</v>
+        <v>12.04856</v>
       </c>
       <c r="AI61" s="4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AJ61" s="4" t="n">
-        <v>286.649</v>
+        <v>1.664</v>
       </c>
       <c r="AK61" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CREDITACC/</t>
+          <t>https://www.screener.in/company/GABRIEL/</t>
         </is>
       </c>
       <c r="AL61" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CREDITACC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GABRIEL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Gabriel India Limited</t>
+          <t>Greenply Industries Limited</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Auto Parts</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>45.2</v>
+          <t>Lumber &amp; Wood Production</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>44.9</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>21.6</v>
+        <v>29.4</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>15.5</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1040.6</v>
+        <v>290.98</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3.15</v>
+        <v>-0.52</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1051.29</v>
+        <v>271.15</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1034.95</v>
+        <v>255.55</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>986.02</v>
+        <v>257.61</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>75.11</v>
+        <v>82.81</v>
       </c>
       <c r="R62" s="2" t="n">
-        <v>48.27</v>
+        <v>66.06</v>
       </c>
       <c r="S62" s="2" t="n">
-        <v>-9.307499999999999</v>
+        <v>10.6994</v>
       </c>
       <c r="T62" s="2" t="n">
-        <v>1.1336</v>
+        <v>8.1403</v>
       </c>
       <c r="U62" s="2" t="n">
-        <v>-10.4411</v>
+        <v>2.5591</v>
       </c>
       <c r="V62" s="2" t="inlineStr"/>
       <c r="W62" s="2" t="n">
-        <v>20.15</v>
+        <v>31.8</v>
       </c>
       <c r="X62" s="2" t="n">
-        <v>315963</v>
+        <v>334921</v>
       </c>
       <c r="Y62" s="2" t="n">
-        <v>267913</v>
+        <v>258864</v>
       </c>
       <c r="Z62" s="2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AA62" s="2" t="n">
-        <v>18443</v>
+        <v>3670</v>
       </c>
       <c r="AB62" s="2" t="n">
-        <v>59.15861</v>
+        <v>40.86231</v>
       </c>
       <c r="AC62" s="2" t="n">
-        <v>28.93234</v>
+        <v>18.370697</v>
       </c>
       <c r="AD62" s="2" t="n">
-        <v>19.58</v>
+        <v>10.54</v>
       </c>
       <c r="AE62" s="2" t="n">
-        <v>10.642</v>
+        <v>57.505</v>
       </c>
       <c r="AF62" s="2" t="n">
-        <v>12.7</v>
+        <v>19.6</v>
       </c>
       <c r="AG62" s="2" t="n">
-        <v>3.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AH62" s="2" t="n">
-        <v>10.937566</v>
+        <v>4.067731</v>
       </c>
       <c r="AI62" s="2" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="AJ62" s="2" t="n">
-        <v>1.664</v>
+        <v>1.286</v>
       </c>
       <c r="AK62" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/GABRIEL/</t>
+          <t>https://www.screener.in/company/GREENPLY/</t>
         </is>
       </c>
       <c r="AL62" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GABRIEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GREENPLY</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Greenply Industries Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Lumber &amp; Wood Production</t>
+          <t>Thermal Coal</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>29.4</v>
+        <v>14.4</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>15.5</v>
+        <v>30.3</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
@@ -8869,132 +8871,132 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy</t>
+          <t>📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base | 💎 High ROE</t>
         </is>
       </c>
       <c r="J63" s="4" t="n">
-        <v>290.98</v>
+        <v>443.5</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-0.52</v>
+        <v>-0.61</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>271.15</v>
+        <v>460.83</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>255.55</v>
+        <v>457.27</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>258.37</v>
+        <v>423.68</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>82.81</v>
+        <v>90.28</v>
       </c>
       <c r="R63" s="4" t="n">
-        <v>66.06</v>
+        <v>37.48</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>10.6994</v>
+        <v>-1.5253</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>8.1403</v>
+        <v>1.372</v>
       </c>
       <c r="U63" s="4" t="n">
-        <v>2.5591</v>
+        <v>-2.8973</v>
       </c>
       <c r="V63" s="4" t="inlineStr"/>
       <c r="W63" s="4" t="n">
-        <v>31.8</v>
+        <v>12.86</v>
       </c>
       <c r="X63" s="4" t="n">
-        <v>334921</v>
+        <v>9946830</v>
       </c>
       <c r="Y63" s="4" t="n">
-        <v>258864</v>
+        <v>21732036</v>
       </c>
       <c r="Z63" s="4" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>3634</v>
+        <v>273656</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>40.4701</v>
+        <v>8.798296000000001</v>
       </c>
       <c r="AC63" s="4" t="n">
-        <v>18.19437</v>
+        <v>7.7288027</v>
       </c>
       <c r="AD63" s="4" t="n">
-        <v>10.54</v>
+        <v>28.12</v>
       </c>
       <c r="AE63" s="4" t="n">
-        <v>57.505</v>
+        <v>11.629</v>
       </c>
       <c r="AF63" s="4" t="n">
-        <v>19.6</v>
+        <v>16.2</v>
       </c>
       <c r="AG63" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="AH63" s="4" t="n">
-        <v>4.0286875</v>
+        <v>2.297444</v>
       </c>
       <c r="AI63" s="4" t="n">
-        <v>17</v>
+        <v>496</v>
       </c>
       <c r="AJ63" s="4" t="n">
-        <v>1.286</v>
+        <v>1.856</v>
       </c>
       <c r="AK63" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/GREENPLY/</t>
+          <t>https://www.screener.in/company/COALINDIA/</t>
         </is>
       </c>
       <c r="AL63" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GREENPLY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>HFCL Limited</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>14.4</v>
+        <v>33</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>30.3</v>
+        <v>11.2</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
@@ -9003,23 +9005,23 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base | 💎 High ROE</t>
+          <t>📈 EMA Bull Stack</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>443.5</v>
+        <v>171.86</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-0.61</v>
+        <v>5</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>460.83</v>
+        <v>167.72</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>457.27</v>
+        <v>141.12</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>423.82</v>
+        <v>98.5</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -9032,103 +9034,101 @@
         </is>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>90.28</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="R64" s="2" t="n">
-        <v>37.48</v>
+        <v>57.43</v>
       </c>
       <c r="S64" s="2" t="n">
-        <v>-1.5253</v>
+        <v>11.8951</v>
       </c>
       <c r="T64" s="2" t="n">
-        <v>1.372</v>
+        <v>15.5985</v>
       </c>
       <c r="U64" s="2" t="n">
-        <v>-2.8973</v>
+        <v>-3.7034</v>
       </c>
       <c r="V64" s="2" t="inlineStr"/>
       <c r="W64" s="2" t="n">
-        <v>12.86</v>
+        <v>56.56</v>
       </c>
       <c r="X64" s="2" t="n">
-        <v>9946830</v>
+        <v>9299089</v>
       </c>
       <c r="Y64" s="2" t="n">
-        <v>21732036</v>
+        <v>52265068</v>
       </c>
       <c r="Z64" s="2" t="n">
-        <v>0.46</v>
+        <v>0.18</v>
       </c>
       <c r="AA64" s="2" t="n">
-        <v>273317</v>
+        <v>27614</v>
       </c>
       <c r="AB64" s="2" t="n">
-        <v>8.787398</v>
+        <v>84.71831</v>
       </c>
       <c r="AC64" s="2" t="n">
-        <v>7.7192297</v>
+        <v>34.701923</v>
       </c>
       <c r="AD64" s="2" t="n">
-        <v>28.12</v>
+        <v>7.27</v>
       </c>
       <c r="AE64" s="2" t="n">
-        <v>11.629</v>
+        <v>38.321</v>
       </c>
       <c r="AF64" s="2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="AG64" s="2" t="n">
-        <v>12.9</v>
-      </c>
+        <v>127.8</v>
+      </c>
+      <c r="AG64" s="2" t="inlineStr"/>
       <c r="AH64" s="2" t="n">
-        <v>2.2945986</v>
+        <v>5.4429464</v>
       </c>
       <c r="AI64" s="2" t="n">
-        <v>496</v>
+        <v>6</v>
       </c>
       <c r="AJ64" s="2" t="n">
-        <v>1.856</v>
+        <v>1.991</v>
       </c>
       <c r="AK64" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/COALINDIA/</t>
+          <t>https://www.screener.in/company/HFCL/</t>
         </is>
       </c>
       <c r="AL64" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:COALINDIA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>HFCL Limited</t>
+          <t>Alkyl Amines Chemicals Limited</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>44.2</v>
+        <v>44.09999999999999</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>33</v>
+        <v>26.2</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>11.2</v>
+        <v>17.9</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
@@ -9137,130 +9137,126 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack</t>
+          <t>✅ Supertrend Buy | 👤 High Promoter</t>
         </is>
       </c>
       <c r="J65" s="4" t="n">
-        <v>171.86</v>
+        <v>1831.8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>167.72</v>
+        <v>1750.84</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>141.12</v>
+        <v>1653.78</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>98.70999999999999</v>
+        <v>1661.69</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>82.23999999999999</v>
+        <v>75.11</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>57.43</v>
+        <v>60.15</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>11.8951</v>
+        <v>55.846</v>
       </c>
       <c r="T65" s="4" t="n">
-        <v>15.5985</v>
+        <v>55.3054</v>
       </c>
       <c r="U65" s="4" t="n">
-        <v>-3.7034</v>
+        <v>0.5406</v>
       </c>
       <c r="V65" s="4" t="inlineStr"/>
       <c r="W65" s="4" t="n">
-        <v>56.56</v>
+        <v>28.1</v>
       </c>
       <c r="X65" s="4" t="n">
-        <v>9299089</v>
+        <v>49615</v>
       </c>
       <c r="Y65" s="4" t="n">
-        <v>52265068</v>
+        <v>236470</v>
       </c>
       <c r="Z65" s="4" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>26299</v>
+        <v>9282</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>80.68544</v>
+        <v>51.6008</v>
       </c>
       <c r="AC65" s="4" t="n">
-        <v>33.050003</v>
-      </c>
-      <c r="AD65" s="4" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="AE65" s="4" t="n">
-        <v>38.321</v>
-      </c>
+        <v>40.996986</v>
+      </c>
+      <c r="AD65" s="4" t="inlineStr"/>
+      <c r="AE65" s="4" t="inlineStr"/>
       <c r="AF65" s="4" t="n">
-        <v>127.8</v>
-      </c>
-      <c r="AG65" s="4" t="inlineStr"/>
+        <v>-4.6</v>
+      </c>
+      <c r="AG65" s="4" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="AH65" s="4" t="n">
-        <v>5.1838446</v>
+        <v>6.0530863</v>
       </c>
       <c r="AI65" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ65" s="4" t="n">
-        <v>1.991</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="AJ65" s="4" t="inlineStr"/>
       <c r="AK65" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/HFCL/</t>
+          <t>https://www.screener.in/company/ALKYLAMINE/</t>
         </is>
       </c>
       <c r="AL65" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HFCL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ALKYLAMINE</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Alkyl Amines Chemicals Limited</t>
+          <t>Tube Investments of India Limited</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Conglomerates</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>44.09999999999999</v>
+        <v>44</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>26.2</v>
+        <v>27.4</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>17.9</v>
+        <v>16.6</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
@@ -9269,27 +9265,27 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 👤 High Promoter</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1831.8</v>
+        <v>3141.8</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.27</v>
+        <v>5.6</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1750.84</v>
+        <v>3051.86</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1653.78</v>
+        <v>2944.64</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1663.87</v>
+        <v>2810.9</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -9298,97 +9294,99 @@
         </is>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>75.11</v>
+        <v>91.95</v>
       </c>
       <c r="R66" s="2" t="n">
-        <v>60.15</v>
+        <v>57.21</v>
       </c>
       <c r="S66" s="2" t="n">
-        <v>55.846</v>
+        <v>42.7361</v>
       </c>
       <c r="T66" s="2" t="n">
-        <v>55.3054</v>
+        <v>53.255</v>
       </c>
       <c r="U66" s="2" t="n">
-        <v>0.5406</v>
+        <v>-10.5189</v>
       </c>
       <c r="V66" s="2" t="inlineStr"/>
       <c r="W66" s="2" t="n">
-        <v>28.1</v>
+        <v>11.36</v>
       </c>
       <c r="X66" s="2" t="n">
-        <v>49615</v>
+        <v>260594</v>
       </c>
       <c r="Y66" s="2" t="n">
-        <v>236470</v>
+        <v>337953</v>
       </c>
       <c r="Z66" s="2" t="n">
-        <v>0.21</v>
+        <v>0.77</v>
       </c>
       <c r="AA66" s="2" t="n">
-        <v>9369</v>
+        <v>62445</v>
       </c>
       <c r="AB66" s="2" t="n">
-        <v>52.084167</v>
+        <v>97.79024</v>
       </c>
       <c r="AC66" s="2" t="n">
-        <v>41.381023</v>
+        <v>42.47663</v>
       </c>
       <c r="AD66" s="2" t="inlineStr"/>
-      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="n">
+        <v>27.724</v>
+      </c>
       <c r="AF66" s="2" t="n">
-        <v>-4.6</v>
+        <v>20.7</v>
       </c>
       <c r="AG66" s="2" t="n">
-        <v>-3.5</v>
+        <v>-14.2</v>
       </c>
       <c r="AH66" s="2" t="n">
-        <v>6.110502</v>
+        <v>8.046120999999999</v>
       </c>
       <c r="AI66" s="2" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="AJ66" s="2" t="inlineStr"/>
       <c r="AK66" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/ALKYLAMINE/</t>
+          <t>https://www.screener.in/company/TIINDIA/</t>
         </is>
       </c>
       <c r="AL66" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ALKYLAMINE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TIINDIA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Tube Investments of India Limited</t>
+          <t>The Phoenix Mills Limited</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Conglomerates</t>
+          <t>Real Estate - Diversified</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
         <v>44</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>27.4</v>
+        <v>25</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>16.6</v>
+        <v>19</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
@@ -9397,23 +9395,23 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J67" s="4" t="n">
-        <v>3141.8</v>
+        <v>1757.6</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>5.6</v>
+        <v>1.43</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>3051.86</v>
+        <v>1752.28</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>2944.64</v>
+        <v>1741.79</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>2811.64</v>
+        <v>1700.99</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
@@ -9426,99 +9424,103 @@
         </is>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>91.95</v>
+        <v>88.19</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>57.21</v>
+        <v>51.2</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>42.7361</v>
+        <v>-1.6971</v>
       </c>
       <c r="T67" s="4" t="n">
-        <v>53.255</v>
+        <v>-0.1818</v>
       </c>
       <c r="U67" s="4" t="n">
-        <v>-10.5189</v>
+        <v>-1.5152</v>
       </c>
       <c r="V67" s="4" t="inlineStr"/>
       <c r="W67" s="4" t="n">
-        <v>11.36</v>
+        <v>14.69</v>
       </c>
       <c r="X67" s="4" t="n">
-        <v>260594</v>
+        <v>408513</v>
       </c>
       <c r="Y67" s="4" t="n">
-        <v>337953</v>
+        <v>449558</v>
       </c>
       <c r="Z67" s="4" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="AA67" s="4" t="n">
-        <v>60813</v>
+        <v>66053</v>
       </c>
       <c r="AB67" s="4" t="n">
-        <v>95.23492</v>
+        <v>52.798744</v>
       </c>
       <c r="AC67" s="4" t="n">
-        <v>41.36669</v>
-      </c>
-      <c r="AD67" s="4" t="inlineStr"/>
+        <v>35.74719</v>
+      </c>
+      <c r="AD67" s="4" t="n">
+        <v>11.06</v>
+      </c>
       <c r="AE67" s="4" t="n">
-        <v>27.724</v>
+        <v>37.211</v>
       </c>
       <c r="AF67" s="4" t="n">
-        <v>20.7</v>
+        <v>33.7</v>
       </c>
       <c r="AG67" s="4" t="n">
-        <v>-14.2</v>
+        <v>50</v>
       </c>
       <c r="AH67" s="4" t="n">
-        <v>7.8358707</v>
+        <v>6.009951</v>
       </c>
       <c r="AI67" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ67" s="4" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="AJ67" s="4" t="n">
+        <v>0.87</v>
+      </c>
       <c r="AK67" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/TIINDIA/</t>
+          <t>https://www.screener.in/company/PHOENIXLTD/</t>
         </is>
       </c>
       <c r="AL67" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TIINDIA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>The Phoenix Mills Limited</t>
+          <t>Hindalco Industries Limited</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Real Estate - Diversified</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
@@ -9527,23 +9529,23 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 📉 Tight Base</t>
+          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1757.6</v>
+        <v>1021.6</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.43</v>
+        <v>-0.26</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1752.28</v>
+        <v>1078.25</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1741.79</v>
+        <v>1050.14</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1703.06</v>
+        <v>917.1</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -9552,107 +9554,107 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>88.19</v>
+        <v>86.87</v>
       </c>
       <c r="R68" s="2" t="n">
-        <v>51.2</v>
+        <v>38.24</v>
       </c>
       <c r="S68" s="2" t="n">
-        <v>-1.6971</v>
+        <v>-2.0832</v>
       </c>
       <c r="T68" s="2" t="n">
-        <v>-0.1818</v>
+        <v>13.7829</v>
       </c>
       <c r="U68" s="2" t="n">
-        <v>-1.5152</v>
+        <v>-15.8661</v>
       </c>
       <c r="V68" s="2" t="inlineStr"/>
       <c r="W68" s="2" t="n">
-        <v>14.69</v>
+        <v>25.45</v>
       </c>
       <c r="X68" s="2" t="n">
-        <v>408513</v>
+        <v>9388824</v>
       </c>
       <c r="Y68" s="2" t="n">
-        <v>449558</v>
+        <v>6093587</v>
       </c>
       <c r="Z68" s="2" t="n">
-        <v>0.91</v>
+        <v>1.54</v>
       </c>
       <c r="AA68" s="2" t="n">
-        <v>62859</v>
+        <v>226724</v>
       </c>
       <c r="AB68" s="2" t="n">
-        <v>50.245853</v>
+        <v>16.850592</v>
       </c>
       <c r="AC68" s="2" t="n">
-        <v>34.01877</v>
+        <v>9.384221</v>
       </c>
       <c r="AD68" s="2" t="n">
-        <v>11.06</v>
+        <v>10.29</v>
       </c>
       <c r="AE68" s="2" t="n">
-        <v>37.211</v>
+        <v>72.598</v>
       </c>
       <c r="AF68" s="2" t="n">
-        <v>33.7</v>
+        <v>20.4</v>
       </c>
       <c r="AG68" s="2" t="n">
-        <v>50</v>
+        <v>-50.9</v>
       </c>
       <c r="AH68" s="2" t="n">
-        <v>5.719362</v>
+        <v>1.6477231</v>
       </c>
       <c r="AI68" s="2" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="AJ68" s="2" t="n">
-        <v>0.87</v>
+        <v>1.21</v>
       </c>
       <c r="AK68" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/PHOENIXLTD/</t>
+          <t>https://www.screener.in/company/HINDALCO/</t>
         </is>
       </c>
       <c r="AL68" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HINDALCO</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Hindalco Industries Limited</t>
+          <t>NIIT Limited</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Aluminum</t>
+          <t>Education &amp; Training Services</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>43.6</v>
+        <v>43.59999999999999</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>24</v>
+        <v>29.4</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>19.6</v>
+        <v>14.2</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
@@ -9661,100 +9663,98 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy</t>
         </is>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1021.6</v>
+        <v>87.27</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-0.26</v>
+        <v>2.61</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>1078.25</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>1050.14</v>
+        <v>75.7</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>917.0700000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>86.87</v>
+        <v>60.34</v>
       </c>
       <c r="R69" s="4" t="n">
-        <v>38.24</v>
+        <v>59.94</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>-2.0832</v>
+        <v>6.2609</v>
       </c>
       <c r="T69" s="4" t="n">
-        <v>13.7829</v>
+        <v>5.4083</v>
       </c>
       <c r="U69" s="4" t="n">
-        <v>-15.8661</v>
+        <v>0.8526</v>
       </c>
       <c r="V69" s="4" t="inlineStr"/>
       <c r="W69" s="4" t="n">
-        <v>25.45</v>
+        <v>34.85</v>
       </c>
       <c r="X69" s="4" t="n">
-        <v>9388824</v>
+        <v>811591</v>
       </c>
       <c r="Y69" s="4" t="n">
-        <v>6093587</v>
+        <v>3473085</v>
       </c>
       <c r="Z69" s="4" t="n">
-        <v>1.54</v>
+        <v>0.23</v>
       </c>
       <c r="AA69" s="4" t="n">
-        <v>228445</v>
+        <v>1219</v>
       </c>
       <c r="AB69" s="4" t="n">
-        <v>16.978561</v>
+        <v>223.17499</v>
       </c>
       <c r="AC69" s="4" t="n">
-        <v>9.576549</v>
+        <v>27.896873</v>
       </c>
       <c r="AD69" s="4" t="n">
-        <v>10.29</v>
+        <v>0.57</v>
       </c>
       <c r="AE69" s="4" t="n">
-        <v>72.598</v>
+        <v>0.65</v>
       </c>
       <c r="AF69" s="4" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AG69" s="4" t="n">
-        <v>-50.9</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="AG69" s="4" t="inlineStr"/>
       <c r="AH69" s="4" t="n">
-        <v>1.6602366</v>
+        <v>1.1519154</v>
       </c>
       <c r="AI69" s="4" t="n">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="AJ69" s="4" t="n">
-        <v>1.21</v>
+        <v>5.709</v>
       </c>
       <c r="AK69" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/HINDALCO/</t>
+          <t>https://www.screener.in/company/NIITLTD/</t>
         </is>
       </c>
       <c r="AL69" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HINDALCO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NIITLTD</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
         <v>1420.11</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1286.42</v>
+        <v>1285.8</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -9852,13 +9852,13 @@
         <v>0.55</v>
       </c>
       <c r="AA70" s="2" t="n">
-        <v>84742</v>
+        <v>81030</v>
       </c>
       <c r="AB70" s="2" t="n">
-        <v>24.392183</v>
+        <v>23.323948</v>
       </c>
       <c r="AC70" s="2" t="n">
-        <v>16.637215</v>
+        <v>15.923627</v>
       </c>
       <c r="AD70" s="2" t="n">
         <v>9.93</v>
@@ -9873,7 +9873,7 @@
         <v>1.9</v>
       </c>
       <c r="AH70" s="2" t="n">
-        <v>2.2578084</v>
+        <v>2.1589296</v>
       </c>
       <c r="AI70" s="2" t="n">
         <v>27</v>
@@ -9945,7 +9945,7 @@
         <v>501.77</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>480.21</v>
+        <v>480.26</v>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
@@ -9986,13 +9986,13 @@
         <v>0.41</v>
       </c>
       <c r="AA71" s="4" t="n">
-        <v>176624</v>
+        <v>182982</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>55.553196</v>
+        <v>57.553192</v>
       </c>
       <c r="AC71" s="4" t="n">
-        <v>43.181507</v>
+        <v>44.736107</v>
       </c>
       <c r="AD71" s="4" t="inlineStr"/>
       <c r="AE71" s="4" t="n">
@@ -10005,7 +10005,7 @@
         <v>20</v>
       </c>
       <c r="AH71" s="4" t="n">
-        <v>9.020401</v>
+        <v>9.345148999999999</v>
       </c>
       <c r="AI71" s="4" t="n">
         <v>38</v>
@@ -10075,7 +10075,7 @@
         <v>45.79</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>47.32</v>
+        <v>47.24</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -10116,13 +10116,13 @@
         <v>1.39</v>
       </c>
       <c r="AA72" s="2" t="n">
-        <v>2306</v>
+        <v>2354</v>
       </c>
       <c r="AB72" s="2" t="n">
-        <v>12.571427</v>
+        <v>12.83535</v>
       </c>
       <c r="AC72" s="2" t="n">
-        <v>3.9066966</v>
+        <v>3.9887133</v>
       </c>
       <c r="AD72" s="2" t="inlineStr"/>
       <c r="AE72" s="2" t="n">
@@ -10135,7 +10135,7 @@
         <v>17</v>
       </c>
       <c r="AH72" s="2" t="n">
-        <v>2.3964918</v>
+        <v>2.4468033</v>
       </c>
       <c r="AI72" s="2" t="n">
         <v>62</v>
@@ -10205,7 +10205,7 @@
         <v>895.08</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>863.8200000000001</v>
+        <v>864.46</v>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
@@ -10246,13 +10246,13 @@
         <v>1.48</v>
       </c>
       <c r="AA73" s="4" t="n">
-        <v>71474</v>
+        <v>72709</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>80.61072</v>
+        <v>82.00351999999999</v>
       </c>
       <c r="AC73" s="4" t="n">
-        <v>12.656256</v>
+        <v>12.874931</v>
       </c>
       <c r="AD73" s="4" t="n">
         <v>1.36</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AG73" s="4" t="inlineStr"/>
       <c r="AH73" s="4" t="n">
-        <v>1.0866604</v>
+        <v>1.1054357</v>
       </c>
       <c r="AI73" s="4" t="n">
         <v>16</v>
@@ -10283,32 +10283,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Mangalore Refinery and Petrochemicals Limited</t>
+          <t>Steel Authority of India Limited</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Refining &amp; Marketing</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>42.2</v>
+        <v>41.59999999999999</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>21.4</v>
+        <v>19.2</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>20.8</v>
+        <v>22.4</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -10317,132 +10317,128 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 👤 High Promoter</t>
+          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>161.01</v>
+        <v>184.09</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>3.41</v>
+        <v>1.51</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>155.7</v>
+        <v>191.51</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>161.2</v>
+        <v>184.84</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>159.55</v>
+        <v>158.34</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>75.95</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>54.22</v>
+        <v>42.45</v>
       </c>
       <c r="S74" s="2" t="n">
-        <v>-0.7235</v>
+        <v>-0.6437</v>
       </c>
       <c r="T74" s="2" t="n">
-        <v>-2.8323</v>
+        <v>2.658</v>
       </c>
       <c r="U74" s="2" t="n">
-        <v>2.1088</v>
+        <v>-3.3018</v>
       </c>
       <c r="V74" s="2" t="inlineStr"/>
       <c r="W74" s="2" t="n">
-        <v>18.54</v>
+        <v>29.02</v>
       </c>
       <c r="X74" s="2" t="n">
-        <v>7838745</v>
+        <v>10126753</v>
       </c>
       <c r="Y74" s="2" t="n">
-        <v>6798901</v>
+        <v>22688156</v>
       </c>
       <c r="Z74" s="2" t="n">
-        <v>1.15</v>
+        <v>0.45</v>
       </c>
       <c r="AA74" s="2" t="n">
-        <v>28219</v>
+        <v>75386</v>
       </c>
       <c r="AB74" s="2" t="n">
-        <v>14.663935</v>
+        <v>22.339045</v>
       </c>
       <c r="AC74" s="2" t="n">
-        <v>3.3968353</v>
-      </c>
-      <c r="AD74" s="2" t="n">
-        <v>14.17</v>
-      </c>
+        <v>11.473204</v>
+      </c>
+      <c r="AD74" s="2" t="inlineStr"/>
       <c r="AE74" s="2" t="n">
-        <v>108.059</v>
+        <v>57.763</v>
       </c>
       <c r="AF74" s="2" t="n">
-        <v>-3.4</v>
+        <v>11.8</v>
       </c>
       <c r="AG74" s="2" t="n">
-        <v>-68.2</v>
+        <v>167.6</v>
       </c>
       <c r="AH74" s="2" t="n">
-        <v>1.9803209</v>
+        <v>1.298329</v>
       </c>
       <c r="AI74" s="2" t="n">
-        <v>248</v>
-      </c>
-      <c r="AJ74" s="2" t="n">
-        <v>1.143</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AJ74" s="2" t="inlineStr"/>
       <c r="AK74" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MRPL/</t>
+          <t>https://www.screener.in/company/SAIL/</t>
         </is>
       </c>
       <c r="AL74" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MRPL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SAIL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Steel Authority of India Limited</t>
+          <t>Mangalore Refinery and Petrochemicals Limited</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Oil &amp; Gas Refining &amp; Marketing</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>41.59999999999999</v>
+        <v>41.5</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>19.2</v>
+        <v>21.4</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>22.4</v>
+        <v>20.1</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
@@ -10451,96 +10447,100 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy | 👤 High Promoter</t>
         </is>
       </c>
       <c r="J75" s="4" t="n">
-        <v>184.09</v>
+        <v>161.01</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1.51</v>
+        <v>3.41</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>191.51</v>
+        <v>155.7</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>184.84</v>
+        <v>161.2</v>
       </c>
       <c r="N75" s="4" t="n">
-        <v>158.41</v>
+        <v>159.22</v>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>87.79000000000001</v>
+        <v>75.95</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>42.45</v>
+        <v>54.22</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>-0.6437</v>
+        <v>-0.7235</v>
       </c>
       <c r="T75" s="4" t="n">
-        <v>2.658</v>
+        <v>-2.8323</v>
       </c>
       <c r="U75" s="4" t="n">
-        <v>-3.3018</v>
+        <v>2.1088</v>
       </c>
       <c r="V75" s="4" t="inlineStr"/>
       <c r="W75" s="4" t="n">
-        <v>29.02</v>
+        <v>18.54</v>
       </c>
       <c r="X75" s="4" t="n">
-        <v>10126753</v>
+        <v>7838745</v>
       </c>
       <c r="Y75" s="4" t="n">
-        <v>22688156</v>
+        <v>6798901</v>
       </c>
       <c r="Z75" s="4" t="n">
-        <v>0.45</v>
+        <v>1.15</v>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>76039</v>
+        <v>29610</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>22.532434</v>
+        <v>15.387068</v>
       </c>
       <c r="AC75" s="4" t="n">
-        <v>11.572528</v>
-      </c>
-      <c r="AD75" s="4" t="inlineStr"/>
+        <v>3.5643458</v>
+      </c>
+      <c r="AD75" s="4" t="n">
+        <v>14.17</v>
+      </c>
       <c r="AE75" s="4" t="n">
-        <v>57.763</v>
+        <v>108.059</v>
       </c>
       <c r="AF75" s="4" t="n">
-        <v>11.8</v>
+        <v>-3.4</v>
       </c>
       <c r="AG75" s="4" t="n">
-        <v>167.6</v>
+        <v>-68.2</v>
       </c>
       <c r="AH75" s="4" t="n">
-        <v>1.3095686</v>
+        <v>2.077978</v>
       </c>
       <c r="AI75" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="AJ75" s="4" t="inlineStr"/>
+        <v>248</v>
+      </c>
+      <c r="AJ75" s="4" t="n">
+        <v>1.143</v>
+      </c>
       <c r="AK75" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/SAIL/</t>
+          <t>https://www.screener.in/company/MRPL/</t>
         </is>
       </c>
       <c r="AL75" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SAIL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MRPL</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
         <v>490.03</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>547.59</v>
+        <v>546.11</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -10642,13 +10642,13 @@
         <v>0.72</v>
       </c>
       <c r="AA76" s="2" t="n">
-        <v>3865</v>
+        <v>3939</v>
       </c>
       <c r="AB76" s="2" t="n">
-        <v>114.9901</v>
+        <v>117.207924</v>
       </c>
       <c r="AC76" s="2" t="n">
-        <v>25.581497</v>
+        <v>26.07489</v>
       </c>
       <c r="AD76" s="2" t="n">
         <v>1.47</v>
@@ -10661,7 +10661,7 @@
         <v>-99.09999999999999</v>
       </c>
       <c r="AH76" s="2" t="n">
-        <v>1.3572356</v>
+        <v>1.3834126</v>
       </c>
       <c r="AI76" s="2" t="n">
         <v>0</v>
@@ -10733,7 +10733,7 @@
         <v>384.46</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>401.84</v>
+        <v>401.88</v>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
@@ -10774,13 +10774,13 @@
         <v>1.15</v>
       </c>
       <c r="AA77" s="4" t="n">
-        <v>401141</v>
+        <v>403578</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>20.78866</v>
+        <v>20.91495</v>
       </c>
       <c r="AC77" s="4" t="n">
-        <v>14.403571</v>
+        <v>14.491072</v>
       </c>
       <c r="AD77" s="4" t="n">
         <v>11.39</v>
@@ -10793,7 +10793,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH77" s="4" t="n">
-        <v>2.2144375</v>
+        <v>2.22789</v>
       </c>
       <c r="AI77" s="4" t="n">
         <v>12</v>
@@ -10863,7 +10863,7 @@
         <v>70.47</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>72.56999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -10904,13 +10904,13 @@
         <v>1.73</v>
       </c>
       <c r="AA78" s="2" t="n">
-        <v>65891</v>
+        <v>67467</v>
       </c>
       <c r="AB78" s="2" t="n">
-        <v>40.69149</v>
+        <v>41.664894</v>
       </c>
       <c r="AC78" s="2" t="n">
-        <v>11.840291</v>
+        <v>12.123529</v>
       </c>
       <c r="AD78" s="2" t="inlineStr"/>
       <c r="AE78" s="2" t="inlineStr"/>
@@ -10921,7 +10921,7 @@
         <v>-23.2</v>
       </c>
       <c r="AH78" s="2" t="n">
-        <v>1.4041593</v>
+        <v>1.437749</v>
       </c>
       <c r="AI78" s="2" t="n">
         <v>33</v>
@@ -10941,32 +10941,32 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Limited</t>
+          <t>Bharat Heavy Electricals Limited</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Information Technology Services</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>39.90000000000001</v>
+        <v>39.6</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>16.8</v>
+        <v>24.8</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>23.1</v>
+        <v>14.8</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
@@ -10975,23 +10975,23 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 📉 Tight Base | 💎 High ROE</t>
+          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J79" s="4" t="n">
-        <v>757.55</v>
+        <v>378.75</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>4.83</v>
+        <v>2.19</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>759.55</v>
+        <v>391.26</v>
       </c>
       <c r="M79" s="4" t="n">
-        <v>751.83</v>
+        <v>366.41</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>745.51</v>
+        <v>300.72</v>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
@@ -11004,103 +11004,103 @@
         </is>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>87.98999999999999</v>
+        <v>89.14</v>
       </c>
       <c r="R79" s="4" t="n">
-        <v>49.32</v>
+        <v>45.68</v>
       </c>
       <c r="S79" s="4" t="n">
-        <v>-5.3701</v>
+        <v>2.3723</v>
       </c>
       <c r="T79" s="4" t="n">
-        <v>-0.4009</v>
+        <v>9.6897</v>
       </c>
       <c r="U79" s="4" t="n">
-        <v>-4.9692</v>
+        <v>-7.3174</v>
       </c>
       <c r="V79" s="4" t="inlineStr"/>
       <c r="W79" s="4" t="n">
-        <v>10.89</v>
+        <v>30.95</v>
       </c>
       <c r="X79" s="4" t="n">
-        <v>910431</v>
+        <v>9280094</v>
       </c>
       <c r="Y79" s="4" t="n">
-        <v>1043797</v>
+        <v>10877791</v>
       </c>
       <c r="Z79" s="4" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="AA79" s="4" t="n">
-        <v>18786</v>
+        <v>133311</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>39.517475</v>
+        <v>83.591705</v>
       </c>
       <c r="AC79" s="4" t="n">
-        <v>29.331627</v>
+        <v>29.556381</v>
       </c>
       <c r="AD79" s="4" t="n">
-        <v>38.69</v>
+        <v>6.29</v>
       </c>
       <c r="AE79" s="4" t="n">
-        <v>4.863</v>
+        <v>31.312</v>
       </c>
       <c r="AF79" s="4" t="n">
-        <v>11</v>
+        <v>36.9</v>
       </c>
       <c r="AG79" s="4" t="n">
-        <v>10.6</v>
+        <v>156.4</v>
       </c>
       <c r="AH79" s="4" t="n">
-        <v>14.217747</v>
+        <v>5.09319</v>
       </c>
       <c r="AI79" s="4" t="n">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="AJ79" s="4" t="n">
-        <v>3.426</v>
+        <v>1.593</v>
       </c>
       <c r="AK79" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CAMS/</t>
+          <t>https://www.screener.in/company/BHEL/</t>
         </is>
       </c>
       <c r="AL79" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CAMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BHEL</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Limited</t>
+          <t>Grasim Industries Limited</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>39.6</v>
+        <v>39.3</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>24.8</v>
+        <v>27.4</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>14.8</v>
+        <v>11.9</v>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
@@ -11109,23 +11109,23 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>378.75</v>
+        <v>3105.5</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2.19</v>
+        <v>0.52</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>391.26</v>
+        <v>3065.02</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>366.41</v>
+        <v>2963.71</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>300.72</v>
+        <v>2836.82</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -11134,87 +11134,87 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>89.14</v>
+        <v>97.12</v>
       </c>
       <c r="R80" s="2" t="n">
-        <v>45.68</v>
+        <v>60.64</v>
       </c>
       <c r="S80" s="2" t="n">
-        <v>2.3723</v>
+        <v>46.3838</v>
       </c>
       <c r="T80" s="2" t="n">
-        <v>9.6897</v>
+        <v>60.9556</v>
       </c>
       <c r="U80" s="2" t="n">
-        <v>-7.3174</v>
+        <v>-14.5718</v>
       </c>
       <c r="V80" s="2" t="inlineStr"/>
       <c r="W80" s="2" t="n">
-        <v>30.95</v>
+        <v>16.7</v>
       </c>
       <c r="X80" s="2" t="n">
-        <v>9280094</v>
+        <v>536817</v>
       </c>
       <c r="Y80" s="2" t="n">
-        <v>10877791</v>
+        <v>919946</v>
       </c>
       <c r="Z80" s="2" t="n">
-        <v>0.85</v>
+        <v>0.58</v>
       </c>
       <c r="AA80" s="2" t="n">
-        <v>131883</v>
+        <v>214608</v>
       </c>
       <c r="AB80" s="2" t="n">
-        <v>82.69651</v>
+        <v>43.361195</v>
       </c>
       <c r="AC80" s="2" t="n">
-        <v>29.239857</v>
+        <v>21.551044</v>
       </c>
       <c r="AD80" s="2" t="n">
         <v>6.29</v>
       </c>
       <c r="AE80" s="2" t="n">
-        <v>31.312</v>
+        <v>134.138</v>
       </c>
       <c r="AF80" s="2" t="n">
-        <v>36.9</v>
+        <v>10.5</v>
       </c>
       <c r="AG80" s="2" t="n">
-        <v>156.4</v>
+        <v>60.8</v>
       </c>
       <c r="AH80" s="2" t="n">
-        <v>5.038646</v>
+        <v>2.0739546</v>
       </c>
       <c r="AI80" s="2" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="AJ80" s="2" t="n">
-        <v>1.593</v>
+        <v>0.947</v>
       </c>
       <c r="AK80" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BHEL/</t>
+          <t>https://www.screener.in/company/GRASIM/</t>
         </is>
       </c>
       <c r="AL80" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BHEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Grasim Industries Limited</t>
+          <t>National Aluminium Company Limited</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -11224,17 +11224,17 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>27.4</v>
+        <v>8.4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>11.9</v>
+        <v>30.8</v>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
@@ -11243,132 +11243,132 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
+          <t>💎 High ROE</t>
         </is>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3105.5</v>
+        <v>376.85</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0.52</v>
+        <v>1.69</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>3065.02</v>
+        <v>400.7</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>2963.71</v>
+        <v>400.87</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>2835.39</v>
+        <v>331.87</v>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>97.12</v>
+        <v>84.78</v>
       </c>
       <c r="R81" s="4" t="n">
-        <v>60.64</v>
+        <v>38.06</v>
       </c>
       <c r="S81" s="4" t="n">
-        <v>46.3838</v>
+        <v>-8.0471</v>
       </c>
       <c r="T81" s="4" t="n">
-        <v>60.9556</v>
+        <v>-2.1822</v>
       </c>
       <c r="U81" s="4" t="n">
-        <v>-14.5718</v>
+        <v>-5.8649</v>
       </c>
       <c r="V81" s="4" t="inlineStr"/>
       <c r="W81" s="4" t="n">
-        <v>16.7</v>
+        <v>20.69</v>
       </c>
       <c r="X81" s="4" t="n">
-        <v>536817</v>
+        <v>7674222</v>
       </c>
       <c r="Y81" s="4" t="n">
-        <v>919946</v>
+        <v>13480873</v>
       </c>
       <c r="Z81" s="4" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>210607</v>
+        <v>70224</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>42.552753</v>
+        <v>11.437332</v>
       </c>
       <c r="AC81" s="4" t="n">
-        <v>21.149239</v>
+        <v>10.143707</v>
       </c>
       <c r="AD81" s="4" t="n">
-        <v>6.29</v>
+        <v>29.42</v>
       </c>
       <c r="AE81" s="4" t="n">
-        <v>134.138</v>
+        <v>0.277</v>
       </c>
       <c r="AF81" s="4" t="n">
-        <v>10.5</v>
+        <v>-4.8</v>
       </c>
       <c r="AG81" s="4" t="n">
-        <v>60.8</v>
+        <v>-16.7</v>
       </c>
       <c r="AH81" s="4" t="n">
-        <v>2.0352871</v>
+        <v>3.250557</v>
       </c>
       <c r="AI81" s="4" t="n">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="AJ81" s="4" t="n">
-        <v>0.947</v>
+        <v>3.604</v>
       </c>
       <c r="AK81" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/GRASIM/</t>
+          <t>https://www.screener.in/company/NATIONALUM/</t>
         </is>
       </c>
       <c r="AL81" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>National Aluminium Company Limited</t>
+          <t>Biocon Limited</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Aluminum</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>39.2</v>
+        <v>38.5</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>8.4</v>
+        <v>32.2</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>30.8</v>
+        <v>6.3</v>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
@@ -11377,132 +11377,132 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>💎 High ROE</t>
+          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>376.85</v>
+        <v>419</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1.69</v>
+        <v>0.73</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>400.7</v>
+        <v>415.05</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>400.87</v>
+        <v>401.17</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>331.99</v>
+        <v>379.71</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>84.78</v>
+        <v>95.14</v>
       </c>
       <c r="R82" s="2" t="n">
-        <v>38.06</v>
+        <v>57.17</v>
       </c>
       <c r="S82" s="2" t="n">
-        <v>-8.0471</v>
+        <v>5.3097</v>
       </c>
       <c r="T82" s="2" t="n">
-        <v>-2.1822</v>
+        <v>8.3249</v>
       </c>
       <c r="U82" s="2" t="n">
-        <v>-5.8649</v>
+        <v>-3.0152</v>
       </c>
       <c r="V82" s="2" t="inlineStr"/>
       <c r="W82" s="2" t="n">
-        <v>20.69</v>
+        <v>28.2</v>
       </c>
       <c r="X82" s="2" t="n">
-        <v>7674222</v>
+        <v>1674659</v>
       </c>
       <c r="Y82" s="2" t="n">
-        <v>13480873</v>
+        <v>3207699</v>
       </c>
       <c r="Z82" s="2" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="AA82" s="2" t="n">
-        <v>69213</v>
+        <v>67380</v>
       </c>
       <c r="AB82" s="2" t="n">
-        <v>11.272809</v>
+        <v>148.0605</v>
       </c>
       <c r="AC82" s="2" t="n">
-        <v>9.997792</v>
+        <v>35.336002</v>
       </c>
       <c r="AD82" s="2" t="n">
-        <v>29.42</v>
+        <v>1.15</v>
       </c>
       <c r="AE82" s="2" t="n">
-        <v>0.277</v>
+        <v>42.145</v>
       </c>
       <c r="AF82" s="2" t="n">
-        <v>-4.8</v>
+        <v>2.3</v>
       </c>
       <c r="AG82" s="2" t="n">
-        <v>-16.7</v>
+        <v>-72.5</v>
       </c>
       <c r="AH82" s="2" t="n">
-        <v>3.2037985</v>
+        <v>1.9483194</v>
       </c>
       <c r="AI82" s="2" t="n">
-        <v>212</v>
+        <v>12</v>
       </c>
       <c r="AJ82" s="2" t="n">
-        <v>3.604</v>
+        <v>1.221</v>
       </c>
       <c r="AK82" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/NATIONALUM/</t>
+          <t>https://www.screener.in/company/BIOCON/</t>
         </is>
       </c>
       <c r="AL82" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BIOCON</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Biocon Limited</t>
+          <t>CESC Limited</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>38.5</v>
+        <v>37.90000000000001</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>32.2</v>
+        <v>16.8</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>6.3</v>
+        <v>21.1</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
@@ -11511,23 +11511,23 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
+          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J83" s="4" t="n">
-        <v>419</v>
+        <v>168.15</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0.73</v>
+        <v>0.1</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>415.05</v>
+        <v>176.32</v>
       </c>
       <c r="M83" s="4" t="n">
-        <v>401.17</v>
+        <v>174.88</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>380.05</v>
+        <v>166.74</v>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
@@ -11536,107 +11536,107 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>95.14</v>
+        <v>82.22</v>
       </c>
       <c r="R83" s="4" t="n">
-        <v>57.17</v>
+        <v>36.54</v>
       </c>
       <c r="S83" s="4" t="n">
-        <v>5.3097</v>
+        <v>-2.4231</v>
       </c>
       <c r="T83" s="4" t="n">
-        <v>8.3249</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="U83" s="4" t="n">
-        <v>-3.0152</v>
+        <v>-1.8814</v>
       </c>
       <c r="V83" s="4" t="inlineStr"/>
       <c r="W83" s="4" t="n">
-        <v>28.2</v>
+        <v>23.28</v>
       </c>
       <c r="X83" s="4" t="n">
-        <v>1674659</v>
+        <v>1031409</v>
       </c>
       <c r="Y83" s="4" t="n">
-        <v>3207699</v>
+        <v>2348283</v>
       </c>
       <c r="Z83" s="4" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="AA83" s="4" t="n">
-        <v>67857</v>
+        <v>22403</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>149.11032</v>
+        <v>14.519758</v>
       </c>
       <c r="AC83" s="4" t="n">
-        <v>35.586555</v>
+        <v>11.786825</v>
       </c>
       <c r="AD83" s="4" t="n">
-        <v>1.15</v>
+        <v>12.55</v>
       </c>
       <c r="AE83" s="4" t="n">
-        <v>42.145</v>
+        <v>164.311</v>
       </c>
       <c r="AF83" s="4" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="AG83" s="4" t="n">
-        <v>-72.5</v>
+        <v>17.8</v>
       </c>
       <c r="AH83" s="4" t="n">
-        <v>1.9621341</v>
+        <v>1.7889577</v>
       </c>
       <c r="AI83" s="4" t="n">
-        <v>12</v>
+        <v>357</v>
       </c>
       <c r="AJ83" s="4" t="n">
-        <v>1.221</v>
+        <v>0.921</v>
       </c>
       <c r="AK83" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BIOCON/</t>
+          <t>https://www.screener.in/company/CESC/</t>
         </is>
       </c>
       <c r="AL83" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BIOCON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CESC Limited</t>
+          <t>Berger Paints India Limited</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>37.90000000000001</v>
+        <v>37.9</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>16.8</v>
+        <v>19</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
@@ -11645,132 +11645,132 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 📉 Tight Base</t>
+          <t>✅ Supertrend Buy | 📉 Tight Base | 👤 High Promoter</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>168.15</v>
+        <v>515.15</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>176.32</v>
+        <v>504.47</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>174.88</v>
+        <v>491.35</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>166.7</v>
+        <v>501.18</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>82.22</v>
+        <v>85.72</v>
       </c>
       <c r="R84" s="2" t="n">
-        <v>36.54</v>
+        <v>56.9</v>
       </c>
       <c r="S84" s="2" t="n">
-        <v>-2.4231</v>
+        <v>5.3538</v>
       </c>
       <c r="T84" s="2" t="n">
-        <v>-0.5417999999999999</v>
+        <v>6.3005</v>
       </c>
       <c r="U84" s="2" t="n">
-        <v>-1.8814</v>
+        <v>-0.9468</v>
       </c>
       <c r="V84" s="2" t="inlineStr"/>
       <c r="W84" s="2" t="n">
-        <v>23.28</v>
+        <v>19.69</v>
       </c>
       <c r="X84" s="2" t="n">
-        <v>1031409</v>
+        <v>382979</v>
       </c>
       <c r="Y84" s="2" t="n">
-        <v>2348283</v>
+        <v>353638</v>
       </c>
       <c r="Z84" s="2" t="n">
-        <v>0.44</v>
+        <v>1.08</v>
       </c>
       <c r="AA84" s="2" t="n">
-        <v>22289</v>
+        <v>60562</v>
       </c>
       <c r="AB84" s="2" t="n">
-        <v>14.445875</v>
+        <v>53.657024</v>
       </c>
       <c r="AC84" s="2" t="n">
-        <v>11.726849</v>
+        <v>40.96528</v>
       </c>
       <c r="AD84" s="2" t="n">
-        <v>12.55</v>
+        <v>17.23</v>
       </c>
       <c r="AE84" s="2" t="n">
-        <v>164.311</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="AF84" s="2" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="AG84" s="2" t="n">
-        <v>17.8</v>
+        <v>27.7</v>
       </c>
       <c r="AH84" s="2" t="n">
-        <v>1.7798548</v>
+        <v>8.759888</v>
       </c>
       <c r="AI84" s="2" t="n">
-        <v>357</v>
+        <v>74</v>
       </c>
       <c r="AJ84" s="2" t="n">
-        <v>0.921</v>
+        <v>2.115</v>
       </c>
       <c r="AK84" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/CESC/</t>
+          <t>https://www.screener.in/company/BERGEPAINT/</t>
         </is>
       </c>
       <c r="AL84" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CESC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Berger Paints India Limited</t>
+          <t>Manappuram Finance Limited</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Credit Services</t>
         </is>
       </c>
       <c r="E85" s="6" t="n">
-        <v>37.9</v>
+        <v>37.40000000000001</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>18.9</v>
+        <v>15.8</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
@@ -11779,132 +11779,130 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>✅ Supertrend Buy | 📉 Tight Base | 👤 High Promoter</t>
+          <t>📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
         </is>
       </c>
       <c r="J85" s="4" t="n">
-        <v>515.15</v>
+        <v>305.2</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0.23</v>
+        <v>4.5</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>504.47</v>
+        <v>307.48</v>
       </c>
       <c r="M85" s="4" t="n">
-        <v>491.35</v>
+        <v>301.13</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>503.02</v>
+        <v>284.79</v>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>85.72</v>
+        <v>91.38</v>
       </c>
       <c r="R85" s="4" t="n">
-        <v>56.9</v>
+        <v>49.12</v>
       </c>
       <c r="S85" s="4" t="n">
-        <v>5.3538</v>
+        <v>-0.9019</v>
       </c>
       <c r="T85" s="4" t="n">
-        <v>6.3005</v>
+        <v>2.8638</v>
       </c>
       <c r="U85" s="4" t="n">
-        <v>-0.9468</v>
+        <v>-3.7657</v>
       </c>
       <c r="V85" s="4" t="inlineStr"/>
       <c r="W85" s="4" t="n">
-        <v>19.69</v>
+        <v>24.31</v>
       </c>
       <c r="X85" s="4" t="n">
-        <v>382979</v>
+        <v>2267599</v>
       </c>
       <c r="Y85" s="4" t="n">
-        <v>353638</v>
+        <v>3423878</v>
       </c>
       <c r="Z85" s="4" t="n">
-        <v>1.08</v>
+        <v>0.66</v>
       </c>
       <c r="AA85" s="4" t="n">
-        <v>60067</v>
+        <v>29838</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>53.217976</v>
+        <v>27.103241</v>
       </c>
       <c r="AC85" s="4" t="n">
-        <v>40.63008</v>
+        <v>10.859829</v>
       </c>
       <c r="AD85" s="4" t="n">
-        <v>17.23</v>
+        <v>6.97</v>
       </c>
       <c r="AE85" s="4" t="n">
-        <v>9.164999999999999</v>
+        <v>360.191</v>
       </c>
       <c r="AF85" s="4" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AG85" s="4" t="n">
-        <v>27.7</v>
-      </c>
+        <v>109.3</v>
+      </c>
+      <c r="AG85" s="4" t="inlineStr"/>
       <c r="AH85" s="4" t="n">
-        <v>8.68821</v>
+        <v>1.6759967</v>
       </c>
       <c r="AI85" s="4" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AJ85" s="4" t="n">
-        <v>2.115</v>
+        <v>94.116</v>
       </c>
       <c r="AK85" s="4" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/BERGEPAINT/</t>
+          <t>https://www.screener.in/company/MANAPPURAM/</t>
         </is>
       </c>
       <c r="AL85" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BERGEPAINT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Manappuram Finance Limited</t>
+          <t>Computer Age Management Services Limited</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Credit Services</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="E86" s="6" t="n">
         <v>37.40000000000001</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>21.6</v>
+        <v>16.8</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>15.8</v>
+        <v>20.6</v>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
@@ -11913,23 +11911,23 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>📈 EMA Bull Stack | 🏆 Near 52W High | 📉 Tight Base</t>
+          <t>📈 EMA Bull Stack | 📉 Tight Base | 💎 High ROE</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>305.2</v>
+        <v>757.55</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>4.5</v>
+        <v>4.83</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>307.48</v>
+        <v>759.55</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>301.13</v>
+        <v>751.83</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>284.65</v>
+        <v>744.33</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -11942,69 +11940,71 @@
         </is>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>91.38</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="R86" s="2" t="n">
-        <v>49.12</v>
+        <v>49.32</v>
       </c>
       <c r="S86" s="2" t="n">
-        <v>-0.9019</v>
+        <v>-5.3701</v>
       </c>
       <c r="T86" s="2" t="n">
-        <v>2.8638</v>
+        <v>-0.4009</v>
       </c>
       <c r="U86" s="2" t="n">
-        <v>-3.7657</v>
+        <v>-4.9692</v>
       </c>
       <c r="V86" s="2" t="inlineStr"/>
       <c r="W86" s="2" t="n">
-        <v>24.31</v>
+        <v>10.89</v>
       </c>
       <c r="X86" s="2" t="n">
-        <v>2267599</v>
+        <v>910431</v>
       </c>
       <c r="Y86" s="2" t="n">
-        <v>3423878</v>
+        <v>1043797</v>
       </c>
       <c r="Z86" s="2" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="AA86" s="2" t="n">
-        <v>28669</v>
+        <v>19277</v>
       </c>
       <c r="AB86" s="2" t="n">
-        <v>26.040956</v>
+        <v>40.55034</v>
       </c>
       <c r="AC86" s="2" t="n">
-        <v>10.434189</v>
+        <v>30.074137</v>
       </c>
       <c r="AD86" s="2" t="n">
-        <v>6.97</v>
+        <v>38.69</v>
       </c>
       <c r="AE86" s="2" t="n">
-        <v>360.191</v>
+        <v>4.863</v>
       </c>
       <c r="AF86" s="2" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AG86" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AG86" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="AH86" s="2" t="n">
-        <v>1.6103077</v>
+        <v>14.589354</v>
       </c>
       <c r="AI86" s="2" t="n">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="AJ86" s="2" t="n">
-        <v>94.116</v>
+        <v>3.426</v>
       </c>
       <c r="AK86" s="2" t="inlineStr">
         <is>
-          <t>https://www.screener.in/company/MANAPPURAM/</t>
+          <t>https://www.screener.in/company/CAMS/</t>
         </is>
       </c>
       <c r="AL86" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANAPPURAM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CAMS</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
         <v>539.2</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>465.17</v>
+        <v>464.81</v>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
@@ -12102,13 +12102,13 @@
         <v>0.87</v>
       </c>
       <c r="AA87" s="4" t="n">
-        <v>49318</v>
+        <v>49908</v>
       </c>
       <c r="AB87" s="4" t="n">
-        <v>53.74078</v>
+        <v>54.38356</v>
       </c>
       <c r="AC87" s="4" t="n">
-        <v>25.628141</v>
+        <v>25.934673</v>
       </c>
       <c r="AD87" s="4" t="n">
         <v>30.6</v>
@@ -12123,7 +12123,7 @@
         <v>136.6</v>
       </c>
       <c r="AH87" s="4" t="n">
-        <v>14.769766</v>
+        <v>14.946424</v>
       </c>
       <c r="AI87" s="4" t="n">
         <v>48</v>
@@ -12164,13 +12164,13 @@
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>35.3</v>
+        <v>34.59999999999999</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>21.4</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>162.67</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>165.07</v>
+        <v>164.85</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -12236,13 +12236,13 @@
         <v>0.6</v>
       </c>
       <c r="AA88" s="2" t="n">
-        <v>112105</v>
+        <v>115333</v>
       </c>
       <c r="AB88" s="2" t="n">
-        <v>14.787511</v>
+        <v>15.213357</v>
       </c>
       <c r="AC88" s="2" t="n">
-        <v>9.551387999999999</v>
+        <v>9.826446000000001</v>
       </c>
       <c r="AD88" s="2" t="n">
         <v>8.69</v>
@@ -12257,7 +12257,7 @@
         <v>-40.3</v>
       </c>
       <c r="AH88" s="2" t="n">
-        <v>1.2578478</v>
+        <v>1.2940708</v>
       </c>
       <c r="AI88" s="2" t="n">
         <v>733</v>
@@ -12329,7 +12329,7 @@
         <v>3600.88</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>3332.02</v>
+        <v>3332.84</v>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
@@ -12370,13 +12370,13 @@
         <v>0.41</v>
       </c>
       <c r="AA89" s="4" t="n">
-        <v>127121</v>
+        <v>128267</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>75.18113</v>
+        <v>75.859314</v>
       </c>
       <c r="AC89" s="4" t="n">
-        <v>51.517048</v>
+        <v>51.981762</v>
       </c>
       <c r="AD89" s="4" t="inlineStr"/>
       <c r="AE89" s="4" t="n">
@@ -12389,7 +12389,7 @@
         <v>-36.4</v>
       </c>
       <c r="AH89" s="4" t="n">
-        <v>9.1783085</v>
+        <v>9.261103</v>
       </c>
       <c r="AI89" s="4" t="n">
         <v>39</v>
@@ -12461,7 +12461,7 @@
         <v>6762.44</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>6058.12</v>
+        <v>6049.25</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -12502,13 +12502,13 @@
         <v>0.5</v>
       </c>
       <c r="AA90" s="2" t="n">
-        <v>143473</v>
+        <v>146694</v>
       </c>
       <c r="AB90" s="2" t="n">
-        <v>92.59435999999999</v>
+        <v>94.673134</v>
       </c>
       <c r="AC90" s="2" t="n">
-        <v>66.126976</v>
+        <v>67.61154000000001</v>
       </c>
       <c r="AD90" s="2" t="inlineStr"/>
       <c r="AE90" s="2" t="n">
@@ -12521,7 +12521,7 @@
         <v>276</v>
       </c>
       <c r="AH90" s="2" t="n">
-        <v>18.309435</v>
+        <v>18.72049</v>
       </c>
       <c r="AI90" s="2" t="n">
         <v>58</v>
@@ -12591,7 +12591,7 @@
         <v>1347.98</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>1387.35</v>
+        <v>1387.57</v>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
@@ -12632,13 +12632,13 @@
         <v>0.53</v>
       </c>
       <c r="AA91" s="4" t="n">
-        <v>112242</v>
+        <v>111588</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>28.988108</v>
+        <v>28.819113</v>
       </c>
       <c r="AC91" s="4" t="n">
-        <v>21.977686</v>
+        <v>21.84956</v>
       </c>
       <c r="AD91" s="4" t="n">
         <v>11.74</v>
@@ -12653,7 +12653,7 @@
         <v>-54.6</v>
       </c>
       <c r="AH91" s="4" t="n">
-        <v>3.2595665</v>
+        <v>3.2405639</v>
       </c>
       <c r="AI91" s="4" t="n">
         <v>94</v>
@@ -12725,7 +12725,7 @@
         <v>2242.82</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>2067.49</v>
+        <v>2066.73</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -12766,13 +12766,13 @@
         <v>0.63</v>
       </c>
       <c r="AA92" s="2" t="n">
-        <v>61345</v>
+        <v>60859</v>
       </c>
       <c r="AB92" s="2" t="n">
-        <v>45.043518</v>
+        <v>44.687115</v>
       </c>
       <c r="AC92" s="2" t="n">
-        <v>22.190546</v>
+        <v>22.014965</v>
       </c>
       <c r="AD92" s="2" t="n">
         <v>14.07</v>
@@ -12787,7 +12787,7 @@
         <v>6575</v>
       </c>
       <c r="AH92" s="2" t="n">
-        <v>5.8360963</v>
+        <v>5.789919</v>
       </c>
       <c r="AI92" s="2" t="n">
         <v>23</v>
@@ -12859,7 +12859,7 @@
         <v>1285.9</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>1265.16</v>
+        <v>1265.07</v>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
@@ -12900,13 +12900,13 @@
         <v>0.95</v>
       </c>
       <c r="AA93" s="4" t="n">
-        <v>106203</v>
+        <v>106544</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>24.813229</v>
+        <v>24.892996</v>
       </c>
       <c r="AC93" s="4" t="n">
-        <v>19.770636</v>
+        <v>19.834192</v>
       </c>
       <c r="AD93" s="4" t="n">
         <v>11.83</v>
@@ -12921,7 +12921,7 @@
         <v>-86.2</v>
       </c>
       <c r="AH93" s="4" t="n">
-        <v>2.816547</v>
+        <v>2.825601</v>
       </c>
       <c r="AI93" s="4" t="n">
         <v>63</v>
@@ -12993,7 +12993,7 @@
         <v>430.72</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>408.37</v>
+        <v>407.55</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -13034,13 +13034,13 @@
         <v>0.95</v>
       </c>
       <c r="AA94" s="2" t="n">
-        <v>138951</v>
+        <v>140089</v>
       </c>
       <c r="AB94" s="2" t="n">
-        <v>5.365061</v>
+        <v>5.4090214</v>
       </c>
       <c r="AC94" s="2" t="n">
-        <v>6.465959</v>
+        <v>6.51894</v>
       </c>
       <c r="AD94" s="2" t="n">
         <v>20.47</v>
@@ -13055,7 +13055,7 @@
         <v>10.8</v>
       </c>
       <c r="AH94" s="2" t="n">
-        <v>1.0457569</v>
+        <v>1.0543257</v>
       </c>
       <c r="AI94" s="2" t="n">
         <v>347</v>
@@ -13127,7 +13127,7 @@
         <v>135.24</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>130.45</v>
+        <v>130.3</v>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
@@ -13168,13 +13168,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AA95" s="4" t="n">
-        <v>13242</v>
+        <v>13853</v>
       </c>
       <c r="AB95" s="4" t="n">
-        <v>65.042244</v>
+        <v>68.042244</v>
       </c>
       <c r="AC95" s="4" t="n">
-        <v>14.777599</v>
+        <v>15.459199</v>
       </c>
       <c r="AD95" s="4" t="n">
         <v>4.3</v>
@@ -13189,7 +13189,7 @@
         <v>-22.1</v>
       </c>
       <c r="AH95" s="4" t="n">
-        <v>2.8660085</v>
+        <v>2.9982</v>
       </c>
       <c r="AI95" s="4" t="n">
         <v>7</v>
@@ -13261,7 +13261,7 @@
         <v>7588.9</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>7280.93</v>
+        <v>7280.51</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -13302,13 +13302,13 @@
         <v>1.01</v>
       </c>
       <c r="AA96" s="2" t="n">
-        <v>26169</v>
+        <v>26874</v>
       </c>
       <c r="AB96" s="2" t="n">
-        <v>147.04716</v>
+        <v>151.01071</v>
       </c>
       <c r="AC96" s="2" t="n">
-        <v>39.08519</v>
+        <v>40.120815</v>
       </c>
       <c r="AD96" s="2" t="n">
         <v>5.58</v>
@@ -13323,7 +13323,7 @@
         <v>11</v>
       </c>
       <c r="AH96" s="2" t="n">
-        <v>5.972908</v>
+        <v>6.1339025</v>
       </c>
       <c r="AI96" s="2" t="n">
         <v>0</v>
@@ -13395,7 +13395,7 @@
         <v>202.82</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>186.15</v>
+        <v>186.18</v>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
@@ -13436,13 +13436,13 @@
         <v>0.84</v>
       </c>
       <c r="AA97" s="4" t="n">
-        <v>246768</v>
+        <v>246045</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>22.87399</v>
+        <v>22.806938</v>
       </c>
       <c r="AC97" s="4" t="n">
-        <v>10.524468</v>
+        <v>10.493617</v>
       </c>
       <c r="AD97" s="4" t="n">
         <v>11.16</v>
@@ -13457,7 +13457,7 @@
         <v>125.2</v>
       </c>
       <c r="AH97" s="4" t="n">
-        <v>2.5958724</v>
+        <v>2.588263</v>
       </c>
       <c r="AI97" s="4" t="n">
         <v>202</v>
@@ -14023,7 +14023,7 @@
         <v>3765.73</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>3091.23</v>
+        <v>3092.67</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -14064,13 +14064,13 @@
         <v>0.73</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>164121</v>
+        <v>167569</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>67.11676</v>
+        <v>68.526825</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>40.356247</v>
+        <v>41.204098</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>36</v>
@@ -14085,7 +14085,7 @@
         <v>64</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>20.873882</v>
+        <v>21.312424</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>25</v>
@@ -14157,7 +14157,7 @@
         <v>981.77</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>922.16</v>
+        <v>922.6</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -14202,13 +14202,13 @@
         <v>2.35</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>75996</v>
+        <v>77350</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>28.989439</v>
+        <v>29.506138</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>16.740313</v>
+        <v>17.038687</v>
       </c>
       <c r="AD3" s="4" t="inlineStr"/>
       <c r="AE3" s="4" t="inlineStr"/>
@@ -14219,7 +14219,7 @@
         <v>62.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>3.800012</v>
+        <v>3.8677423</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>10</v>
@@ -14289,7 +14289,7 @@
         <v>730.51</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>720.17</v>
+        <v>720.5</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -14330,13 +14330,13 @@
         <v>5.69</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>33148</v>
+        <v>34549</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>36.90504</v>
+        <v>38.464245</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>27.03451</v>
+        <v>28.176691</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.26</v>
@@ -14351,7 +14351,7 @@
         <v>45.8</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>5.5767155</v>
+        <v>5.812326</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>85</v>
@@ -14423,7 +14423,7 @@
         <v>9027.620000000001</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>8158.75</v>
+        <v>8158.26</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -14464,13 +14464,13 @@
         <v>0.53</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>81209</v>
+        <v>81605</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>30.8643</v>
+        <v>31.014858</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>24.328379</v>
+        <v>24.447054</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>32.61</v>
@@ -14485,7 +14485,7 @@
         <v>30.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>10.371437</v>
+        <v>10.4220295</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>713</v>
@@ -14557,7 +14557,7 @@
         <v>4045.71</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3383.54</v>
+        <v>3380.7</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -14598,13 +14598,13 @@
         <v>1.78</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>26121</v>
+        <v>26263</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>126.58388</v>
+        <v>127.27096</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>63.013733</v>
+        <v>63.355762</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>32.83</v>
@@ -14619,7 +14619,7 @@
         <v>64.3</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>36.019722</v>
+        <v>36.215233</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>5</v>
@@ -14691,7 +14691,7 @@
         <v>2622.28</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2384.78</v>
+        <v>2380.51</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -14732,13 +14732,13 @@
         <v>0.99</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>400840</v>
+        <v>403707</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>39.684868</v>
+        <v>39.968758</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>51.63206</v>
+        <v>52.001415</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>13.66</v>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
-        <v>4.6668615</v>
+        <v>4.7002463</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>4</v>
@@ -14823,7 +14823,7 @@
         <v>335.31</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>304.69</v>
+        <v>305.22</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -14864,13 +14864,13 @@
         <v>1.95</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>22662</v>
+        <v>23083</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>25.965223</v>
+        <v>26.447834</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>19.23719</v>
+        <v>19.594748</v>
       </c>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
@@ -14881,7 +14881,7 @@
         <v>367.9</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>1.3521404</v>
+        <v>1.3772724</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>33</v>
@@ -14951,7 +14951,7 @@
         <v>469.61</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>423.29</v>
+        <v>424.55</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -14992,13 +14992,13 @@
         <v>0.73</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>8418</v>
+        <v>8525</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>51.80216</v>
+        <v>52.45837</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>38.747257</v>
+        <v>39.238094</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>28.75</v>
@@ -15013,7 +15013,7 @@
         <v>116.3</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>15.739199</v>
+        <v>15.938578</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>309</v>
@@ -15085,7 +15085,7 @@
         <v>506.37</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>372.46</v>
+        <v>372.1</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -15126,13 +15126,13 @@
         <v>0.76</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>7728</v>
+        <v>7738</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>41.665497</v>
+        <v>41.71831</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>28.686062</v>
+        <v>28.722425</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>25.31</v>
@@ -15147,7 +15147,7 @@
         <v>113</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>10.492109</v>
+        <v>10.505409</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>0</v>
@@ -15219,7 +15219,7 @@
         <v>1698.35</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1525.77</v>
+        <v>1524.23</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -15260,13 +15260,13 @@
         <v>1.17</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>417685</v>
+        <v>415819</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>31.154839</v>
+        <v>31.01564</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>23.459633</v>
+        <v>23.291836</v>
       </c>
       <c r="AD11" s="4" t="n">
         <v>15.59</v>
@@ -15281,7 +15281,7 @@
         <v>3.6</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>4.3527536</v>
+        <v>4.3333054</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>41</v>
@@ -15600,7 +15600,7 @@
         <v>3765.73</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>3091.23</v>
+        <v>3092.67</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -15641,13 +15641,13 @@
         <v>0.73</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>164121</v>
+        <v>167569</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>67.11676</v>
+        <v>68.526825</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>40.356247</v>
+        <v>41.204098</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>36</v>
@@ -15662,7 +15662,7 @@
         <v>64</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>20.873882</v>
+        <v>21.312424</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>25</v>
@@ -15734,7 +15734,7 @@
         <v>981.77</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>922.16</v>
+        <v>922.6</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -15779,13 +15779,13 @@
         <v>2.35</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>75996</v>
+        <v>77350</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>28.989439</v>
+        <v>29.506138</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>16.740313</v>
+        <v>17.038687</v>
       </c>
       <c r="AD3" s="4" t="inlineStr"/>
       <c r="AE3" s="4" t="inlineStr"/>
@@ -15796,7 +15796,7 @@
         <v>62.6</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>3.800012</v>
+        <v>3.8677423</v>
       </c>
       <c r="AI3" s="4" t="n">
         <v>10</v>
@@ -15866,7 +15866,7 @@
         <v>730.51</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>720.17</v>
+        <v>720.5</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -15907,13 +15907,13 @@
         <v>5.69</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>33148</v>
+        <v>34549</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>36.90504</v>
+        <v>38.464245</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>27.03451</v>
+        <v>28.176691</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>15.26</v>
@@ -15928,7 +15928,7 @@
         <v>45.8</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>5.5767155</v>
+        <v>5.812326</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>85</v>
@@ -16000,7 +16000,7 @@
         <v>9027.620000000001</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>8158.75</v>
+        <v>8158.26</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -16041,13 +16041,13 @@
         <v>0.53</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>81209</v>
+        <v>81605</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>30.8643</v>
+        <v>31.014858</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>24.328379</v>
+        <v>24.447054</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>32.61</v>
@@ -16062,7 +16062,7 @@
         <v>30.6</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>10.371437</v>
+        <v>10.4220295</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>713</v>
@@ -16134,7 +16134,7 @@
         <v>4045.71</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3383.54</v>
+        <v>3380.7</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -16175,13 +16175,13 @@
         <v>1.78</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>26121</v>
+        <v>26263</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>126.58388</v>
+        <v>127.27096</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>63.013733</v>
+        <v>63.355762</v>
       </c>
       <c r="AD6" s="2" t="n">
         <v>32.83</v>
@@ -16196,7 +16196,7 @@
         <v>64.3</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>36.019722</v>
+        <v>36.215233</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>5</v>
@@ -16268,7 +16268,7 @@
         <v>2622.28</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2384.78</v>
+        <v>2380.51</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -16309,13 +16309,13 @@
         <v>0.99</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>400840</v>
+        <v>403707</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>39.684868</v>
+        <v>39.968758</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>51.63206</v>
+        <v>52.001415</v>
       </c>
       <c r="AD7" s="4" t="n">
         <v>13.66</v>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
-        <v>4.6668615</v>
+        <v>4.7002463</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>4</v>
@@ -16400,7 +16400,7 @@
         <v>335.31</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>304.69</v>
+        <v>305.22</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -16441,13 +16441,13 @@
         <v>1.95</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>22662</v>
+        <v>23083</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>25.965223</v>
+        <v>26.447834</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>19.23719</v>
+        <v>19.594748</v>
       </c>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
@@ -16458,7 +16458,7 @@
         <v>367.9</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>1.3521404</v>
+        <v>1.3772724</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>33</v>
@@ -16528,7 +16528,7 @@
         <v>469.61</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>423.29</v>
+        <v>424.55</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -16569,13 +16569,13 @@
         <v>0.73</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>8418</v>
+        <v>8525</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>51.80216</v>
+        <v>52.45837</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>38.747257</v>
+        <v>39.238094</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>28.75</v>
@@ -16590,7 +16590,7 @@
         <v>116.3</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>15.739199</v>
+        <v>15.938578</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>309</v>
@@ -16662,7 +16662,7 @@
         <v>506.37</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>372.46</v>
+        <v>372.1</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -16703,13 +16703,13 @@
         <v>0.76</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>7728</v>
+        <v>7738</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>41.665497</v>
+        <v>41.71831</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>28.686062</v>
+        <v>28.722425</v>
       </c>
       <c r="AD10" s="2" t="n">
         <v>25.31</v>
@@ -16724,7 +16724,7 @@
         <v>113</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>10.492109</v>
+        <v>10.505409</v>
       </c>
       <c r="AI10" s="2" t="n">
         <v>0</v>
@@ -16796,7 +16796,7 @@
         <v>1698.35</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1525.77</v>
+        <v>1524.23</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -16837,13 +16837,13 @@
         <v>1.17</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>417685</v>
+        <v>415819</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>31.154839</v>
+        <v>31.01564</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>23.459633</v>
+        <v>23.291836</v>
       </c>
       <c r="AD11" s="4" t="n">
         <v>15.59</v>
@@ -16858,7 +16858,7 @@
         <v>3.6</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>4.3527536</v>
+        <v>4.3333054</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>41</v>
@@ -16903,7 +16903,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run Date: 13-Jun-2026 14:47 IST</t>
+          <t>Run Date: 15-Jun-2026 20:47 IST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16971,7 +16971,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -16981,7 +16981,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -17007,7 +17007,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="14">
